--- a/data/freight/world container index.xlsx
+++ b/data/freight/world container index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\freight\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D06477D-2119-4890-AB10-87136DDC208A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D519113-1594-4712-9B77-CEE7332857B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WCI" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="19">
   <si>
     <t>WCI Composite</t>
   </si>
@@ -98,29 +98,29 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="178" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="179" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -129,7 +129,7 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -137,7 +137,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -176,7 +176,7 @@
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -187,35 +187,35 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표 [0]" xfId="2" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -233,7 +233,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2580,6 +2580,9 @@
                 <c:pt idx="765">
                   <c:v>46128</c:v>
                 </c:pt>
+                <c:pt idx="766">
+                  <c:v>46135</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4886,6 +4889,9 @@
                 </c:pt>
                 <c:pt idx="765">
                   <c:v>2245.9</c:v>
+                </c:pt>
+                <c:pt idx="766">
+                  <c:v>2231.71</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7228,6 +7234,9 @@
                 <c:pt idx="765">
                   <c:v>46128</c:v>
                 </c:pt>
+                <c:pt idx="766">
+                  <c:v>46135</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9534,6 +9543,9 @@
                 </c:pt>
                 <c:pt idx="765">
                   <c:v>2229</c:v>
+                </c:pt>
+                <c:pt idx="766">
+                  <c:v>2147</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11876,6 +11888,9 @@
                 <c:pt idx="765">
                   <c:v>46128</c:v>
                 </c:pt>
+                <c:pt idx="766">
+                  <c:v>46135</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -14182,6 +14197,9 @@
                 </c:pt>
                 <c:pt idx="765">
                   <c:v>3343</c:v>
+                </c:pt>
+                <c:pt idx="766">
+                  <c:v>3071</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16524,6 +16542,9 @@
                 <c:pt idx="765">
                   <c:v>46128</c:v>
                 </c:pt>
+                <c:pt idx="766">
+                  <c:v>46135</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -18830,6 +18851,9 @@
                 </c:pt>
                 <c:pt idx="765">
                   <c:v>2810</c:v>
+                </c:pt>
+                <c:pt idx="766">
+                  <c:v>2934</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -21172,6 +21196,9 @@
                 <c:pt idx="765">
                   <c:v>46128</c:v>
                 </c:pt>
+                <c:pt idx="766">
+                  <c:v>46135</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -23478,6 +23505,9 @@
                 </c:pt>
                 <c:pt idx="765">
                   <c:v>3552</c:v>
+                </c:pt>
+                <c:pt idx="766">
+                  <c:v>3562</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -25820,6 +25850,9 @@
                 <c:pt idx="765">
                   <c:v>46128</c:v>
                 </c:pt>
+                <c:pt idx="766">
+                  <c:v>46135</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -28126,6 +28159,9 @@
                 </c:pt>
                 <c:pt idx="765">
                   <c:v>599</c:v>
+                </c:pt>
+                <c:pt idx="766">
+                  <c:v>607</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -30470,6 +30506,9 @@
                 <c:pt idx="765">
                   <c:v>46128</c:v>
                 </c:pt>
+                <c:pt idx="766">
+                  <c:v>46135</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -32776,6 +32815,9 @@
                 </c:pt>
                 <c:pt idx="765">
                   <c:v>762</c:v>
+                </c:pt>
+                <c:pt idx="766">
+                  <c:v>784</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -35120,6 +35162,9 @@
                 <c:pt idx="765">
                   <c:v>46128</c:v>
                 </c:pt>
+                <c:pt idx="766">
+                  <c:v>46135</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -37426,6 +37471,9 @@
                 </c:pt>
                 <c:pt idx="765">
                   <c:v>1022</c:v>
+                </c:pt>
+                <c:pt idx="766">
+                  <c:v>1031</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -39770,6 +39818,9 @@
                 <c:pt idx="765">
                   <c:v>46128</c:v>
                 </c:pt>
+                <c:pt idx="766">
+                  <c:v>46135</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -42076,6 +42127,9 @@
                 </c:pt>
                 <c:pt idx="765">
                   <c:v>2030</c:v>
+                </c:pt>
+                <c:pt idx="766">
+                  <c:v>2326</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -43153,19 +43207,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M767"/>
-  <sheetFormatPr defaultColWidth="7.6328125" defaultRowHeight="13.5"/>
+  <dimension ref="A1:M768"/>
+  <sheetFormatPr defaultColWidth="7.59765625" defaultRowHeight="12.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.09765625" style="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.81640625" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.90625" style="7" customWidth="1"/>
-    <col min="5" max="5" width="18.08984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="13" width="10.453125" style="9" customWidth="1"/>
-    <col min="14" max="16384" width="7.6328125" style="9"/>
+    <col min="3" max="3" width="11.796875" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.8984375" style="7" customWidth="1"/>
+    <col min="5" max="5" width="18.09765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="13" width="10.5" style="9" customWidth="1"/>
+    <col min="14" max="16384" width="7.59765625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="6" customFormat="1">
+    <row r="1" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
         <v>16</v>
       </c>
@@ -43206,7 +43260,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A2" s="7">
         <v>40716</v>
       </c>
@@ -43247,7 +43301,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A3" s="7">
         <v>40723</v>
       </c>
@@ -43288,7 +43342,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A4" s="7">
         <v>40730</v>
       </c>
@@ -43329,7 +43383,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A5" s="7">
         <v>40737</v>
       </c>
@@ -43370,7 +43424,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A6" s="7">
         <v>40744</v>
       </c>
@@ -43411,7 +43465,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A7" s="7">
         <v>40751</v>
       </c>
@@ -43452,7 +43506,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A8" s="7">
         <v>40758</v>
       </c>
@@ -43493,7 +43547,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A9" s="7">
         <v>40765</v>
       </c>
@@ -43534,7 +43588,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A10" s="7">
         <v>40772</v>
       </c>
@@ -43575,7 +43629,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A11" s="7">
         <v>40779</v>
       </c>
@@ -43616,7 +43670,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A12" s="7">
         <v>40786</v>
       </c>
@@ -43657,7 +43711,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A13" s="7">
         <v>40793</v>
       </c>
@@ -43698,7 +43752,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A14" s="7">
         <v>40800</v>
       </c>
@@ -43739,7 +43793,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A15" s="7">
         <v>40807</v>
       </c>
@@ -43780,7 +43834,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A16" s="7">
         <v>40814</v>
       </c>
@@ -43821,7 +43875,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A17" s="7">
         <v>40821</v>
       </c>
@@ -43862,7 +43916,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A18" s="7">
         <v>40828</v>
       </c>
@@ -43903,7 +43957,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A19" s="7">
         <v>40835</v>
       </c>
@@ -43944,7 +43998,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A20" s="7">
         <v>40842</v>
       </c>
@@ -43985,7 +44039,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A21" s="7">
         <v>40849</v>
       </c>
@@ -44026,7 +44080,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A22" s="7">
         <v>40856</v>
       </c>
@@ -44067,7 +44121,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="23" spans="1:13">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A23" s="7">
         <v>40863</v>
       </c>
@@ -44108,7 +44162,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A24" s="7">
         <v>40870</v>
       </c>
@@ -44149,7 +44203,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A25" s="7">
         <v>40877</v>
       </c>
@@ -44190,7 +44244,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="26" spans="1:13">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A26" s="7">
         <v>40884</v>
       </c>
@@ -44231,7 +44285,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="27" spans="1:13">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A27" s="7">
         <v>40891</v>
       </c>
@@ -44272,7 +44326,7 @@
         <v>2183</v>
       </c>
     </row>
-    <row r="28" spans="1:13">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A28" s="7">
         <v>40898</v>
       </c>
@@ -44313,7 +44367,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="29" spans="1:13">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A29" s="7">
         <v>40905</v>
       </c>
@@ -44354,7 +44408,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="30" spans="1:13">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A30" s="7">
         <v>40912</v>
       </c>
@@ -44395,7 +44449,7 @@
         <v>2208</v>
       </c>
     </row>
-    <row r="31" spans="1:13">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A31" s="7">
         <v>40919</v>
       </c>
@@ -44436,7 +44490,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="32" spans="1:13">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A32" s="7">
         <v>40926</v>
       </c>
@@ -44477,7 +44531,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="33" spans="1:13">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A33" s="7">
         <v>40933</v>
       </c>
@@ -44518,7 +44572,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="34" spans="1:13">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A34" s="7">
         <v>40940</v>
       </c>
@@ -44559,7 +44613,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="35" spans="1:13">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A35" s="7">
         <v>40947</v>
       </c>
@@ -44600,7 +44654,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="36" spans="1:13">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A36" s="7">
         <v>40954</v>
       </c>
@@ -44641,7 +44695,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="37" spans="1:13">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A37" s="7">
         <v>40961</v>
       </c>
@@ -44682,7 +44736,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="38" spans="1:13">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A38" s="7">
         <v>40968</v>
       </c>
@@ -44723,7 +44777,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="39" spans="1:13">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A39" s="7">
         <v>40975</v>
       </c>
@@ -44764,7 +44818,7 @@
         <v>2220</v>
       </c>
     </row>
-    <row r="40" spans="1:13">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A40" s="7">
         <v>40982</v>
       </c>
@@ -44805,7 +44859,7 @@
         <v>2420</v>
       </c>
     </row>
-    <row r="41" spans="1:13">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A41" s="7">
         <v>40989</v>
       </c>
@@ -44846,7 +44900,7 @@
         <v>2419</v>
       </c>
     </row>
-    <row r="42" spans="1:13">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A42" s="7">
         <v>40996</v>
       </c>
@@ -44887,7 +44941,7 @@
         <v>2454</v>
       </c>
     </row>
-    <row r="43" spans="1:13">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A43" s="7">
         <v>41003</v>
       </c>
@@ -44928,7 +44982,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="44" spans="1:13">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A44" s="7">
         <v>41010</v>
       </c>
@@ -44969,7 +45023,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="45" spans="1:13">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A45" s="7">
         <v>41017</v>
       </c>
@@ -45010,7 +45064,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="46" spans="1:13">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A46" s="7">
         <v>41024</v>
       </c>
@@ -45051,7 +45105,7 @@
         <v>2529</v>
       </c>
     </row>
-    <row r="47" spans="1:13">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A47" s="7">
         <v>41031</v>
       </c>
@@ -45092,7 +45146,7 @@
         <v>2534</v>
       </c>
     </row>
-    <row r="48" spans="1:13">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A48" s="7">
         <v>41038</v>
       </c>
@@ -45133,7 +45187,7 @@
         <v>2516</v>
       </c>
     </row>
-    <row r="49" spans="1:13">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A49" s="7">
         <v>41045</v>
       </c>
@@ -45174,7 +45228,7 @@
         <v>2668</v>
       </c>
     </row>
-    <row r="50" spans="1:13">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A50" s="7">
         <v>41052</v>
       </c>
@@ -45215,7 +45269,7 @@
         <v>2676</v>
       </c>
     </row>
-    <row r="51" spans="1:13">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A51" s="7">
         <v>41059</v>
       </c>
@@ -45256,7 +45310,7 @@
         <v>2605</v>
       </c>
     </row>
-    <row r="52" spans="1:13">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A52" s="7">
         <v>41066</v>
       </c>
@@ -45297,7 +45351,7 @@
         <v>2674</v>
       </c>
     </row>
-    <row r="53" spans="1:13">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A53" s="7">
         <v>41073</v>
       </c>
@@ -45338,7 +45392,7 @@
         <v>2696</v>
       </c>
     </row>
-    <row r="54" spans="1:13">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A54" s="7">
         <v>41080</v>
       </c>
@@ -45379,7 +45433,7 @@
         <v>2696</v>
       </c>
     </row>
-    <row r="55" spans="1:13">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A55" s="7">
         <v>41087</v>
       </c>
@@ -45420,7 +45474,7 @@
         <v>2696</v>
       </c>
     </row>
-    <row r="56" spans="1:13">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A56" s="7">
         <v>41094</v>
       </c>
@@ -45461,7 +45515,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="57" spans="1:13">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A57" s="7">
         <v>41101</v>
       </c>
@@ -45502,7 +45556,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="58" spans="1:13">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A58" s="7">
         <v>41108</v>
       </c>
@@ -45543,7 +45597,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="59" spans="1:13">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A59" s="7">
         <v>41115</v>
       </c>
@@ -45584,7 +45638,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="60" spans="1:13">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A60" s="7">
         <v>41122</v>
       </c>
@@ -45625,7 +45679,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="61" spans="1:13">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A61" s="7">
         <v>41129</v>
       </c>
@@ -45666,7 +45720,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="62" spans="1:13">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A62" s="7">
         <v>41136</v>
       </c>
@@ -45707,7 +45761,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="63" spans="1:13">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A63" s="7">
         <v>41143</v>
       </c>
@@ -45748,7 +45802,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="64" spans="1:13">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A64" s="7">
         <v>41150</v>
       </c>
@@ -45789,7 +45843,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="65" spans="1:13">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A65" s="7">
         <v>41157</v>
       </c>
@@ -45830,7 +45884,7 @@
         <v>2660</v>
       </c>
     </row>
-    <row r="66" spans="1:13">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A66" s="7">
         <v>41164</v>
       </c>
@@ -45871,7 +45925,7 @@
         <v>2659</v>
       </c>
     </row>
-    <row r="67" spans="1:13">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A67" s="7">
         <v>41171</v>
       </c>
@@ -45912,7 +45966,7 @@
         <v>2659</v>
       </c>
     </row>
-    <row r="68" spans="1:13">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A68" s="7">
         <v>41178</v>
       </c>
@@ -45953,7 +46007,7 @@
         <v>2527</v>
       </c>
     </row>
-    <row r="69" spans="1:13">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A69" s="7">
         <v>41185</v>
       </c>
@@ -45994,7 +46048,7 @@
         <v>2428</v>
       </c>
     </row>
-    <row r="70" spans="1:13">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A70" s="7">
         <v>41192</v>
       </c>
@@ -46035,7 +46089,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="71" spans="1:13">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A71" s="7">
         <v>41199</v>
       </c>
@@ -46076,7 +46130,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="72" spans="1:13">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A72" s="7">
         <v>41206</v>
       </c>
@@ -46117,7 +46171,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="73" spans="1:13">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A73" s="7">
         <v>41213</v>
       </c>
@@ -46158,7 +46212,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="74" spans="1:13">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A74" s="7">
         <v>41220</v>
       </c>
@@ -46199,7 +46253,7 @@
         <v>2624</v>
       </c>
     </row>
-    <row r="75" spans="1:13">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A75" s="7">
         <v>41227</v>
       </c>
@@ -46240,7 +46294,7 @@
         <v>2624</v>
       </c>
     </row>
-    <row r="76" spans="1:13">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A76" s="7">
         <v>41234</v>
       </c>
@@ -46281,7 +46335,7 @@
         <v>2418</v>
       </c>
     </row>
-    <row r="77" spans="1:13">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A77" s="7">
         <v>41241</v>
       </c>
@@ -46322,7 +46376,7 @@
         <v>2418</v>
       </c>
     </row>
-    <row r="78" spans="1:13">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A78" s="7">
         <v>41248</v>
       </c>
@@ -46363,7 +46417,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="79" spans="1:13">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A79" s="7">
         <v>41255</v>
       </c>
@@ -46404,7 +46458,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="80" spans="1:13">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A80" s="7">
         <v>41262</v>
       </c>
@@ -46445,7 +46499,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="81" spans="1:13">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A81" s="7">
         <v>41269</v>
       </c>
@@ -46486,7 +46540,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="82" spans="1:13">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A82" s="7">
         <v>41276</v>
       </c>
@@ -46527,7 +46581,7 @@
         <v>2443</v>
       </c>
     </row>
-    <row r="83" spans="1:13">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A83" s="7">
         <v>41283</v>
       </c>
@@ -46568,7 +46622,7 @@
         <v>2443</v>
       </c>
     </row>
-    <row r="84" spans="1:13">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A84" s="7">
         <v>41290</v>
       </c>
@@ -46609,7 +46663,7 @@
         <v>2430</v>
       </c>
     </row>
-    <row r="85" spans="1:13">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A85" s="7">
         <v>41297</v>
       </c>
@@ -46650,7 +46704,7 @@
         <v>2430</v>
       </c>
     </row>
-    <row r="86" spans="1:13">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A86" s="7">
         <v>41304</v>
       </c>
@@ -46691,7 +46745,7 @@
         <v>2496</v>
       </c>
     </row>
-    <row r="87" spans="1:13">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A87" s="7">
         <v>41311</v>
       </c>
@@ -46732,7 +46786,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="88" spans="1:13">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A88" s="7">
         <v>41318</v>
       </c>
@@ -46773,7 +46827,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="89" spans="1:13">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A89" s="7">
         <v>41325</v>
       </c>
@@ -46814,7 +46868,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="90" spans="1:13">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A90" s="7">
         <v>41332</v>
       </c>
@@ -46855,7 +46909,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="91" spans="1:13">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A91" s="7">
         <v>41339</v>
       </c>
@@ -46896,7 +46950,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="92" spans="1:13">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A92" s="7">
         <v>41346</v>
       </c>
@@ -46937,7 +46991,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="93" spans="1:13">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A93" s="7">
         <v>41353</v>
       </c>
@@ -46978,7 +47032,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="94" spans="1:13">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A94" s="7">
         <v>41360</v>
       </c>
@@ -47019,7 +47073,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="95" spans="1:13">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A95" s="7">
         <v>41367</v>
       </c>
@@ -47060,7 +47114,7 @@
         <v>2411</v>
       </c>
     </row>
-    <row r="96" spans="1:13">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A96" s="7">
         <v>41374</v>
       </c>
@@ -47101,7 +47155,7 @@
         <v>2411</v>
       </c>
     </row>
-    <row r="97" spans="1:13">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A97" s="7">
         <v>41381</v>
       </c>
@@ -47142,7 +47196,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="98" spans="1:13">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A98" s="7">
         <v>41388</v>
       </c>
@@ -47183,7 +47237,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="99" spans="1:13">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A99" s="7">
         <v>41395</v>
       </c>
@@ -47224,7 +47278,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="100" spans="1:13">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A100" s="7">
         <v>41402</v>
       </c>
@@ -47265,7 +47319,7 @@
         <v>2091</v>
       </c>
     </row>
-    <row r="101" spans="1:13">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A101" s="7">
         <v>41409</v>
       </c>
@@ -47306,7 +47360,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="102" spans="1:13">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A102" s="7">
         <v>41416</v>
       </c>
@@ -47347,7 +47401,7 @@
         <v>2034</v>
       </c>
     </row>
-    <row r="103" spans="1:13">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A103" s="7">
         <v>41423</v>
       </c>
@@ -47388,7 +47442,7 @@
         <v>2082</v>
       </c>
     </row>
-    <row r="104" spans="1:13">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A104" s="7">
         <v>41430</v>
       </c>
@@ -47429,7 +47483,7 @@
         <v>2053</v>
       </c>
     </row>
-    <row r="105" spans="1:13">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A105" s="7">
         <v>41437</v>
       </c>
@@ -47470,7 +47524,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="106" spans="1:13">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A106" s="7">
         <v>41444</v>
       </c>
@@ -47511,7 +47565,7 @@
         <v>2047</v>
       </c>
     </row>
-    <row r="107" spans="1:13">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A107" s="7">
         <v>41451</v>
       </c>
@@ -47552,7 +47606,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="108" spans="1:13">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A108" s="7">
         <v>41458</v>
       </c>
@@ -47593,7 +47647,7 @@
         <v>1965</v>
       </c>
     </row>
-    <row r="109" spans="1:13">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A109" s="7">
         <v>41465</v>
       </c>
@@ -47634,7 +47688,7 @@
         <v>1967</v>
       </c>
     </row>
-    <row r="110" spans="1:13">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A110" s="7">
         <v>41472</v>
       </c>
@@ -47675,7 +47729,7 @@
         <v>1970</v>
       </c>
     </row>
-    <row r="111" spans="1:13">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A111" s="7">
         <v>41479</v>
       </c>
@@ -47716,7 +47770,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="112" spans="1:13">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A112" s="7">
         <v>41486</v>
       </c>
@@ -47757,7 +47811,7 @@
         <v>1928</v>
       </c>
     </row>
-    <row r="113" spans="1:13">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A113" s="7">
         <v>41493</v>
       </c>
@@ -47798,7 +47852,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="114" spans="1:13">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A114" s="7">
         <v>41500</v>
       </c>
@@ -47839,7 +47893,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="115" spans="1:13">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A115" s="7">
         <v>41507</v>
       </c>
@@ -47880,7 +47934,7 @@
         <v>1897</v>
       </c>
     </row>
-    <row r="116" spans="1:13">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A116" s="7">
         <v>41514</v>
       </c>
@@ -47921,7 +47975,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="117" spans="1:13">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A117" s="7">
         <v>41521</v>
       </c>
@@ -47962,7 +48016,7 @@
         <v>1909</v>
       </c>
     </row>
-    <row r="118" spans="1:13">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A118" s="7">
         <v>41528</v>
       </c>
@@ -48003,7 +48057,7 @@
         <v>1963</v>
       </c>
     </row>
-    <row r="119" spans="1:13">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A119" s="7">
         <v>41535</v>
       </c>
@@ -48044,7 +48098,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="120" spans="1:13">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A120" s="7">
         <v>41542</v>
       </c>
@@ -48085,7 +48139,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="121" spans="1:13">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A121" s="7">
         <v>41549</v>
       </c>
@@ -48126,7 +48180,7 @@
         <v>2047</v>
       </c>
     </row>
-    <row r="122" spans="1:13">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A122" s="7">
         <v>41556</v>
       </c>
@@ -48167,7 +48221,7 @@
         <v>1966</v>
       </c>
     </row>
-    <row r="123" spans="1:13">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A123" s="7">
         <v>41563</v>
       </c>
@@ -48208,7 +48262,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="124" spans="1:13">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A124" s="7">
         <v>41570</v>
       </c>
@@ -48249,7 +48303,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="125" spans="1:13">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A125" s="7">
         <v>41577</v>
       </c>
@@ -48290,7 +48344,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="126" spans="1:13">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A126" s="7">
         <v>41584</v>
       </c>
@@ -48331,7 +48385,7 @@
         <v>1946</v>
       </c>
     </row>
-    <row r="127" spans="1:13">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A127" s="7">
         <v>41591</v>
       </c>
@@ -48372,7 +48426,7 @@
         <v>1948</v>
       </c>
     </row>
-    <row r="128" spans="1:13">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A128" s="7">
         <v>41598</v>
       </c>
@@ -48413,7 +48467,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="129" spans="1:13">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A129" s="7">
         <v>41605</v>
       </c>
@@ -48454,7 +48508,7 @@
         <v>1994</v>
       </c>
     </row>
-    <row r="130" spans="1:13">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A130" s="7">
         <v>41612</v>
       </c>
@@ -48495,7 +48549,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="131" spans="1:13">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A131" s="7">
         <v>41619</v>
       </c>
@@ -48536,7 +48590,7 @@
         <v>1971</v>
       </c>
     </row>
-    <row r="132" spans="1:13">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A132" s="7">
         <v>41626</v>
       </c>
@@ -48577,7 +48631,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="133" spans="1:13">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A133" s="7">
         <v>41640</v>
       </c>
@@ -48618,7 +48672,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="134" spans="1:13">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A134" s="7">
         <v>41647</v>
       </c>
@@ -48659,7 +48713,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="135" spans="1:13">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A135" s="7">
         <v>41654</v>
       </c>
@@ -48700,7 +48754,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="136" spans="1:13">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A136" s="7">
         <v>41661</v>
       </c>
@@ -48741,7 +48795,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="137" spans="1:13">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A137" s="7">
         <v>41668</v>
       </c>
@@ -48782,7 +48836,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="138" spans="1:13">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A138" s="7">
         <v>41675</v>
       </c>
@@ -48823,7 +48877,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="139" spans="1:13">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A139" s="7">
         <v>41682</v>
       </c>
@@ -48864,7 +48918,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="140" spans="1:13">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A140" s="7">
         <v>41689</v>
       </c>
@@ -48905,7 +48959,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="141" spans="1:13">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A141" s="7">
         <v>41696</v>
       </c>
@@ -48946,7 +49000,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="142" spans="1:13">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A142" s="7">
         <v>41703</v>
       </c>
@@ -48987,7 +49041,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="143" spans="1:13">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A143" s="7">
         <v>41710</v>
       </c>
@@ -49028,7 +49082,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="144" spans="1:13">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A144" s="7">
         <v>41717</v>
       </c>
@@ -49069,7 +49123,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="145" spans="1:13">
+    <row r="145" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A145" s="7">
         <v>41724</v>
       </c>
@@ -49110,7 +49164,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="146" spans="1:13">
+    <row r="146" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A146" s="7">
         <v>41731</v>
       </c>
@@ -49151,7 +49205,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="147" spans="1:13">
+    <row r="147" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A147" s="7">
         <v>41738</v>
       </c>
@@ -49192,7 +49246,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="148" spans="1:13">
+    <row r="148" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A148" s="7">
         <v>41745</v>
       </c>
@@ -49233,7 +49287,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="149" spans="1:13">
+    <row r="149" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A149" s="7">
         <v>41752</v>
       </c>
@@ -49274,7 +49328,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="150" spans="1:13">
+    <row r="150" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A150" s="7">
         <v>41759</v>
       </c>
@@ -49315,7 +49369,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="151" spans="1:13">
+    <row r="151" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A151" s="7">
         <v>41766</v>
       </c>
@@ -49356,7 +49410,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="152" spans="1:13">
+    <row r="152" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A152" s="7">
         <v>41773</v>
       </c>
@@ -49397,7 +49451,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="153" spans="1:13">
+    <row r="153" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A153" s="7">
         <v>41780</v>
       </c>
@@ -49438,7 +49492,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="154" spans="1:13">
+    <row r="154" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A154" s="7">
         <v>41787</v>
       </c>
@@ -49479,7 +49533,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="155" spans="1:13">
+    <row r="155" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A155" s="7">
         <v>41794</v>
       </c>
@@ -49520,7 +49574,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="156" spans="1:13">
+    <row r="156" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A156" s="7">
         <v>41801</v>
       </c>
@@ -49561,7 +49615,7 @@
         <v>2142</v>
       </c>
     </row>
-    <row r="157" spans="1:13">
+    <row r="157" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A157" s="7">
         <v>41808</v>
       </c>
@@ -49602,7 +49656,7 @@
         <v>2142</v>
       </c>
     </row>
-    <row r="158" spans="1:13">
+    <row r="158" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A158" s="7">
         <v>41815</v>
       </c>
@@ -49643,7 +49697,7 @@
         <v>2138</v>
       </c>
     </row>
-    <row r="159" spans="1:13">
+    <row r="159" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A159" s="7">
         <v>41822</v>
       </c>
@@ -49684,7 +49738,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="160" spans="1:13">
+    <row r="160" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A160" s="7">
         <v>41829</v>
       </c>
@@ -49725,7 +49779,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="161" spans="1:13">
+    <row r="161" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A161" s="7">
         <v>41836</v>
       </c>
@@ -49766,7 +49820,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="162" spans="1:13">
+    <row r="162" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A162" s="7">
         <v>41843</v>
       </c>
@@ -49807,7 +49861,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="163" spans="1:13">
+    <row r="163" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A163" s="7">
         <v>41850</v>
       </c>
@@ -49848,7 +49902,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="164" spans="1:13">
+    <row r="164" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A164" s="7">
         <v>41857</v>
       </c>
@@ -49889,7 +49943,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="165" spans="1:13">
+    <row r="165" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A165" s="7">
         <v>41864</v>
       </c>
@@ -49930,7 +49984,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="166" spans="1:13">
+    <row r="166" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A166" s="7">
         <v>41871</v>
       </c>
@@ -49971,7 +50025,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="167" spans="1:13">
+    <row r="167" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A167" s="7">
         <v>41878</v>
       </c>
@@ -50012,7 +50066,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="168" spans="1:13">
+    <row r="168" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A168" s="7">
         <v>41885</v>
       </c>
@@ -50053,7 +50107,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="169" spans="1:13">
+    <row r="169" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A169" s="7">
         <v>41892</v>
       </c>
@@ -50094,7 +50148,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="170" spans="1:13">
+    <row r="170" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A170" s="7">
         <v>41899</v>
       </c>
@@ -50135,7 +50189,7 @@
         <v>2203</v>
       </c>
     </row>
-    <row r="171" spans="1:13">
+    <row r="171" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A171" s="7">
         <v>41906</v>
       </c>
@@ -50176,7 +50230,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="172" spans="1:13">
+    <row r="172" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A172" s="7">
         <v>41913</v>
       </c>
@@ -50217,7 +50271,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="173" spans="1:13">
+    <row r="173" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A173" s="7">
         <v>41920</v>
       </c>
@@ -50258,7 +50312,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="174" spans="1:13">
+    <row r="174" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A174" s="7">
         <v>41927</v>
       </c>
@@ -50299,7 +50353,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="175" spans="1:13">
+    <row r="175" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A175" s="7">
         <v>41934</v>
       </c>
@@ -50340,7 +50394,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="176" spans="1:13">
+    <row r="176" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A176" s="7">
         <v>41941</v>
       </c>
@@ -50381,7 +50435,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="177" spans="1:13">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A177" s="7">
         <v>41948</v>
       </c>
@@ -50422,7 +50476,7 @@
         <v>2232</v>
       </c>
     </row>
-    <row r="178" spans="1:13">
+    <row r="178" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A178" s="7">
         <v>41955</v>
       </c>
@@ -50463,7 +50517,7 @@
         <v>2232</v>
       </c>
     </row>
-    <row r="179" spans="1:13">
+    <row r="179" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A179" s="7">
         <v>41962</v>
       </c>
@@ -50504,7 +50558,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="180" spans="1:13">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A180" s="7">
         <v>41969</v>
       </c>
@@ -50545,7 +50599,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="181" spans="1:13">
+    <row r="181" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A181" s="7">
         <v>41976</v>
       </c>
@@ -50586,7 +50640,7 @@
         <v>2229</v>
       </c>
     </row>
-    <row r="182" spans="1:13">
+    <row r="182" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A182" s="7">
         <v>41983</v>
       </c>
@@ -50627,7 +50681,7 @@
         <v>2219</v>
       </c>
     </row>
-    <row r="183" spans="1:13">
+    <row r="183" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A183" s="7">
         <v>41990</v>
       </c>
@@ -50668,7 +50722,7 @@
         <v>2219</v>
       </c>
     </row>
-    <row r="184" spans="1:13">
+    <row r="184" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A184" s="7">
         <v>42011</v>
       </c>
@@ -50709,7 +50763,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="185" spans="1:13">
+    <row r="185" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A185" s="7">
         <v>42018</v>
       </c>
@@ -50750,7 +50804,7 @@
         <v>2274</v>
       </c>
     </row>
-    <row r="186" spans="1:13">
+    <row r="186" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A186" s="7">
         <v>42025</v>
       </c>
@@ -50791,7 +50845,7 @@
         <v>2268</v>
       </c>
     </row>
-    <row r="187" spans="1:13">
+    <row r="187" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A187" s="7">
         <v>42032</v>
       </c>
@@ -50832,7 +50886,7 @@
         <v>2260</v>
       </c>
     </row>
-    <row r="188" spans="1:13">
+    <row r="188" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A188" s="7">
         <v>42039</v>
       </c>
@@ -50873,7 +50927,7 @@
         <v>2276</v>
       </c>
     </row>
-    <row r="189" spans="1:13">
+    <row r="189" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A189" s="7">
         <v>42046</v>
       </c>
@@ -50914,7 +50968,7 @@
         <v>2333</v>
       </c>
     </row>
-    <row r="190" spans="1:13">
+    <row r="190" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A190" s="7">
         <v>42053</v>
       </c>
@@ -50955,7 +51009,7 @@
         <v>2287</v>
       </c>
     </row>
-    <row r="191" spans="1:13">
+    <row r="191" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A191" s="7">
         <v>42060</v>
       </c>
@@ -50996,7 +51050,7 @@
         <v>2287</v>
       </c>
     </row>
-    <row r="192" spans="1:13">
+    <row r="192" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A192" s="7">
         <v>42067</v>
       </c>
@@ -51037,7 +51091,7 @@
         <v>2309</v>
       </c>
     </row>
-    <row r="193" spans="1:13">
+    <row r="193" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A193" s="7">
         <v>42074</v>
       </c>
@@ -51078,7 +51132,7 @@
         <v>2277</v>
       </c>
     </row>
-    <row r="194" spans="1:13">
+    <row r="194" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A194" s="7">
         <v>42081</v>
       </c>
@@ -51119,7 +51173,7 @@
         <v>2277</v>
       </c>
     </row>
-    <row r="195" spans="1:13">
+    <row r="195" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A195" s="7">
         <v>42088</v>
       </c>
@@ -51160,7 +51214,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="196" spans="1:13">
+    <row r="196" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A196" s="7">
         <v>42095</v>
       </c>
@@ -51201,7 +51255,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="197" spans="1:13">
+    <row r="197" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A197" s="7">
         <v>42102</v>
       </c>
@@ -51242,7 +51296,7 @@
         <v>2290</v>
       </c>
     </row>
-    <row r="198" spans="1:13">
+    <row r="198" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A198" s="7">
         <v>42109</v>
       </c>
@@ -51283,7 +51337,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="199" spans="1:13">
+    <row r="199" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A199" s="7">
         <v>42116</v>
       </c>
@@ -51324,7 +51378,7 @@
         <v>2237</v>
       </c>
     </row>
-    <row r="200" spans="1:13">
+    <row r="200" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A200" s="7">
         <v>42123</v>
       </c>
@@ -51365,7 +51419,7 @@
         <v>2253</v>
       </c>
     </row>
-    <row r="201" spans="1:13">
+    <row r="201" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A201" s="7">
         <v>42130</v>
       </c>
@@ -51406,7 +51460,7 @@
         <v>2263</v>
       </c>
     </row>
-    <row r="202" spans="1:13">
+    <row r="202" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A202" s="7">
         <v>42137</v>
       </c>
@@ -51447,7 +51501,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="203" spans="1:13">
+    <row r="203" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A203" s="7">
         <v>42144</v>
       </c>
@@ -51488,7 +51542,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="204" spans="1:13">
+    <row r="204" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A204" s="7">
         <v>42151</v>
       </c>
@@ -51529,7 +51583,7 @@
         <v>2154</v>
       </c>
     </row>
-    <row r="205" spans="1:13">
+    <row r="205" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A205" s="7">
         <v>42158</v>
       </c>
@@ -51570,7 +51624,7 @@
         <v>2199</v>
       </c>
     </row>
-    <row r="206" spans="1:13">
+    <row r="206" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A206" s="7">
         <v>42165</v>
       </c>
@@ -51611,7 +51665,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="207" spans="1:13">
+    <row r="207" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A207" s="7">
         <v>42172</v>
       </c>
@@ -51652,7 +51706,7 @@
         <v>2207</v>
       </c>
     </row>
-    <row r="208" spans="1:13">
+    <row r="208" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A208" s="7">
         <v>42179</v>
       </c>
@@ -51693,7 +51747,7 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="209" spans="1:13">
+    <row r="209" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A209" s="7">
         <v>42186</v>
       </c>
@@ -51734,7 +51788,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="210" spans="1:13">
+    <row r="210" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A210" s="7">
         <v>42193</v>
       </c>
@@ -51775,7 +51829,7 @@
         <v>2210</v>
       </c>
     </row>
-    <row r="211" spans="1:13">
+    <row r="211" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A211" s="7">
         <v>42200</v>
       </c>
@@ -51816,7 +51870,7 @@
         <v>2195</v>
       </c>
     </row>
-    <row r="212" spans="1:13">
+    <row r="212" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A212" s="7">
         <v>42207</v>
       </c>
@@ -51857,7 +51911,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="213" spans="1:13">
+    <row r="213" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A213" s="7">
         <v>42214</v>
       </c>
@@ -51898,7 +51952,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="214" spans="1:13">
+    <row r="214" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A214" s="7">
         <v>42221</v>
       </c>
@@ -51939,7 +51993,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="215" spans="1:13">
+    <row r="215" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A215" s="7">
         <v>42228</v>
       </c>
@@ -51980,7 +52034,7 @@
         <v>2184</v>
       </c>
     </row>
-    <row r="216" spans="1:13">
+    <row r="216" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A216" s="7">
         <v>42235</v>
       </c>
@@ -52021,7 +52075,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="217" spans="1:13">
+    <row r="217" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A217" s="7">
         <v>42242</v>
       </c>
@@ -52062,7 +52116,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="218" spans="1:13">
+    <row r="218" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A218" s="7">
         <v>42249</v>
       </c>
@@ -52103,7 +52157,7 @@
         <v>2147</v>
       </c>
     </row>
-    <row r="219" spans="1:13">
+    <row r="219" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A219" s="7">
         <v>42256</v>
       </c>
@@ -52144,7 +52198,7 @@
         <v>2138</v>
       </c>
     </row>
-    <row r="220" spans="1:13">
+    <row r="220" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A220" s="7">
         <v>42263</v>
       </c>
@@ -52185,7 +52239,7 @@
         <v>2139</v>
       </c>
     </row>
-    <row r="221" spans="1:13">
+    <row r="221" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A221" s="7">
         <v>42270</v>
       </c>
@@ -52226,7 +52280,7 @@
         <v>2090</v>
       </c>
     </row>
-    <row r="222" spans="1:13">
+    <row r="222" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A222" s="7">
         <v>42277</v>
       </c>
@@ -52267,7 +52321,7 @@
         <v>2074</v>
       </c>
     </row>
-    <row r="223" spans="1:13">
+    <row r="223" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A223" s="7">
         <v>42284</v>
       </c>
@@ -52308,7 +52362,7 @@
         <v>2095</v>
       </c>
     </row>
-    <row r="224" spans="1:13">
+    <row r="224" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A224" s="7">
         <v>42291</v>
       </c>
@@ -52349,7 +52403,7 @@
         <v>2079</v>
       </c>
     </row>
-    <row r="225" spans="1:13">
+    <row r="225" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A225" s="7">
         <v>42298</v>
       </c>
@@ -52390,7 +52444,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="226" spans="1:13">
+    <row r="226" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A226" s="7">
         <v>42305</v>
       </c>
@@ -52431,7 +52485,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="227" spans="1:13">
+    <row r="227" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A227" s="7">
         <v>42312</v>
       </c>
@@ -52472,7 +52526,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="228" spans="1:13">
+    <row r="228" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A228" s="7">
         <v>42319</v>
       </c>
@@ -52513,7 +52567,7 @@
         <v>2066</v>
       </c>
     </row>
-    <row r="229" spans="1:13">
+    <row r="229" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A229" s="7">
         <v>42326</v>
       </c>
@@ -52554,7 +52608,7 @@
         <v>2066</v>
       </c>
     </row>
-    <row r="230" spans="1:13">
+    <row r="230" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A230" s="7">
         <v>42333</v>
       </c>
@@ -52595,7 +52649,7 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="231" spans="1:13">
+    <row r="231" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A231" s="7">
         <v>42340</v>
       </c>
@@ -52636,7 +52690,7 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="232" spans="1:13">
+    <row r="232" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A232" s="7">
         <v>42347</v>
       </c>
@@ -52677,7 +52731,7 @@
         <v>2079</v>
       </c>
     </row>
-    <row r="233" spans="1:13">
+    <row r="233" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A233" s="7">
         <v>42354</v>
       </c>
@@ -52718,7 +52772,7 @@
         <v>2074</v>
       </c>
     </row>
-    <row r="234" spans="1:13">
+    <row r="234" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A234" s="7">
         <v>42361</v>
       </c>
@@ -52759,7 +52813,7 @@
         <v>2077</v>
       </c>
     </row>
-    <row r="235" spans="1:13">
+    <row r="235" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A235" s="7">
         <v>42368</v>
       </c>
@@ -52800,7 +52854,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="236" spans="1:13">
+    <row r="236" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A236" s="7">
         <v>42375</v>
       </c>
@@ -52841,7 +52895,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="237" spans="1:13">
+    <row r="237" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A237" s="7">
         <v>42382</v>
       </c>
@@ -52882,7 +52936,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="238" spans="1:13">
+    <row r="238" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A238" s="7">
         <v>42389</v>
       </c>
@@ -52923,7 +52977,7 @@
         <v>2042</v>
       </c>
     </row>
-    <row r="239" spans="1:13">
+    <row r="239" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A239" s="7">
         <v>42396</v>
       </c>
@@ -52964,7 +53018,7 @@
         <v>2042</v>
       </c>
     </row>
-    <row r="240" spans="1:13">
+    <row r="240" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A240" s="7">
         <v>42403</v>
       </c>
@@ -53005,7 +53059,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="241" spans="1:13">
+    <row r="241" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A241" s="7">
         <v>42410</v>
       </c>
@@ -53046,7 +53100,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="242" spans="1:13">
+    <row r="242" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A242" s="7">
         <v>42417</v>
       </c>
@@ -53087,7 +53141,7 @@
         <v>2048</v>
       </c>
     </row>
-    <row r="243" spans="1:13">
+    <row r="243" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A243" s="7">
         <v>42424</v>
       </c>
@@ -53128,7 +53182,7 @@
         <v>1880</v>
       </c>
     </row>
-    <row r="244" spans="1:13">
+    <row r="244" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A244" s="7">
         <v>42431</v>
       </c>
@@ -53169,7 +53223,7 @@
         <v>1856</v>
       </c>
     </row>
-    <row r="245" spans="1:13">
+    <row r="245" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A245" s="7">
         <v>42438</v>
       </c>
@@ -53210,7 +53264,7 @@
         <v>1857</v>
       </c>
     </row>
-    <row r="246" spans="1:13">
+    <row r="246" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A246" s="7">
         <v>42445</v>
       </c>
@@ -53251,7 +53305,7 @@
         <v>1846</v>
       </c>
     </row>
-    <row r="247" spans="1:13">
+    <row r="247" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A247" s="7">
         <v>42452</v>
       </c>
@@ -53292,7 +53346,7 @@
         <v>1835</v>
       </c>
     </row>
-    <row r="248" spans="1:13">
+    <row r="248" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A248" s="7">
         <v>42459</v>
       </c>
@@ -53333,7 +53387,7 @@
         <v>1828</v>
       </c>
     </row>
-    <row r="249" spans="1:13">
+    <row r="249" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A249" s="7">
         <v>42466</v>
       </c>
@@ -53374,7 +53428,7 @@
         <v>1872</v>
       </c>
     </row>
-    <row r="250" spans="1:13">
+    <row r="250" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A250" s="7">
         <v>42473</v>
       </c>
@@ -53415,7 +53469,7 @@
         <v>1847</v>
       </c>
     </row>
-    <row r="251" spans="1:13">
+    <row r="251" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A251" s="7">
         <v>42480</v>
       </c>
@@ -53456,7 +53510,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="252" spans="1:13">
+    <row r="252" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A252" s="7">
         <v>42487</v>
       </c>
@@ -53497,7 +53551,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="253" spans="1:13">
+    <row r="253" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A253" s="7">
         <v>42494</v>
       </c>
@@ -53538,7 +53592,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="254" spans="1:13">
+    <row r="254" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A254" s="7">
         <v>42501</v>
       </c>
@@ -53579,7 +53633,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="255" spans="1:13">
+    <row r="255" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A255" s="7">
         <v>42508</v>
       </c>
@@ -53620,7 +53674,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="256" spans="1:13">
+    <row r="256" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A256" s="7">
         <v>42515</v>
       </c>
@@ -53661,7 +53715,7 @@
         <v>1843</v>
       </c>
     </row>
-    <row r="257" spans="1:13">
+    <row r="257" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A257" s="7">
         <v>42522</v>
       </c>
@@ -53702,7 +53756,7 @@
         <v>1844</v>
       </c>
     </row>
-    <row r="258" spans="1:13">
+    <row r="258" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A258" s="7">
         <v>42529</v>
       </c>
@@ -53743,7 +53797,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="259" spans="1:13">
+    <row r="259" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A259" s="7">
         <v>42536</v>
       </c>
@@ -53784,7 +53838,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="260" spans="1:13">
+    <row r="260" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A260" s="7">
         <v>42543</v>
       </c>
@@ -53825,7 +53879,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="261" spans="1:13">
+    <row r="261" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A261" s="7">
         <v>42550</v>
       </c>
@@ -53866,7 +53920,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="262" spans="1:13">
+    <row r="262" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A262" s="7">
         <v>42557</v>
       </c>
@@ -53907,7 +53961,7 @@
         <v>1848</v>
       </c>
     </row>
-    <row r="263" spans="1:13">
+    <row r="263" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A263" s="7">
         <v>42564</v>
       </c>
@@ -53948,7 +54002,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="264" spans="1:13">
+    <row r="264" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A264" s="7">
         <v>42571</v>
       </c>
@@ -53989,7 +54043,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="265" spans="1:13">
+    <row r="265" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A265" s="7">
         <v>42578</v>
       </c>
@@ -54030,7 +54084,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="266" spans="1:13">
+    <row r="266" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A266" s="7">
         <v>42585</v>
       </c>
@@ -54071,7 +54125,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="267" spans="1:13">
+    <row r="267" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A267" s="7">
         <v>42592</v>
       </c>
@@ -54112,7 +54166,7 @@
         <v>1816</v>
       </c>
     </row>
-    <row r="268" spans="1:13">
+    <row r="268" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A268" s="7">
         <v>42599</v>
       </c>
@@ -54153,7 +54207,7 @@
         <v>1814</v>
       </c>
     </row>
-    <row r="269" spans="1:13">
+    <row r="269" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A269" s="7">
         <v>42606</v>
       </c>
@@ -54194,7 +54248,7 @@
         <v>1814</v>
       </c>
     </row>
-    <row r="270" spans="1:13">
+    <row r="270" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A270" s="7">
         <v>42613</v>
       </c>
@@ -54235,7 +54289,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="271" spans="1:13">
+    <row r="271" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A271" s="7">
         <v>42620</v>
       </c>
@@ -54276,7 +54330,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="272" spans="1:13">
+    <row r="272" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A272" s="7">
         <v>42627</v>
       </c>
@@ -54317,7 +54371,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="273" spans="1:13">
+    <row r="273" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A273" s="7">
         <v>42634</v>
       </c>
@@ -54358,7 +54412,7 @@
         <v>1766</v>
       </c>
     </row>
-    <row r="274" spans="1:13">
+    <row r="274" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A274" s="7">
         <v>42641</v>
       </c>
@@ -54399,7 +54453,7 @@
         <v>1766</v>
       </c>
     </row>
-    <row r="275" spans="1:13">
+    <row r="275" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A275" s="7">
         <v>42648</v>
       </c>
@@ -54440,7 +54494,7 @@
         <v>1743</v>
       </c>
     </row>
-    <row r="276" spans="1:13">
+    <row r="276" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A276" s="7">
         <v>42655</v>
       </c>
@@ -54481,7 +54535,7 @@
         <v>1770</v>
       </c>
     </row>
-    <row r="277" spans="1:13">
+    <row r="277" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A277" s="7">
         <v>42662</v>
       </c>
@@ -54522,7 +54576,7 @@
         <v>1770</v>
       </c>
     </row>
-    <row r="278" spans="1:13">
+    <row r="278" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A278" s="7">
         <v>42669</v>
       </c>
@@ -54563,7 +54617,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="279" spans="1:13">
+    <row r="279" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A279" s="7">
         <v>42676</v>
       </c>
@@ -54604,7 +54658,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="280" spans="1:13">
+    <row r="280" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A280" s="7">
         <v>42683</v>
       </c>
@@ -54645,7 +54699,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="281" spans="1:13">
+    <row r="281" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A281" s="7">
         <v>42690</v>
       </c>
@@ -54686,7 +54740,7 @@
         <v>1740</v>
       </c>
     </row>
-    <row r="282" spans="1:13">
+    <row r="282" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A282" s="7">
         <v>42697</v>
       </c>
@@ -54727,7 +54781,7 @@
         <v>1745</v>
       </c>
     </row>
-    <row r="283" spans="1:13">
+    <row r="283" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A283" s="7">
         <v>42704</v>
       </c>
@@ -54768,7 +54822,7 @@
         <v>1735</v>
       </c>
     </row>
-    <row r="284" spans="1:13">
+    <row r="284" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A284" s="7">
         <v>42711</v>
       </c>
@@ -54809,7 +54863,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="285" spans="1:13">
+    <row r="285" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A285" s="7">
         <v>42718</v>
       </c>
@@ -54850,7 +54904,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="286" spans="1:13">
+    <row r="286" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A286" s="7">
         <v>42725</v>
       </c>
@@ -54891,7 +54945,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="287" spans="1:13">
+    <row r="287" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A287" s="7">
         <v>42732</v>
       </c>
@@ -54932,7 +54986,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="288" spans="1:13">
+    <row r="288" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A288" s="7">
         <v>42739</v>
       </c>
@@ -54973,7 +55027,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="289" spans="1:13">
+    <row r="289" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A289" s="7">
         <v>42746</v>
       </c>
@@ -55014,7 +55068,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="290" spans="1:13">
+    <row r="290" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A290" s="7">
         <v>42753</v>
       </c>
@@ -55055,7 +55109,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="291" spans="1:13">
+    <row r="291" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A291" s="7">
         <v>42760</v>
       </c>
@@ -55096,7 +55150,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="292" spans="1:13">
+    <row r="292" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A292" s="7">
         <v>42767</v>
       </c>
@@ -55137,7 +55191,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="293" spans="1:13">
+    <row r="293" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A293" s="7">
         <v>42774</v>
       </c>
@@ -55178,7 +55232,7 @@
         <v>1778</v>
       </c>
     </row>
-    <row r="294" spans="1:13">
+    <row r="294" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A294" s="7">
         <v>42781</v>
       </c>
@@ -55219,7 +55273,7 @@
         <v>1728</v>
       </c>
     </row>
-    <row r="295" spans="1:13">
+    <row r="295" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A295" s="7">
         <v>42788</v>
       </c>
@@ -55260,7 +55314,7 @@
         <v>1728</v>
       </c>
     </row>
-    <row r="296" spans="1:13">
+    <row r="296" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A296" s="7">
         <v>42795</v>
       </c>
@@ -55301,7 +55355,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="297" spans="1:13">
+    <row r="297" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A297" s="7">
         <v>42802</v>
       </c>
@@ -55342,7 +55396,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="298" spans="1:13">
+    <row r="298" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A298" s="7">
         <v>42809</v>
       </c>
@@ -55383,7 +55437,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="299" spans="1:13">
+    <row r="299" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A299" s="7">
         <v>42816</v>
       </c>
@@ -55424,7 +55478,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="300" spans="1:13">
+    <row r="300" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A300" s="7">
         <v>42823</v>
       </c>
@@ -55465,7 +55519,7 @@
         <v>1777</v>
       </c>
     </row>
-    <row r="301" spans="1:13">
+    <row r="301" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A301" s="7">
         <v>42830</v>
       </c>
@@ -55506,7 +55560,7 @@
         <v>1810</v>
       </c>
     </row>
-    <row r="302" spans="1:13">
+    <row r="302" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A302" s="7">
         <v>42837</v>
       </c>
@@ -55547,7 +55601,7 @@
         <v>1810</v>
       </c>
     </row>
-    <row r="303" spans="1:13">
+    <row r="303" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A303" s="7">
         <v>42844</v>
       </c>
@@ -55588,7 +55642,7 @@
         <v>1775</v>
       </c>
     </row>
-    <row r="304" spans="1:13">
+    <row r="304" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A304" s="7">
         <v>42851</v>
       </c>
@@ -55629,7 +55683,7 @@
         <v>1802</v>
       </c>
     </row>
-    <row r="305" spans="1:13">
+    <row r="305" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A305" s="7">
         <v>42858</v>
       </c>
@@ -55670,7 +55724,7 @@
         <v>1778</v>
       </c>
     </row>
-    <row r="306" spans="1:13">
+    <row r="306" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A306" s="7">
         <v>42865</v>
       </c>
@@ -55711,7 +55765,7 @@
         <v>1749</v>
       </c>
     </row>
-    <row r="307" spans="1:13">
+    <row r="307" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A307" s="7">
         <v>42872</v>
       </c>
@@ -55752,7 +55806,7 @@
         <v>1755</v>
       </c>
     </row>
-    <row r="308" spans="1:13">
+    <row r="308" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A308" s="7">
         <v>42879</v>
       </c>
@@ -55793,7 +55847,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="309" spans="1:13">
+    <row r="309" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A309" s="7">
         <v>42886</v>
       </c>
@@ -55834,7 +55888,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="310" spans="1:13">
+    <row r="310" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A310" s="7">
         <v>42893</v>
       </c>
@@ -55875,7 +55929,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="311" spans="1:13">
+    <row r="311" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A311" s="7">
         <v>42900</v>
       </c>
@@ -55916,7 +55970,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="312" spans="1:13">
+    <row r="312" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A312" s="7">
         <v>42907</v>
       </c>
@@ -55957,7 +56011,7 @@
         <v>1734</v>
       </c>
     </row>
-    <row r="313" spans="1:13">
+    <row r="313" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A313" s="7">
         <v>42914</v>
       </c>
@@ -55998,7 +56052,7 @@
         <v>1734</v>
       </c>
     </row>
-    <row r="314" spans="1:13">
+    <row r="314" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A314" s="7">
         <v>42921</v>
       </c>
@@ -56039,7 +56093,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="315" spans="1:13">
+    <row r="315" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A315" s="7">
         <v>42928</v>
       </c>
@@ -56080,7 +56134,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="316" spans="1:13">
+    <row r="316" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A316" s="7">
         <v>42935</v>
       </c>
@@ -56121,7 +56175,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="317" spans="1:13">
+    <row r="317" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A317" s="7">
         <v>42942</v>
       </c>
@@ -56162,7 +56216,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="318" spans="1:13">
+    <row r="318" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A318" s="7">
         <v>42949</v>
       </c>
@@ -56203,7 +56257,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="319" spans="1:13">
+    <row r="319" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A319" s="7">
         <v>42956</v>
       </c>
@@ -56244,7 +56298,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="320" spans="1:13">
+    <row r="320" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A320" s="7">
         <v>42963</v>
       </c>
@@ -56285,7 +56339,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="321" spans="1:13">
+    <row r="321" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A321" s="7">
         <v>42970</v>
       </c>
@@ -56326,7 +56380,7 @@
         <v>1730</v>
       </c>
     </row>
-    <row r="322" spans="1:13">
+    <row r="322" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A322" s="7">
         <v>42977</v>
       </c>
@@ -56367,7 +56421,7 @@
         <v>1730</v>
       </c>
     </row>
-    <row r="323" spans="1:13">
+    <row r="323" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A323" s="7">
         <v>42984</v>
       </c>
@@ -56408,7 +56462,7 @@
         <v>1742</v>
       </c>
     </row>
-    <row r="324" spans="1:13">
+    <row r="324" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A324" s="7">
         <v>42991</v>
       </c>
@@ -56449,7 +56503,7 @@
         <v>1742</v>
       </c>
     </row>
-    <row r="325" spans="1:13">
+    <row r="325" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A325" s="7">
         <v>42998</v>
       </c>
@@ -56490,7 +56544,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="326" spans="1:13">
+    <row r="326" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A326" s="7">
         <v>43005</v>
       </c>
@@ -56531,7 +56585,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="327" spans="1:13">
+    <row r="327" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A327" s="7">
         <v>43012</v>
       </c>
@@ -56572,7 +56626,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="328" spans="1:13">
+    <row r="328" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A328" s="7">
         <v>43019</v>
       </c>
@@ -56613,7 +56667,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="329" spans="1:13">
+    <row r="329" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A329" s="7">
         <v>43026</v>
       </c>
@@ -56654,7 +56708,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="330" spans="1:13">
+    <row r="330" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A330" s="7">
         <v>43033</v>
       </c>
@@ -56695,7 +56749,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="331" spans="1:13">
+    <row r="331" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A331" s="7">
         <v>43040</v>
       </c>
@@ -56736,7 +56790,7 @@
         <v>1691</v>
       </c>
     </row>
-    <row r="332" spans="1:13">
+    <row r="332" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A332" s="7">
         <v>43047</v>
       </c>
@@ -56777,7 +56831,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="333" spans="1:13">
+    <row r="333" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A333" s="7">
         <v>43054</v>
       </c>
@@ -56818,7 +56872,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="334" spans="1:13">
+    <row r="334" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A334" s="7">
         <v>43061</v>
       </c>
@@ -56859,7 +56913,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="335" spans="1:13">
+    <row r="335" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A335" s="7">
         <v>43068</v>
       </c>
@@ -56900,7 +56954,7 @@
         <v>1853</v>
       </c>
     </row>
-    <row r="336" spans="1:13">
+    <row r="336" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A336" s="7">
         <v>43075</v>
       </c>
@@ -56941,7 +56995,7 @@
         <v>2063</v>
       </c>
     </row>
-    <row r="337" spans="1:13">
+    <row r="337" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A337" s="7">
         <v>43082</v>
       </c>
@@ -56982,7 +57036,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="338" spans="1:13">
+    <row r="338" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A338" s="7">
         <v>43089</v>
       </c>
@@ -57023,7 +57077,7 @@
         <v>1748</v>
       </c>
     </row>
-    <row r="339" spans="1:13">
+    <row r="339" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A339" s="7">
         <v>43096</v>
       </c>
@@ -57064,7 +57118,7 @@
         <v>1824</v>
       </c>
     </row>
-    <row r="340" spans="1:13">
+    <row r="340" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A340" s="7">
         <v>43103</v>
       </c>
@@ -57105,7 +57159,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="341" spans="1:13">
+    <row r="341" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A341" s="7">
         <v>43110</v>
       </c>
@@ -57146,7 +57200,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="342" spans="1:13">
+    <row r="342" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A342" s="7">
         <v>43117</v>
       </c>
@@ -57187,7 +57241,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="343" spans="1:13">
+    <row r="343" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A343" s="7">
         <v>43124</v>
       </c>
@@ -57228,7 +57282,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="344" spans="1:13">
+    <row r="344" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A344" s="7">
         <v>43131</v>
       </c>
@@ -57269,7 +57323,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="345" spans="1:13">
+    <row r="345" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A345" s="7">
         <v>43138</v>
       </c>
@@ -57310,7 +57364,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="346" spans="1:13">
+    <row r="346" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A346" s="7">
         <v>43145</v>
       </c>
@@ -57351,7 +57405,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="347" spans="1:13">
+    <row r="347" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A347" s="7">
         <v>43152</v>
       </c>
@@ -57392,7 +57446,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="348" spans="1:13">
+    <row r="348" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A348" s="7">
         <v>43159</v>
       </c>
@@ -57433,7 +57487,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="349" spans="1:13">
+    <row r="349" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A349" s="7">
         <v>43166</v>
       </c>
@@ -57474,7 +57528,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="350" spans="1:13">
+    <row r="350" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A350" s="7">
         <v>43173</v>
       </c>
@@ -57515,7 +57569,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="351" spans="1:13">
+    <row r="351" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A351" s="7">
         <v>43180</v>
       </c>
@@ -57556,7 +57610,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="352" spans="1:13">
+    <row r="352" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A352" s="7">
         <v>43187</v>
       </c>
@@ -57597,7 +57651,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="353" spans="1:13">
+    <row r="353" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A353" s="7">
         <v>43194</v>
       </c>
@@ -57638,7 +57692,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="354" spans="1:13">
+    <row r="354" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A354" s="7">
         <v>43201</v>
       </c>
@@ -57679,7 +57733,7 @@
         <v>1864</v>
       </c>
     </row>
-    <row r="355" spans="1:13">
+    <row r="355" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A355" s="7">
         <v>43208</v>
       </c>
@@ -57720,7 +57774,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="356" spans="1:13">
+    <row r="356" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A356" s="7">
         <v>43215</v>
       </c>
@@ -57761,7 +57815,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="357" spans="1:13">
+    <row r="357" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A357" s="7">
         <v>43222</v>
       </c>
@@ -57802,7 +57856,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="358" spans="1:13">
+    <row r="358" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A358" s="7">
         <v>43229</v>
       </c>
@@ -57843,7 +57897,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="359" spans="1:13">
+    <row r="359" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A359" s="7">
         <v>43236</v>
       </c>
@@ -57884,7 +57938,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="360" spans="1:13">
+    <row r="360" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A360" s="7">
         <v>43243</v>
       </c>
@@ -57925,7 +57979,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="361" spans="1:13">
+    <row r="361" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A361" s="7">
         <v>43250</v>
       </c>
@@ -57966,7 +58020,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="362" spans="1:13">
+    <row r="362" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A362" s="7">
         <v>43257</v>
       </c>
@@ -58007,7 +58061,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="363" spans="1:13">
+    <row r="363" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A363" s="7">
         <v>43264</v>
       </c>
@@ -58048,7 +58102,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="364" spans="1:13">
+    <row r="364" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A364" s="7">
         <v>43271</v>
       </c>
@@ -58089,7 +58143,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="365" spans="1:13">
+    <row r="365" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A365" s="7">
         <v>43278</v>
       </c>
@@ -58130,7 +58184,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="366" spans="1:13">
+    <row r="366" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A366" s="7">
         <v>43285</v>
       </c>
@@ -58171,7 +58225,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="367" spans="1:13">
+    <row r="367" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A367" s="7">
         <v>43292</v>
       </c>
@@ -58212,7 +58266,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="368" spans="1:13">
+    <row r="368" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A368" s="7">
         <v>43299</v>
       </c>
@@ -58253,7 +58307,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="369" spans="1:13">
+    <row r="369" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A369" s="7">
         <v>43306</v>
       </c>
@@ -58294,7 +58348,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="370" spans="1:13">
+    <row r="370" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A370" s="7">
         <v>43313</v>
       </c>
@@ -58335,7 +58389,7 @@
         <v>1965</v>
       </c>
     </row>
-    <row r="371" spans="1:13">
+    <row r="371" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A371" s="7">
         <v>43320</v>
       </c>
@@ -58376,7 +58430,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="372" spans="1:13">
+    <row r="372" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A372" s="7">
         <v>43327</v>
       </c>
@@ -58417,7 +58471,7 @@
         <v>1962</v>
       </c>
     </row>
-    <row r="373" spans="1:13">
+    <row r="373" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A373" s="7">
         <v>43334</v>
       </c>
@@ -58458,7 +58512,7 @@
         <v>1962</v>
       </c>
     </row>
-    <row r="374" spans="1:13">
+    <row r="374" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A374" s="7">
         <v>43341</v>
       </c>
@@ -58499,7 +58553,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="375" spans="1:13">
+    <row r="375" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A375" s="7">
         <v>43348</v>
       </c>
@@ -58540,7 +58594,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="376" spans="1:13">
+    <row r="376" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A376" s="7">
         <v>43355</v>
       </c>
@@ -58581,7 +58635,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="377" spans="1:13">
+    <row r="377" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A377" s="7">
         <v>43362</v>
       </c>
@@ -58622,7 +58676,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="378" spans="1:13">
+    <row r="378" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A378" s="7">
         <v>43369</v>
       </c>
@@ -58663,7 +58717,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="379" spans="1:13">
+    <row r="379" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A379" s="7">
         <v>43376</v>
       </c>
@@ -58704,7 +58758,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="380" spans="1:13">
+    <row r="380" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A380" s="7">
         <v>43383</v>
       </c>
@@ -58745,7 +58799,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="381" spans="1:13">
+    <row r="381" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A381" s="7">
         <v>43390</v>
       </c>
@@ -58786,7 +58840,7 @@
         <v>1970</v>
       </c>
     </row>
-    <row r="382" spans="1:13">
+    <row r="382" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A382" s="7">
         <v>43397</v>
       </c>
@@ -58827,7 +58881,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="383" spans="1:13">
+    <row r="383" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A383" s="7">
         <v>43404</v>
       </c>
@@ -58868,7 +58922,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="384" spans="1:13">
+    <row r="384" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A384" s="7">
         <v>43411</v>
       </c>
@@ -58909,7 +58963,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="385" spans="1:13">
+    <row r="385" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A385" s="7">
         <v>43418</v>
       </c>
@@ -58950,7 +59004,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="386" spans="1:13">
+    <row r="386" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A386" s="7">
         <v>43425</v>
       </c>
@@ -58991,7 +59045,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="387" spans="1:13">
+    <row r="387" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A387" s="7">
         <v>43432</v>
       </c>
@@ -59032,7 +59086,7 @@
         <v>2045</v>
       </c>
     </row>
-    <row r="388" spans="1:13">
+    <row r="388" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A388" s="7">
         <v>43439</v>
       </c>
@@ -59073,7 +59127,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="389" spans="1:13">
+    <row r="389" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A389" s="7">
         <v>43446</v>
       </c>
@@ -59114,7 +59168,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="390" spans="1:13">
+    <row r="390" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A390" s="7">
         <v>43453</v>
       </c>
@@ -59155,7 +59209,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="391" spans="1:13">
+    <row r="391" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A391" s="7">
         <v>43460</v>
       </c>
@@ -59196,7 +59250,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="392" spans="1:13">
+    <row r="392" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A392" s="7">
         <v>43467</v>
       </c>
@@ -59237,7 +59291,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="393" spans="1:13">
+    <row r="393" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A393" s="7">
         <v>43474</v>
       </c>
@@ -59278,7 +59332,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="394" spans="1:13">
+    <row r="394" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A394" s="7">
         <v>43481</v>
       </c>
@@ -59319,7 +59373,7 @@
         <v>2049</v>
       </c>
     </row>
-    <row r="395" spans="1:13">
+    <row r="395" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A395" s="7">
         <v>43488</v>
       </c>
@@ -59360,7 +59414,7 @@
         <v>2049</v>
       </c>
     </row>
-    <row r="396" spans="1:13">
+    <row r="396" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A396" s="7">
         <v>43495</v>
       </c>
@@ -59401,7 +59455,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="397" spans="1:13">
+    <row r="397" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A397" s="7">
         <v>43502</v>
       </c>
@@ -59442,7 +59496,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="398" spans="1:13">
+    <row r="398" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A398" s="7">
         <v>43509</v>
       </c>
@@ -59483,7 +59537,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="399" spans="1:13">
+    <row r="399" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A399" s="7">
         <v>43516</v>
       </c>
@@ -59524,7 +59578,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="400" spans="1:13">
+    <row r="400" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A400" s="7">
         <v>43523</v>
       </c>
@@ -59565,7 +59619,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="401" spans="1:13">
+    <row r="401" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A401" s="7">
         <v>43530</v>
       </c>
@@ -59606,7 +59660,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="402" spans="1:13">
+    <row r="402" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A402" s="7">
         <v>43537</v>
       </c>
@@ -59647,7 +59701,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="403" spans="1:13">
+    <row r="403" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A403" s="7">
         <v>43544</v>
       </c>
@@ -59688,7 +59742,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="404" spans="1:13">
+    <row r="404" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A404" s="7">
         <v>43551</v>
       </c>
@@ -59729,7 +59783,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="405" spans="1:13">
+    <row r="405" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A405" s="7">
         <v>43558</v>
       </c>
@@ -59770,7 +59824,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="406" spans="1:13">
+    <row r="406" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A406" s="7">
         <v>43565</v>
       </c>
@@ -59811,7 +59865,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="407" spans="1:13">
+    <row r="407" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A407" s="7">
         <v>43572</v>
       </c>
@@ -59852,7 +59906,7 @@
         <v>2302</v>
       </c>
     </row>
-    <row r="408" spans="1:13">
+    <row r="408" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A408" s="7">
         <v>43579</v>
       </c>
@@ -59893,7 +59947,7 @@
         <v>2302</v>
       </c>
     </row>
-    <row r="409" spans="1:13">
+    <row r="409" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A409" s="7">
         <v>43586</v>
       </c>
@@ -59934,7 +59988,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="410" spans="1:13">
+    <row r="410" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A410" s="7">
         <v>43593</v>
       </c>
@@ -59975,7 +60029,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="411" spans="1:13">
+    <row r="411" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A411" s="7">
         <v>43600</v>
       </c>
@@ -60016,7 +60070,7 @@
         <v>2343</v>
       </c>
     </row>
-    <row r="412" spans="1:13">
+    <row r="412" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A412" s="7">
         <v>43607</v>
       </c>
@@ -60057,7 +60111,7 @@
         <v>2343</v>
       </c>
     </row>
-    <row r="413" spans="1:13">
+    <row r="413" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A413" s="7">
         <v>43614</v>
       </c>
@@ -60098,7 +60152,7 @@
         <v>2272</v>
       </c>
     </row>
-    <row r="414" spans="1:13">
+    <row r="414" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A414" s="7">
         <v>43621</v>
       </c>
@@ -60139,7 +60193,7 @@
         <v>2344</v>
       </c>
     </row>
-    <row r="415" spans="1:13">
+    <row r="415" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A415" s="7">
         <v>43628</v>
       </c>
@@ -60180,7 +60234,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="416" spans="1:13">
+    <row r="416" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A416" s="7">
         <v>43635</v>
       </c>
@@ -60221,7 +60275,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="417" spans="1:13">
+    <row r="417" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A417" s="7">
         <v>43642</v>
       </c>
@@ -60262,7 +60316,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="418" spans="1:13">
+    <row r="418" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A418" s="7">
         <v>43649</v>
       </c>
@@ -60303,7 +60357,7 @@
         <v>2378</v>
       </c>
     </row>
-    <row r="419" spans="1:13">
+    <row r="419" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A419" s="7">
         <v>43656</v>
       </c>
@@ -60344,7 +60398,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="420" spans="1:13">
+    <row r="420" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A420" s="7">
         <v>43663</v>
       </c>
@@ -60385,7 +60439,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="421" spans="1:13">
+    <row r="421" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A421" s="7">
         <v>43670</v>
       </c>
@@ -60426,7 +60480,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="422" spans="1:13">
+    <row r="422" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A422" s="7">
         <v>43677</v>
       </c>
@@ -60467,7 +60521,7 @@
         <v>2369</v>
       </c>
     </row>
-    <row r="423" spans="1:13">
+    <row r="423" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A423" s="7">
         <v>43684</v>
       </c>
@@ -60508,7 +60562,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="424" spans="1:13">
+    <row r="424" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A424" s="7">
         <v>43691</v>
       </c>
@@ -60549,7 +60603,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="425" spans="1:13">
+    <row r="425" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A425" s="7">
         <v>43698</v>
       </c>
@@ -60590,7 +60644,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="426" spans="1:13">
+    <row r="426" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A426" s="7">
         <v>43705</v>
       </c>
@@ -60631,7 +60685,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="427" spans="1:13">
+    <row r="427" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A427" s="7">
         <v>43712</v>
       </c>
@@ -60672,7 +60726,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="428" spans="1:13">
+    <row r="428" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A428" s="7">
         <v>43719</v>
       </c>
@@ -60713,7 +60767,7 @@
         <v>2346</v>
       </c>
     </row>
-    <row r="429" spans="1:13">
+    <row r="429" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A429" s="7">
         <v>43726</v>
       </c>
@@ -60754,7 +60808,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="430" spans="1:13">
+    <row r="430" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A430" s="7">
         <v>43733</v>
       </c>
@@ -60795,7 +60849,7 @@
         <v>2346</v>
       </c>
     </row>
-    <row r="431" spans="1:13">
+    <row r="431" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A431" s="7">
         <v>43740</v>
       </c>
@@ -60836,7 +60890,7 @@
         <v>2349</v>
       </c>
     </row>
-    <row r="432" spans="1:13">
+    <row r="432" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A432" s="7">
         <v>43747</v>
       </c>
@@ -60877,7 +60931,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="433" spans="1:13">
+    <row r="433" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A433" s="7">
         <v>43754</v>
       </c>
@@ -60918,7 +60972,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="434" spans="1:13">
+    <row r="434" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A434" s="7">
         <v>43761</v>
       </c>
@@ -60959,7 +61013,7 @@
         <v>2350</v>
       </c>
     </row>
-    <row r="435" spans="1:13">
+    <row r="435" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A435" s="7">
         <v>43768</v>
       </c>
@@ -61000,7 +61054,7 @@
         <v>2356</v>
       </c>
     </row>
-    <row r="436" spans="1:13">
+    <row r="436" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A436" s="7">
         <v>43775</v>
       </c>
@@ -61041,7 +61095,7 @@
         <v>2363</v>
       </c>
     </row>
-    <row r="437" spans="1:13">
+    <row r="437" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A437" s="7">
         <v>43782</v>
       </c>
@@ -61082,7 +61136,7 @@
         <v>2338</v>
       </c>
     </row>
-    <row r="438" spans="1:13">
+    <row r="438" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A438" s="7">
         <v>43789</v>
       </c>
@@ -61123,7 +61177,7 @@
         <v>2391</v>
       </c>
     </row>
-    <row r="439" spans="1:13">
+    <row r="439" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A439" s="7">
         <v>43796</v>
       </c>
@@ -61164,7 +61218,7 @@
         <v>2397</v>
       </c>
     </row>
-    <row r="440" spans="1:13">
+    <row r="440" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A440" s="7">
         <v>43803</v>
       </c>
@@ -61205,7 +61259,7 @@
         <v>2388</v>
       </c>
     </row>
-    <row r="441" spans="1:13">
+    <row r="441" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A441" s="7">
         <v>43810</v>
       </c>
@@ -61246,7 +61300,7 @@
         <v>2363</v>
       </c>
     </row>
-    <row r="442" spans="1:13">
+    <row r="442" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A442" s="7">
         <v>43817</v>
       </c>
@@ -61287,7 +61341,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="443" spans="1:13">
+    <row r="443" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A443" s="7">
         <v>43831</v>
       </c>
@@ -61328,7 +61382,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="444" spans="1:13">
+    <row r="444" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A444" s="7">
         <v>43838</v>
       </c>
@@ -61369,7 +61423,7 @@
         <v>2415</v>
       </c>
     </row>
-    <row r="445" spans="1:13">
+    <row r="445" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A445" s="7">
         <v>43845</v>
       </c>
@@ -61410,7 +61464,7 @@
         <v>2415</v>
       </c>
     </row>
-    <row r="446" spans="1:13">
+    <row r="446" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A446" s="7">
         <v>43852</v>
       </c>
@@ -61451,7 +61505,7 @@
         <v>2410</v>
       </c>
     </row>
-    <row r="447" spans="1:13">
+    <row r="447" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A447" s="7">
         <v>43859</v>
       </c>
@@ -61492,7 +61546,7 @@
         <v>2344</v>
       </c>
     </row>
-    <row r="448" spans="1:13">
+    <row r="448" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A448" s="7">
         <v>43866</v>
       </c>
@@ -61533,7 +61587,7 @@
         <v>2188</v>
       </c>
     </row>
-    <row r="449" spans="1:13">
+    <row r="449" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A449" s="7">
         <v>43873</v>
       </c>
@@ -61574,7 +61628,7 @@
         <v>2214</v>
       </c>
     </row>
-    <row r="450" spans="1:13">
+    <row r="450" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A450" s="7">
         <v>43880</v>
       </c>
@@ -61615,7 +61669,7 @@
         <v>2214</v>
       </c>
     </row>
-    <row r="451" spans="1:13">
+    <row r="451" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A451" s="7">
         <v>43887</v>
       </c>
@@ -61656,7 +61710,7 @@
         <v>2206</v>
       </c>
     </row>
-    <row r="452" spans="1:13">
+    <row r="452" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A452" s="7">
         <v>43894</v>
       </c>
@@ -61697,7 +61751,7 @@
         <v>2217</v>
       </c>
     </row>
-    <row r="453" spans="1:13">
+    <row r="453" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A453" s="7">
         <v>43901</v>
       </c>
@@ -61738,7 +61792,7 @@
         <v>2234</v>
       </c>
     </row>
-    <row r="454" spans="1:13">
+    <row r="454" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A454" s="7">
         <v>43908</v>
       </c>
@@ -61779,7 +61833,7 @@
         <v>2513</v>
       </c>
     </row>
-    <row r="455" spans="1:13">
+    <row r="455" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A455" s="7">
         <v>43915</v>
       </c>
@@ -61820,7 +61874,7 @@
         <v>2322</v>
       </c>
     </row>
-    <row r="456" spans="1:13">
+    <row r="456" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A456" s="7">
         <v>43922</v>
       </c>
@@ -61861,7 +61915,7 @@
         <v>2322</v>
       </c>
     </row>
-    <row r="457" spans="1:13">
+    <row r="457" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A457" s="7">
         <v>43929</v>
       </c>
@@ -61902,7 +61956,7 @@
         <v>2548</v>
       </c>
     </row>
-    <row r="458" spans="1:13">
+    <row r="458" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A458" s="7">
         <v>43936</v>
       </c>
@@ -61943,7 +61997,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="459" spans="1:13">
+    <row r="459" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A459" s="7">
         <v>43943</v>
       </c>
@@ -61984,7 +62038,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="460" spans="1:13">
+    <row r="460" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A460" s="7">
         <v>43950</v>
       </c>
@@ -62025,7 +62079,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="461" spans="1:13">
+    <row r="461" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A461" s="7">
         <v>43957</v>
       </c>
@@ -62066,7 +62120,7 @@
         <v>2592</v>
       </c>
     </row>
-    <row r="462" spans="1:13">
+    <row r="462" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A462" s="7">
         <v>43964</v>
       </c>
@@ -62107,7 +62161,7 @@
         <v>2592</v>
       </c>
     </row>
-    <row r="463" spans="1:13">
+    <row r="463" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A463" s="7">
         <v>43971</v>
       </c>
@@ -62148,7 +62202,7 @@
         <v>2516</v>
       </c>
     </row>
-    <row r="464" spans="1:13">
+    <row r="464" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A464" s="7">
         <v>43978</v>
       </c>
@@ -62189,7 +62243,7 @@
         <v>2516</v>
       </c>
     </row>
-    <row r="465" spans="1:13">
+    <row r="465" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A465" s="7">
         <v>43985</v>
       </c>
@@ -62230,7 +62284,7 @@
         <v>2398</v>
       </c>
     </row>
-    <row r="466" spans="1:13">
+    <row r="466" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A466" s="7">
         <v>43992</v>
       </c>
@@ -62271,7 +62325,7 @@
         <v>2398</v>
       </c>
     </row>
-    <row r="467" spans="1:13">
+    <row r="467" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A467" s="7">
         <v>43999</v>
       </c>
@@ -62312,7 +62366,7 @@
         <v>2577</v>
       </c>
     </row>
-    <row r="468" spans="1:13">
+    <row r="468" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A468" s="7">
         <v>44006</v>
       </c>
@@ -62353,7 +62407,7 @@
         <v>2443</v>
       </c>
     </row>
-    <row r="469" spans="1:13">
+    <row r="469" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A469" s="7">
         <v>44013</v>
       </c>
@@ -62394,7 +62448,7 @@
         <v>2369</v>
       </c>
     </row>
-    <row r="470" spans="1:13">
+    <row r="470" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A470" s="7">
         <v>44020</v>
       </c>
@@ -62435,7 +62489,7 @@
         <v>2326</v>
       </c>
     </row>
-    <row r="471" spans="1:13">
+    <row r="471" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A471" s="7">
         <v>44027</v>
       </c>
@@ -62476,7 +62530,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="472" spans="1:13">
+    <row r="472" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A472" s="7">
         <v>44034</v>
       </c>
@@ -62517,7 +62571,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="473" spans="1:13">
+    <row r="473" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A473" s="7">
         <v>44041</v>
       </c>
@@ -62558,7 +62612,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="474" spans="1:13">
+    <row r="474" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A474" s="7">
         <v>44048</v>
       </c>
@@ -62599,7 +62653,7 @@
         <v>2264</v>
       </c>
     </row>
-    <row r="475" spans="1:13">
+    <row r="475" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A475" s="7">
         <v>44055</v>
       </c>
@@ -62640,7 +62694,7 @@
         <v>2202</v>
       </c>
     </row>
-    <row r="476" spans="1:13">
+    <row r="476" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A476" s="7">
         <v>44062</v>
       </c>
@@ -62681,7 +62735,7 @@
         <v>2449</v>
       </c>
     </row>
-    <row r="477" spans="1:13">
+    <row r="477" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A477" s="7">
         <v>44069</v>
       </c>
@@ -62722,7 +62776,7 @@
         <v>2449</v>
       </c>
     </row>
-    <row r="478" spans="1:13">
+    <row r="478" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A478" s="7">
         <v>44076</v>
       </c>
@@ -62763,7 +62817,7 @@
         <v>2449</v>
       </c>
     </row>
-    <row r="479" spans="1:13">
+    <row r="479" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A479" s="7">
         <v>44083</v>
       </c>
@@ -62804,7 +62858,7 @@
         <v>2421</v>
       </c>
     </row>
-    <row r="480" spans="1:13">
+    <row r="480" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A480" s="7">
         <v>44090</v>
       </c>
@@ -62845,7 +62899,7 @@
         <v>2437</v>
       </c>
     </row>
-    <row r="481" spans="1:13">
+    <row r="481" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A481" s="7">
         <v>44097</v>
       </c>
@@ -62886,7 +62940,7 @@
         <v>2437</v>
       </c>
     </row>
-    <row r="482" spans="1:13">
+    <row r="482" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A482" s="7">
         <v>44104</v>
       </c>
@@ -62927,7 +62981,7 @@
         <v>2222</v>
       </c>
     </row>
-    <row r="483" spans="1:13">
+    <row r="483" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A483" s="7">
         <v>44111</v>
       </c>
@@ -62968,7 +63022,7 @@
         <v>2134</v>
       </c>
     </row>
-    <row r="484" spans="1:13">
+    <row r="484" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A484" s="7">
         <v>44118</v>
       </c>
@@ -63009,7 +63063,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="485" spans="1:13">
+    <row r="485" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A485" s="7">
         <v>44125</v>
       </c>
@@ -63050,7 +63104,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="486" spans="1:13">
+    <row r="486" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A486" s="7">
         <v>44132</v>
       </c>
@@ -63091,7 +63145,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="487" spans="1:13">
+    <row r="487" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A487" s="7">
         <v>44139</v>
       </c>
@@ -63132,7 +63186,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="488" spans="1:13">
+    <row r="488" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A488" s="7">
         <v>44146</v>
       </c>
@@ -63173,7 +63227,7 @@
         <v>2034</v>
       </c>
     </row>
-    <row r="489" spans="1:13">
+    <row r="489" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A489" s="7">
         <v>44153</v>
       </c>
@@ -63214,7 +63268,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="490" spans="1:13">
+    <row r="490" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A490" s="7">
         <v>44160</v>
       </c>
@@ -63255,7 +63309,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="491" spans="1:13">
+    <row r="491" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A491" s="7">
         <v>44167</v>
       </c>
@@ -63296,7 +63350,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="492" spans="1:13">
+    <row r="492" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A492" s="7">
         <v>44174</v>
       </c>
@@ -63337,7 +63391,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="493" spans="1:13">
+    <row r="493" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A493" s="7">
         <v>44181</v>
       </c>
@@ -63378,7 +63432,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="494" spans="1:13">
+    <row r="494" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A494" s="7">
         <v>44188</v>
       </c>
@@ -63419,7 +63473,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="495" spans="1:13">
+    <row r="495" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A495" s="7">
         <v>44195</v>
       </c>
@@ -63460,7 +63514,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="496" spans="1:13">
+    <row r="496" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A496" s="7">
         <v>44202</v>
       </c>
@@ -63501,7 +63555,7 @@
         <v>2185</v>
       </c>
     </row>
-    <row r="497" spans="1:13">
+    <row r="497" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A497" s="7">
         <v>44209</v>
       </c>
@@ -63542,7 +63596,7 @@
         <v>2116</v>
       </c>
     </row>
-    <row r="498" spans="1:13">
+    <row r="498" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A498" s="7">
         <v>44216</v>
       </c>
@@ -63583,7 +63637,7 @@
         <v>2283</v>
       </c>
     </row>
-    <row r="499" spans="1:13">
+    <row r="499" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A499" s="7">
         <v>44223</v>
       </c>
@@ -63624,7 +63678,7 @@
         <v>2283</v>
       </c>
     </row>
-    <row r="500" spans="1:13">
+    <row r="500" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A500" s="7">
         <v>44230</v>
       </c>
@@ -63665,7 +63719,7 @@
         <v>2254</v>
       </c>
     </row>
-    <row r="501" spans="1:13">
+    <row r="501" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A501" s="7">
         <v>44237</v>
       </c>
@@ -63706,7 +63760,7 @@
         <v>2299</v>
       </c>
     </row>
-    <row r="502" spans="1:13">
+    <row r="502" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A502" s="7">
         <v>44244</v>
       </c>
@@ -63747,7 +63801,7 @@
         <v>2299</v>
       </c>
     </row>
-    <row r="503" spans="1:13">
+    <row r="503" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A503" s="7">
         <v>44251</v>
       </c>
@@ -63788,7 +63842,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="504" spans="1:13">
+    <row r="504" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A504" s="7">
         <v>44258</v>
       </c>
@@ -63829,7 +63883,7 @@
         <v>2342</v>
       </c>
     </row>
-    <row r="505" spans="1:13">
+    <row r="505" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A505" s="7">
         <v>44265</v>
       </c>
@@ -63870,7 +63924,7 @@
         <v>2359</v>
       </c>
     </row>
-    <row r="506" spans="1:13">
+    <row r="506" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A506" s="7">
         <v>44272</v>
       </c>
@@ -63911,7 +63965,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="507" spans="1:13">
+    <row r="507" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A507" s="7">
         <v>44279</v>
       </c>
@@ -63952,7 +64006,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="508" spans="1:13">
+    <row r="508" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A508" s="7">
         <v>44286</v>
       </c>
@@ -63993,7 +64047,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="509" spans="1:13">
+    <row r="509" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A509" s="7">
         <v>44293</v>
       </c>
@@ -64034,7 +64088,7 @@
         <v>2621</v>
       </c>
     </row>
-    <row r="510" spans="1:13">
+    <row r="510" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A510" s="7">
         <v>44300</v>
       </c>
@@ -64075,7 +64129,7 @@
         <v>2623</v>
       </c>
     </row>
-    <row r="511" spans="1:13">
+    <row r="511" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A511" s="7">
         <v>44307</v>
       </c>
@@ -64116,7 +64170,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="512" spans="1:13">
+    <row r="512" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A512" s="7">
         <v>44314</v>
       </c>
@@ -64157,7 +64211,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="513" spans="1:13">
+    <row r="513" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A513" s="7">
         <v>44321</v>
       </c>
@@ -64198,7 +64252,7 @@
         <v>3505</v>
       </c>
     </row>
-    <row r="514" spans="1:13">
+    <row r="514" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A514" s="7">
         <v>44328</v>
       </c>
@@ -64239,7 +64293,7 @@
         <v>3550</v>
       </c>
     </row>
-    <row r="515" spans="1:13">
+    <row r="515" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A515" s="7">
         <v>44335</v>
       </c>
@@ -64280,7 +64334,7 @@
         <v>3553</v>
       </c>
     </row>
-    <row r="516" spans="1:13">
+    <row r="516" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A516" s="7">
         <v>44342</v>
       </c>
@@ -64321,7 +64375,7 @@
         <v>3670</v>
       </c>
     </row>
-    <row r="517" spans="1:13">
+    <row r="517" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A517" s="7">
         <v>44349</v>
       </c>
@@ -64362,7 +64416,7 @@
         <v>3720</v>
       </c>
     </row>
-    <row r="518" spans="1:13">
+    <row r="518" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A518" s="7">
         <v>44356</v>
       </c>
@@ -64403,7 +64457,7 @@
         <v>3988</v>
       </c>
     </row>
-    <row r="519" spans="1:13">
+    <row r="519" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A519" s="7">
         <v>44363</v>
       </c>
@@ -64444,7 +64498,7 @@
         <v>4607</v>
       </c>
     </row>
-    <row r="520" spans="1:13">
+    <row r="520" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A520" s="7">
         <v>44370</v>
       </c>
@@ -64485,7 +64539,7 @@
         <v>4744</v>
       </c>
     </row>
-    <row r="521" spans="1:13">
+    <row r="521" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A521" s="7">
         <v>44377</v>
       </c>
@@ -64526,7 +64580,7 @@
         <v>5008</v>
       </c>
     </row>
-    <row r="522" spans="1:13">
+    <row r="522" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A522" s="7">
         <v>44384</v>
       </c>
@@ -64567,7 +64621,7 @@
         <v>5336</v>
       </c>
     </row>
-    <row r="523" spans="1:13">
+    <row r="523" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A523" s="7">
         <v>44391</v>
       </c>
@@ -64608,7 +64662,7 @@
         <v>5362</v>
       </c>
     </row>
-    <row r="524" spans="1:13">
+    <row r="524" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A524" s="7">
         <v>44398</v>
       </c>
@@ -64649,7 +64703,7 @@
         <v>5364</v>
       </c>
     </row>
-    <row r="525" spans="1:13">
+    <row r="525" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A525" s="7">
         <v>44405</v>
       </c>
@@ -64690,7 +64744,7 @@
         <v>5624</v>
       </c>
     </row>
-    <row r="526" spans="1:13">
+    <row r="526" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A526" s="7">
         <v>44412</v>
       </c>
@@ -64731,7 +64785,7 @@
         <v>6417</v>
       </c>
     </row>
-    <row r="527" spans="1:13">
+    <row r="527" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A527" s="7">
         <v>44419</v>
       </c>
@@ -64772,7 +64826,7 @@
         <v>6390</v>
       </c>
     </row>
-    <row r="528" spans="1:13">
+    <row r="528" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A528" s="7">
         <v>44426</v>
       </c>
@@ -64813,7 +64867,7 @@
         <v>6435</v>
       </c>
     </row>
-    <row r="529" spans="1:13">
+    <row r="529" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A529" s="7">
         <v>44433</v>
       </c>
@@ -64854,7 +64908,7 @@
         <v>6461</v>
       </c>
     </row>
-    <row r="530" spans="1:13">
+    <row r="530" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A530" s="7">
         <v>44440</v>
       </c>
@@ -64895,7 +64949,7 @@
         <v>5776</v>
       </c>
     </row>
-    <row r="531" spans="1:13">
+    <row r="531" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A531" s="7">
         <v>44447</v>
       </c>
@@ -64936,7 +64990,7 @@
         <v>6160</v>
       </c>
     </row>
-    <row r="532" spans="1:13">
+    <row r="532" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A532" s="7">
         <v>44454</v>
       </c>
@@ -64977,7 +65031,7 @@
         <v>6162</v>
       </c>
     </row>
-    <row r="533" spans="1:13">
+    <row r="533" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A533" s="7">
         <v>44461</v>
       </c>
@@ -65018,7 +65072,7 @@
         <v>6179</v>
       </c>
     </row>
-    <row r="534" spans="1:13">
+    <row r="534" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A534" s="7">
         <v>44468</v>
       </c>
@@ -65059,7 +65113,7 @@
         <v>6192</v>
       </c>
     </row>
-    <row r="535" spans="1:13">
+    <row r="535" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A535" s="7">
         <v>44475</v>
       </c>
@@ -65100,7 +65154,7 @@
         <v>6209</v>
       </c>
     </row>
-    <row r="536" spans="1:13">
+    <row r="536" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A536" s="7">
         <v>44482</v>
       </c>
@@ -65141,7 +65195,7 @@
         <v>6200</v>
       </c>
     </row>
-    <row r="537" spans="1:13">
+    <row r="537" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A537" s="7">
         <v>44489</v>
       </c>
@@ -65182,7 +65236,7 @@
         <v>6157</v>
       </c>
     </row>
-    <row r="538" spans="1:13">
+    <row r="538" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A538" s="7">
         <v>44496</v>
       </c>
@@ -65223,7 +65277,7 @@
         <v>6161</v>
       </c>
     </row>
-    <row r="539" spans="1:13">
+    <row r="539" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A539" s="7">
         <v>44503</v>
       </c>
@@ -65264,7 +65318,7 @@
         <v>6123</v>
       </c>
     </row>
-    <row r="540" spans="1:13">
+    <row r="540" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A540" s="7">
         <v>44510</v>
       </c>
@@ -65305,7 +65359,7 @@
         <v>6255</v>
       </c>
     </row>
-    <row r="541" spans="1:13">
+    <row r="541" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A541" s="7">
         <v>44517</v>
       </c>
@@ -65346,7 +65400,7 @@
         <v>6272</v>
       </c>
     </row>
-    <row r="542" spans="1:13">
+    <row r="542" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A542" s="7">
         <v>44524</v>
       </c>
@@ -65387,7 +65441,7 @@
         <v>6232</v>
       </c>
     </row>
-    <row r="543" spans="1:13">
+    <row r="543" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A543" s="7">
         <v>44531</v>
       </c>
@@ -65428,7 +65482,7 @@
         <v>6214</v>
       </c>
     </row>
-    <row r="544" spans="1:13">
+    <row r="544" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A544" s="7">
         <v>44538</v>
       </c>
@@ -65469,7 +65523,7 @@
         <v>6283</v>
       </c>
     </row>
-    <row r="545" spans="1:13">
+    <row r="545" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A545" s="7">
         <v>44545</v>
       </c>
@@ -65510,7 +65564,7 @@
         <v>6272</v>
       </c>
     </row>
-    <row r="546" spans="1:13">
+    <row r="546" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A546" s="7">
         <v>44552</v>
       </c>
@@ -65551,7 +65605,7 @@
         <v>6290</v>
       </c>
     </row>
-    <row r="547" spans="1:13">
+    <row r="547" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A547" s="7">
         <v>44566</v>
       </c>
@@ -65592,7 +65646,7 @@
         <v>6280</v>
       </c>
     </row>
-    <row r="548" spans="1:13">
+    <row r="548" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A548" s="7">
         <v>44573</v>
       </c>
@@ -65633,7 +65687,7 @@
         <v>6233</v>
       </c>
     </row>
-    <row r="549" spans="1:13">
+    <row r="549" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A549" s="7">
         <v>44580</v>
       </c>
@@ -65674,7 +65728,7 @@
         <v>6292</v>
       </c>
     </row>
-    <row r="550" spans="1:13">
+    <row r="550" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A550" s="7">
         <v>44587</v>
       </c>
@@ -65715,7 +65769,7 @@
         <v>6315</v>
       </c>
     </row>
-    <row r="551" spans="1:13">
+    <row r="551" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A551" s="7">
         <v>44594</v>
       </c>
@@ -65756,7 +65810,7 @@
         <v>6455</v>
       </c>
     </row>
-    <row r="552" spans="1:13">
+    <row r="552" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A552" s="7">
         <v>44601</v>
       </c>
@@ -65797,7 +65851,7 @@
         <v>6453</v>
       </c>
     </row>
-    <row r="553" spans="1:13">
+    <row r="553" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A553" s="7">
         <v>44608</v>
       </c>
@@ -65838,7 +65892,7 @@
         <v>6514</v>
       </c>
     </row>
-    <row r="554" spans="1:13">
+    <row r="554" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A554" s="7">
         <v>44615</v>
       </c>
@@ -65879,7 +65933,7 @@
         <v>6518</v>
       </c>
     </row>
-    <row r="555" spans="1:13">
+    <row r="555" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A555" s="7">
         <v>44622</v>
       </c>
@@ -65920,7 +65974,7 @@
         <v>6476</v>
       </c>
     </row>
-    <row r="556" spans="1:13">
+    <row r="556" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A556" s="7">
         <v>44629</v>
       </c>
@@ -65961,7 +66015,7 @@
         <v>6494</v>
       </c>
     </row>
-    <row r="557" spans="1:13">
+    <row r="557" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A557" s="7">
         <v>44636</v>
       </c>
@@ -66002,7 +66056,7 @@
         <v>6491</v>
       </c>
     </row>
-    <row r="558" spans="1:13">
+    <row r="558" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A558" s="7">
         <v>44643</v>
       </c>
@@ -66043,7 +66097,7 @@
         <v>6793</v>
       </c>
     </row>
-    <row r="559" spans="1:13">
+    <row r="559" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A559" s="7">
         <v>44650</v>
       </c>
@@ -66084,7 +66138,7 @@
         <v>6680</v>
       </c>
     </row>
-    <row r="560" spans="1:13">
+    <row r="560" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A560" s="7">
         <v>44657</v>
       </c>
@@ -66125,7 +66179,7 @@
         <v>6903</v>
       </c>
     </row>
-    <row r="561" spans="1:13">
+    <row r="561" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A561" s="7">
         <v>44664</v>
       </c>
@@ -66166,7 +66220,7 @@
         <v>6929</v>
       </c>
     </row>
-    <row r="562" spans="1:13">
+    <row r="562" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A562" s="7">
         <v>44671</v>
       </c>
@@ -66207,7 +66261,7 @@
         <v>6934</v>
       </c>
     </row>
-    <row r="563" spans="1:13">
+    <row r="563" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A563" s="7">
         <v>44678</v>
       </c>
@@ -66248,7 +66302,7 @@
         <v>6940</v>
       </c>
     </row>
-    <row r="564" spans="1:13">
+    <row r="564" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A564" s="7">
         <v>44685</v>
       </c>
@@ -66289,7 +66343,7 @@
         <v>7212</v>
       </c>
     </row>
-    <row r="565" spans="1:13">
+    <row r="565" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A565" s="7">
         <v>44692</v>
       </c>
@@ -66330,7 +66384,7 @@
         <v>7201</v>
       </c>
     </row>
-    <row r="566" spans="1:13">
+    <row r="566" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A566" s="7">
         <v>44699</v>
       </c>
@@ -66371,7 +66425,7 @@
         <v>7189</v>
       </c>
     </row>
-    <row r="567" spans="1:13">
+    <row r="567" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A567" s="7">
         <v>44706</v>
       </c>
@@ -66412,7 +66466,7 @@
         <v>7186</v>
       </c>
     </row>
-    <row r="568" spans="1:13">
+    <row r="568" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A568" s="7">
         <v>44713</v>
       </c>
@@ -66453,7 +66507,7 @@
         <v>7186</v>
       </c>
     </row>
-    <row r="569" spans="1:13">
+    <row r="569" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A569" s="7">
         <v>44720</v>
       </c>
@@ -66494,7 +66548,7 @@
         <v>7100</v>
       </c>
     </row>
-    <row r="570" spans="1:13">
+    <row r="570" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A570" s="7">
         <v>44727</v>
       </c>
@@ -66535,7 +66589,7 @@
         <v>6938</v>
       </c>
     </row>
-    <row r="571" spans="1:13">
+    <row r="571" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A571" s="7">
         <v>44734</v>
       </c>
@@ -66576,7 +66630,7 @@
         <v>6849</v>
       </c>
     </row>
-    <row r="572" spans="1:13">
+    <row r="572" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A572" s="7">
         <v>44741</v>
       </c>
@@ -66617,7 +66671,7 @@
         <v>6783</v>
       </c>
     </row>
-    <row r="573" spans="1:13">
+    <row r="573" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A573" s="7">
         <v>44748</v>
       </c>
@@ -66658,7 +66712,7 @@
         <v>6801</v>
       </c>
     </row>
-    <row r="574" spans="1:13">
+    <row r="574" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A574" s="7">
         <v>44755</v>
       </c>
@@ -66699,7 +66753,7 @@
         <v>6929</v>
       </c>
     </row>
-    <row r="575" spans="1:13">
+    <row r="575" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A575" s="7">
         <v>44762</v>
       </c>
@@ -66740,7 +66794,7 @@
         <v>6926</v>
       </c>
     </row>
-    <row r="576" spans="1:13">
+    <row r="576" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A576" s="7">
         <v>44769</v>
       </c>
@@ -66781,7 +66835,7 @@
         <v>6921</v>
       </c>
     </row>
-    <row r="577" spans="1:13">
+    <row r="577" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A577" s="7">
         <v>44776</v>
       </c>
@@ -66822,7 +66876,7 @@
         <v>6939</v>
       </c>
     </row>
-    <row r="578" spans="1:13">
+    <row r="578" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A578" s="7">
         <v>44783</v>
       </c>
@@ -66863,7 +66917,7 @@
         <v>6945</v>
       </c>
     </row>
-    <row r="579" spans="1:13">
+    <row r="579" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A579" s="7">
         <v>44790</v>
       </c>
@@ -66904,7 +66958,7 @@
         <v>6936</v>
       </c>
     </row>
-    <row r="580" spans="1:13">
+    <row r="580" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A580" s="7">
         <v>44797</v>
       </c>
@@ -66945,7 +66999,7 @@
         <v>6922</v>
       </c>
     </row>
-    <row r="581" spans="1:13">
+    <row r="581" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A581" s="7">
         <v>44804</v>
       </c>
@@ -66986,7 +67040,7 @@
         <v>6839</v>
       </c>
     </row>
-    <row r="582" spans="1:13">
+    <row r="582" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A582" s="7">
         <v>44811</v>
       </c>
@@ -67027,7 +67081,7 @@
         <v>6688</v>
       </c>
     </row>
-    <row r="583" spans="1:13">
+    <row r="583" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A583" s="7">
         <v>44818</v>
       </c>
@@ -67068,7 +67122,7 @@
         <v>6607</v>
       </c>
     </row>
-    <row r="584" spans="1:13">
+    <row r="584" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A584" s="7">
         <v>44825</v>
       </c>
@@ -67109,7 +67163,7 @@
         <v>6737</v>
       </c>
     </row>
-    <row r="585" spans="1:13">
+    <row r="585" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A585" s="7">
         <v>44832</v>
       </c>
@@ -67150,7 +67204,7 @@
         <v>7038</v>
       </c>
     </row>
-    <row r="586" spans="1:13">
+    <row r="586" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A586" s="7">
         <v>44839</v>
       </c>
@@ -67191,7 +67245,7 @@
         <v>7252</v>
       </c>
     </row>
-    <row r="587" spans="1:13">
+    <row r="587" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A587" s="7">
         <v>44846</v>
       </c>
@@ -67232,7 +67286,7 @@
         <v>7295</v>
       </c>
     </row>
-    <row r="588" spans="1:13">
+    <row r="588" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A588" s="7">
         <v>44853</v>
       </c>
@@ -67273,7 +67327,7 @@
         <v>7264</v>
       </c>
     </row>
-    <row r="589" spans="1:13">
+    <row r="589" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A589" s="7">
         <v>44860</v>
       </c>
@@ -67314,7 +67368,7 @@
         <v>7284</v>
       </c>
     </row>
-    <row r="590" spans="1:13">
+    <row r="590" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A590" s="7">
         <v>44867</v>
       </c>
@@ -67355,7 +67409,7 @@
         <v>7426</v>
       </c>
     </row>
-    <row r="591" spans="1:13">
+    <row r="591" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A591" s="7">
         <v>44874</v>
       </c>
@@ -67396,7 +67450,7 @@
         <v>7336</v>
       </c>
     </row>
-    <row r="592" spans="1:13">
+    <row r="592" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A592" s="7">
         <v>44881</v>
       </c>
@@ -67437,7 +67491,7 @@
         <v>7363</v>
       </c>
     </row>
-    <row r="593" spans="1:13">
+    <row r="593" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A593" s="7">
         <v>44888</v>
       </c>
@@ -67478,7 +67532,7 @@
         <v>7224</v>
       </c>
     </row>
-    <row r="594" spans="1:13">
+    <row r="594" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A594" s="7">
         <v>44895</v>
       </c>
@@ -67519,7 +67573,7 @@
         <v>7240</v>
       </c>
     </row>
-    <row r="595" spans="1:13">
+    <row r="595" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A595" s="7">
         <v>44902</v>
       </c>
@@ -67560,7 +67614,7 @@
         <v>7151</v>
       </c>
     </row>
-    <row r="596" spans="1:13">
+    <row r="596" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A596" s="7">
         <v>44909</v>
       </c>
@@ -67601,7 +67655,7 @@
         <v>7050</v>
       </c>
     </row>
-    <row r="597" spans="1:13">
+    <row r="597" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A597" s="7">
         <v>44916</v>
       </c>
@@ -67642,7 +67696,7 @@
         <v>6989</v>
       </c>
     </row>
-    <row r="598" spans="1:13">
+    <row r="598" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A598" s="7">
         <v>44930</v>
       </c>
@@ -67683,7 +67737,7 @@
         <v>6589</v>
       </c>
     </row>
-    <row r="599" spans="1:13">
+    <row r="599" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A599" s="7">
         <v>44937</v>
       </c>
@@ -67724,7 +67778,7 @@
         <v>6363</v>
       </c>
     </row>
-    <row r="600" spans="1:13">
+    <row r="600" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A600" s="7">
         <v>44944</v>
       </c>
@@ -67765,7 +67819,7 @@
         <v>6296</v>
       </c>
     </row>
-    <row r="601" spans="1:13">
+    <row r="601" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A601" s="7">
         <v>44951</v>
       </c>
@@ -67806,7 +67860,7 @@
         <v>6322</v>
       </c>
     </row>
-    <row r="602" spans="1:13">
+    <row r="602" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A602" s="7">
         <v>44958</v>
       </c>
@@ -67847,7 +67901,7 @@
         <v>6262</v>
       </c>
     </row>
-    <row r="603" spans="1:13">
+    <row r="603" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A603" s="7">
         <v>44965</v>
       </c>
@@ -67888,7 +67942,7 @@
         <v>6010</v>
       </c>
     </row>
-    <row r="604" spans="1:13">
+    <row r="604" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A604" s="7">
         <v>44972</v>
       </c>
@@ -67929,7 +67983,7 @@
         <v>5675</v>
       </c>
     </row>
-    <row r="605" spans="1:13">
+    <row r="605" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A605" s="7">
         <v>44979</v>
       </c>
@@ -67970,7 +68024,7 @@
         <v>5640</v>
       </c>
     </row>
-    <row r="606" spans="1:13">
+    <row r="606" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A606" s="7">
         <v>44986</v>
       </c>
@@ -68011,7 +68065,7 @@
         <v>5573</v>
       </c>
     </row>
-    <row r="607" spans="1:13">
+    <row r="607" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A607" s="7">
         <v>44993</v>
       </c>
@@ -68052,7 +68106,7 @@
         <v>5377</v>
       </c>
     </row>
-    <row r="608" spans="1:13">
+    <row r="608" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A608" s="7">
         <v>45000</v>
       </c>
@@ -68093,7 +68147,7 @@
         <v>5326</v>
       </c>
     </row>
-    <row r="609" spans="1:13">
+    <row r="609" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A609" s="7">
         <v>45007</v>
       </c>
@@ -68134,7 +68188,7 @@
         <v>5061</v>
       </c>
     </row>
-    <row r="610" spans="1:13">
+    <row r="610" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A610" s="7">
         <v>45014</v>
       </c>
@@ -68175,7 +68229,7 @@
         <v>4978</v>
       </c>
     </row>
-    <row r="611" spans="1:13">
+    <row r="611" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A611" s="7">
         <v>45021</v>
       </c>
@@ -68216,7 +68270,7 @@
         <v>4936</v>
       </c>
     </row>
-    <row r="612" spans="1:13">
+    <row r="612" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A612" s="7">
         <v>45028</v>
       </c>
@@ -68257,7 +68311,7 @@
         <v>4919</v>
       </c>
     </row>
-    <row r="613" spans="1:13">
+    <row r="613" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A613" s="7">
         <v>45035</v>
       </c>
@@ -68298,7 +68352,7 @@
         <v>4881</v>
       </c>
     </row>
-    <row r="614" spans="1:13">
+    <row r="614" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A614" s="7">
         <v>45042</v>
       </c>
@@ -68339,7 +68393,7 @@
         <v>4806</v>
       </c>
     </row>
-    <row r="615" spans="1:13">
+    <row r="615" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A615" s="7">
         <v>45049</v>
       </c>
@@ -68380,7 +68434,7 @@
         <v>4783</v>
       </c>
     </row>
-    <row r="616" spans="1:13">
+    <row r="616" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A616" s="7">
         <v>45056</v>
       </c>
@@ -68421,7 +68475,7 @@
         <v>4530</v>
       </c>
     </row>
-    <row r="617" spans="1:13">
+    <row r="617" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A617" s="7">
         <v>45063</v>
       </c>
@@ -68462,7 +68516,7 @@
         <v>4434</v>
       </c>
     </row>
-    <row r="618" spans="1:13">
+    <row r="618" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A618" s="7">
         <v>45070</v>
       </c>
@@ -68503,7 +68557,7 @@
         <v>3969</v>
       </c>
     </row>
-    <row r="619" spans="1:13">
+    <row r="619" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A619" s="7">
         <v>45077</v>
       </c>
@@ -68544,7 +68598,7 @@
         <v>3714</v>
       </c>
     </row>
-    <row r="620" spans="1:13">
+    <row r="620" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A620" s="7">
         <v>45084</v>
       </c>
@@ -68585,7 +68639,7 @@
         <v>3375</v>
       </c>
     </row>
-    <row r="621" spans="1:13">
+    <row r="621" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A621" s="7">
         <v>45091</v>
       </c>
@@ -68626,7 +68680,7 @@
         <v>3195</v>
       </c>
     </row>
-    <row r="622" spans="1:13">
+    <row r="622" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A622" s="7">
         <v>45098</v>
       </c>
@@ -68667,7 +68721,7 @@
         <v>3226</v>
       </c>
     </row>
-    <row r="623" spans="1:13">
+    <row r="623" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A623" s="7">
         <v>45105</v>
       </c>
@@ -68708,7 +68762,7 @@
         <v>2670</v>
       </c>
     </row>
-    <row r="624" spans="1:13">
+    <row r="624" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A624" s="7">
         <v>45112</v>
       </c>
@@ -68749,7 +68803,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="625" spans="1:13">
+    <row r="625" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A625" s="7">
         <v>45119</v>
       </c>
@@ -68790,7 +68844,7 @@
         <v>1769</v>
       </c>
     </row>
-    <row r="626" spans="1:13">
+    <row r="626" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A626" s="7">
         <v>45126</v>
       </c>
@@ -68831,7 +68885,7 @@
         <v>1640</v>
       </c>
     </row>
-    <row r="627" spans="1:13">
+    <row r="627" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A627" s="7">
         <v>45133</v>
       </c>
@@ -68872,7 +68926,7 @@
         <v>1590</v>
       </c>
     </row>
-    <row r="628" spans="1:13">
+    <row r="628" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A628" s="7">
         <v>45140</v>
       </c>
@@ -68913,7 +68967,7 @@
         <v>1587</v>
       </c>
     </row>
-    <row r="629" spans="1:13">
+    <row r="629" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A629" s="7">
         <v>45147</v>
       </c>
@@ -68954,7 +69008,7 @@
         <v>1593</v>
       </c>
     </row>
-    <row r="630" spans="1:13">
+    <row r="630" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A630" s="7">
         <v>45154</v>
       </c>
@@ -68995,7 +69049,7 @@
         <v>1577</v>
       </c>
     </row>
-    <row r="631" spans="1:13">
+    <row r="631" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A631" s="7">
         <v>45161</v>
       </c>
@@ -69036,7 +69090,7 @@
         <v>1585</v>
       </c>
     </row>
-    <row r="632" spans="1:13">
+    <row r="632" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A632" s="7">
         <v>45168</v>
       </c>
@@ -69077,7 +69131,7 @@
         <v>1562</v>
       </c>
     </row>
-    <row r="633" spans="1:13">
+    <row r="633" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A633" s="7">
         <v>45175</v>
       </c>
@@ -69118,7 +69172,7 @@
         <v>1561</v>
       </c>
     </row>
-    <row r="634" spans="1:13">
+    <row r="634" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A634" s="7">
         <v>45182</v>
       </c>
@@ -69159,7 +69213,7 @@
         <v>1565</v>
       </c>
     </row>
-    <row r="635" spans="1:13">
+    <row r="635" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A635" s="7">
         <v>45189</v>
       </c>
@@ -69200,7 +69254,7 @@
         <v>1534</v>
       </c>
     </row>
-    <row r="636" spans="1:13">
+    <row r="636" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A636" s="7">
         <v>45196</v>
       </c>
@@ -69241,7 +69295,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="637" spans="1:13">
+    <row r="637" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A637" s="7">
         <v>45203</v>
       </c>
@@ -69282,7 +69336,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="638" spans="1:13">
+    <row r="638" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A638" s="7">
         <v>45210</v>
       </c>
@@ -69323,7 +69377,7 @@
         <v>1535</v>
       </c>
     </row>
-    <row r="639" spans="1:13">
+    <row r="639" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A639" s="7">
         <v>45217</v>
       </c>
@@ -69364,7 +69418,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="640" spans="1:13">
+    <row r="640" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A640" s="7">
         <v>45224</v>
       </c>
@@ -69405,7 +69459,7 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="641" spans="1:13">
+    <row r="641" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A641" s="7">
         <v>45231</v>
       </c>
@@ -69446,7 +69500,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="642" spans="1:13">
+    <row r="642" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A642" s="7">
         <v>45238</v>
       </c>
@@ -69487,7 +69541,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="643" spans="1:13">
+    <row r="643" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A643" s="7">
         <v>45245</v>
       </c>
@@ -69528,7 +69582,7 @@
         <v>1510</v>
       </c>
     </row>
-    <row r="644" spans="1:13">
+    <row r="644" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A644" s="7">
         <v>45252</v>
       </c>
@@ -69569,7 +69623,7 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="645" spans="1:13">
+    <row r="645" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A645" s="7">
         <v>45259</v>
       </c>
@@ -69610,7 +69664,7 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="646" spans="1:13">
+    <row r="646" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A646" s="7">
         <v>45266</v>
       </c>
@@ -69651,7 +69705,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="647" spans="1:13">
+    <row r="647" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A647" s="7">
         <v>45273</v>
       </c>
@@ -69692,7 +69746,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="648" spans="1:13">
+    <row r="648" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A648" s="7">
         <v>45280</v>
       </c>
@@ -69733,7 +69787,7 @@
         <v>1480</v>
       </c>
     </row>
-    <row r="649" spans="1:13">
+    <row r="649" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A649" s="7">
         <v>45294</v>
       </c>
@@ -69774,7 +69828,7 @@
         <v>1503</v>
       </c>
     </row>
-    <row r="650" spans="1:13">
+    <row r="650" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A650" s="7">
         <v>45301</v>
       </c>
@@ -69815,7 +69869,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="651" spans="1:13">
+    <row r="651" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A651" s="7">
         <v>45308</v>
       </c>
@@ -69856,7 +69910,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="652" spans="1:13">
+    <row r="652" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A652" s="7">
         <v>45315</v>
       </c>
@@ -69897,7 +69951,7 @@
         <v>1576</v>
       </c>
     </row>
-    <row r="653" spans="1:13">
+    <row r="653" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A653" s="7">
         <v>45322</v>
       </c>
@@ -69938,7 +69992,7 @@
         <v>1589</v>
       </c>
     </row>
-    <row r="654" spans="1:13">
+    <row r="654" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A654" s="7">
         <v>45329</v>
       </c>
@@ -69979,7 +70033,7 @@
         <v>1978</v>
       </c>
     </row>
-    <row r="655" spans="1:13">
+    <row r="655" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A655" s="7">
         <v>45336</v>
       </c>
@@ -70020,7 +70074,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="656" spans="1:13">
+    <row r="656" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A656" s="7">
         <v>45343</v>
       </c>
@@ -70061,7 +70115,7 @@
         <v>2204</v>
       </c>
     </row>
-    <row r="657" spans="1:13">
+    <row r="657" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A657" s="7">
         <v>45350</v>
       </c>
@@ -70102,7 +70156,7 @@
         <v>2220</v>
       </c>
     </row>
-    <row r="658" spans="1:13">
+    <row r="658" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A658" s="7">
         <v>45357</v>
       </c>
@@ -70143,7 +70197,7 @@
         <v>2192</v>
       </c>
     </row>
-    <row r="659" spans="1:13">
+    <row r="659" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A659" s="7">
         <v>45364</v>
       </c>
@@ -70184,7 +70238,7 @@
         <v>2242</v>
       </c>
     </row>
-    <row r="660" spans="1:13">
+    <row r="660" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A660" s="7">
         <v>45371</v>
       </c>
@@ -70225,7 +70279,7 @@
         <v>2281</v>
       </c>
     </row>
-    <row r="661" spans="1:13">
+    <row r="661" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A661" s="7">
         <v>45378</v>
       </c>
@@ -70266,7 +70320,7 @@
         <v>2261</v>
       </c>
     </row>
-    <row r="662" spans="1:13">
+    <row r="662" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A662" s="7">
         <v>45385</v>
       </c>
@@ -70307,7 +70361,7 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="663" spans="1:13">
+    <row r="663" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A663" s="7">
         <v>45392</v>
       </c>
@@ -70348,7 +70402,7 @@
         <v>2224</v>
       </c>
     </row>
-    <row r="664" spans="1:13">
+    <row r="664" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A664" s="7">
         <v>45399</v>
       </c>
@@ -70389,7 +70443,7 @@
         <v>2291</v>
       </c>
     </row>
-    <row r="665" spans="1:13">
+    <row r="665" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A665" s="7">
         <v>45406</v>
       </c>
@@ -70430,7 +70484,7 @@
         <v>2214</v>
       </c>
     </row>
-    <row r="666" spans="1:13">
+    <row r="666" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A666" s="7">
         <v>45413</v>
       </c>
@@ -70471,7 +70525,7 @@
         <v>2210</v>
       </c>
     </row>
-    <row r="667" spans="1:13">
+    <row r="667" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A667" s="7">
         <v>45420</v>
       </c>
@@ -70512,7 +70566,7 @@
         <v>2160</v>
       </c>
     </row>
-    <row r="668" spans="1:13">
+    <row r="668" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A668" s="7">
         <v>45427</v>
       </c>
@@ -70553,7 +70607,7 @@
         <v>2209</v>
       </c>
     </row>
-    <row r="669" spans="1:13">
+    <row r="669" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A669" s="7">
         <v>45434</v>
       </c>
@@ -70594,7 +70648,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="670" spans="1:13">
+    <row r="670" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A670" s="7">
         <v>45441</v>
       </c>
@@ -70635,7 +70689,7 @@
         <v>2222</v>
       </c>
     </row>
-    <row r="671" spans="1:13">
+    <row r="671" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A671" s="7">
         <v>45448</v>
       </c>
@@ -70676,7 +70730,7 @@
         <v>2136</v>
       </c>
     </row>
-    <row r="672" spans="1:13">
+    <row r="672" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A672" s="7">
         <v>45455</v>
       </c>
@@ -70717,7 +70771,7 @@
         <v>2118</v>
       </c>
     </row>
-    <row r="673" spans="1:13">
+    <row r="673" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A673" s="7">
         <v>45462</v>
       </c>
@@ -70758,7 +70812,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="674" spans="1:13">
+    <row r="674" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A674" s="7">
         <v>45469</v>
       </c>
@@ -70799,7 +70853,7 @@
         <v>2044</v>
       </c>
     </row>
-    <row r="675" spans="1:13">
+    <row r="675" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A675" s="7">
         <v>45476</v>
       </c>
@@ -70840,7 +70894,7 @@
         <v>1977</v>
       </c>
     </row>
-    <row r="676" spans="1:13">
+    <row r="676" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A676" s="7">
         <v>45483</v>
       </c>
@@ -70881,7 +70935,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="677" spans="1:13">
+    <row r="677" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A677" s="7">
         <v>45490</v>
       </c>
@@ -70922,7 +70976,7 @@
         <v>1943</v>
       </c>
     </row>
-    <row r="678" spans="1:13">
+    <row r="678" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A678" s="7">
         <v>45497</v>
       </c>
@@ -70963,7 +71017,7 @@
         <v>1954</v>
       </c>
     </row>
-    <row r="679" spans="1:13">
+    <row r="679" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A679" s="7">
         <v>45504</v>
       </c>
@@ -71004,7 +71058,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="680" spans="1:13">
+    <row r="680" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A680" s="7">
         <v>45511</v>
       </c>
@@ -71045,7 +71099,7 @@
         <v>1967</v>
       </c>
     </row>
-    <row r="681" spans="1:13">
+    <row r="681" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A681" s="7">
         <v>45518</v>
       </c>
@@ -71086,7 +71140,7 @@
         <v>1961</v>
       </c>
     </row>
-    <row r="682" spans="1:13">
+    <row r="682" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A682" s="7">
         <v>45525</v>
       </c>
@@ -71127,7 +71181,7 @@
         <v>1934</v>
       </c>
     </row>
-    <row r="683" spans="1:13">
+    <row r="683" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A683" s="7">
         <v>45532</v>
       </c>
@@ -71168,7 +71222,7 @@
         <v>1908</v>
       </c>
     </row>
-    <row r="684" spans="1:13">
+    <row r="684" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A684" s="7">
         <v>45539</v>
       </c>
@@ -71209,7 +71263,7 @@
         <v>2212</v>
       </c>
     </row>
-    <row r="685" spans="1:13">
+    <row r="685" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A685" s="7">
         <v>45546</v>
       </c>
@@ -71250,7 +71304,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="686" spans="1:13">
+    <row r="686" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A686" s="7">
         <v>45553</v>
       </c>
@@ -71291,7 +71345,7 @@
         <v>2056</v>
       </c>
     </row>
-    <row r="687" spans="1:13">
+    <row r="687" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A687" s="7">
         <v>45560</v>
       </c>
@@ -71332,7 +71386,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="688" spans="1:13">
+    <row r="688" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A688" s="7">
         <v>45567</v>
       </c>
@@ -71373,7 +71427,7 @@
         <v>2061</v>
       </c>
     </row>
-    <row r="689" spans="1:13">
+    <row r="689" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A689" s="7">
         <v>45574</v>
       </c>
@@ -71414,7 +71468,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="690" spans="1:13">
+    <row r="690" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A690" s="7">
         <v>45581</v>
       </c>
@@ -71455,7 +71509,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="691" spans="1:13">
+    <row r="691" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A691" s="7">
         <v>45588</v>
       </c>
@@ -71496,7 +71550,7 @@
         <v>2663</v>
       </c>
     </row>
-    <row r="692" spans="1:13">
+    <row r="692" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A692" s="7">
         <v>45595</v>
       </c>
@@ -71537,7 +71591,7 @@
         <v>2664</v>
       </c>
     </row>
-    <row r="693" spans="1:13">
+    <row r="693" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A693" s="7">
         <v>45602</v>
       </c>
@@ -71578,7 +71632,7 @@
         <v>2624</v>
       </c>
     </row>
-    <row r="694" spans="1:13">
+    <row r="694" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A694" s="7">
         <v>45609</v>
       </c>
@@ -71619,7 +71673,7 @@
         <v>2658</v>
       </c>
     </row>
-    <row r="695" spans="1:13">
+    <row r="695" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A695" s="7">
         <v>45616</v>
       </c>
@@ -71660,7 +71714,7 @@
         <v>2672</v>
       </c>
     </row>
-    <row r="696" spans="1:13">
+    <row r="696" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A696" s="7">
         <v>45623</v>
       </c>
@@ -71701,7 +71755,7 @@
         <v>2665</v>
       </c>
     </row>
-    <row r="697" spans="1:13">
+    <row r="697" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A697" s="7">
         <v>45630</v>
       </c>
@@ -71742,7 +71796,7 @@
         <v>2649</v>
       </c>
     </row>
-    <row r="698" spans="1:13">
+    <row r="698" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A698" s="7">
         <v>45637</v>
       </c>
@@ -71783,7 +71837,7 @@
         <v>2622</v>
       </c>
     </row>
-    <row r="699" spans="1:13">
+    <row r="699" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A699" s="7">
         <v>45644</v>
       </c>
@@ -71824,7 +71878,7 @@
         <v>2713</v>
       </c>
     </row>
-    <row r="700" spans="1:13">
+    <row r="700" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A700" s="7">
         <v>45658</v>
       </c>
@@ -71865,7 +71919,7 @@
         <v>2720</v>
       </c>
     </row>
-    <row r="701" spans="1:13">
+    <row r="701" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A701" s="7">
         <v>45665</v>
       </c>
@@ -71906,7 +71960,7 @@
         <v>2698</v>
       </c>
     </row>
-    <row r="702" spans="1:13">
+    <row r="702" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A702" s="7">
         <v>45672</v>
       </c>
@@ -71947,7 +72001,7 @@
         <v>2798</v>
       </c>
     </row>
-    <row r="703" spans="1:13">
+    <row r="703" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A703" s="7">
         <v>45679</v>
       </c>
@@ -71988,7 +72042,7 @@
         <v>2778</v>
       </c>
     </row>
-    <row r="704" spans="1:13">
+    <row r="704" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A704" s="7">
         <v>45686</v>
       </c>
@@ -72029,7 +72083,7 @@
         <v>2732</v>
       </c>
     </row>
-    <row r="705" spans="1:13">
+    <row r="705" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A705" s="7">
         <v>45693</v>
       </c>
@@ -72070,7 +72124,7 @@
         <v>2469</v>
       </c>
     </row>
-    <row r="706" spans="1:13">
+    <row r="706" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A706" s="7">
         <v>45700</v>
       </c>
@@ -72111,7 +72165,7 @@
         <v>2463</v>
       </c>
     </row>
-    <row r="707" spans="1:13">
+    <row r="707" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A707" s="7">
         <v>45707</v>
       </c>
@@ -72152,7 +72206,7 @@
         <v>2394</v>
       </c>
     </row>
-    <row r="708" spans="1:13">
+    <row r="708" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A708" s="7">
         <v>45714</v>
       </c>
@@ -72193,7 +72247,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="709" spans="1:13">
+    <row r="709" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A709" s="7">
         <v>45721</v>
       </c>
@@ -72234,7 +72288,7 @@
         <v>2359</v>
       </c>
     </row>
-    <row r="710" spans="1:13">
+    <row r="710" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A710" s="7">
         <v>45728</v>
       </c>
@@ -72275,7 +72329,7 @@
         <v>2373</v>
       </c>
     </row>
-    <row r="711" spans="1:13">
+    <row r="711" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A711" s="7">
         <v>45735</v>
       </c>
@@ -72316,7 +72370,7 @@
         <v>2316</v>
       </c>
     </row>
-    <row r="712" spans="1:13">
+    <row r="712" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A712" s="7">
         <v>45742</v>
       </c>
@@ -72357,7 +72411,7 @@
         <v>2162</v>
       </c>
     </row>
-    <row r="713" spans="1:13">
+    <row r="713" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A713" s="7">
         <v>45749</v>
       </c>
@@ -72398,7 +72452,7 @@
         <v>2124</v>
       </c>
     </row>
-    <row r="714" spans="1:13">
+    <row r="714" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A714" s="7">
         <v>45756</v>
       </c>
@@ -72439,7 +72493,7 @@
         <v>2153</v>
       </c>
     </row>
-    <row r="715" spans="1:13">
+    <row r="715" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A715" s="7">
         <v>45763</v>
       </c>
@@ -72480,7 +72534,7 @@
         <v>2129</v>
       </c>
     </row>
-    <row r="716" spans="1:13">
+    <row r="716" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A716" s="7">
         <v>45770</v>
       </c>
@@ -72521,7 +72575,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="717" spans="1:13">
+    <row r="717" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A717" s="7">
         <v>45777</v>
       </c>
@@ -72562,7 +72616,7 @@
         <v>2041</v>
       </c>
     </row>
-    <row r="718" spans="1:13">
+    <row r="718" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A718" s="7">
         <v>45784</v>
       </c>
@@ -72603,7 +72657,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="719" spans="1:13">
+    <row r="719" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A719" s="7">
         <v>45791</v>
       </c>
@@ -72644,7 +72698,7 @@
         <v>1961</v>
       </c>
     </row>
-    <row r="720" spans="1:13">
+    <row r="720" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A720" s="7">
         <v>45798</v>
       </c>
@@ -72685,7 +72739,7 @@
         <v>1952</v>
       </c>
     </row>
-    <row r="721" spans="1:13">
+    <row r="721" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A721" s="7">
         <v>45805</v>
       </c>
@@ -72726,7 +72780,7 @@
         <v>1939</v>
       </c>
     </row>
-    <row r="722" spans="1:13">
+    <row r="722" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A722" s="7">
         <v>45812</v>
       </c>
@@ -72767,7 +72821,7 @@
         <v>1977</v>
       </c>
     </row>
-    <row r="723" spans="1:13">
+    <row r="723" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A723" s="7">
         <v>45819</v>
       </c>
@@ -72808,7 +72862,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="724" spans="1:13">
+    <row r="724" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A724" s="7">
         <v>45826</v>
       </c>
@@ -72849,7 +72903,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="725" spans="1:13">
+    <row r="725" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A725" s="7">
         <v>45833</v>
       </c>
@@ -72890,7 +72944,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="726" spans="1:13">
+    <row r="726" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A726" s="7">
         <v>45840</v>
       </c>
@@ -72931,7 +72985,7 @@
         <v>2119</v>
       </c>
     </row>
-    <row r="727" spans="1:13">
+    <row r="727" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A727" s="7">
         <v>45847</v>
       </c>
@@ -72972,7 +73026,7 @@
         <v>1990</v>
       </c>
     </row>
-    <row r="728" spans="1:13">
+    <row r="728" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A728" s="7">
         <v>45854</v>
       </c>
@@ -73013,7 +73067,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="729" spans="1:13">
+    <row r="729" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A729" s="7">
         <v>45861</v>
       </c>
@@ -73054,7 +73108,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="730" spans="1:13">
+    <row r="730" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A730" s="7">
         <v>45868</v>
       </c>
@@ -73095,7 +73149,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="731" spans="1:13">
+    <row r="731" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A731" s="7">
         <v>45875</v>
       </c>
@@ -73136,7 +73190,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="732" spans="1:13">
+    <row r="732" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A732" s="7">
         <v>45882</v>
       </c>
@@ -73177,7 +73231,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="733" spans="1:13">
+    <row r="733" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A733" s="7">
         <v>45889</v>
       </c>
@@ -73218,7 +73272,7 @@
         <v>1951</v>
       </c>
     </row>
-    <row r="734" spans="1:13">
+    <row r="734" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A734" s="7">
         <v>45896</v>
       </c>
@@ -73259,7 +73313,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="735" spans="1:13">
+    <row r="735" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A735" s="7">
         <v>45903</v>
       </c>
@@ -73300,7 +73354,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="736" spans="1:13">
+    <row r="736" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A736" s="7">
         <v>45910</v>
       </c>
@@ -73341,7 +73395,7 @@
         <v>1938</v>
       </c>
     </row>
-    <row r="737" spans="1:13">
+    <row r="737" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A737" s="7">
         <v>45917</v>
       </c>
@@ -73382,7 +73436,7 @@
         <v>1926</v>
       </c>
     </row>
-    <row r="738" spans="1:13">
+    <row r="738" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A738" s="7">
         <v>45924</v>
       </c>
@@ -73423,7 +73477,7 @@
         <v>1819</v>
       </c>
     </row>
-    <row r="739" spans="1:13">
+    <row r="739" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A739" s="7">
         <v>45931</v>
       </c>
@@ -73464,7 +73518,7 @@
         <v>1796</v>
       </c>
     </row>
-    <row r="740" spans="1:13">
+    <row r="740" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A740" s="7">
         <v>45938</v>
       </c>
@@ -73505,7 +73559,7 @@
         <v>1759</v>
       </c>
     </row>
-    <row r="741" spans="1:13">
+    <row r="741" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A741" s="7">
         <v>45945</v>
       </c>
@@ -73546,7 +73600,7 @@
         <v>1797</v>
       </c>
     </row>
-    <row r="742" spans="1:13">
+    <row r="742" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A742" s="7">
         <v>45952</v>
       </c>
@@ -73587,7 +73641,7 @@
         <v>1720</v>
       </c>
     </row>
-    <row r="743" spans="1:13">
+    <row r="743" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A743" s="7">
         <v>45959</v>
       </c>
@@ -73628,7 +73682,7 @@
         <v>1678</v>
       </c>
     </row>
-    <row r="744" spans="1:13">
+    <row r="744" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A744" s="7">
         <v>45966</v>
       </c>
@@ -73669,7 +73723,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="745" spans="1:13">
+    <row r="745" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A745" s="7">
         <v>45973</v>
       </c>
@@ -73710,7 +73764,7 @@
         <v>1633</v>
       </c>
     </row>
-    <row r="746" spans="1:13">
+    <row r="746" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A746" s="7">
         <v>45980</v>
       </c>
@@ -73751,7 +73805,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="747" spans="1:13">
+    <row r="747" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A747" s="7">
         <v>45987</v>
       </c>
@@ -73792,7 +73846,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="748" spans="1:13">
+    <row r="748" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A748" s="7">
         <v>45994</v>
       </c>
@@ -73833,7 +73887,7 @@
         <v>1632</v>
       </c>
     </row>
-    <row r="749" spans="1:13">
+    <row r="749" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A749" s="7">
         <v>46001</v>
       </c>
@@ -73874,7 +73928,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="750" spans="1:13">
+    <row r="750" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A750" s="7">
         <v>46008</v>
       </c>
@@ -73915,7 +73969,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="751" spans="1:13">
+    <row r="751" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A751" s="7">
         <v>46015</v>
       </c>
@@ -73956,7 +74010,7 @@
         <v>1652</v>
       </c>
     </row>
-    <row r="752" spans="1:13">
+    <row r="752" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A752" s="7">
         <v>46022</v>
       </c>
@@ -73997,7 +74051,7 @@
         <v>1652</v>
       </c>
     </row>
-    <row r="753" spans="1:13">
+    <row r="753" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A753" s="7">
         <v>46029</v>
       </c>
@@ -74038,7 +74092,7 @@
         <v>1685</v>
       </c>
     </row>
-    <row r="754" spans="1:13">
+    <row r="754" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A754" s="7">
         <v>46036</v>
       </c>
@@ -74079,7 +74133,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="755" spans="1:13">
+    <row r="755" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A755" s="7">
         <v>46043</v>
       </c>
@@ -74120,7 +74174,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="756" spans="1:13">
+    <row r="756" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A756" s="7">
         <v>46050</v>
       </c>
@@ -74161,7 +74215,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="757" spans="1:13">
+    <row r="757" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A757" s="7">
         <v>46057</v>
       </c>
@@ -74202,7 +74256,7 @@
         <v>1598</v>
       </c>
     </row>
-    <row r="758" spans="1:13">
+    <row r="758" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A758" s="7">
         <v>46064</v>
       </c>
@@ -74243,7 +74297,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="759" spans="1:13">
+    <row r="759" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A759" s="7">
         <v>46071</v>
       </c>
@@ -74284,7 +74338,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="760" spans="1:13">
+    <row r="760" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A760" s="7">
         <v>46078</v>
       </c>
@@ -74325,7 +74379,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="761" spans="1:13">
+    <row r="761" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A761" s="7">
         <v>46085</v>
       </c>
@@ -74366,7 +74420,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="762" spans="1:13">
+    <row r="762" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A762" s="7">
         <v>46092</v>
       </c>
@@ -74407,7 +74461,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="763" spans="1:13">
+    <row r="763" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A763" s="7">
         <v>46099</v>
       </c>
@@ -74448,7 +74502,7 @@
         <v>1504</v>
       </c>
     </row>
-    <row r="764" spans="1:13">
+    <row r="764" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A764" s="7">
         <v>46106</v>
       </c>
@@ -74489,7 +74543,7 @@
         <v>1542</v>
       </c>
     </row>
-    <row r="765" spans="1:13">
+    <row r="765" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A765" s="7">
         <v>46113</v>
       </c>
@@ -74530,7 +74584,7 @@
         <v>1579</v>
       </c>
     </row>
-    <row r="766" spans="1:13">
+    <row r="766" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A766" s="7">
         <v>46120</v>
       </c>
@@ -74571,7 +74625,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="767" spans="1:13">
+    <row r="767" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A767" s="7">
         <v>46127</v>
       </c>
@@ -74610,6 +74664,47 @@
       </c>
       <c r="M767" s="9">
         <v>2030</v>
+      </c>
+    </row>
+    <row r="768" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A768" s="7">
+        <v>46134</v>
+      </c>
+      <c r="B768" s="7">
+        <v>46135</v>
+      </c>
+      <c r="C768" s="11">
+        <v>0.583333333333381</v>
+      </c>
+      <c r="D768" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E768" s="8">
+        <v>2231.71</v>
+      </c>
+      <c r="F768" s="9">
+        <v>2147</v>
+      </c>
+      <c r="G768" s="9">
+        <v>3071</v>
+      </c>
+      <c r="H768" s="9">
+        <v>2934</v>
+      </c>
+      <c r="I768" s="9">
+        <v>3562</v>
+      </c>
+      <c r="J768" s="9">
+        <v>607</v>
+      </c>
+      <c r="K768" s="9">
+        <v>784</v>
+      </c>
+      <c r="L768" s="9">
+        <v>1031</v>
+      </c>
+      <c r="M768" s="9">
+        <v>2326</v>
       </c>
     </row>
   </sheetData>
@@ -74622,7 +74717,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86BC2DE8-BCE4-43AE-95F3-3DF06CDF8905}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -74633,12 +74728,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C789BCF2-DC16-4FFC-AF71-3351D156D960}">
   <dimension ref="B2:N3"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
@@ -74657,7 +74752,7 @@
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
     </row>
-    <row r="3" spans="2:14">
+    <row r="3" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B3" s="3" t="s">
         <v>10</v>
       </c>

--- a/data/freight/world container index.xlsx
+++ b/data/freight/world container index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41A07486-4593-4A04-8E84-C58396AB6566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2F6437E-1C20-484F-9351-70CD2690DD4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4911,6 +4911,9 @@
                 <c:pt idx="767">
                   <c:v>2216.42</c:v>
                 </c:pt>
+                <c:pt idx="768">
+                  <c:v>2285.6</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -9574,6 +9577,9 @@
                 <c:pt idx="767">
                   <c:v>2127</c:v>
                 </c:pt>
+                <c:pt idx="768">
+                  <c:v>2170</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -14237,6 +14243,9 @@
                 <c:pt idx="767">
                   <c:v>3039</c:v>
                 </c:pt>
+                <c:pt idx="768">
+                  <c:v>3075</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -18900,6 +18909,9 @@
                 <c:pt idx="767">
                   <c:v>2930</c:v>
                 </c:pt>
+                <c:pt idx="768">
+                  <c:v>3062</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -23563,6 +23575,9 @@
                 <c:pt idx="767">
                   <c:v>3483</c:v>
                 </c:pt>
+                <c:pt idx="768">
+                  <c:v>3721</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -28225,6 +28240,9 @@
                 </c:pt>
                 <c:pt idx="767">
                   <c:v>616</c:v>
+                </c:pt>
+                <c:pt idx="768">
+                  <c:v>631</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -32891,6 +32909,9 @@
                 <c:pt idx="767">
                   <c:v>796</c:v>
                 </c:pt>
+                <c:pt idx="768">
+                  <c:v>792</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -37556,6 +37577,9 @@
                 <c:pt idx="767">
                   <c:v>1014</c:v>
                 </c:pt>
+                <c:pt idx="768">
+                  <c:v>1023</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -42220,6 +42244,9 @@
                 </c:pt>
                 <c:pt idx="767">
                   <c:v>2327</c:v>
+                </c:pt>
+                <c:pt idx="768">
+                  <c:v>2314</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -74851,6 +74878,33 @@
       <c r="D770" s="7" t="s">
         <v>15</v>
       </c>
+      <c r="E770" s="8">
+        <v>2285.6</v>
+      </c>
+      <c r="F770" s="9">
+        <v>2170</v>
+      </c>
+      <c r="G770" s="9">
+        <v>3075</v>
+      </c>
+      <c r="H770" s="9">
+        <v>3062</v>
+      </c>
+      <c r="I770" s="9">
+        <v>3721</v>
+      </c>
+      <c r="J770" s="9">
+        <v>631</v>
+      </c>
+      <c r="K770" s="9">
+        <v>792</v>
+      </c>
+      <c r="L770" s="9">
+        <v>1023</v>
+      </c>
+      <c r="M770" s="9">
+        <v>2314</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/data/freight/world container index.xlsx
+++ b/data/freight/world container index.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1DE0117-81E9-4D69-B662-9583E3E4A91A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65ED9D3E-C752-46E6-AF5B-CF3E8EE6CE20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2500" yWindow="1930" windowWidth="17280" windowHeight="10690" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WCI" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="19">
   <si>
     <t>WCI Composite</t>
   </si>
@@ -2604,6 +2604,9 @@
                 <c:pt idx="770">
                   <c:v>46163</c:v>
                 </c:pt>
+                <c:pt idx="771">
+                  <c:v>46170</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4925,6 +4928,9 @@
                 </c:pt>
                 <c:pt idx="770">
                   <c:v>2711.77</c:v>
+                </c:pt>
+                <c:pt idx="771">
+                  <c:v>2799.55</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7282,6 +7288,9 @@
                 <c:pt idx="770">
                   <c:v>46163</c:v>
                 </c:pt>
+                <c:pt idx="771">
+                  <c:v>46170</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9603,6 +9612,9 @@
                 </c:pt>
                 <c:pt idx="770">
                   <c:v>2773</c:v>
+                </c:pt>
+                <c:pt idx="771">
+                  <c:v>2861</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11960,6 +11972,9 @@
                 <c:pt idx="770">
                   <c:v>46163</c:v>
                 </c:pt>
+                <c:pt idx="771">
+                  <c:v>46170</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -14281,6 +14296,9 @@
                 </c:pt>
                 <c:pt idx="770">
                   <c:v>4082</c:v>
+                </c:pt>
+                <c:pt idx="771">
+                  <c:v>4253</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16638,6 +16656,9 @@
                 <c:pt idx="770">
                   <c:v>46163</c:v>
                 </c:pt>
+                <c:pt idx="771">
+                  <c:v>46170</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -18959,6 +18980,9 @@
                 </c:pt>
                 <c:pt idx="770">
                   <c:v>3385</c:v>
+                </c:pt>
+                <c:pt idx="771">
+                  <c:v>3473</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -21316,6 +21340,9 @@
                 <c:pt idx="770">
                   <c:v>46163</c:v>
                 </c:pt>
+                <c:pt idx="771">
+                  <c:v>46170</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -23637,6 +23664,9 @@
                 </c:pt>
                 <c:pt idx="770">
                   <c:v>4317</c:v>
+                </c:pt>
+                <c:pt idx="771">
+                  <c:v>4597</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -25994,6 +26024,9 @@
                 <c:pt idx="770">
                   <c:v>46163</c:v>
                 </c:pt>
+                <c:pt idx="771">
+                  <c:v>46170</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -28315,6 +28348,9 @@
                 </c:pt>
                 <c:pt idx="770">
                   <c:v>650</c:v>
+                </c:pt>
+                <c:pt idx="771">
+                  <c:v>651</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -30674,6 +30710,9 @@
                 <c:pt idx="770">
                   <c:v>46163</c:v>
                 </c:pt>
+                <c:pt idx="771">
+                  <c:v>46170</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -32995,6 +33034,9 @@
                 </c:pt>
                 <c:pt idx="770">
                   <c:v>809</c:v>
+                </c:pt>
+                <c:pt idx="771">
+                  <c:v>790</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -35354,6 +35396,9 @@
                 <c:pt idx="770">
                   <c:v>46163</c:v>
                 </c:pt>
+                <c:pt idx="771">
+                  <c:v>46170</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -37675,6 +37720,9 @@
                 </c:pt>
                 <c:pt idx="770">
                   <c:v>1002</c:v>
+                </c:pt>
+                <c:pt idx="771">
+                  <c:v>977</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -40034,6 +40082,9 @@
                 <c:pt idx="770">
                   <c:v>46163</c:v>
                 </c:pt>
+                <c:pt idx="771">
+                  <c:v>46170</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -42355,6 +42406,9 @@
                 </c:pt>
                 <c:pt idx="770">
                   <c:v>2453</c:v>
+                </c:pt>
+                <c:pt idx="771">
+                  <c:v>2435</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -43432,7 +43486,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M772"/>
+  <dimension ref="A1:M773"/>
   <sheetFormatPr defaultColWidth="7.54296875" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="12.54296875" style="7" bestFit="1" customWidth="1"/>
@@ -75094,6 +75148,47 @@
       </c>
       <c r="M772" s="9">
         <v>2453</v>
+      </c>
+    </row>
+    <row r="773" spans="1:13">
+      <c r="A773" s="7">
+        <v>46169</v>
+      </c>
+      <c r="B773" s="7">
+        <v>46170</v>
+      </c>
+      <c r="C773" s="11">
+        <v>0.58333333333313697</v>
+      </c>
+      <c r="D773" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E773" s="8">
+        <v>2799.55</v>
+      </c>
+      <c r="F773" s="9">
+        <v>2861</v>
+      </c>
+      <c r="G773" s="9">
+        <v>4253</v>
+      </c>
+      <c r="H773" s="9">
+        <v>3473</v>
+      </c>
+      <c r="I773" s="9">
+        <v>4597</v>
+      </c>
+      <c r="J773" s="9">
+        <v>651</v>
+      </c>
+      <c r="K773" s="9">
+        <v>790</v>
+      </c>
+      <c r="L773" s="9">
+        <v>977</v>
+      </c>
+      <c r="M773" s="9">
+        <v>2435</v>
       </c>
     </row>
   </sheetData>

--- a/data/freight/world container index.xlsx
+++ b/data/freight/world container index.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65ED9D3E-C752-46E6-AF5B-CF3E8EE6CE20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1080B8F9-D201-4B87-9FA7-1FE05AE85C7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2500" yWindow="1930" windowWidth="17280" windowHeight="10690" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WCI" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="19">
   <si>
     <t>WCI Composite</t>
   </si>
@@ -2607,6 +2607,9 @@
                 <c:pt idx="771">
                   <c:v>46170</c:v>
                 </c:pt>
+                <c:pt idx="772">
+                  <c:v>46177</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4931,6 +4934,9 @@
                 </c:pt>
                 <c:pt idx="771">
                   <c:v>2799.55</c:v>
+                </c:pt>
+                <c:pt idx="772">
+                  <c:v>3432.93</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7291,6 +7297,9 @@
                 <c:pt idx="771">
                   <c:v>46170</c:v>
                 </c:pt>
+                <c:pt idx="772">
+                  <c:v>46177</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9615,6 +9624,9 @@
                 </c:pt>
                 <c:pt idx="771">
                   <c:v>2861</c:v>
+                </c:pt>
+                <c:pt idx="772">
+                  <c:v>3579</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11975,6 +11987,9 @@
                 <c:pt idx="771">
                   <c:v>46170</c:v>
                 </c:pt>
+                <c:pt idx="772">
+                  <c:v>46177</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -14299,6 +14314,9 @@
                 </c:pt>
                 <c:pt idx="771">
                   <c:v>4253</c:v>
+                </c:pt>
+                <c:pt idx="772">
+                  <c:v>5089</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16659,6 +16677,9 @@
                 <c:pt idx="771">
                   <c:v>46170</c:v>
                 </c:pt>
+                <c:pt idx="772">
+                  <c:v>46177</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -18983,6 +19004,9 @@
                 </c:pt>
                 <c:pt idx="771">
                   <c:v>3473</c:v>
+                </c:pt>
+                <c:pt idx="772">
+                  <c:v>4565</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -21343,6 +21367,9 @@
                 <c:pt idx="771">
                   <c:v>46170</c:v>
                 </c:pt>
+                <c:pt idx="772">
+                  <c:v>46177</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -23667,6 +23694,9 @@
                 </c:pt>
                 <c:pt idx="771">
                   <c:v>4597</c:v>
+                </c:pt>
+                <c:pt idx="772">
+                  <c:v>5505</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -26027,6 +26057,9 @@
                 <c:pt idx="771">
                   <c:v>46170</c:v>
                 </c:pt>
+                <c:pt idx="772">
+                  <c:v>46177</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -28351,6 +28384,9 @@
                 </c:pt>
                 <c:pt idx="771">
                   <c:v>651</c:v>
+                </c:pt>
+                <c:pt idx="772">
+                  <c:v>617</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -30713,6 +30749,9 @@
                 <c:pt idx="771">
                   <c:v>46170</c:v>
                 </c:pt>
+                <c:pt idx="772">
+                  <c:v>46177</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -33037,6 +33076,9 @@
                 </c:pt>
                 <c:pt idx="771">
                   <c:v>790</c:v>
+                </c:pt>
+                <c:pt idx="772">
+                  <c:v>783</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -35399,6 +35441,9 @@
                 <c:pt idx="771">
                   <c:v>46170</c:v>
                 </c:pt>
+                <c:pt idx="772">
+                  <c:v>46177</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -37723,6 +37768,9 @@
                 </c:pt>
                 <c:pt idx="771">
                   <c:v>977</c:v>
+                </c:pt>
+                <c:pt idx="772">
+                  <c:v>966</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -40085,6 +40133,9 @@
                 <c:pt idx="771">
                   <c:v>46170</c:v>
                 </c:pt>
+                <c:pt idx="772">
+                  <c:v>46177</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -42409,6 +42460,9 @@
                 </c:pt>
                 <c:pt idx="771">
                   <c:v>2435</c:v>
+                </c:pt>
+                <c:pt idx="772">
+                  <c:v>2560</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -43486,7 +43540,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M773"/>
+  <dimension ref="A1:M774"/>
   <sheetFormatPr defaultColWidth="7.54296875" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="12.54296875" style="7" bestFit="1" customWidth="1"/>
@@ -75189,6 +75243,47 @@
       </c>
       <c r="M773" s="9">
         <v>2435</v>
+      </c>
+    </row>
+    <row r="774" spans="1:13">
+      <c r="A774" s="7">
+        <v>46176</v>
+      </c>
+      <c r="B774" s="7">
+        <v>46177</v>
+      </c>
+      <c r="C774" s="11">
+        <v>0.58333333333345305</v>
+      </c>
+      <c r="D774" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E774" s="8">
+        <v>3432.93</v>
+      </c>
+      <c r="F774" s="9">
+        <v>3579</v>
+      </c>
+      <c r="G774" s="9">
+        <v>5089</v>
+      </c>
+      <c r="H774" s="9">
+        <v>4565</v>
+      </c>
+      <c r="I774" s="9">
+        <v>5505</v>
+      </c>
+      <c r="J774" s="9">
+        <v>617</v>
+      </c>
+      <c r="K774" s="9">
+        <v>783</v>
+      </c>
+      <c r="L774" s="9">
+        <v>966</v>
+      </c>
+      <c r="M774" s="9">
+        <v>2560</v>
       </c>
     </row>
   </sheetData>

--- a/data/freight/world container index.xlsx
+++ b/data/freight/world container index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41D265F4-3F47-434F-9B2D-E9FAFD760A8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02C7E092-B50C-4138-ACFA-7D04CFAA87B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="19">
   <si>
     <t>WCI Composite</t>
   </si>
@@ -173,7 +173,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -187,10 +187,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -200,13 +200,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="쉼표 [0]" xfId="2" builtinId="6"/>
@@ -2600,6 +2599,9 @@
                 <c:pt idx="773">
                   <c:v>46184</c:v>
                 </c:pt>
+                <c:pt idx="774">
+                  <c:v>46191</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4930,6 +4932,9 @@
                 </c:pt>
                 <c:pt idx="773">
                   <c:v>3549.26</c:v>
+                </c:pt>
+                <c:pt idx="774">
+                  <c:v>3969</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7296,6 +7301,9 @@
                 <c:pt idx="773">
                   <c:v>46184</c:v>
                 </c:pt>
+                <c:pt idx="774">
+                  <c:v>46191</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9626,6 +9634,9 @@
                 </c:pt>
                 <c:pt idx="773">
                   <c:v>3768</c:v>
+                </c:pt>
+                <c:pt idx="774">
+                  <c:v>4342</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11992,6 +12003,9 @@
                 <c:pt idx="773">
                   <c:v>46184</c:v>
                 </c:pt>
+                <c:pt idx="774">
+                  <c:v>46191</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -14322,6 +14336,9 @@
                 </c:pt>
                 <c:pt idx="773">
                   <c:v>5139</c:v>
+                </c:pt>
+                <c:pt idx="774">
+                  <c:v>5756</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16688,6 +16705,9 @@
                 <c:pt idx="773">
                   <c:v>46184</c:v>
                 </c:pt>
+                <c:pt idx="774">
+                  <c:v>46191</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -19018,6 +19038,9 @@
                 </c:pt>
                 <c:pt idx="773">
                   <c:v>4683</c:v>
+                </c:pt>
+                <c:pt idx="774">
+                  <c:v>5142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -21384,6 +21407,9 @@
                 <c:pt idx="773">
                   <c:v>46184</c:v>
                 </c:pt>
+                <c:pt idx="774">
+                  <c:v>46191</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -23714,6 +23740,9 @@
                 </c:pt>
                 <c:pt idx="773">
                   <c:v>5870</c:v>
+                </c:pt>
+                <c:pt idx="774">
+                  <c:v>6769</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -26080,6 +26109,9 @@
                 <c:pt idx="773">
                   <c:v>46184</c:v>
                 </c:pt>
+                <c:pt idx="774">
+                  <c:v>46191</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -28410,6 +28442,9 @@
                 </c:pt>
                 <c:pt idx="773">
                   <c:v>624</c:v>
+                </c:pt>
+                <c:pt idx="774">
+                  <c:v>643</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -30778,6 +30813,9 @@
                 <c:pt idx="773">
                   <c:v>46184</c:v>
                 </c:pt>
+                <c:pt idx="774">
+                  <c:v>46191</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -33108,6 +33146,9 @@
                 </c:pt>
                 <c:pt idx="773">
                   <c:v>812</c:v>
+                </c:pt>
+                <c:pt idx="774">
+                  <c:v>822</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -35476,6 +35517,9 @@
                 <c:pt idx="773">
                   <c:v>46184</c:v>
                 </c:pt>
+                <c:pt idx="774">
+                  <c:v>46191</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -37806,6 +37850,9 @@
                 </c:pt>
                 <c:pt idx="773">
                   <c:v>956</c:v>
+                </c:pt>
+                <c:pt idx="774">
+                  <c:v>957</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -40174,6 +40221,9 @@
                 <c:pt idx="773">
                   <c:v>46184</c:v>
                 </c:pt>
+                <c:pt idx="774">
+                  <c:v>46191</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -42504,6 +42554,9 @@
                 </c:pt>
                 <c:pt idx="773">
                   <c:v>2508</c:v>
+                </c:pt>
+                <c:pt idx="774">
+                  <c:v>2507</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -43581,7 +43634,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M775"/>
+  <dimension ref="A1:M776"/>
   <sheetFormatPr defaultColWidth="7.5546875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="5" bestFit="1" customWidth="1"/>
@@ -43589,7 +43642,13 @@
     <col min="3" max="3" width="10.21875" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.77734375" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="13" width="10.44140625" style="8" customWidth="1"/>
+    <col min="6" max="6" width="21" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.21875" style="8" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20" style="8" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21" style="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.21875" style="8" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="21.5546875" style="8" bestFit="1" customWidth="1"/>
     <col min="14" max="16384" width="7.5546875" style="8"/>
   </cols>
   <sheetData>
@@ -75366,6 +75425,47 @@
       </c>
       <c r="M775" s="8">
         <v>2508</v>
+      </c>
+    </row>
+    <row r="776" spans="1:13">
+      <c r="A776" s="5">
+        <v>46190</v>
+      </c>
+      <c r="B776" s="5">
+        <v>46191</v>
+      </c>
+      <c r="C776" s="6">
+        <v>0.58333333333408499</v>
+      </c>
+      <c r="D776" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E776" s="7">
+        <v>3969</v>
+      </c>
+      <c r="F776" s="8">
+        <v>4342</v>
+      </c>
+      <c r="G776" s="8">
+        <v>5756</v>
+      </c>
+      <c r="H776" s="8">
+        <v>5142</v>
+      </c>
+      <c r="I776" s="8">
+        <v>6769</v>
+      </c>
+      <c r="J776" s="8">
+        <v>643</v>
+      </c>
+      <c r="K776" s="8">
+        <v>822</v>
+      </c>
+      <c r="L776" s="8">
+        <v>957</v>
+      </c>
+      <c r="M776" s="8">
+        <v>2507</v>
       </c>
     </row>
   </sheetData>
@@ -75391,9 +75491,7 @@
   <dimension ref="B2:N3"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="12"/>
-    <col min="2" max="2" width="10.44140625" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.88671875" style="12"/>
+    <col min="2" max="2" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:14">

--- a/data/freight/world container index.xlsx
+++ b/data/freight/world container index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10118"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data/freight/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02C7E092-B50C-4138-ACFA-7D04CFAA87B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB082035-55E6-DD49-AE07-0D08ED6A2E59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22160" yWindow="600" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WCI" sheetId="1" r:id="rId1"/>
@@ -112,7 +112,7 @@
     <numFmt numFmtId="165" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -208,9 +208,9 @@
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="쉼표 [0]" xfId="2" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
+    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -228,7 +228,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -43635,24 +43635,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M776"/>
-  <sheetFormatPr defaultColWidth="7.5546875" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="7.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.21875" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.21875" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1640625" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.77734375" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21" style="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.21875" style="8" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20" style="8" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21" style="8" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22.21875" style="8" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="21.5546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="7.5546875" style="8"/>
+    <col min="5" max="5" width="15.83203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="13" width="10.5" style="8" customWidth="1"/>
+    <col min="14" max="16384" width="7.5" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="4" customFormat="1">
+    <row r="1" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
@@ -43693,7 +43687,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="5">
         <v>40716</v>
       </c>
@@ -43734,7 +43728,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="5">
         <v>40723</v>
       </c>
@@ -43775,7 +43769,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="5">
         <v>40730</v>
       </c>
@@ -43816,7 +43810,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="5">
         <v>40737</v>
       </c>
@@ -43857,7 +43851,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="5">
         <v>40744</v>
       </c>
@@ -43898,7 +43892,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="5">
         <v>40751</v>
       </c>
@@ -43939,7 +43933,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="5">
         <v>40758</v>
       </c>
@@ -43980,7 +43974,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="5">
         <v>40765</v>
       </c>
@@ -44021,7 +44015,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="5">
         <v>40772</v>
       </c>
@@ -44062,7 +44056,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="5">
         <v>40779</v>
       </c>
@@ -44103,7 +44097,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="5">
         <v>40786</v>
       </c>
@@ -44144,7 +44138,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" s="5">
         <v>40793</v>
       </c>
@@ -44185,7 +44179,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" s="5">
         <v>40800</v>
       </c>
@@ -44226,7 +44220,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" s="5">
         <v>40807</v>
       </c>
@@ -44267,7 +44261,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="5">
         <v>40814</v>
       </c>
@@ -44308,7 +44302,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" s="5">
         <v>40821</v>
       </c>
@@ -44349,7 +44343,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" s="5">
         <v>40828</v>
       </c>
@@ -44390,7 +44384,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" s="5">
         <v>40835</v>
       </c>
@@ -44431,7 +44425,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20" s="5">
         <v>40842</v>
       </c>
@@ -44472,7 +44466,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21" s="5">
         <v>40849</v>
       </c>
@@ -44513,7 +44507,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22" s="5">
         <v>40856</v>
       </c>
@@ -44554,7 +44548,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="23" spans="1:13">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23" s="5">
         <v>40863</v>
       </c>
@@ -44595,7 +44589,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24" s="5">
         <v>40870</v>
       </c>
@@ -44636,7 +44630,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" s="5">
         <v>40877</v>
       </c>
@@ -44677,7 +44671,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="26" spans="1:13">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26" s="5">
         <v>40884</v>
       </c>
@@ -44718,7 +44712,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="27" spans="1:13">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27" s="5">
         <v>40891</v>
       </c>
@@ -44759,7 +44753,7 @@
         <v>2183</v>
       </c>
     </row>
-    <row r="28" spans="1:13">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28" s="5">
         <v>40898</v>
       </c>
@@ -44800,7 +44794,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="29" spans="1:13">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29" s="5">
         <v>40905</v>
       </c>
@@ -44841,7 +44835,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="30" spans="1:13">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30" s="5">
         <v>40912</v>
       </c>
@@ -44882,7 +44876,7 @@
         <v>2208</v>
       </c>
     </row>
-    <row r="31" spans="1:13">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31" s="5">
         <v>40919</v>
       </c>
@@ -44923,7 +44917,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="32" spans="1:13">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A32" s="5">
         <v>40926</v>
       </c>
@@ -44964,7 +44958,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="33" spans="1:13">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A33" s="5">
         <v>40933</v>
       </c>
@@ -45005,7 +44999,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="34" spans="1:13">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A34" s="5">
         <v>40940</v>
       </c>
@@ -45046,7 +45040,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="35" spans="1:13">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A35" s="5">
         <v>40947</v>
       </c>
@@ -45087,7 +45081,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="36" spans="1:13">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A36" s="5">
         <v>40954</v>
       </c>
@@ -45128,7 +45122,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="37" spans="1:13">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A37" s="5">
         <v>40961</v>
       </c>
@@ -45169,7 +45163,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="38" spans="1:13">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A38" s="5">
         <v>40968</v>
       </c>
@@ -45210,7 +45204,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="39" spans="1:13">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A39" s="5">
         <v>40975</v>
       </c>
@@ -45251,7 +45245,7 @@
         <v>2220</v>
       </c>
     </row>
-    <row r="40" spans="1:13">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A40" s="5">
         <v>40982</v>
       </c>
@@ -45292,7 +45286,7 @@
         <v>2420</v>
       </c>
     </row>
-    <row r="41" spans="1:13">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A41" s="5">
         <v>40989</v>
       </c>
@@ -45333,7 +45327,7 @@
         <v>2419</v>
       </c>
     </row>
-    <row r="42" spans="1:13">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A42" s="5">
         <v>40996</v>
       </c>
@@ -45374,7 +45368,7 @@
         <v>2454</v>
       </c>
     </row>
-    <row r="43" spans="1:13">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A43" s="5">
         <v>41003</v>
       </c>
@@ -45415,7 +45409,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="44" spans="1:13">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A44" s="5">
         <v>41010</v>
       </c>
@@ -45456,7 +45450,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="45" spans="1:13">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A45" s="5">
         <v>41017</v>
       </c>
@@ -45497,7 +45491,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="46" spans="1:13">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A46" s="5">
         <v>41024</v>
       </c>
@@ -45538,7 +45532,7 @@
         <v>2529</v>
       </c>
     </row>
-    <row r="47" spans="1:13">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A47" s="5">
         <v>41031</v>
       </c>
@@ -45579,7 +45573,7 @@
         <v>2534</v>
       </c>
     </row>
-    <row r="48" spans="1:13">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A48" s="5">
         <v>41038</v>
       </c>
@@ -45620,7 +45614,7 @@
         <v>2516</v>
       </c>
     </row>
-    <row r="49" spans="1:13">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A49" s="5">
         <v>41045</v>
       </c>
@@ -45661,7 +45655,7 @@
         <v>2668</v>
       </c>
     </row>
-    <row r="50" spans="1:13">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A50" s="5">
         <v>41052</v>
       </c>
@@ -45702,7 +45696,7 @@
         <v>2676</v>
       </c>
     </row>
-    <row r="51" spans="1:13">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A51" s="5">
         <v>41059</v>
       </c>
@@ -45743,7 +45737,7 @@
         <v>2605</v>
       </c>
     </row>
-    <row r="52" spans="1:13">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A52" s="5">
         <v>41066</v>
       </c>
@@ -45784,7 +45778,7 @@
         <v>2674</v>
       </c>
     </row>
-    <row r="53" spans="1:13">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A53" s="5">
         <v>41073</v>
       </c>
@@ -45825,7 +45819,7 @@
         <v>2696</v>
       </c>
     </row>
-    <row r="54" spans="1:13">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A54" s="5">
         <v>41080</v>
       </c>
@@ -45866,7 +45860,7 @@
         <v>2696</v>
       </c>
     </row>
-    <row r="55" spans="1:13">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A55" s="5">
         <v>41087</v>
       </c>
@@ -45907,7 +45901,7 @@
         <v>2696</v>
       </c>
     </row>
-    <row r="56" spans="1:13">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A56" s="5">
         <v>41094</v>
       </c>
@@ -45948,7 +45942,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="57" spans="1:13">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A57" s="5">
         <v>41101</v>
       </c>
@@ -45989,7 +45983,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="58" spans="1:13">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A58" s="5">
         <v>41108</v>
       </c>
@@ -46030,7 +46024,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="59" spans="1:13">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A59" s="5">
         <v>41115</v>
       </c>
@@ -46071,7 +46065,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="60" spans="1:13">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A60" s="5">
         <v>41122</v>
       </c>
@@ -46112,7 +46106,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="61" spans="1:13">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A61" s="5">
         <v>41129</v>
       </c>
@@ -46153,7 +46147,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="62" spans="1:13">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A62" s="5">
         <v>41136</v>
       </c>
@@ -46194,7 +46188,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="63" spans="1:13">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A63" s="5">
         <v>41143</v>
       </c>
@@ -46235,7 +46229,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="64" spans="1:13">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A64" s="5">
         <v>41150</v>
       </c>
@@ -46276,7 +46270,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="65" spans="1:13">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A65" s="5">
         <v>41157</v>
       </c>
@@ -46317,7 +46311,7 @@
         <v>2660</v>
       </c>
     </row>
-    <row r="66" spans="1:13">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A66" s="5">
         <v>41164</v>
       </c>
@@ -46358,7 +46352,7 @@
         <v>2659</v>
       </c>
     </row>
-    <row r="67" spans="1:13">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A67" s="5">
         <v>41171</v>
       </c>
@@ -46399,7 +46393,7 @@
         <v>2659</v>
       </c>
     </row>
-    <row r="68" spans="1:13">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A68" s="5">
         <v>41178</v>
       </c>
@@ -46440,7 +46434,7 @@
         <v>2527</v>
       </c>
     </row>
-    <row r="69" spans="1:13">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A69" s="5">
         <v>41185</v>
       </c>
@@ -46481,7 +46475,7 @@
         <v>2428</v>
       </c>
     </row>
-    <row r="70" spans="1:13">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A70" s="5">
         <v>41192</v>
       </c>
@@ -46522,7 +46516,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="71" spans="1:13">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A71" s="5">
         <v>41199</v>
       </c>
@@ -46563,7 +46557,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="72" spans="1:13">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A72" s="5">
         <v>41206</v>
       </c>
@@ -46604,7 +46598,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="73" spans="1:13">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A73" s="5">
         <v>41213</v>
       </c>
@@ -46645,7 +46639,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="74" spans="1:13">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A74" s="5">
         <v>41220</v>
       </c>
@@ -46686,7 +46680,7 @@
         <v>2624</v>
       </c>
     </row>
-    <row r="75" spans="1:13">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A75" s="5">
         <v>41227</v>
       </c>
@@ -46727,7 +46721,7 @@
         <v>2624</v>
       </c>
     </row>
-    <row r="76" spans="1:13">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A76" s="5">
         <v>41234</v>
       </c>
@@ -46768,7 +46762,7 @@
         <v>2418</v>
       </c>
     </row>
-    <row r="77" spans="1:13">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A77" s="5">
         <v>41241</v>
       </c>
@@ -46809,7 +46803,7 @@
         <v>2418</v>
       </c>
     </row>
-    <row r="78" spans="1:13">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A78" s="5">
         <v>41248</v>
       </c>
@@ -46850,7 +46844,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="79" spans="1:13">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A79" s="5">
         <v>41255</v>
       </c>
@@ -46891,7 +46885,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="80" spans="1:13">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A80" s="5">
         <v>41262</v>
       </c>
@@ -46932,7 +46926,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="81" spans="1:13">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A81" s="5">
         <v>41269</v>
       </c>
@@ -46973,7 +46967,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="82" spans="1:13">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A82" s="5">
         <v>41276</v>
       </c>
@@ -47014,7 +47008,7 @@
         <v>2443</v>
       </c>
     </row>
-    <row r="83" spans="1:13">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A83" s="5">
         <v>41283</v>
       </c>
@@ -47055,7 +47049,7 @@
         <v>2443</v>
       </c>
     </row>
-    <row r="84" spans="1:13">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A84" s="5">
         <v>41290</v>
       </c>
@@ -47096,7 +47090,7 @@
         <v>2430</v>
       </c>
     </row>
-    <row r="85" spans="1:13">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A85" s="5">
         <v>41297</v>
       </c>
@@ -47137,7 +47131,7 @@
         <v>2430</v>
       </c>
     </row>
-    <row r="86" spans="1:13">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A86" s="5">
         <v>41304</v>
       </c>
@@ -47178,7 +47172,7 @@
         <v>2496</v>
       </c>
     </row>
-    <row r="87" spans="1:13">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A87" s="5">
         <v>41311</v>
       </c>
@@ -47219,7 +47213,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="88" spans="1:13">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A88" s="5">
         <v>41318</v>
       </c>
@@ -47260,7 +47254,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="89" spans="1:13">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A89" s="5">
         <v>41325</v>
       </c>
@@ -47301,7 +47295,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="90" spans="1:13">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A90" s="5">
         <v>41332</v>
       </c>
@@ -47342,7 +47336,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="91" spans="1:13">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A91" s="5">
         <v>41339</v>
       </c>
@@ -47383,7 +47377,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="92" spans="1:13">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A92" s="5">
         <v>41346</v>
       </c>
@@ -47424,7 +47418,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="93" spans="1:13">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A93" s="5">
         <v>41353</v>
       </c>
@@ -47465,7 +47459,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="94" spans="1:13">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A94" s="5">
         <v>41360</v>
       </c>
@@ -47506,7 +47500,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="95" spans="1:13">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A95" s="5">
         <v>41367</v>
       </c>
@@ -47547,7 +47541,7 @@
         <v>2411</v>
       </c>
     </row>
-    <row r="96" spans="1:13">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A96" s="5">
         <v>41374</v>
       </c>
@@ -47588,7 +47582,7 @@
         <v>2411</v>
       </c>
     </row>
-    <row r="97" spans="1:13">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A97" s="5">
         <v>41381</v>
       </c>
@@ -47629,7 +47623,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="98" spans="1:13">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A98" s="5">
         <v>41388</v>
       </c>
@@ -47670,7 +47664,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="99" spans="1:13">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A99" s="5">
         <v>41395</v>
       </c>
@@ -47711,7 +47705,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="100" spans="1:13">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A100" s="5">
         <v>41402</v>
       </c>
@@ -47752,7 +47746,7 @@
         <v>2091</v>
       </c>
     </row>
-    <row r="101" spans="1:13">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A101" s="5">
         <v>41409</v>
       </c>
@@ -47793,7 +47787,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="102" spans="1:13">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A102" s="5">
         <v>41416</v>
       </c>
@@ -47834,7 +47828,7 @@
         <v>2034</v>
       </c>
     </row>
-    <row r="103" spans="1:13">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A103" s="5">
         <v>41423</v>
       </c>
@@ -47875,7 +47869,7 @@
         <v>2082</v>
       </c>
     </row>
-    <row r="104" spans="1:13">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A104" s="5">
         <v>41430</v>
       </c>
@@ -47916,7 +47910,7 @@
         <v>2053</v>
       </c>
     </row>
-    <row r="105" spans="1:13">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A105" s="5">
         <v>41437</v>
       </c>
@@ -47957,7 +47951,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="106" spans="1:13">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A106" s="5">
         <v>41444</v>
       </c>
@@ -47998,7 +47992,7 @@
         <v>2047</v>
       </c>
     </row>
-    <row r="107" spans="1:13">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A107" s="5">
         <v>41451</v>
       </c>
@@ -48039,7 +48033,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="108" spans="1:13">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A108" s="5">
         <v>41458</v>
       </c>
@@ -48080,7 +48074,7 @@
         <v>1965</v>
       </c>
     </row>
-    <row r="109" spans="1:13">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A109" s="5">
         <v>41465</v>
       </c>
@@ -48121,7 +48115,7 @@
         <v>1967</v>
       </c>
     </row>
-    <row r="110" spans="1:13">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A110" s="5">
         <v>41472</v>
       </c>
@@ -48162,7 +48156,7 @@
         <v>1970</v>
       </c>
     </row>
-    <row r="111" spans="1:13">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A111" s="5">
         <v>41479</v>
       </c>
@@ -48203,7 +48197,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="112" spans="1:13">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A112" s="5">
         <v>41486</v>
       </c>
@@ -48244,7 +48238,7 @@
         <v>1928</v>
       </c>
     </row>
-    <row r="113" spans="1:13">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A113" s="5">
         <v>41493</v>
       </c>
@@ -48285,7 +48279,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="114" spans="1:13">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A114" s="5">
         <v>41500</v>
       </c>
@@ -48326,7 +48320,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="115" spans="1:13">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A115" s="5">
         <v>41507</v>
       </c>
@@ -48367,7 +48361,7 @@
         <v>1897</v>
       </c>
     </row>
-    <row r="116" spans="1:13">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A116" s="5">
         <v>41514</v>
       </c>
@@ -48408,7 +48402,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="117" spans="1:13">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A117" s="5">
         <v>41521</v>
       </c>
@@ -48449,7 +48443,7 @@
         <v>1909</v>
       </c>
     </row>
-    <row r="118" spans="1:13">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A118" s="5">
         <v>41528</v>
       </c>
@@ -48490,7 +48484,7 @@
         <v>1963</v>
       </c>
     </row>
-    <row r="119" spans="1:13">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A119" s="5">
         <v>41535</v>
       </c>
@@ -48531,7 +48525,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="120" spans="1:13">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A120" s="5">
         <v>41542</v>
       </c>
@@ -48572,7 +48566,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="121" spans="1:13">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A121" s="5">
         <v>41549</v>
       </c>
@@ -48613,7 +48607,7 @@
         <v>2047</v>
       </c>
     </row>
-    <row r="122" spans="1:13">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A122" s="5">
         <v>41556</v>
       </c>
@@ -48654,7 +48648,7 @@
         <v>1966</v>
       </c>
     </row>
-    <row r="123" spans="1:13">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A123" s="5">
         <v>41563</v>
       </c>
@@ -48695,7 +48689,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="124" spans="1:13">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A124" s="5">
         <v>41570</v>
       </c>
@@ -48736,7 +48730,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="125" spans="1:13">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A125" s="5">
         <v>41577</v>
       </c>
@@ -48777,7 +48771,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="126" spans="1:13">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A126" s="5">
         <v>41584</v>
       </c>
@@ -48818,7 +48812,7 @@
         <v>1946</v>
       </c>
     </row>
-    <row r="127" spans="1:13">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A127" s="5">
         <v>41591</v>
       </c>
@@ -48859,7 +48853,7 @@
         <v>1948</v>
       </c>
     </row>
-    <row r="128" spans="1:13">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A128" s="5">
         <v>41598</v>
       </c>
@@ -48900,7 +48894,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="129" spans="1:13">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A129" s="5">
         <v>41605</v>
       </c>
@@ -48941,7 +48935,7 @@
         <v>1994</v>
       </c>
     </row>
-    <row r="130" spans="1:13">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A130" s="5">
         <v>41612</v>
       </c>
@@ -48982,7 +48976,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="131" spans="1:13">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A131" s="5">
         <v>41619</v>
       </c>
@@ -49023,7 +49017,7 @@
         <v>1971</v>
       </c>
     </row>
-    <row r="132" spans="1:13">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A132" s="5">
         <v>41626</v>
       </c>
@@ -49064,7 +49058,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="133" spans="1:13">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A133" s="5">
         <v>41640</v>
       </c>
@@ -49105,7 +49099,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="134" spans="1:13">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A134" s="5">
         <v>41647</v>
       </c>
@@ -49146,7 +49140,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="135" spans="1:13">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A135" s="5">
         <v>41654</v>
       </c>
@@ -49187,7 +49181,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="136" spans="1:13">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A136" s="5">
         <v>41661</v>
       </c>
@@ -49228,7 +49222,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="137" spans="1:13">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A137" s="5">
         <v>41668</v>
       </c>
@@ -49269,7 +49263,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="138" spans="1:13">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A138" s="5">
         <v>41675</v>
       </c>
@@ -49310,7 +49304,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="139" spans="1:13">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A139" s="5">
         <v>41682</v>
       </c>
@@ -49351,7 +49345,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="140" spans="1:13">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A140" s="5">
         <v>41689</v>
       </c>
@@ -49392,7 +49386,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="141" spans="1:13">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A141" s="5">
         <v>41696</v>
       </c>
@@ -49433,7 +49427,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="142" spans="1:13">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A142" s="5">
         <v>41703</v>
       </c>
@@ -49474,7 +49468,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="143" spans="1:13">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A143" s="5">
         <v>41710</v>
       </c>
@@ -49515,7 +49509,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="144" spans="1:13">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A144" s="5">
         <v>41717</v>
       </c>
@@ -49556,7 +49550,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="145" spans="1:13">
+    <row r="145" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A145" s="5">
         <v>41724</v>
       </c>
@@ -49597,7 +49591,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="146" spans="1:13">
+    <row r="146" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A146" s="5">
         <v>41731</v>
       </c>
@@ -49638,7 +49632,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="147" spans="1:13">
+    <row r="147" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A147" s="5">
         <v>41738</v>
       </c>
@@ -49679,7 +49673,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="148" spans="1:13">
+    <row r="148" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A148" s="5">
         <v>41745</v>
       </c>
@@ -49720,7 +49714,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="149" spans="1:13">
+    <row r="149" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A149" s="5">
         <v>41752</v>
       </c>
@@ -49761,7 +49755,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="150" spans="1:13">
+    <row r="150" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A150" s="5">
         <v>41759</v>
       </c>
@@ -49802,7 +49796,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="151" spans="1:13">
+    <row r="151" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A151" s="5">
         <v>41766</v>
       </c>
@@ -49843,7 +49837,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="152" spans="1:13">
+    <row r="152" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A152" s="5">
         <v>41773</v>
       </c>
@@ -49884,7 +49878,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="153" spans="1:13">
+    <row r="153" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A153" s="5">
         <v>41780</v>
       </c>
@@ -49925,7 +49919,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="154" spans="1:13">
+    <row r="154" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A154" s="5">
         <v>41787</v>
       </c>
@@ -49966,7 +49960,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="155" spans="1:13">
+    <row r="155" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A155" s="5">
         <v>41794</v>
       </c>
@@ -50007,7 +50001,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="156" spans="1:13">
+    <row r="156" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A156" s="5">
         <v>41801</v>
       </c>
@@ -50048,7 +50042,7 @@
         <v>2142</v>
       </c>
     </row>
-    <row r="157" spans="1:13">
+    <row r="157" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A157" s="5">
         <v>41808</v>
       </c>
@@ -50089,7 +50083,7 @@
         <v>2142</v>
       </c>
     </row>
-    <row r="158" spans="1:13">
+    <row r="158" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A158" s="5">
         <v>41815</v>
       </c>
@@ -50130,7 +50124,7 @@
         <v>2138</v>
       </c>
     </row>
-    <row r="159" spans="1:13">
+    <row r="159" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A159" s="5">
         <v>41822</v>
       </c>
@@ -50171,7 +50165,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="160" spans="1:13">
+    <row r="160" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A160" s="5">
         <v>41829</v>
       </c>
@@ -50212,7 +50206,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="161" spans="1:13">
+    <row r="161" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A161" s="5">
         <v>41836</v>
       </c>
@@ -50253,7 +50247,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="162" spans="1:13">
+    <row r="162" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A162" s="5">
         <v>41843</v>
       </c>
@@ -50294,7 +50288,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="163" spans="1:13">
+    <row r="163" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A163" s="5">
         <v>41850</v>
       </c>
@@ -50335,7 +50329,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="164" spans="1:13">
+    <row r="164" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A164" s="5">
         <v>41857</v>
       </c>
@@ -50376,7 +50370,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="165" spans="1:13">
+    <row r="165" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A165" s="5">
         <v>41864</v>
       </c>
@@ -50417,7 +50411,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="166" spans="1:13">
+    <row r="166" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A166" s="5">
         <v>41871</v>
       </c>
@@ -50458,7 +50452,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="167" spans="1:13">
+    <row r="167" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A167" s="5">
         <v>41878</v>
       </c>
@@ -50499,7 +50493,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="168" spans="1:13">
+    <row r="168" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A168" s="5">
         <v>41885</v>
       </c>
@@ -50540,7 +50534,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="169" spans="1:13">
+    <row r="169" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A169" s="5">
         <v>41892</v>
       </c>
@@ -50581,7 +50575,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="170" spans="1:13">
+    <row r="170" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A170" s="5">
         <v>41899</v>
       </c>
@@ -50622,7 +50616,7 @@
         <v>2203</v>
       </c>
     </row>
-    <row r="171" spans="1:13">
+    <row r="171" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A171" s="5">
         <v>41906</v>
       </c>
@@ -50663,7 +50657,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="172" spans="1:13">
+    <row r="172" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A172" s="5">
         <v>41913</v>
       </c>
@@ -50704,7 +50698,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="173" spans="1:13">
+    <row r="173" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A173" s="5">
         <v>41920</v>
       </c>
@@ -50745,7 +50739,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="174" spans="1:13">
+    <row r="174" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A174" s="5">
         <v>41927</v>
       </c>
@@ -50786,7 +50780,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="175" spans="1:13">
+    <row r="175" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A175" s="5">
         <v>41934</v>
       </c>
@@ -50827,7 +50821,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="176" spans="1:13">
+    <row r="176" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A176" s="5">
         <v>41941</v>
       </c>
@@ -50868,7 +50862,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="177" spans="1:13">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A177" s="5">
         <v>41948</v>
       </c>
@@ -50909,7 +50903,7 @@
         <v>2232</v>
       </c>
     </row>
-    <row r="178" spans="1:13">
+    <row r="178" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A178" s="5">
         <v>41955</v>
       </c>
@@ -50950,7 +50944,7 @@
         <v>2232</v>
       </c>
     </row>
-    <row r="179" spans="1:13">
+    <row r="179" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A179" s="5">
         <v>41962</v>
       </c>
@@ -50991,7 +50985,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="180" spans="1:13">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A180" s="5">
         <v>41969</v>
       </c>
@@ -51032,7 +51026,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="181" spans="1:13">
+    <row r="181" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A181" s="5">
         <v>41976</v>
       </c>
@@ -51073,7 +51067,7 @@
         <v>2229</v>
       </c>
     </row>
-    <row r="182" spans="1:13">
+    <row r="182" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A182" s="5">
         <v>41983</v>
       </c>
@@ -51114,7 +51108,7 @@
         <v>2219</v>
       </c>
     </row>
-    <row r="183" spans="1:13">
+    <row r="183" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A183" s="5">
         <v>41990</v>
       </c>
@@ -51155,7 +51149,7 @@
         <v>2219</v>
       </c>
     </row>
-    <row r="184" spans="1:13">
+    <row r="184" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A184" s="5">
         <v>42011</v>
       </c>
@@ -51196,7 +51190,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="185" spans="1:13">
+    <row r="185" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A185" s="5">
         <v>42018</v>
       </c>
@@ -51237,7 +51231,7 @@
         <v>2274</v>
       </c>
     </row>
-    <row r="186" spans="1:13">
+    <row r="186" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A186" s="5">
         <v>42025</v>
       </c>
@@ -51278,7 +51272,7 @@
         <v>2268</v>
       </c>
     </row>
-    <row r="187" spans="1:13">
+    <row r="187" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A187" s="5">
         <v>42032</v>
       </c>
@@ -51319,7 +51313,7 @@
         <v>2260</v>
       </c>
     </row>
-    <row r="188" spans="1:13">
+    <row r="188" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A188" s="5">
         <v>42039</v>
       </c>
@@ -51360,7 +51354,7 @@
         <v>2276</v>
       </c>
     </row>
-    <row r="189" spans="1:13">
+    <row r="189" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A189" s="5">
         <v>42046</v>
       </c>
@@ -51401,7 +51395,7 @@
         <v>2333</v>
       </c>
     </row>
-    <row r="190" spans="1:13">
+    <row r="190" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A190" s="5">
         <v>42053</v>
       </c>
@@ -51442,7 +51436,7 @@
         <v>2287</v>
       </c>
     </row>
-    <row r="191" spans="1:13">
+    <row r="191" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A191" s="5">
         <v>42060</v>
       </c>
@@ -51483,7 +51477,7 @@
         <v>2287</v>
       </c>
     </row>
-    <row r="192" spans="1:13">
+    <row r="192" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A192" s="5">
         <v>42067</v>
       </c>
@@ -51524,7 +51518,7 @@
         <v>2309</v>
       </c>
     </row>
-    <row r="193" spans="1:13">
+    <row r="193" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A193" s="5">
         <v>42074</v>
       </c>
@@ -51565,7 +51559,7 @@
         <v>2277</v>
       </c>
     </row>
-    <row r="194" spans="1:13">
+    <row r="194" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A194" s="5">
         <v>42081</v>
       </c>
@@ -51606,7 +51600,7 @@
         <v>2277</v>
       </c>
     </row>
-    <row r="195" spans="1:13">
+    <row r="195" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A195" s="5">
         <v>42088</v>
       </c>
@@ -51647,7 +51641,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="196" spans="1:13">
+    <row r="196" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A196" s="5">
         <v>42095</v>
       </c>
@@ -51688,7 +51682,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="197" spans="1:13">
+    <row r="197" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A197" s="5">
         <v>42102</v>
       </c>
@@ -51729,7 +51723,7 @@
         <v>2290</v>
       </c>
     </row>
-    <row r="198" spans="1:13">
+    <row r="198" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A198" s="5">
         <v>42109</v>
       </c>
@@ -51770,7 +51764,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="199" spans="1:13">
+    <row r="199" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A199" s="5">
         <v>42116</v>
       </c>
@@ -51811,7 +51805,7 @@
         <v>2237</v>
       </c>
     </row>
-    <row r="200" spans="1:13">
+    <row r="200" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A200" s="5">
         <v>42123</v>
       </c>
@@ -51852,7 +51846,7 @@
         <v>2253</v>
       </c>
     </row>
-    <row r="201" spans="1:13">
+    <row r="201" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A201" s="5">
         <v>42130</v>
       </c>
@@ -51893,7 +51887,7 @@
         <v>2263</v>
       </c>
     </row>
-    <row r="202" spans="1:13">
+    <row r="202" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A202" s="5">
         <v>42137</v>
       </c>
@@ -51934,7 +51928,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="203" spans="1:13">
+    <row r="203" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A203" s="5">
         <v>42144</v>
       </c>
@@ -51975,7 +51969,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="204" spans="1:13">
+    <row r="204" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A204" s="5">
         <v>42151</v>
       </c>
@@ -52016,7 +52010,7 @@
         <v>2154</v>
       </c>
     </row>
-    <row r="205" spans="1:13">
+    <row r="205" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A205" s="5">
         <v>42158</v>
       </c>
@@ -52057,7 +52051,7 @@
         <v>2199</v>
       </c>
     </row>
-    <row r="206" spans="1:13">
+    <row r="206" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A206" s="5">
         <v>42165</v>
       </c>
@@ -52098,7 +52092,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="207" spans="1:13">
+    <row r="207" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A207" s="5">
         <v>42172</v>
       </c>
@@ -52139,7 +52133,7 @@
         <v>2207</v>
       </c>
     </row>
-    <row r="208" spans="1:13">
+    <row r="208" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A208" s="5">
         <v>42179</v>
       </c>
@@ -52180,7 +52174,7 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="209" spans="1:13">
+    <row r="209" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A209" s="5">
         <v>42186</v>
       </c>
@@ -52221,7 +52215,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="210" spans="1:13">
+    <row r="210" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A210" s="5">
         <v>42193</v>
       </c>
@@ -52262,7 +52256,7 @@
         <v>2210</v>
       </c>
     </row>
-    <row r="211" spans="1:13">
+    <row r="211" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A211" s="5">
         <v>42200</v>
       </c>
@@ -52303,7 +52297,7 @@
         <v>2195</v>
       </c>
     </row>
-    <row r="212" spans="1:13">
+    <row r="212" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A212" s="5">
         <v>42207</v>
       </c>
@@ -52344,7 +52338,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="213" spans="1:13">
+    <row r="213" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A213" s="5">
         <v>42214</v>
       </c>
@@ -52385,7 +52379,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="214" spans="1:13">
+    <row r="214" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A214" s="5">
         <v>42221</v>
       </c>
@@ -52426,7 +52420,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="215" spans="1:13">
+    <row r="215" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A215" s="5">
         <v>42228</v>
       </c>
@@ -52467,7 +52461,7 @@
         <v>2184</v>
       </c>
     </row>
-    <row r="216" spans="1:13">
+    <row r="216" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A216" s="5">
         <v>42235</v>
       </c>
@@ -52508,7 +52502,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="217" spans="1:13">
+    <row r="217" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A217" s="5">
         <v>42242</v>
       </c>
@@ -52549,7 +52543,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="218" spans="1:13">
+    <row r="218" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A218" s="5">
         <v>42249</v>
       </c>
@@ -52590,7 +52584,7 @@
         <v>2147</v>
       </c>
     </row>
-    <row r="219" spans="1:13">
+    <row r="219" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A219" s="5">
         <v>42256</v>
       </c>
@@ -52631,7 +52625,7 @@
         <v>2138</v>
       </c>
     </row>
-    <row r="220" spans="1:13">
+    <row r="220" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A220" s="5">
         <v>42263</v>
       </c>
@@ -52672,7 +52666,7 @@
         <v>2139</v>
       </c>
     </row>
-    <row r="221" spans="1:13">
+    <row r="221" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A221" s="5">
         <v>42270</v>
       </c>
@@ -52713,7 +52707,7 @@
         <v>2090</v>
       </c>
     </row>
-    <row r="222" spans="1:13">
+    <row r="222" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A222" s="5">
         <v>42277</v>
       </c>
@@ -52754,7 +52748,7 @@
         <v>2074</v>
       </c>
     </row>
-    <row r="223" spans="1:13">
+    <row r="223" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A223" s="5">
         <v>42284</v>
       </c>
@@ -52795,7 +52789,7 @@
         <v>2095</v>
       </c>
     </row>
-    <row r="224" spans="1:13">
+    <row r="224" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A224" s="5">
         <v>42291</v>
       </c>
@@ -52836,7 +52830,7 @@
         <v>2079</v>
       </c>
     </row>
-    <row r="225" spans="1:13">
+    <row r="225" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A225" s="5">
         <v>42298</v>
       </c>
@@ -52877,7 +52871,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="226" spans="1:13">
+    <row r="226" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A226" s="5">
         <v>42305</v>
       </c>
@@ -52918,7 +52912,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="227" spans="1:13">
+    <row r="227" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A227" s="5">
         <v>42312</v>
       </c>
@@ -52959,7 +52953,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="228" spans="1:13">
+    <row r="228" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A228" s="5">
         <v>42319</v>
       </c>
@@ -53000,7 +52994,7 @@
         <v>2066</v>
       </c>
     </row>
-    <row r="229" spans="1:13">
+    <row r="229" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A229" s="5">
         <v>42326</v>
       </c>
@@ -53041,7 +53035,7 @@
         <v>2066</v>
       </c>
     </row>
-    <row r="230" spans="1:13">
+    <row r="230" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A230" s="5">
         <v>42333</v>
       </c>
@@ -53082,7 +53076,7 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="231" spans="1:13">
+    <row r="231" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A231" s="5">
         <v>42340</v>
       </c>
@@ -53123,7 +53117,7 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="232" spans="1:13">
+    <row r="232" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A232" s="5">
         <v>42347</v>
       </c>
@@ -53164,7 +53158,7 @@
         <v>2079</v>
       </c>
     </row>
-    <row r="233" spans="1:13">
+    <row r="233" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A233" s="5">
         <v>42354</v>
       </c>
@@ -53205,7 +53199,7 @@
         <v>2074</v>
       </c>
     </row>
-    <row r="234" spans="1:13">
+    <row r="234" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A234" s="5">
         <v>42361</v>
       </c>
@@ -53246,7 +53240,7 @@
         <v>2077</v>
       </c>
     </row>
-    <row r="235" spans="1:13">
+    <row r="235" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A235" s="5">
         <v>42368</v>
       </c>
@@ -53287,7 +53281,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="236" spans="1:13">
+    <row r="236" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A236" s="5">
         <v>42375</v>
       </c>
@@ -53328,7 +53322,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="237" spans="1:13">
+    <row r="237" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A237" s="5">
         <v>42382</v>
       </c>
@@ -53369,7 +53363,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="238" spans="1:13">
+    <row r="238" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A238" s="5">
         <v>42389</v>
       </c>
@@ -53410,7 +53404,7 @@
         <v>2042</v>
       </c>
     </row>
-    <row r="239" spans="1:13">
+    <row r="239" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A239" s="5">
         <v>42396</v>
       </c>
@@ -53451,7 +53445,7 @@
         <v>2042</v>
       </c>
     </row>
-    <row r="240" spans="1:13">
+    <row r="240" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A240" s="5">
         <v>42403</v>
       </c>
@@ -53492,7 +53486,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="241" spans="1:13">
+    <row r="241" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A241" s="5">
         <v>42410</v>
       </c>
@@ -53533,7 +53527,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="242" spans="1:13">
+    <row r="242" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A242" s="5">
         <v>42417</v>
       </c>
@@ -53574,7 +53568,7 @@
         <v>2048</v>
       </c>
     </row>
-    <row r="243" spans="1:13">
+    <row r="243" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A243" s="5">
         <v>42424</v>
       </c>
@@ -53615,7 +53609,7 @@
         <v>1880</v>
       </c>
     </row>
-    <row r="244" spans="1:13">
+    <row r="244" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A244" s="5">
         <v>42431</v>
       </c>
@@ -53656,7 +53650,7 @@
         <v>1856</v>
       </c>
     </row>
-    <row r="245" spans="1:13">
+    <row r="245" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A245" s="5">
         <v>42438</v>
       </c>
@@ -53697,7 +53691,7 @@
         <v>1857</v>
       </c>
     </row>
-    <row r="246" spans="1:13">
+    <row r="246" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A246" s="5">
         <v>42445</v>
       </c>
@@ -53738,7 +53732,7 @@
         <v>1846</v>
       </c>
     </row>
-    <row r="247" spans="1:13">
+    <row r="247" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A247" s="5">
         <v>42452</v>
       </c>
@@ -53779,7 +53773,7 @@
         <v>1835</v>
       </c>
     </row>
-    <row r="248" spans="1:13">
+    <row r="248" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A248" s="5">
         <v>42459</v>
       </c>
@@ -53820,7 +53814,7 @@
         <v>1828</v>
       </c>
     </row>
-    <row r="249" spans="1:13">
+    <row r="249" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A249" s="5">
         <v>42466</v>
       </c>
@@ -53861,7 +53855,7 @@
         <v>1872</v>
       </c>
     </row>
-    <row r="250" spans="1:13">
+    <row r="250" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A250" s="5">
         <v>42473</v>
       </c>
@@ -53902,7 +53896,7 @@
         <v>1847</v>
       </c>
     </row>
-    <row r="251" spans="1:13">
+    <row r="251" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A251" s="5">
         <v>42480</v>
       </c>
@@ -53943,7 +53937,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="252" spans="1:13">
+    <row r="252" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A252" s="5">
         <v>42487</v>
       </c>
@@ -53984,7 +53978,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="253" spans="1:13">
+    <row r="253" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A253" s="5">
         <v>42494</v>
       </c>
@@ -54025,7 +54019,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="254" spans="1:13">
+    <row r="254" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A254" s="5">
         <v>42501</v>
       </c>
@@ -54066,7 +54060,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="255" spans="1:13">
+    <row r="255" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A255" s="5">
         <v>42508</v>
       </c>
@@ -54107,7 +54101,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="256" spans="1:13">
+    <row r="256" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A256" s="5">
         <v>42515</v>
       </c>
@@ -54148,7 +54142,7 @@
         <v>1843</v>
       </c>
     </row>
-    <row r="257" spans="1:13">
+    <row r="257" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A257" s="5">
         <v>42522</v>
       </c>
@@ -54189,7 +54183,7 @@
         <v>1844</v>
       </c>
     </row>
-    <row r="258" spans="1:13">
+    <row r="258" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A258" s="5">
         <v>42529</v>
       </c>
@@ -54230,7 +54224,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="259" spans="1:13">
+    <row r="259" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A259" s="5">
         <v>42536</v>
       </c>
@@ -54271,7 +54265,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="260" spans="1:13">
+    <row r="260" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A260" s="5">
         <v>42543</v>
       </c>
@@ -54312,7 +54306,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="261" spans="1:13">
+    <row r="261" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A261" s="5">
         <v>42550</v>
       </c>
@@ -54353,7 +54347,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="262" spans="1:13">
+    <row r="262" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A262" s="5">
         <v>42557</v>
       </c>
@@ -54394,7 +54388,7 @@
         <v>1848</v>
       </c>
     </row>
-    <row r="263" spans="1:13">
+    <row r="263" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A263" s="5">
         <v>42564</v>
       </c>
@@ -54435,7 +54429,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="264" spans="1:13">
+    <row r="264" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A264" s="5">
         <v>42571</v>
       </c>
@@ -54476,7 +54470,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="265" spans="1:13">
+    <row r="265" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A265" s="5">
         <v>42578</v>
       </c>
@@ -54517,7 +54511,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="266" spans="1:13">
+    <row r="266" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A266" s="5">
         <v>42585</v>
       </c>
@@ -54558,7 +54552,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="267" spans="1:13">
+    <row r="267" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A267" s="5">
         <v>42592</v>
       </c>
@@ -54599,7 +54593,7 @@
         <v>1816</v>
       </c>
     </row>
-    <row r="268" spans="1:13">
+    <row r="268" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A268" s="5">
         <v>42599</v>
       </c>
@@ -54640,7 +54634,7 @@
         <v>1814</v>
       </c>
     </row>
-    <row r="269" spans="1:13">
+    <row r="269" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A269" s="5">
         <v>42606</v>
       </c>
@@ -54681,7 +54675,7 @@
         <v>1814</v>
       </c>
     </row>
-    <row r="270" spans="1:13">
+    <row r="270" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A270" s="5">
         <v>42613</v>
       </c>
@@ -54722,7 +54716,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="271" spans="1:13">
+    <row r="271" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A271" s="5">
         <v>42620</v>
       </c>
@@ -54763,7 +54757,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="272" spans="1:13">
+    <row r="272" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A272" s="5">
         <v>42627</v>
       </c>
@@ -54804,7 +54798,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="273" spans="1:13">
+    <row r="273" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A273" s="5">
         <v>42634</v>
       </c>
@@ -54845,7 +54839,7 @@
         <v>1766</v>
       </c>
     </row>
-    <row r="274" spans="1:13">
+    <row r="274" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A274" s="5">
         <v>42641</v>
       </c>
@@ -54886,7 +54880,7 @@
         <v>1766</v>
       </c>
     </row>
-    <row r="275" spans="1:13">
+    <row r="275" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A275" s="5">
         <v>42648</v>
       </c>
@@ -54927,7 +54921,7 @@
         <v>1743</v>
       </c>
     </row>
-    <row r="276" spans="1:13">
+    <row r="276" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A276" s="5">
         <v>42655</v>
       </c>
@@ -54968,7 +54962,7 @@
         <v>1770</v>
       </c>
     </row>
-    <row r="277" spans="1:13">
+    <row r="277" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A277" s="5">
         <v>42662</v>
       </c>
@@ -55009,7 +55003,7 @@
         <v>1770</v>
       </c>
     </row>
-    <row r="278" spans="1:13">
+    <row r="278" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A278" s="5">
         <v>42669</v>
       </c>
@@ -55050,7 +55044,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="279" spans="1:13">
+    <row r="279" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A279" s="5">
         <v>42676</v>
       </c>
@@ -55091,7 +55085,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="280" spans="1:13">
+    <row r="280" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A280" s="5">
         <v>42683</v>
       </c>
@@ -55132,7 +55126,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="281" spans="1:13">
+    <row r="281" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A281" s="5">
         <v>42690</v>
       </c>
@@ -55173,7 +55167,7 @@
         <v>1740</v>
       </c>
     </row>
-    <row r="282" spans="1:13">
+    <row r="282" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A282" s="5">
         <v>42697</v>
       </c>
@@ -55214,7 +55208,7 @@
         <v>1745</v>
       </c>
     </row>
-    <row r="283" spans="1:13">
+    <row r="283" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A283" s="5">
         <v>42704</v>
       </c>
@@ -55255,7 +55249,7 @@
         <v>1735</v>
       </c>
     </row>
-    <row r="284" spans="1:13">
+    <row r="284" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A284" s="5">
         <v>42711</v>
       </c>
@@ -55296,7 +55290,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="285" spans="1:13">
+    <row r="285" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A285" s="5">
         <v>42718</v>
       </c>
@@ -55337,7 +55331,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="286" spans="1:13">
+    <row r="286" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A286" s="5">
         <v>42725</v>
       </c>
@@ -55378,7 +55372,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="287" spans="1:13">
+    <row r="287" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A287" s="5">
         <v>42732</v>
       </c>
@@ -55419,7 +55413,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="288" spans="1:13">
+    <row r="288" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A288" s="5">
         <v>42739</v>
       </c>
@@ -55460,7 +55454,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="289" spans="1:13">
+    <row r="289" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A289" s="5">
         <v>42746</v>
       </c>
@@ -55501,7 +55495,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="290" spans="1:13">
+    <row r="290" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A290" s="5">
         <v>42753</v>
       </c>
@@ -55542,7 +55536,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="291" spans="1:13">
+    <row r="291" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A291" s="5">
         <v>42760</v>
       </c>
@@ -55583,7 +55577,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="292" spans="1:13">
+    <row r="292" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A292" s="5">
         <v>42767</v>
       </c>
@@ -55624,7 +55618,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="293" spans="1:13">
+    <row r="293" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A293" s="5">
         <v>42774</v>
       </c>
@@ -55665,7 +55659,7 @@
         <v>1778</v>
       </c>
     </row>
-    <row r="294" spans="1:13">
+    <row r="294" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A294" s="5">
         <v>42781</v>
       </c>
@@ -55706,7 +55700,7 @@
         <v>1728</v>
       </c>
     </row>
-    <row r="295" spans="1:13">
+    <row r="295" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A295" s="5">
         <v>42788</v>
       </c>
@@ -55747,7 +55741,7 @@
         <v>1728</v>
       </c>
     </row>
-    <row r="296" spans="1:13">
+    <row r="296" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A296" s="5">
         <v>42795</v>
       </c>
@@ -55788,7 +55782,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="297" spans="1:13">
+    <row r="297" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A297" s="5">
         <v>42802</v>
       </c>
@@ -55829,7 +55823,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="298" spans="1:13">
+    <row r="298" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A298" s="5">
         <v>42809</v>
       </c>
@@ -55870,7 +55864,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="299" spans="1:13">
+    <row r="299" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A299" s="5">
         <v>42816</v>
       </c>
@@ -55911,7 +55905,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="300" spans="1:13">
+    <row r="300" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A300" s="5">
         <v>42823</v>
       </c>
@@ -55952,7 +55946,7 @@
         <v>1777</v>
       </c>
     </row>
-    <row r="301" spans="1:13">
+    <row r="301" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A301" s="5">
         <v>42830</v>
       </c>
@@ -55993,7 +55987,7 @@
         <v>1810</v>
       </c>
     </row>
-    <row r="302" spans="1:13">
+    <row r="302" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A302" s="5">
         <v>42837</v>
       </c>
@@ -56034,7 +56028,7 @@
         <v>1810</v>
       </c>
     </row>
-    <row r="303" spans="1:13">
+    <row r="303" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A303" s="5">
         <v>42844</v>
       </c>
@@ -56075,7 +56069,7 @@
         <v>1775</v>
       </c>
     </row>
-    <row r="304" spans="1:13">
+    <row r="304" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A304" s="5">
         <v>42851</v>
       </c>
@@ -56116,7 +56110,7 @@
         <v>1802</v>
       </c>
     </row>
-    <row r="305" spans="1:13">
+    <row r="305" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A305" s="5">
         <v>42858</v>
       </c>
@@ -56157,7 +56151,7 @@
         <v>1778</v>
       </c>
     </row>
-    <row r="306" spans="1:13">
+    <row r="306" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A306" s="5">
         <v>42865</v>
       </c>
@@ -56198,7 +56192,7 @@
         <v>1749</v>
       </c>
     </row>
-    <row r="307" spans="1:13">
+    <row r="307" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A307" s="5">
         <v>42872</v>
       </c>
@@ -56239,7 +56233,7 @@
         <v>1755</v>
       </c>
     </row>
-    <row r="308" spans="1:13">
+    <row r="308" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A308" s="5">
         <v>42879</v>
       </c>
@@ -56280,7 +56274,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="309" spans="1:13">
+    <row r="309" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A309" s="5">
         <v>42886</v>
       </c>
@@ -56321,7 +56315,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="310" spans="1:13">
+    <row r="310" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A310" s="5">
         <v>42893</v>
       </c>
@@ -56362,7 +56356,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="311" spans="1:13">
+    <row r="311" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A311" s="5">
         <v>42900</v>
       </c>
@@ -56403,7 +56397,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="312" spans="1:13">
+    <row r="312" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A312" s="5">
         <v>42907</v>
       </c>
@@ -56444,7 +56438,7 @@
         <v>1734</v>
       </c>
     </row>
-    <row r="313" spans="1:13">
+    <row r="313" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A313" s="5">
         <v>42914</v>
       </c>
@@ -56485,7 +56479,7 @@
         <v>1734</v>
       </c>
     </row>
-    <row r="314" spans="1:13">
+    <row r="314" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A314" s="5">
         <v>42921</v>
       </c>
@@ -56526,7 +56520,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="315" spans="1:13">
+    <row r="315" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A315" s="5">
         <v>42928</v>
       </c>
@@ -56567,7 +56561,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="316" spans="1:13">
+    <row r="316" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A316" s="5">
         <v>42935</v>
       </c>
@@ -56608,7 +56602,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="317" spans="1:13">
+    <row r="317" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A317" s="5">
         <v>42942</v>
       </c>
@@ -56649,7 +56643,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="318" spans="1:13">
+    <row r="318" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A318" s="5">
         <v>42949</v>
       </c>
@@ -56690,7 +56684,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="319" spans="1:13">
+    <row r="319" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A319" s="5">
         <v>42956</v>
       </c>
@@ -56731,7 +56725,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="320" spans="1:13">
+    <row r="320" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A320" s="5">
         <v>42963</v>
       </c>
@@ -56772,7 +56766,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="321" spans="1:13">
+    <row r="321" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A321" s="5">
         <v>42970</v>
       </c>
@@ -56813,7 +56807,7 @@
         <v>1730</v>
       </c>
     </row>
-    <row r="322" spans="1:13">
+    <row r="322" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A322" s="5">
         <v>42977</v>
       </c>
@@ -56854,7 +56848,7 @@
         <v>1730</v>
       </c>
     </row>
-    <row r="323" spans="1:13">
+    <row r="323" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A323" s="5">
         <v>42984</v>
       </c>
@@ -56895,7 +56889,7 @@
         <v>1742</v>
       </c>
     </row>
-    <row r="324" spans="1:13">
+    <row r="324" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A324" s="5">
         <v>42991</v>
       </c>
@@ -56936,7 +56930,7 @@
         <v>1742</v>
       </c>
     </row>
-    <row r="325" spans="1:13">
+    <row r="325" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A325" s="5">
         <v>42998</v>
       </c>
@@ -56977,7 +56971,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="326" spans="1:13">
+    <row r="326" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A326" s="5">
         <v>43005</v>
       </c>
@@ -57018,7 +57012,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="327" spans="1:13">
+    <row r="327" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A327" s="5">
         <v>43012</v>
       </c>
@@ -57059,7 +57053,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="328" spans="1:13">
+    <row r="328" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A328" s="5">
         <v>43019</v>
       </c>
@@ -57100,7 +57094,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="329" spans="1:13">
+    <row r="329" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A329" s="5">
         <v>43026</v>
       </c>
@@ -57141,7 +57135,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="330" spans="1:13">
+    <row r="330" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A330" s="5">
         <v>43033</v>
       </c>
@@ -57182,7 +57176,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="331" spans="1:13">
+    <row r="331" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A331" s="5">
         <v>43040</v>
       </c>
@@ -57223,7 +57217,7 @@
         <v>1691</v>
       </c>
     </row>
-    <row r="332" spans="1:13">
+    <row r="332" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A332" s="5">
         <v>43047</v>
       </c>
@@ -57264,7 +57258,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="333" spans="1:13">
+    <row r="333" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A333" s="5">
         <v>43054</v>
       </c>
@@ -57305,7 +57299,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="334" spans="1:13">
+    <row r="334" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A334" s="5">
         <v>43061</v>
       </c>
@@ -57346,7 +57340,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="335" spans="1:13">
+    <row r="335" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A335" s="5">
         <v>43068</v>
       </c>
@@ -57387,7 +57381,7 @@
         <v>1853</v>
       </c>
     </row>
-    <row r="336" spans="1:13">
+    <row r="336" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A336" s="5">
         <v>43075</v>
       </c>
@@ -57428,7 +57422,7 @@
         <v>2063</v>
       </c>
     </row>
-    <row r="337" spans="1:13">
+    <row r="337" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A337" s="5">
         <v>43082</v>
       </c>
@@ -57469,7 +57463,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="338" spans="1:13">
+    <row r="338" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A338" s="5">
         <v>43089</v>
       </c>
@@ -57510,7 +57504,7 @@
         <v>1748</v>
       </c>
     </row>
-    <row r="339" spans="1:13">
+    <row r="339" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A339" s="5">
         <v>43096</v>
       </c>
@@ -57551,7 +57545,7 @@
         <v>1824</v>
       </c>
     </row>
-    <row r="340" spans="1:13">
+    <row r="340" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A340" s="5">
         <v>43103</v>
       </c>
@@ -57592,7 +57586,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="341" spans="1:13">
+    <row r="341" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A341" s="5">
         <v>43110</v>
       </c>
@@ -57633,7 +57627,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="342" spans="1:13">
+    <row r="342" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A342" s="5">
         <v>43117</v>
       </c>
@@ -57674,7 +57668,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="343" spans="1:13">
+    <row r="343" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A343" s="5">
         <v>43124</v>
       </c>
@@ -57715,7 +57709,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="344" spans="1:13">
+    <row r="344" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A344" s="5">
         <v>43131</v>
       </c>
@@ -57756,7 +57750,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="345" spans="1:13">
+    <row r="345" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A345" s="5">
         <v>43138</v>
       </c>
@@ -57797,7 +57791,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="346" spans="1:13">
+    <row r="346" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A346" s="5">
         <v>43145</v>
       </c>
@@ -57838,7 +57832,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="347" spans="1:13">
+    <row r="347" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A347" s="5">
         <v>43152</v>
       </c>
@@ -57879,7 +57873,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="348" spans="1:13">
+    <row r="348" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A348" s="5">
         <v>43159</v>
       </c>
@@ -57920,7 +57914,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="349" spans="1:13">
+    <row r="349" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A349" s="5">
         <v>43166</v>
       </c>
@@ -57961,7 +57955,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="350" spans="1:13">
+    <row r="350" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A350" s="5">
         <v>43173</v>
       </c>
@@ -58002,7 +57996,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="351" spans="1:13">
+    <row r="351" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A351" s="5">
         <v>43180</v>
       </c>
@@ -58043,7 +58037,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="352" spans="1:13">
+    <row r="352" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A352" s="5">
         <v>43187</v>
       </c>
@@ -58084,7 +58078,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="353" spans="1:13">
+    <row r="353" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A353" s="5">
         <v>43194</v>
       </c>
@@ -58125,7 +58119,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="354" spans="1:13">
+    <row r="354" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A354" s="5">
         <v>43201</v>
       </c>
@@ -58166,7 +58160,7 @@
         <v>1864</v>
       </c>
     </row>
-    <row r="355" spans="1:13">
+    <row r="355" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A355" s="5">
         <v>43208</v>
       </c>
@@ -58207,7 +58201,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="356" spans="1:13">
+    <row r="356" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A356" s="5">
         <v>43215</v>
       </c>
@@ -58248,7 +58242,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="357" spans="1:13">
+    <row r="357" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A357" s="5">
         <v>43222</v>
       </c>
@@ -58289,7 +58283,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="358" spans="1:13">
+    <row r="358" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A358" s="5">
         <v>43229</v>
       </c>
@@ -58330,7 +58324,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="359" spans="1:13">
+    <row r="359" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A359" s="5">
         <v>43236</v>
       </c>
@@ -58371,7 +58365,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="360" spans="1:13">
+    <row r="360" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A360" s="5">
         <v>43243</v>
       </c>
@@ -58412,7 +58406,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="361" spans="1:13">
+    <row r="361" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A361" s="5">
         <v>43250</v>
       </c>
@@ -58453,7 +58447,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="362" spans="1:13">
+    <row r="362" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A362" s="5">
         <v>43257</v>
       </c>
@@ -58494,7 +58488,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="363" spans="1:13">
+    <row r="363" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A363" s="5">
         <v>43264</v>
       </c>
@@ -58535,7 +58529,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="364" spans="1:13">
+    <row r="364" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A364" s="5">
         <v>43271</v>
       </c>
@@ -58576,7 +58570,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="365" spans="1:13">
+    <row r="365" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A365" s="5">
         <v>43278</v>
       </c>
@@ -58617,7 +58611,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="366" spans="1:13">
+    <row r="366" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A366" s="5">
         <v>43285</v>
       </c>
@@ -58658,7 +58652,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="367" spans="1:13">
+    <row r="367" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A367" s="5">
         <v>43292</v>
       </c>
@@ -58699,7 +58693,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="368" spans="1:13">
+    <row r="368" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A368" s="5">
         <v>43299</v>
       </c>
@@ -58740,7 +58734,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="369" spans="1:13">
+    <row r="369" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A369" s="5">
         <v>43306</v>
       </c>
@@ -58781,7 +58775,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="370" spans="1:13">
+    <row r="370" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A370" s="5">
         <v>43313</v>
       </c>
@@ -58822,7 +58816,7 @@
         <v>1965</v>
       </c>
     </row>
-    <row r="371" spans="1:13">
+    <row r="371" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A371" s="5">
         <v>43320</v>
       </c>
@@ -58863,7 +58857,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="372" spans="1:13">
+    <row r="372" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A372" s="5">
         <v>43327</v>
       </c>
@@ -58904,7 +58898,7 @@
         <v>1962</v>
       </c>
     </row>
-    <row r="373" spans="1:13">
+    <row r="373" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A373" s="5">
         <v>43334</v>
       </c>
@@ -58945,7 +58939,7 @@
         <v>1962</v>
       </c>
     </row>
-    <row r="374" spans="1:13">
+    <row r="374" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A374" s="5">
         <v>43341</v>
       </c>
@@ -58986,7 +58980,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="375" spans="1:13">
+    <row r="375" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A375" s="5">
         <v>43348</v>
       </c>
@@ -59027,7 +59021,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="376" spans="1:13">
+    <row r="376" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A376" s="5">
         <v>43355</v>
       </c>
@@ -59068,7 +59062,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="377" spans="1:13">
+    <row r="377" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A377" s="5">
         <v>43362</v>
       </c>
@@ -59109,7 +59103,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="378" spans="1:13">
+    <row r="378" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A378" s="5">
         <v>43369</v>
       </c>
@@ -59150,7 +59144,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="379" spans="1:13">
+    <row r="379" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A379" s="5">
         <v>43376</v>
       </c>
@@ -59191,7 +59185,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="380" spans="1:13">
+    <row r="380" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A380" s="5">
         <v>43383</v>
       </c>
@@ -59232,7 +59226,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="381" spans="1:13">
+    <row r="381" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A381" s="5">
         <v>43390</v>
       </c>
@@ -59273,7 +59267,7 @@
         <v>1970</v>
       </c>
     </row>
-    <row r="382" spans="1:13">
+    <row r="382" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A382" s="5">
         <v>43397</v>
       </c>
@@ -59314,7 +59308,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="383" spans="1:13">
+    <row r="383" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A383" s="5">
         <v>43404</v>
       </c>
@@ -59355,7 +59349,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="384" spans="1:13">
+    <row r="384" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A384" s="5">
         <v>43411</v>
       </c>
@@ -59396,7 +59390,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="385" spans="1:13">
+    <row r="385" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A385" s="5">
         <v>43418</v>
       </c>
@@ -59437,7 +59431,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="386" spans="1:13">
+    <row r="386" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A386" s="5">
         <v>43425</v>
       </c>
@@ -59478,7 +59472,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="387" spans="1:13">
+    <row r="387" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A387" s="5">
         <v>43432</v>
       </c>
@@ -59519,7 +59513,7 @@
         <v>2045</v>
       </c>
     </row>
-    <row r="388" spans="1:13">
+    <row r="388" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A388" s="5">
         <v>43439</v>
       </c>
@@ -59560,7 +59554,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="389" spans="1:13">
+    <row r="389" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A389" s="5">
         <v>43446</v>
       </c>
@@ -59601,7 +59595,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="390" spans="1:13">
+    <row r="390" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A390" s="5">
         <v>43453</v>
       </c>
@@ -59642,7 +59636,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="391" spans="1:13">
+    <row r="391" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A391" s="5">
         <v>43460</v>
       </c>
@@ -59683,7 +59677,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="392" spans="1:13">
+    <row r="392" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A392" s="5">
         <v>43467</v>
       </c>
@@ -59724,7 +59718,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="393" spans="1:13">
+    <row r="393" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A393" s="5">
         <v>43474</v>
       </c>
@@ -59765,7 +59759,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="394" spans="1:13">
+    <row r="394" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A394" s="5">
         <v>43481</v>
       </c>
@@ -59806,7 +59800,7 @@
         <v>2049</v>
       </c>
     </row>
-    <row r="395" spans="1:13">
+    <row r="395" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A395" s="5">
         <v>43488</v>
       </c>
@@ -59847,7 +59841,7 @@
         <v>2049</v>
       </c>
     </row>
-    <row r="396" spans="1:13">
+    <row r="396" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A396" s="5">
         <v>43495</v>
       </c>
@@ -59888,7 +59882,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="397" spans="1:13">
+    <row r="397" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A397" s="5">
         <v>43502</v>
       </c>
@@ -59929,7 +59923,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="398" spans="1:13">
+    <row r="398" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A398" s="5">
         <v>43509</v>
       </c>
@@ -59970,7 +59964,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="399" spans="1:13">
+    <row r="399" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A399" s="5">
         <v>43516</v>
       </c>
@@ -60011,7 +60005,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="400" spans="1:13">
+    <row r="400" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A400" s="5">
         <v>43523</v>
       </c>
@@ -60052,7 +60046,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="401" spans="1:13">
+    <row r="401" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A401" s="5">
         <v>43530</v>
       </c>
@@ -60093,7 +60087,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="402" spans="1:13">
+    <row r="402" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A402" s="5">
         <v>43537</v>
       </c>
@@ -60134,7 +60128,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="403" spans="1:13">
+    <row r="403" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A403" s="5">
         <v>43544</v>
       </c>
@@ -60175,7 +60169,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="404" spans="1:13">
+    <row r="404" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A404" s="5">
         <v>43551</v>
       </c>
@@ -60216,7 +60210,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="405" spans="1:13">
+    <row r="405" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A405" s="5">
         <v>43558</v>
       </c>
@@ -60257,7 +60251,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="406" spans="1:13">
+    <row r="406" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A406" s="5">
         <v>43565</v>
       </c>
@@ -60298,7 +60292,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="407" spans="1:13">
+    <row r="407" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A407" s="5">
         <v>43572</v>
       </c>
@@ -60339,7 +60333,7 @@
         <v>2302</v>
       </c>
     </row>
-    <row r="408" spans="1:13">
+    <row r="408" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A408" s="5">
         <v>43579</v>
       </c>
@@ -60380,7 +60374,7 @@
         <v>2302</v>
       </c>
     </row>
-    <row r="409" spans="1:13">
+    <row r="409" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A409" s="5">
         <v>43586</v>
       </c>
@@ -60421,7 +60415,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="410" spans="1:13">
+    <row r="410" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A410" s="5">
         <v>43593</v>
       </c>
@@ -60462,7 +60456,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="411" spans="1:13">
+    <row r="411" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A411" s="5">
         <v>43600</v>
       </c>
@@ -60503,7 +60497,7 @@
         <v>2343</v>
       </c>
     </row>
-    <row r="412" spans="1:13">
+    <row r="412" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A412" s="5">
         <v>43607</v>
       </c>
@@ -60544,7 +60538,7 @@
         <v>2343</v>
       </c>
     </row>
-    <row r="413" spans="1:13">
+    <row r="413" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A413" s="5">
         <v>43614</v>
       </c>
@@ -60585,7 +60579,7 @@
         <v>2272</v>
       </c>
     </row>
-    <row r="414" spans="1:13">
+    <row r="414" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A414" s="5">
         <v>43621</v>
       </c>
@@ -60626,7 +60620,7 @@
         <v>2344</v>
       </c>
     </row>
-    <row r="415" spans="1:13">
+    <row r="415" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A415" s="5">
         <v>43628</v>
       </c>
@@ -60667,7 +60661,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="416" spans="1:13">
+    <row r="416" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A416" s="5">
         <v>43635</v>
       </c>
@@ -60708,7 +60702,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="417" spans="1:13">
+    <row r="417" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A417" s="5">
         <v>43642</v>
       </c>
@@ -60749,7 +60743,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="418" spans="1:13">
+    <row r="418" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A418" s="5">
         <v>43649</v>
       </c>
@@ -60790,7 +60784,7 @@
         <v>2378</v>
       </c>
     </row>
-    <row r="419" spans="1:13">
+    <row r="419" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A419" s="5">
         <v>43656</v>
       </c>
@@ -60831,7 +60825,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="420" spans="1:13">
+    <row r="420" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A420" s="5">
         <v>43663</v>
       </c>
@@ -60872,7 +60866,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="421" spans="1:13">
+    <row r="421" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A421" s="5">
         <v>43670</v>
       </c>
@@ -60913,7 +60907,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="422" spans="1:13">
+    <row r="422" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A422" s="5">
         <v>43677</v>
       </c>
@@ -60954,7 +60948,7 @@
         <v>2369</v>
       </c>
     </row>
-    <row r="423" spans="1:13">
+    <row r="423" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A423" s="5">
         <v>43684</v>
       </c>
@@ -60995,7 +60989,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="424" spans="1:13">
+    <row r="424" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A424" s="5">
         <v>43691</v>
       </c>
@@ -61036,7 +61030,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="425" spans="1:13">
+    <row r="425" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A425" s="5">
         <v>43698</v>
       </c>
@@ -61077,7 +61071,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="426" spans="1:13">
+    <row r="426" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A426" s="5">
         <v>43705</v>
       </c>
@@ -61118,7 +61112,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="427" spans="1:13">
+    <row r="427" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A427" s="5">
         <v>43712</v>
       </c>
@@ -61159,7 +61153,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="428" spans="1:13">
+    <row r="428" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A428" s="5">
         <v>43719</v>
       </c>
@@ -61200,7 +61194,7 @@
         <v>2346</v>
       </c>
     </row>
-    <row r="429" spans="1:13">
+    <row r="429" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A429" s="5">
         <v>43726</v>
       </c>
@@ -61241,7 +61235,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="430" spans="1:13">
+    <row r="430" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A430" s="5">
         <v>43733</v>
       </c>
@@ -61282,7 +61276,7 @@
         <v>2346</v>
       </c>
     </row>
-    <row r="431" spans="1:13">
+    <row r="431" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A431" s="5">
         <v>43740</v>
       </c>
@@ -61323,7 +61317,7 @@
         <v>2349</v>
       </c>
     </row>
-    <row r="432" spans="1:13">
+    <row r="432" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A432" s="5">
         <v>43747</v>
       </c>
@@ -61364,7 +61358,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="433" spans="1:13">
+    <row r="433" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A433" s="5">
         <v>43754</v>
       </c>
@@ -61405,7 +61399,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="434" spans="1:13">
+    <row r="434" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A434" s="5">
         <v>43761</v>
       </c>
@@ -61446,7 +61440,7 @@
         <v>2350</v>
       </c>
     </row>
-    <row r="435" spans="1:13">
+    <row r="435" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A435" s="5">
         <v>43768</v>
       </c>
@@ -61487,7 +61481,7 @@
         <v>2356</v>
       </c>
     </row>
-    <row r="436" spans="1:13">
+    <row r="436" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A436" s="5">
         <v>43775</v>
       </c>
@@ -61528,7 +61522,7 @@
         <v>2363</v>
       </c>
     </row>
-    <row r="437" spans="1:13">
+    <row r="437" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A437" s="5">
         <v>43782</v>
       </c>
@@ -61569,7 +61563,7 @@
         <v>2338</v>
       </c>
     </row>
-    <row r="438" spans="1:13">
+    <row r="438" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A438" s="5">
         <v>43789</v>
       </c>
@@ -61610,7 +61604,7 @@
         <v>2391</v>
       </c>
     </row>
-    <row r="439" spans="1:13">
+    <row r="439" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A439" s="5">
         <v>43796</v>
       </c>
@@ -61651,7 +61645,7 @@
         <v>2397</v>
       </c>
     </row>
-    <row r="440" spans="1:13">
+    <row r="440" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A440" s="5">
         <v>43803</v>
       </c>
@@ -61692,7 +61686,7 @@
         <v>2388</v>
       </c>
     </row>
-    <row r="441" spans="1:13">
+    <row r="441" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A441" s="5">
         <v>43810</v>
       </c>
@@ -61733,7 +61727,7 @@
         <v>2363</v>
       </c>
     </row>
-    <row r="442" spans="1:13">
+    <row r="442" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A442" s="5">
         <v>43817</v>
       </c>
@@ -61774,7 +61768,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="443" spans="1:13">
+    <row r="443" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A443" s="5">
         <v>43831</v>
       </c>
@@ -61815,7 +61809,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="444" spans="1:13">
+    <row r="444" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A444" s="5">
         <v>43838</v>
       </c>
@@ -61856,7 +61850,7 @@
         <v>2415</v>
       </c>
     </row>
-    <row r="445" spans="1:13">
+    <row r="445" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A445" s="5">
         <v>43845</v>
       </c>
@@ -61897,7 +61891,7 @@
         <v>2415</v>
       </c>
     </row>
-    <row r="446" spans="1:13">
+    <row r="446" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A446" s="5">
         <v>43852</v>
       </c>
@@ -61938,7 +61932,7 @@
         <v>2410</v>
       </c>
     </row>
-    <row r="447" spans="1:13">
+    <row r="447" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A447" s="5">
         <v>43859</v>
       </c>
@@ -61979,7 +61973,7 @@
         <v>2344</v>
       </c>
     </row>
-    <row r="448" spans="1:13">
+    <row r="448" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A448" s="5">
         <v>43866</v>
       </c>
@@ -62020,7 +62014,7 @@
         <v>2188</v>
       </c>
     </row>
-    <row r="449" spans="1:13">
+    <row r="449" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A449" s="5">
         <v>43873</v>
       </c>
@@ -62061,7 +62055,7 @@
         <v>2214</v>
       </c>
     </row>
-    <row r="450" spans="1:13">
+    <row r="450" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A450" s="5">
         <v>43880</v>
       </c>
@@ -62102,7 +62096,7 @@
         <v>2214</v>
       </c>
     </row>
-    <row r="451" spans="1:13">
+    <row r="451" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A451" s="5">
         <v>43887</v>
       </c>
@@ -62143,7 +62137,7 @@
         <v>2206</v>
       </c>
     </row>
-    <row r="452" spans="1:13">
+    <row r="452" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A452" s="5">
         <v>43894</v>
       </c>
@@ -62184,7 +62178,7 @@
         <v>2217</v>
       </c>
     </row>
-    <row r="453" spans="1:13">
+    <row r="453" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A453" s="5">
         <v>43901</v>
       </c>
@@ -62225,7 +62219,7 @@
         <v>2234</v>
       </c>
     </row>
-    <row r="454" spans="1:13">
+    <row r="454" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A454" s="5">
         <v>43908</v>
       </c>
@@ -62266,7 +62260,7 @@
         <v>2513</v>
       </c>
     </row>
-    <row r="455" spans="1:13">
+    <row r="455" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A455" s="5">
         <v>43915</v>
       </c>
@@ -62307,7 +62301,7 @@
         <v>2322</v>
       </c>
     </row>
-    <row r="456" spans="1:13">
+    <row r="456" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A456" s="5">
         <v>43922</v>
       </c>
@@ -62348,7 +62342,7 @@
         <v>2322</v>
       </c>
     </row>
-    <row r="457" spans="1:13">
+    <row r="457" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A457" s="5">
         <v>43929</v>
       </c>
@@ -62389,7 +62383,7 @@
         <v>2548</v>
       </c>
     </row>
-    <row r="458" spans="1:13">
+    <row r="458" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A458" s="5">
         <v>43936</v>
       </c>
@@ -62430,7 +62424,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="459" spans="1:13">
+    <row r="459" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A459" s="5">
         <v>43943</v>
       </c>
@@ -62471,7 +62465,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="460" spans="1:13">
+    <row r="460" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A460" s="5">
         <v>43950</v>
       </c>
@@ -62512,7 +62506,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="461" spans="1:13">
+    <row r="461" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A461" s="5">
         <v>43957</v>
       </c>
@@ -62553,7 +62547,7 @@
         <v>2592</v>
       </c>
     </row>
-    <row r="462" spans="1:13">
+    <row r="462" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A462" s="5">
         <v>43964</v>
       </c>
@@ -62594,7 +62588,7 @@
         <v>2592</v>
       </c>
     </row>
-    <row r="463" spans="1:13">
+    <row r="463" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A463" s="5">
         <v>43971</v>
       </c>
@@ -62635,7 +62629,7 @@
         <v>2516</v>
       </c>
     </row>
-    <row r="464" spans="1:13">
+    <row r="464" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A464" s="5">
         <v>43978</v>
       </c>
@@ -62676,7 +62670,7 @@
         <v>2516</v>
       </c>
     </row>
-    <row r="465" spans="1:13">
+    <row r="465" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A465" s="5">
         <v>43985</v>
       </c>
@@ -62717,7 +62711,7 @@
         <v>2398</v>
       </c>
     </row>
-    <row r="466" spans="1:13">
+    <row r="466" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A466" s="5">
         <v>43992</v>
       </c>
@@ -62758,7 +62752,7 @@
         <v>2398</v>
       </c>
     </row>
-    <row r="467" spans="1:13">
+    <row r="467" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A467" s="5">
         <v>43999</v>
       </c>
@@ -62799,7 +62793,7 @@
         <v>2577</v>
       </c>
     </row>
-    <row r="468" spans="1:13">
+    <row r="468" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A468" s="5">
         <v>44006</v>
       </c>
@@ -62840,7 +62834,7 @@
         <v>2443</v>
       </c>
     </row>
-    <row r="469" spans="1:13">
+    <row r="469" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A469" s="5">
         <v>44013</v>
       </c>
@@ -62881,7 +62875,7 @@
         <v>2369</v>
       </c>
     </row>
-    <row r="470" spans="1:13">
+    <row r="470" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A470" s="5">
         <v>44020</v>
       </c>
@@ -62922,7 +62916,7 @@
         <v>2326</v>
       </c>
     </row>
-    <row r="471" spans="1:13">
+    <row r="471" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A471" s="5">
         <v>44027</v>
       </c>
@@ -62963,7 +62957,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="472" spans="1:13">
+    <row r="472" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A472" s="5">
         <v>44034</v>
       </c>
@@ -63004,7 +62998,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="473" spans="1:13">
+    <row r="473" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A473" s="5">
         <v>44041</v>
       </c>
@@ -63045,7 +63039,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="474" spans="1:13">
+    <row r="474" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A474" s="5">
         <v>44048</v>
       </c>
@@ -63086,7 +63080,7 @@
         <v>2264</v>
       </c>
     </row>
-    <row r="475" spans="1:13">
+    <row r="475" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A475" s="5">
         <v>44055</v>
       </c>
@@ -63127,7 +63121,7 @@
         <v>2202</v>
       </c>
     </row>
-    <row r="476" spans="1:13">
+    <row r="476" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A476" s="5">
         <v>44062</v>
       </c>
@@ -63168,7 +63162,7 @@
         <v>2449</v>
       </c>
     </row>
-    <row r="477" spans="1:13">
+    <row r="477" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A477" s="5">
         <v>44069</v>
       </c>
@@ -63209,7 +63203,7 @@
         <v>2449</v>
       </c>
     </row>
-    <row r="478" spans="1:13">
+    <row r="478" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A478" s="5">
         <v>44076</v>
       </c>
@@ -63250,7 +63244,7 @@
         <v>2449</v>
       </c>
     </row>
-    <row r="479" spans="1:13">
+    <row r="479" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A479" s="5">
         <v>44083</v>
       </c>
@@ -63291,7 +63285,7 @@
         <v>2421</v>
       </c>
     </row>
-    <row r="480" spans="1:13">
+    <row r="480" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A480" s="5">
         <v>44090</v>
       </c>
@@ -63332,7 +63326,7 @@
         <v>2437</v>
       </c>
     </row>
-    <row r="481" spans="1:13">
+    <row r="481" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A481" s="5">
         <v>44097</v>
       </c>
@@ -63373,7 +63367,7 @@
         <v>2437</v>
       </c>
     </row>
-    <row r="482" spans="1:13">
+    <row r="482" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A482" s="5">
         <v>44104</v>
       </c>
@@ -63414,7 +63408,7 @@
         <v>2222</v>
       </c>
     </row>
-    <row r="483" spans="1:13">
+    <row r="483" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A483" s="5">
         <v>44111</v>
       </c>
@@ -63455,7 +63449,7 @@
         <v>2134</v>
       </c>
     </row>
-    <row r="484" spans="1:13">
+    <row r="484" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A484" s="5">
         <v>44118</v>
       </c>
@@ -63496,7 +63490,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="485" spans="1:13">
+    <row r="485" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A485" s="5">
         <v>44125</v>
       </c>
@@ -63537,7 +63531,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="486" spans="1:13">
+    <row r="486" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A486" s="5">
         <v>44132</v>
       </c>
@@ -63578,7 +63572,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="487" spans="1:13">
+    <row r="487" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A487" s="5">
         <v>44139</v>
       </c>
@@ -63619,7 +63613,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="488" spans="1:13">
+    <row r="488" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A488" s="5">
         <v>44146</v>
       </c>
@@ -63660,7 +63654,7 @@
         <v>2034</v>
       </c>
     </row>
-    <row r="489" spans="1:13">
+    <row r="489" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A489" s="5">
         <v>44153</v>
       </c>
@@ -63701,7 +63695,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="490" spans="1:13">
+    <row r="490" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A490" s="5">
         <v>44160</v>
       </c>
@@ -63742,7 +63736,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="491" spans="1:13">
+    <row r="491" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A491" s="5">
         <v>44167</v>
       </c>
@@ -63783,7 +63777,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="492" spans="1:13">
+    <row r="492" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A492" s="5">
         <v>44174</v>
       </c>
@@ -63824,7 +63818,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="493" spans="1:13">
+    <row r="493" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A493" s="5">
         <v>44181</v>
       </c>
@@ -63865,7 +63859,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="494" spans="1:13">
+    <row r="494" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A494" s="5">
         <v>44188</v>
       </c>
@@ -63906,7 +63900,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="495" spans="1:13">
+    <row r="495" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A495" s="5">
         <v>44195</v>
       </c>
@@ -63947,7 +63941,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="496" spans="1:13">
+    <row r="496" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A496" s="5">
         <v>44202</v>
       </c>
@@ -63988,7 +63982,7 @@
         <v>2185</v>
       </c>
     </row>
-    <row r="497" spans="1:13">
+    <row r="497" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A497" s="5">
         <v>44209</v>
       </c>
@@ -64029,7 +64023,7 @@
         <v>2116</v>
       </c>
     </row>
-    <row r="498" spans="1:13">
+    <row r="498" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A498" s="5">
         <v>44216</v>
       </c>
@@ -64070,7 +64064,7 @@
         <v>2283</v>
       </c>
     </row>
-    <row r="499" spans="1:13">
+    <row r="499" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A499" s="5">
         <v>44223</v>
       </c>
@@ -64111,7 +64105,7 @@
         <v>2283</v>
       </c>
     </row>
-    <row r="500" spans="1:13">
+    <row r="500" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A500" s="5">
         <v>44230</v>
       </c>
@@ -64152,7 +64146,7 @@
         <v>2254</v>
       </c>
     </row>
-    <row r="501" spans="1:13">
+    <row r="501" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A501" s="5">
         <v>44237</v>
       </c>
@@ -64193,7 +64187,7 @@
         <v>2299</v>
       </c>
     </row>
-    <row r="502" spans="1:13">
+    <row r="502" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A502" s="5">
         <v>44244</v>
       </c>
@@ -64234,7 +64228,7 @@
         <v>2299</v>
       </c>
     </row>
-    <row r="503" spans="1:13">
+    <row r="503" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A503" s="5">
         <v>44251</v>
       </c>
@@ -64275,7 +64269,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="504" spans="1:13">
+    <row r="504" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A504" s="5">
         <v>44258</v>
       </c>
@@ -64316,7 +64310,7 @@
         <v>2342</v>
       </c>
     </row>
-    <row r="505" spans="1:13">
+    <row r="505" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A505" s="5">
         <v>44265</v>
       </c>
@@ -64357,7 +64351,7 @@
         <v>2359</v>
       </c>
     </row>
-    <row r="506" spans="1:13">
+    <row r="506" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A506" s="5">
         <v>44272</v>
       </c>
@@ -64398,7 +64392,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="507" spans="1:13">
+    <row r="507" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A507" s="5">
         <v>44279</v>
       </c>
@@ -64439,7 +64433,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="508" spans="1:13">
+    <row r="508" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A508" s="5">
         <v>44286</v>
       </c>
@@ -64480,7 +64474,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="509" spans="1:13">
+    <row r="509" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A509" s="5">
         <v>44293</v>
       </c>
@@ -64521,7 +64515,7 @@
         <v>2621</v>
       </c>
     </row>
-    <row r="510" spans="1:13">
+    <row r="510" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A510" s="5">
         <v>44300</v>
       </c>
@@ -64562,7 +64556,7 @@
         <v>2623</v>
       </c>
     </row>
-    <row r="511" spans="1:13">
+    <row r="511" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A511" s="5">
         <v>44307</v>
       </c>
@@ -64603,7 +64597,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="512" spans="1:13">
+    <row r="512" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A512" s="5">
         <v>44314</v>
       </c>
@@ -64644,7 +64638,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="513" spans="1:13">
+    <row r="513" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A513" s="5">
         <v>44321</v>
       </c>
@@ -64685,7 +64679,7 @@
         <v>3505</v>
       </c>
     </row>
-    <row r="514" spans="1:13">
+    <row r="514" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A514" s="5">
         <v>44328</v>
       </c>
@@ -64726,7 +64720,7 @@
         <v>3550</v>
       </c>
     </row>
-    <row r="515" spans="1:13">
+    <row r="515" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A515" s="5">
         <v>44335</v>
       </c>
@@ -64767,7 +64761,7 @@
         <v>3553</v>
       </c>
     </row>
-    <row r="516" spans="1:13">
+    <row r="516" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A516" s="5">
         <v>44342</v>
       </c>
@@ -64808,7 +64802,7 @@
         <v>3670</v>
       </c>
     </row>
-    <row r="517" spans="1:13">
+    <row r="517" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A517" s="5">
         <v>44349</v>
       </c>
@@ -64849,7 +64843,7 @@
         <v>3720</v>
       </c>
     </row>
-    <row r="518" spans="1:13">
+    <row r="518" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A518" s="5">
         <v>44356</v>
       </c>
@@ -64890,7 +64884,7 @@
         <v>3988</v>
       </c>
     </row>
-    <row r="519" spans="1:13">
+    <row r="519" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A519" s="5">
         <v>44363</v>
       </c>
@@ -64931,7 +64925,7 @@
         <v>4607</v>
       </c>
     </row>
-    <row r="520" spans="1:13">
+    <row r="520" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A520" s="5">
         <v>44370</v>
       </c>
@@ -64972,7 +64966,7 @@
         <v>4744</v>
       </c>
     </row>
-    <row r="521" spans="1:13">
+    <row r="521" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A521" s="5">
         <v>44377</v>
       </c>
@@ -65013,7 +65007,7 @@
         <v>5008</v>
       </c>
     </row>
-    <row r="522" spans="1:13">
+    <row r="522" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A522" s="5">
         <v>44384</v>
       </c>
@@ -65054,7 +65048,7 @@
         <v>5336</v>
       </c>
     </row>
-    <row r="523" spans="1:13">
+    <row r="523" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A523" s="5">
         <v>44391</v>
       </c>
@@ -65095,7 +65089,7 @@
         <v>5362</v>
       </c>
     </row>
-    <row r="524" spans="1:13">
+    <row r="524" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A524" s="5">
         <v>44398</v>
       </c>
@@ -65136,7 +65130,7 @@
         <v>5364</v>
       </c>
     </row>
-    <row r="525" spans="1:13">
+    <row r="525" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A525" s="5">
         <v>44405</v>
       </c>
@@ -65177,7 +65171,7 @@
         <v>5624</v>
       </c>
     </row>
-    <row r="526" spans="1:13">
+    <row r="526" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A526" s="5">
         <v>44412</v>
       </c>
@@ -65218,7 +65212,7 @@
         <v>6417</v>
       </c>
     </row>
-    <row r="527" spans="1:13">
+    <row r="527" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A527" s="5">
         <v>44419</v>
       </c>
@@ -65259,7 +65253,7 @@
         <v>6390</v>
       </c>
     </row>
-    <row r="528" spans="1:13">
+    <row r="528" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A528" s="5">
         <v>44426</v>
       </c>
@@ -65300,7 +65294,7 @@
         <v>6435</v>
       </c>
     </row>
-    <row r="529" spans="1:13">
+    <row r="529" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A529" s="5">
         <v>44433</v>
       </c>
@@ -65341,7 +65335,7 @@
         <v>6461</v>
       </c>
     </row>
-    <row r="530" spans="1:13">
+    <row r="530" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A530" s="5">
         <v>44440</v>
       </c>
@@ -65382,7 +65376,7 @@
         <v>5776</v>
       </c>
     </row>
-    <row r="531" spans="1:13">
+    <row r="531" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A531" s="5">
         <v>44447</v>
       </c>
@@ -65423,7 +65417,7 @@
         <v>6160</v>
       </c>
     </row>
-    <row r="532" spans="1:13">
+    <row r="532" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A532" s="5">
         <v>44454</v>
       </c>
@@ -65464,7 +65458,7 @@
         <v>6162</v>
       </c>
     </row>
-    <row r="533" spans="1:13">
+    <row r="533" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A533" s="5">
         <v>44461</v>
       </c>
@@ -65505,7 +65499,7 @@
         <v>6179</v>
       </c>
     </row>
-    <row r="534" spans="1:13">
+    <row r="534" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A534" s="5">
         <v>44468</v>
       </c>
@@ -65546,7 +65540,7 @@
         <v>6192</v>
       </c>
     </row>
-    <row r="535" spans="1:13">
+    <row r="535" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A535" s="5">
         <v>44475</v>
       </c>
@@ -65587,7 +65581,7 @@
         <v>6209</v>
       </c>
     </row>
-    <row r="536" spans="1:13">
+    <row r="536" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A536" s="5">
         <v>44482</v>
       </c>
@@ -65628,7 +65622,7 @@
         <v>6200</v>
       </c>
     </row>
-    <row r="537" spans="1:13">
+    <row r="537" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A537" s="5">
         <v>44489</v>
       </c>
@@ -65669,7 +65663,7 @@
         <v>6157</v>
       </c>
     </row>
-    <row r="538" spans="1:13">
+    <row r="538" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A538" s="5">
         <v>44496</v>
       </c>
@@ -65710,7 +65704,7 @@
         <v>6161</v>
       </c>
     </row>
-    <row r="539" spans="1:13">
+    <row r="539" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A539" s="5">
         <v>44503</v>
       </c>
@@ -65751,7 +65745,7 @@
         <v>6123</v>
       </c>
     </row>
-    <row r="540" spans="1:13">
+    <row r="540" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A540" s="5">
         <v>44510</v>
       </c>
@@ -65792,7 +65786,7 @@
         <v>6255</v>
       </c>
     </row>
-    <row r="541" spans="1:13">
+    <row r="541" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A541" s="5">
         <v>44517</v>
       </c>
@@ -65833,7 +65827,7 @@
         <v>6272</v>
       </c>
     </row>
-    <row r="542" spans="1:13">
+    <row r="542" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A542" s="5">
         <v>44524</v>
       </c>
@@ -65874,7 +65868,7 @@
         <v>6232</v>
       </c>
     </row>
-    <row r="543" spans="1:13">
+    <row r="543" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A543" s="5">
         <v>44531</v>
       </c>
@@ -65915,7 +65909,7 @@
         <v>6214</v>
       </c>
     </row>
-    <row r="544" spans="1:13">
+    <row r="544" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A544" s="5">
         <v>44538</v>
       </c>
@@ -65956,7 +65950,7 @@
         <v>6283</v>
       </c>
     </row>
-    <row r="545" spans="1:13">
+    <row r="545" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A545" s="5">
         <v>44545</v>
       </c>
@@ -65997,7 +65991,7 @@
         <v>6272</v>
       </c>
     </row>
-    <row r="546" spans="1:13">
+    <row r="546" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A546" s="5">
         <v>44552</v>
       </c>
@@ -66038,7 +66032,7 @@
         <v>6290</v>
       </c>
     </row>
-    <row r="547" spans="1:13">
+    <row r="547" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A547" s="5">
         <v>44566</v>
       </c>
@@ -66079,7 +66073,7 @@
         <v>6280</v>
       </c>
     </row>
-    <row r="548" spans="1:13">
+    <row r="548" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A548" s="5">
         <v>44573</v>
       </c>
@@ -66120,7 +66114,7 @@
         <v>6233</v>
       </c>
     </row>
-    <row r="549" spans="1:13">
+    <row r="549" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A549" s="5">
         <v>44580</v>
       </c>
@@ -66161,7 +66155,7 @@
         <v>6292</v>
       </c>
     </row>
-    <row r="550" spans="1:13">
+    <row r="550" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A550" s="5">
         <v>44587</v>
       </c>
@@ -66202,7 +66196,7 @@
         <v>6315</v>
       </c>
     </row>
-    <row r="551" spans="1:13">
+    <row r="551" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A551" s="5">
         <v>44594</v>
       </c>
@@ -66243,7 +66237,7 @@
         <v>6455</v>
       </c>
     </row>
-    <row r="552" spans="1:13">
+    <row r="552" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A552" s="5">
         <v>44601</v>
       </c>
@@ -66284,7 +66278,7 @@
         <v>6453</v>
       </c>
     </row>
-    <row r="553" spans="1:13">
+    <row r="553" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A553" s="5">
         <v>44608</v>
       </c>
@@ -66325,7 +66319,7 @@
         <v>6514</v>
       </c>
     </row>
-    <row r="554" spans="1:13">
+    <row r="554" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A554" s="5">
         <v>44615</v>
       </c>
@@ -66366,7 +66360,7 @@
         <v>6518</v>
       </c>
     </row>
-    <row r="555" spans="1:13">
+    <row r="555" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A555" s="5">
         <v>44622</v>
       </c>
@@ -66407,7 +66401,7 @@
         <v>6476</v>
       </c>
     </row>
-    <row r="556" spans="1:13">
+    <row r="556" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A556" s="5">
         <v>44629</v>
       </c>
@@ -66448,7 +66442,7 @@
         <v>6494</v>
       </c>
     </row>
-    <row r="557" spans="1:13">
+    <row r="557" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A557" s="5">
         <v>44636</v>
       </c>
@@ -66489,7 +66483,7 @@
         <v>6491</v>
       </c>
     </row>
-    <row r="558" spans="1:13">
+    <row r="558" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A558" s="5">
         <v>44643</v>
       </c>
@@ -66530,7 +66524,7 @@
         <v>6793</v>
       </c>
     </row>
-    <row r="559" spans="1:13">
+    <row r="559" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A559" s="5">
         <v>44650</v>
       </c>
@@ -66571,7 +66565,7 @@
         <v>6680</v>
       </c>
     </row>
-    <row r="560" spans="1:13">
+    <row r="560" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A560" s="5">
         <v>44657</v>
       </c>
@@ -66612,7 +66606,7 @@
         <v>6903</v>
       </c>
     </row>
-    <row r="561" spans="1:13">
+    <row r="561" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A561" s="5">
         <v>44664</v>
       </c>
@@ -66653,7 +66647,7 @@
         <v>6929</v>
       </c>
     </row>
-    <row r="562" spans="1:13">
+    <row r="562" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A562" s="5">
         <v>44671</v>
       </c>
@@ -66694,7 +66688,7 @@
         <v>6934</v>
       </c>
     </row>
-    <row r="563" spans="1:13">
+    <row r="563" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A563" s="5">
         <v>44678</v>
       </c>
@@ -66735,7 +66729,7 @@
         <v>6940</v>
       </c>
     </row>
-    <row r="564" spans="1:13">
+    <row r="564" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A564" s="5">
         <v>44685</v>
       </c>
@@ -66776,7 +66770,7 @@
         <v>7212</v>
       </c>
     </row>
-    <row r="565" spans="1:13">
+    <row r="565" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A565" s="5">
         <v>44692</v>
       </c>
@@ -66817,7 +66811,7 @@
         <v>7201</v>
       </c>
     </row>
-    <row r="566" spans="1:13">
+    <row r="566" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A566" s="5">
         <v>44699</v>
       </c>
@@ -66858,7 +66852,7 @@
         <v>7189</v>
       </c>
     </row>
-    <row r="567" spans="1:13">
+    <row r="567" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A567" s="5">
         <v>44706</v>
       </c>
@@ -66899,7 +66893,7 @@
         <v>7186</v>
       </c>
     </row>
-    <row r="568" spans="1:13">
+    <row r="568" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A568" s="5">
         <v>44713</v>
       </c>
@@ -66940,7 +66934,7 @@
         <v>7186</v>
       </c>
     </row>
-    <row r="569" spans="1:13">
+    <row r="569" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A569" s="5">
         <v>44720</v>
       </c>
@@ -66981,7 +66975,7 @@
         <v>7100</v>
       </c>
     </row>
-    <row r="570" spans="1:13">
+    <row r="570" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A570" s="5">
         <v>44727</v>
       </c>
@@ -67022,7 +67016,7 @@
         <v>6938</v>
       </c>
     </row>
-    <row r="571" spans="1:13">
+    <row r="571" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A571" s="5">
         <v>44734</v>
       </c>
@@ -67063,7 +67057,7 @@
         <v>6849</v>
       </c>
     </row>
-    <row r="572" spans="1:13">
+    <row r="572" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A572" s="5">
         <v>44741</v>
       </c>
@@ -67104,7 +67098,7 @@
         <v>6783</v>
       </c>
     </row>
-    <row r="573" spans="1:13">
+    <row r="573" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A573" s="5">
         <v>44748</v>
       </c>
@@ -67145,7 +67139,7 @@
         <v>6801</v>
       </c>
     </row>
-    <row r="574" spans="1:13">
+    <row r="574" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A574" s="5">
         <v>44755</v>
       </c>
@@ -67186,7 +67180,7 @@
         <v>6929</v>
       </c>
     </row>
-    <row r="575" spans="1:13">
+    <row r="575" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A575" s="5">
         <v>44762</v>
       </c>
@@ -67227,7 +67221,7 @@
         <v>6926</v>
       </c>
     </row>
-    <row r="576" spans="1:13">
+    <row r="576" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A576" s="5">
         <v>44769</v>
       </c>
@@ -67268,7 +67262,7 @@
         <v>6921</v>
       </c>
     </row>
-    <row r="577" spans="1:13">
+    <row r="577" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A577" s="5">
         <v>44776</v>
       </c>
@@ -67309,7 +67303,7 @@
         <v>6939</v>
       </c>
     </row>
-    <row r="578" spans="1:13">
+    <row r="578" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A578" s="5">
         <v>44783</v>
       </c>
@@ -67350,7 +67344,7 @@
         <v>6945</v>
       </c>
     </row>
-    <row r="579" spans="1:13">
+    <row r="579" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A579" s="5">
         <v>44790</v>
       </c>
@@ -67391,7 +67385,7 @@
         <v>6936</v>
       </c>
     </row>
-    <row r="580" spans="1:13">
+    <row r="580" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A580" s="5">
         <v>44797</v>
       </c>
@@ -67432,7 +67426,7 @@
         <v>6922</v>
       </c>
     </row>
-    <row r="581" spans="1:13">
+    <row r="581" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A581" s="5">
         <v>44804</v>
       </c>
@@ -67473,7 +67467,7 @@
         <v>6839</v>
       </c>
     </row>
-    <row r="582" spans="1:13">
+    <row r="582" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A582" s="5">
         <v>44811</v>
       </c>
@@ -67514,7 +67508,7 @@
         <v>6688</v>
       </c>
     </row>
-    <row r="583" spans="1:13">
+    <row r="583" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A583" s="5">
         <v>44818</v>
       </c>
@@ -67555,7 +67549,7 @@
         <v>6607</v>
       </c>
     </row>
-    <row r="584" spans="1:13">
+    <row r="584" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A584" s="5">
         <v>44825</v>
       </c>
@@ -67596,7 +67590,7 @@
         <v>6737</v>
       </c>
     </row>
-    <row r="585" spans="1:13">
+    <row r="585" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A585" s="5">
         <v>44832</v>
       </c>
@@ -67637,7 +67631,7 @@
         <v>7038</v>
       </c>
     </row>
-    <row r="586" spans="1:13">
+    <row r="586" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A586" s="5">
         <v>44839</v>
       </c>
@@ -67678,7 +67672,7 @@
         <v>7252</v>
       </c>
     </row>
-    <row r="587" spans="1:13">
+    <row r="587" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A587" s="5">
         <v>44846</v>
       </c>
@@ -67719,7 +67713,7 @@
         <v>7295</v>
       </c>
     </row>
-    <row r="588" spans="1:13">
+    <row r="588" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A588" s="5">
         <v>44853</v>
       </c>
@@ -67760,7 +67754,7 @@
         <v>7264</v>
       </c>
     </row>
-    <row r="589" spans="1:13">
+    <row r="589" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A589" s="5">
         <v>44860</v>
       </c>
@@ -67801,7 +67795,7 @@
         <v>7284</v>
       </c>
     </row>
-    <row r="590" spans="1:13">
+    <row r="590" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A590" s="5">
         <v>44867</v>
       </c>
@@ -67842,7 +67836,7 @@
         <v>7426</v>
       </c>
     </row>
-    <row r="591" spans="1:13">
+    <row r="591" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A591" s="5">
         <v>44874</v>
       </c>
@@ -67883,7 +67877,7 @@
         <v>7336</v>
       </c>
     </row>
-    <row r="592" spans="1:13">
+    <row r="592" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A592" s="5">
         <v>44881</v>
       </c>
@@ -67924,7 +67918,7 @@
         <v>7363</v>
       </c>
     </row>
-    <row r="593" spans="1:13">
+    <row r="593" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A593" s="5">
         <v>44888</v>
       </c>
@@ -67965,7 +67959,7 @@
         <v>7224</v>
       </c>
     </row>
-    <row r="594" spans="1:13">
+    <row r="594" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A594" s="5">
         <v>44895</v>
       </c>
@@ -68006,7 +68000,7 @@
         <v>7240</v>
       </c>
     </row>
-    <row r="595" spans="1:13">
+    <row r="595" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A595" s="5">
         <v>44902</v>
       </c>
@@ -68047,7 +68041,7 @@
         <v>7151</v>
       </c>
     </row>
-    <row r="596" spans="1:13">
+    <row r="596" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A596" s="5">
         <v>44909</v>
       </c>
@@ -68088,7 +68082,7 @@
         <v>7050</v>
       </c>
     </row>
-    <row r="597" spans="1:13">
+    <row r="597" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A597" s="5">
         <v>44916</v>
       </c>
@@ -68129,7 +68123,7 @@
         <v>6989</v>
       </c>
     </row>
-    <row r="598" spans="1:13">
+    <row r="598" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A598" s="5">
         <v>44930</v>
       </c>
@@ -68170,7 +68164,7 @@
         <v>6589</v>
       </c>
     </row>
-    <row r="599" spans="1:13">
+    <row r="599" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A599" s="5">
         <v>44937</v>
       </c>
@@ -68211,7 +68205,7 @@
         <v>6363</v>
       </c>
     </row>
-    <row r="600" spans="1:13">
+    <row r="600" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A600" s="5">
         <v>44944</v>
       </c>
@@ -68252,7 +68246,7 @@
         <v>6296</v>
       </c>
     </row>
-    <row r="601" spans="1:13">
+    <row r="601" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A601" s="5">
         <v>44951</v>
       </c>
@@ -68293,7 +68287,7 @@
         <v>6322</v>
       </c>
     </row>
-    <row r="602" spans="1:13">
+    <row r="602" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A602" s="5">
         <v>44958</v>
       </c>
@@ -68334,7 +68328,7 @@
         <v>6262</v>
       </c>
     </row>
-    <row r="603" spans="1:13">
+    <row r="603" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A603" s="5">
         <v>44965</v>
       </c>
@@ -68375,7 +68369,7 @@
         <v>6010</v>
       </c>
     </row>
-    <row r="604" spans="1:13">
+    <row r="604" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A604" s="5">
         <v>44972</v>
       </c>
@@ -68416,7 +68410,7 @@
         <v>5675</v>
       </c>
     </row>
-    <row r="605" spans="1:13">
+    <row r="605" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A605" s="5">
         <v>44979</v>
       </c>
@@ -68457,7 +68451,7 @@
         <v>5640</v>
       </c>
     </row>
-    <row r="606" spans="1:13">
+    <row r="606" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A606" s="5">
         <v>44986</v>
       </c>
@@ -68498,7 +68492,7 @@
         <v>5573</v>
       </c>
     </row>
-    <row r="607" spans="1:13">
+    <row r="607" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A607" s="5">
         <v>44993</v>
       </c>
@@ -68539,7 +68533,7 @@
         <v>5377</v>
       </c>
     </row>
-    <row r="608" spans="1:13">
+    <row r="608" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A608" s="5">
         <v>45000</v>
       </c>
@@ -68580,7 +68574,7 @@
         <v>5326</v>
       </c>
     </row>
-    <row r="609" spans="1:13">
+    <row r="609" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A609" s="5">
         <v>45007</v>
       </c>
@@ -68621,7 +68615,7 @@
         <v>5061</v>
       </c>
     </row>
-    <row r="610" spans="1:13">
+    <row r="610" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A610" s="5">
         <v>45014</v>
       </c>
@@ -68662,7 +68656,7 @@
         <v>4978</v>
       </c>
     </row>
-    <row r="611" spans="1:13">
+    <row r="611" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A611" s="5">
         <v>45021</v>
       </c>
@@ -68703,7 +68697,7 @@
         <v>4936</v>
       </c>
     </row>
-    <row r="612" spans="1:13">
+    <row r="612" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A612" s="5">
         <v>45028</v>
       </c>
@@ -68744,7 +68738,7 @@
         <v>4919</v>
       </c>
     </row>
-    <row r="613" spans="1:13">
+    <row r="613" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A613" s="5">
         <v>45035</v>
       </c>
@@ -68785,7 +68779,7 @@
         <v>4881</v>
       </c>
     </row>
-    <row r="614" spans="1:13">
+    <row r="614" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A614" s="5">
         <v>45042</v>
       </c>
@@ -68826,7 +68820,7 @@
         <v>4806</v>
       </c>
     </row>
-    <row r="615" spans="1:13">
+    <row r="615" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A615" s="5">
         <v>45049</v>
       </c>
@@ -68867,7 +68861,7 @@
         <v>4783</v>
       </c>
     </row>
-    <row r="616" spans="1:13">
+    <row r="616" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A616" s="5">
         <v>45056</v>
       </c>
@@ -68908,7 +68902,7 @@
         <v>4530</v>
       </c>
     </row>
-    <row r="617" spans="1:13">
+    <row r="617" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A617" s="5">
         <v>45063</v>
       </c>
@@ -68949,7 +68943,7 @@
         <v>4434</v>
       </c>
     </row>
-    <row r="618" spans="1:13">
+    <row r="618" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A618" s="5">
         <v>45070</v>
       </c>
@@ -68990,7 +68984,7 @@
         <v>3969</v>
       </c>
     </row>
-    <row r="619" spans="1:13">
+    <row r="619" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A619" s="5">
         <v>45077</v>
       </c>
@@ -69031,7 +69025,7 @@
         <v>3714</v>
       </c>
     </row>
-    <row r="620" spans="1:13">
+    <row r="620" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A620" s="5">
         <v>45084</v>
       </c>
@@ -69072,7 +69066,7 @@
         <v>3375</v>
       </c>
     </row>
-    <row r="621" spans="1:13">
+    <row r="621" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A621" s="5">
         <v>45091</v>
       </c>
@@ -69113,7 +69107,7 @@
         <v>3195</v>
       </c>
     </row>
-    <row r="622" spans="1:13">
+    <row r="622" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A622" s="5">
         <v>45098</v>
       </c>
@@ -69154,7 +69148,7 @@
         <v>3226</v>
       </c>
     </row>
-    <row r="623" spans="1:13">
+    <row r="623" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A623" s="5">
         <v>45105</v>
       </c>
@@ -69195,7 +69189,7 @@
         <v>2670</v>
       </c>
     </row>
-    <row r="624" spans="1:13">
+    <row r="624" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A624" s="5">
         <v>45112</v>
       </c>
@@ -69236,7 +69230,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="625" spans="1:13">
+    <row r="625" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A625" s="5">
         <v>45119</v>
       </c>
@@ -69277,7 +69271,7 @@
         <v>1769</v>
       </c>
     </row>
-    <row r="626" spans="1:13">
+    <row r="626" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A626" s="5">
         <v>45126</v>
       </c>
@@ -69318,7 +69312,7 @@
         <v>1640</v>
       </c>
     </row>
-    <row r="627" spans="1:13">
+    <row r="627" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A627" s="5">
         <v>45133</v>
       </c>
@@ -69359,7 +69353,7 @@
         <v>1590</v>
       </c>
     </row>
-    <row r="628" spans="1:13">
+    <row r="628" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A628" s="5">
         <v>45140</v>
       </c>
@@ -69400,7 +69394,7 @@
         <v>1587</v>
       </c>
     </row>
-    <row r="629" spans="1:13">
+    <row r="629" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A629" s="5">
         <v>45147</v>
       </c>
@@ -69441,7 +69435,7 @@
         <v>1593</v>
       </c>
     </row>
-    <row r="630" spans="1:13">
+    <row r="630" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A630" s="5">
         <v>45154</v>
       </c>
@@ -69482,7 +69476,7 @@
         <v>1577</v>
       </c>
     </row>
-    <row r="631" spans="1:13">
+    <row r="631" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A631" s="5">
         <v>45161</v>
       </c>
@@ -69523,7 +69517,7 @@
         <v>1585</v>
       </c>
     </row>
-    <row r="632" spans="1:13">
+    <row r="632" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A632" s="5">
         <v>45168</v>
       </c>
@@ -69564,7 +69558,7 @@
         <v>1562</v>
       </c>
     </row>
-    <row r="633" spans="1:13">
+    <row r="633" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A633" s="5">
         <v>45175</v>
       </c>
@@ -69605,7 +69599,7 @@
         <v>1561</v>
       </c>
     </row>
-    <row r="634" spans="1:13">
+    <row r="634" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A634" s="5">
         <v>45182</v>
       </c>
@@ -69646,7 +69640,7 @@
         <v>1565</v>
       </c>
     </row>
-    <row r="635" spans="1:13">
+    <row r="635" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A635" s="5">
         <v>45189</v>
       </c>
@@ -69687,7 +69681,7 @@
         <v>1534</v>
       </c>
     </row>
-    <row r="636" spans="1:13">
+    <row r="636" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A636" s="5">
         <v>45196</v>
       </c>
@@ -69728,7 +69722,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="637" spans="1:13">
+    <row r="637" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A637" s="5">
         <v>45203</v>
       </c>
@@ -69769,7 +69763,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="638" spans="1:13">
+    <row r="638" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A638" s="5">
         <v>45210</v>
       </c>
@@ -69810,7 +69804,7 @@
         <v>1535</v>
       </c>
     </row>
-    <row r="639" spans="1:13">
+    <row r="639" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A639" s="5">
         <v>45217</v>
       </c>
@@ -69851,7 +69845,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="640" spans="1:13">
+    <row r="640" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A640" s="5">
         <v>45224</v>
       </c>
@@ -69892,7 +69886,7 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="641" spans="1:13">
+    <row r="641" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A641" s="5">
         <v>45231</v>
       </c>
@@ -69933,7 +69927,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="642" spans="1:13">
+    <row r="642" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A642" s="5">
         <v>45238</v>
       </c>
@@ -69974,7 +69968,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="643" spans="1:13">
+    <row r="643" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A643" s="5">
         <v>45245</v>
       </c>
@@ -70015,7 +70009,7 @@
         <v>1510</v>
       </c>
     </row>
-    <row r="644" spans="1:13">
+    <row r="644" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A644" s="5">
         <v>45252</v>
       </c>
@@ -70056,7 +70050,7 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="645" spans="1:13">
+    <row r="645" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A645" s="5">
         <v>45259</v>
       </c>
@@ -70097,7 +70091,7 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="646" spans="1:13">
+    <row r="646" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A646" s="5">
         <v>45266</v>
       </c>
@@ -70138,7 +70132,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="647" spans="1:13">
+    <row r="647" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A647" s="5">
         <v>45273</v>
       </c>
@@ -70179,7 +70173,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="648" spans="1:13">
+    <row r="648" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A648" s="5">
         <v>45280</v>
       </c>
@@ -70220,7 +70214,7 @@
         <v>1480</v>
       </c>
     </row>
-    <row r="649" spans="1:13">
+    <row r="649" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A649" s="5">
         <v>45294</v>
       </c>
@@ -70261,7 +70255,7 @@
         <v>1503</v>
       </c>
     </row>
-    <row r="650" spans="1:13">
+    <row r="650" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A650" s="5">
         <v>45301</v>
       </c>
@@ -70302,7 +70296,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="651" spans="1:13">
+    <row r="651" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A651" s="5">
         <v>45308</v>
       </c>
@@ -70343,7 +70337,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="652" spans="1:13">
+    <row r="652" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A652" s="5">
         <v>45315</v>
       </c>
@@ -70384,7 +70378,7 @@
         <v>1576</v>
       </c>
     </row>
-    <row r="653" spans="1:13">
+    <row r="653" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A653" s="5">
         <v>45322</v>
       </c>
@@ -70425,7 +70419,7 @@
         <v>1589</v>
       </c>
     </row>
-    <row r="654" spans="1:13">
+    <row r="654" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A654" s="5">
         <v>45329</v>
       </c>
@@ -70466,7 +70460,7 @@
         <v>1978</v>
       </c>
     </row>
-    <row r="655" spans="1:13">
+    <row r="655" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A655" s="5">
         <v>45336</v>
       </c>
@@ -70507,7 +70501,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="656" spans="1:13">
+    <row r="656" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A656" s="5">
         <v>45343</v>
       </c>
@@ -70548,7 +70542,7 @@
         <v>2204</v>
       </c>
     </row>
-    <row r="657" spans="1:13">
+    <row r="657" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A657" s="5">
         <v>45350</v>
       </c>
@@ -70589,7 +70583,7 @@
         <v>2220</v>
       </c>
     </row>
-    <row r="658" spans="1:13">
+    <row r="658" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A658" s="5">
         <v>45357</v>
       </c>
@@ -70630,7 +70624,7 @@
         <v>2192</v>
       </c>
     </row>
-    <row r="659" spans="1:13">
+    <row r="659" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A659" s="5">
         <v>45364</v>
       </c>
@@ -70671,7 +70665,7 @@
         <v>2242</v>
       </c>
     </row>
-    <row r="660" spans="1:13">
+    <row r="660" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A660" s="5">
         <v>45371</v>
       </c>
@@ -70712,7 +70706,7 @@
         <v>2281</v>
       </c>
     </row>
-    <row r="661" spans="1:13">
+    <row r="661" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A661" s="5">
         <v>45378</v>
       </c>
@@ -70753,7 +70747,7 @@
         <v>2261</v>
       </c>
     </row>
-    <row r="662" spans="1:13">
+    <row r="662" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A662" s="5">
         <v>45385</v>
       </c>
@@ -70794,7 +70788,7 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="663" spans="1:13">
+    <row r="663" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A663" s="5">
         <v>45392</v>
       </c>
@@ -70835,7 +70829,7 @@
         <v>2224</v>
       </c>
     </row>
-    <row r="664" spans="1:13">
+    <row r="664" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A664" s="5">
         <v>45399</v>
       </c>
@@ -70876,7 +70870,7 @@
         <v>2291</v>
       </c>
     </row>
-    <row r="665" spans="1:13">
+    <row r="665" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A665" s="5">
         <v>45406</v>
       </c>
@@ -70917,7 +70911,7 @@
         <v>2214</v>
       </c>
     </row>
-    <row r="666" spans="1:13">
+    <row r="666" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A666" s="5">
         <v>45413</v>
       </c>
@@ -70958,7 +70952,7 @@
         <v>2210</v>
       </c>
     </row>
-    <row r="667" spans="1:13">
+    <row r="667" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A667" s="5">
         <v>45420</v>
       </c>
@@ -70999,7 +70993,7 @@
         <v>2160</v>
       </c>
     </row>
-    <row r="668" spans="1:13">
+    <row r="668" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A668" s="5">
         <v>45427</v>
       </c>
@@ -71040,7 +71034,7 @@
         <v>2209</v>
       </c>
     </row>
-    <row r="669" spans="1:13">
+    <row r="669" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A669" s="5">
         <v>45434</v>
       </c>
@@ -71081,7 +71075,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="670" spans="1:13">
+    <row r="670" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A670" s="5">
         <v>45441</v>
       </c>
@@ -71122,7 +71116,7 @@
         <v>2222</v>
       </c>
     </row>
-    <row r="671" spans="1:13">
+    <row r="671" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A671" s="5">
         <v>45448</v>
       </c>
@@ -71163,7 +71157,7 @@
         <v>2136</v>
       </c>
     </row>
-    <row r="672" spans="1:13">
+    <row r="672" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A672" s="5">
         <v>45455</v>
       </c>
@@ -71204,7 +71198,7 @@
         <v>2118</v>
       </c>
     </row>
-    <row r="673" spans="1:13">
+    <row r="673" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A673" s="5">
         <v>45462</v>
       </c>
@@ -71245,7 +71239,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="674" spans="1:13">
+    <row r="674" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A674" s="5">
         <v>45469</v>
       </c>
@@ -71286,7 +71280,7 @@
         <v>2044</v>
       </c>
     </row>
-    <row r="675" spans="1:13">
+    <row r="675" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A675" s="5">
         <v>45476</v>
       </c>
@@ -71327,7 +71321,7 @@
         <v>1977</v>
       </c>
     </row>
-    <row r="676" spans="1:13">
+    <row r="676" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A676" s="5">
         <v>45483</v>
       </c>
@@ -71368,7 +71362,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="677" spans="1:13">
+    <row r="677" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A677" s="5">
         <v>45490</v>
       </c>
@@ -71409,7 +71403,7 @@
         <v>1943</v>
       </c>
     </row>
-    <row r="678" spans="1:13">
+    <row r="678" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A678" s="5">
         <v>45497</v>
       </c>
@@ -71450,7 +71444,7 @@
         <v>1954</v>
       </c>
     </row>
-    <row r="679" spans="1:13">
+    <row r="679" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A679" s="5">
         <v>45504</v>
       </c>
@@ -71491,7 +71485,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="680" spans="1:13">
+    <row r="680" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A680" s="5">
         <v>45511</v>
       </c>
@@ -71532,7 +71526,7 @@
         <v>1967</v>
       </c>
     </row>
-    <row r="681" spans="1:13">
+    <row r="681" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A681" s="5">
         <v>45518</v>
       </c>
@@ -71573,7 +71567,7 @@
         <v>1961</v>
       </c>
     </row>
-    <row r="682" spans="1:13">
+    <row r="682" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A682" s="5">
         <v>45525</v>
       </c>
@@ -71614,7 +71608,7 @@
         <v>1934</v>
       </c>
     </row>
-    <row r="683" spans="1:13">
+    <row r="683" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A683" s="5">
         <v>45532</v>
       </c>
@@ -71655,7 +71649,7 @@
         <v>1908</v>
       </c>
     </row>
-    <row r="684" spans="1:13">
+    <row r="684" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A684" s="5">
         <v>45539</v>
       </c>
@@ -71696,7 +71690,7 @@
         <v>2212</v>
       </c>
     </row>
-    <row r="685" spans="1:13">
+    <row r="685" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A685" s="5">
         <v>45546</v>
       </c>
@@ -71737,7 +71731,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="686" spans="1:13">
+    <row r="686" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A686" s="5">
         <v>45553</v>
       </c>
@@ -71778,7 +71772,7 @@
         <v>2056</v>
       </c>
     </row>
-    <row r="687" spans="1:13">
+    <row r="687" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A687" s="5">
         <v>45560</v>
       </c>
@@ -71819,7 +71813,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="688" spans="1:13">
+    <row r="688" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A688" s="5">
         <v>45567</v>
       </c>
@@ -71860,7 +71854,7 @@
         <v>2061</v>
       </c>
     </row>
-    <row r="689" spans="1:13">
+    <row r="689" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A689" s="5">
         <v>45574</v>
       </c>
@@ -71901,7 +71895,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="690" spans="1:13">
+    <row r="690" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A690" s="5">
         <v>45581</v>
       </c>
@@ -71942,7 +71936,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="691" spans="1:13">
+    <row r="691" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A691" s="5">
         <v>45588</v>
       </c>
@@ -71983,7 +71977,7 @@
         <v>2663</v>
       </c>
     </row>
-    <row r="692" spans="1:13">
+    <row r="692" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A692" s="5">
         <v>45595</v>
       </c>
@@ -72024,7 +72018,7 @@
         <v>2664</v>
       </c>
     </row>
-    <row r="693" spans="1:13">
+    <row r="693" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A693" s="5">
         <v>45602</v>
       </c>
@@ -72065,7 +72059,7 @@
         <v>2624</v>
       </c>
     </row>
-    <row r="694" spans="1:13">
+    <row r="694" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A694" s="5">
         <v>45609</v>
       </c>
@@ -72106,7 +72100,7 @@
         <v>2658</v>
       </c>
     </row>
-    <row r="695" spans="1:13">
+    <row r="695" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A695" s="5">
         <v>45616</v>
       </c>
@@ -72147,7 +72141,7 @@
         <v>2672</v>
       </c>
     </row>
-    <row r="696" spans="1:13">
+    <row r="696" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A696" s="5">
         <v>45623</v>
       </c>
@@ -72188,7 +72182,7 @@
         <v>2665</v>
       </c>
     </row>
-    <row r="697" spans="1:13">
+    <row r="697" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A697" s="5">
         <v>45630</v>
       </c>
@@ -72229,7 +72223,7 @@
         <v>2649</v>
       </c>
     </row>
-    <row r="698" spans="1:13">
+    <row r="698" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A698" s="5">
         <v>45637</v>
       </c>
@@ -72270,7 +72264,7 @@
         <v>2622</v>
       </c>
     </row>
-    <row r="699" spans="1:13">
+    <row r="699" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A699" s="5">
         <v>45644</v>
       </c>
@@ -72311,7 +72305,7 @@
         <v>2713</v>
       </c>
     </row>
-    <row r="700" spans="1:13">
+    <row r="700" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A700" s="5">
         <v>45658</v>
       </c>
@@ -72352,7 +72346,7 @@
         <v>2720</v>
       </c>
     </row>
-    <row r="701" spans="1:13">
+    <row r="701" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A701" s="5">
         <v>45665</v>
       </c>
@@ -72393,7 +72387,7 @@
         <v>2698</v>
       </c>
     </row>
-    <row r="702" spans="1:13">
+    <row r="702" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A702" s="5">
         <v>45672</v>
       </c>
@@ -72434,7 +72428,7 @@
         <v>2798</v>
       </c>
     </row>
-    <row r="703" spans="1:13">
+    <row r="703" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A703" s="5">
         <v>45679</v>
       </c>
@@ -72475,7 +72469,7 @@
         <v>2778</v>
       </c>
     </row>
-    <row r="704" spans="1:13">
+    <row r="704" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A704" s="5">
         <v>45686</v>
       </c>
@@ -72516,7 +72510,7 @@
         <v>2732</v>
       </c>
     </row>
-    <row r="705" spans="1:13">
+    <row r="705" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A705" s="5">
         <v>45693</v>
       </c>
@@ -72557,7 +72551,7 @@
         <v>2469</v>
       </c>
     </row>
-    <row r="706" spans="1:13">
+    <row r="706" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A706" s="5">
         <v>45700</v>
       </c>
@@ -72598,7 +72592,7 @@
         <v>2463</v>
       </c>
     </row>
-    <row r="707" spans="1:13">
+    <row r="707" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A707" s="5">
         <v>45707</v>
       </c>
@@ -72639,7 +72633,7 @@
         <v>2394</v>
       </c>
     </row>
-    <row r="708" spans="1:13">
+    <row r="708" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A708" s="5">
         <v>45714</v>
       </c>
@@ -72680,7 +72674,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="709" spans="1:13">
+    <row r="709" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A709" s="5">
         <v>45721</v>
       </c>
@@ -72721,7 +72715,7 @@
         <v>2359</v>
       </c>
     </row>
-    <row r="710" spans="1:13">
+    <row r="710" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A710" s="5">
         <v>45728</v>
       </c>
@@ -72762,7 +72756,7 @@
         <v>2373</v>
       </c>
     </row>
-    <row r="711" spans="1:13">
+    <row r="711" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A711" s="5">
         <v>45735</v>
       </c>
@@ -72803,7 +72797,7 @@
         <v>2316</v>
       </c>
     </row>
-    <row r="712" spans="1:13">
+    <row r="712" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A712" s="5">
         <v>45742</v>
       </c>
@@ -72844,7 +72838,7 @@
         <v>2162</v>
       </c>
     </row>
-    <row r="713" spans="1:13">
+    <row r="713" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A713" s="5">
         <v>45749</v>
       </c>
@@ -72885,7 +72879,7 @@
         <v>2124</v>
       </c>
     </row>
-    <row r="714" spans="1:13">
+    <row r="714" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A714" s="5">
         <v>45756</v>
       </c>
@@ -72926,7 +72920,7 @@
         <v>2153</v>
       </c>
     </row>
-    <row r="715" spans="1:13">
+    <row r="715" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A715" s="5">
         <v>45763</v>
       </c>
@@ -72967,7 +72961,7 @@
         <v>2129</v>
       </c>
     </row>
-    <row r="716" spans="1:13">
+    <row r="716" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A716" s="5">
         <v>45770</v>
       </c>
@@ -73008,7 +73002,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="717" spans="1:13">
+    <row r="717" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A717" s="5">
         <v>45777</v>
       </c>
@@ -73049,7 +73043,7 @@
         <v>2041</v>
       </c>
     </row>
-    <row r="718" spans="1:13">
+    <row r="718" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A718" s="5">
         <v>45784</v>
       </c>
@@ -73090,7 +73084,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="719" spans="1:13">
+    <row r="719" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A719" s="5">
         <v>45791</v>
       </c>
@@ -73131,7 +73125,7 @@
         <v>1961</v>
       </c>
     </row>
-    <row r="720" spans="1:13">
+    <row r="720" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A720" s="5">
         <v>45798</v>
       </c>
@@ -73172,7 +73166,7 @@
         <v>1952</v>
       </c>
     </row>
-    <row r="721" spans="1:13">
+    <row r="721" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A721" s="5">
         <v>45805</v>
       </c>
@@ -73213,7 +73207,7 @@
         <v>1939</v>
       </c>
     </row>
-    <row r="722" spans="1:13">
+    <row r="722" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A722" s="5">
         <v>45812</v>
       </c>
@@ -73254,7 +73248,7 @@
         <v>1977</v>
       </c>
     </row>
-    <row r="723" spans="1:13">
+    <row r="723" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A723" s="5">
         <v>45819</v>
       </c>
@@ -73295,7 +73289,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="724" spans="1:13">
+    <row r="724" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A724" s="5">
         <v>45826</v>
       </c>
@@ -73336,7 +73330,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="725" spans="1:13">
+    <row r="725" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A725" s="5">
         <v>45833</v>
       </c>
@@ -73377,7 +73371,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="726" spans="1:13">
+    <row r="726" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A726" s="5">
         <v>45840</v>
       </c>
@@ -73418,7 +73412,7 @@
         <v>2119</v>
       </c>
     </row>
-    <row r="727" spans="1:13">
+    <row r="727" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A727" s="5">
         <v>45847</v>
       </c>
@@ -73459,7 +73453,7 @@
         <v>1990</v>
       </c>
     </row>
-    <row r="728" spans="1:13">
+    <row r="728" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A728" s="5">
         <v>45854</v>
       </c>
@@ -73500,7 +73494,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="729" spans="1:13">
+    <row r="729" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A729" s="5">
         <v>45861</v>
       </c>
@@ -73541,7 +73535,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="730" spans="1:13">
+    <row r="730" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A730" s="5">
         <v>45868</v>
       </c>
@@ -73582,7 +73576,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="731" spans="1:13">
+    <row r="731" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A731" s="5">
         <v>45875</v>
       </c>
@@ -73623,7 +73617,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="732" spans="1:13">
+    <row r="732" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A732" s="5">
         <v>45882</v>
       </c>
@@ -73664,7 +73658,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="733" spans="1:13">
+    <row r="733" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A733" s="5">
         <v>45889</v>
       </c>
@@ -73705,7 +73699,7 @@
         <v>1951</v>
       </c>
     </row>
-    <row r="734" spans="1:13">
+    <row r="734" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A734" s="5">
         <v>45896</v>
       </c>
@@ -73746,7 +73740,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="735" spans="1:13">
+    <row r="735" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A735" s="5">
         <v>45903</v>
       </c>
@@ -73787,7 +73781,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="736" spans="1:13">
+    <row r="736" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A736" s="5">
         <v>45910</v>
       </c>
@@ -73828,7 +73822,7 @@
         <v>1938</v>
       </c>
     </row>
-    <row r="737" spans="1:13">
+    <row r="737" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A737" s="5">
         <v>45917</v>
       </c>
@@ -73869,7 +73863,7 @@
         <v>1926</v>
       </c>
     </row>
-    <row r="738" spans="1:13">
+    <row r="738" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A738" s="5">
         <v>45924</v>
       </c>
@@ -73910,7 +73904,7 @@
         <v>1819</v>
       </c>
     </row>
-    <row r="739" spans="1:13">
+    <row r="739" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A739" s="5">
         <v>45931</v>
       </c>
@@ -73951,7 +73945,7 @@
         <v>1796</v>
       </c>
     </row>
-    <row r="740" spans="1:13">
+    <row r="740" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A740" s="5">
         <v>45938</v>
       </c>
@@ -73992,7 +73986,7 @@
         <v>1759</v>
       </c>
     </row>
-    <row r="741" spans="1:13">
+    <row r="741" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A741" s="5">
         <v>45945</v>
       </c>
@@ -74033,7 +74027,7 @@
         <v>1797</v>
       </c>
     </row>
-    <row r="742" spans="1:13">
+    <row r="742" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A742" s="5">
         <v>45952</v>
       </c>
@@ -74074,7 +74068,7 @@
         <v>1720</v>
       </c>
     </row>
-    <row r="743" spans="1:13">
+    <row r="743" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A743" s="5">
         <v>45959</v>
       </c>
@@ -74115,7 +74109,7 @@
         <v>1678</v>
       </c>
     </row>
-    <row r="744" spans="1:13">
+    <row r="744" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A744" s="5">
         <v>45966</v>
       </c>
@@ -74156,7 +74150,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="745" spans="1:13">
+    <row r="745" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A745" s="5">
         <v>45973</v>
       </c>
@@ -74197,7 +74191,7 @@
         <v>1633</v>
       </c>
     </row>
-    <row r="746" spans="1:13">
+    <row r="746" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A746" s="5">
         <v>45980</v>
       </c>
@@ -74238,7 +74232,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="747" spans="1:13">
+    <row r="747" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A747" s="5">
         <v>45987</v>
       </c>
@@ -74279,7 +74273,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="748" spans="1:13">
+    <row r="748" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A748" s="5">
         <v>45994</v>
       </c>
@@ -74320,7 +74314,7 @@
         <v>1632</v>
       </c>
     </row>
-    <row r="749" spans="1:13">
+    <row r="749" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A749" s="5">
         <v>46001</v>
       </c>
@@ -74361,7 +74355,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="750" spans="1:13">
+    <row r="750" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A750" s="5">
         <v>46008</v>
       </c>
@@ -74402,7 +74396,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="751" spans="1:13">
+    <row r="751" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A751" s="5">
         <v>46015</v>
       </c>
@@ -74443,7 +74437,7 @@
         <v>1652</v>
       </c>
     </row>
-    <row r="752" spans="1:13">
+    <row r="752" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A752" s="5">
         <v>46022</v>
       </c>
@@ -74484,7 +74478,7 @@
         <v>1652</v>
       </c>
     </row>
-    <row r="753" spans="1:13">
+    <row r="753" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A753" s="5">
         <v>46029</v>
       </c>
@@ -74525,7 +74519,7 @@
         <v>1685</v>
       </c>
     </row>
-    <row r="754" spans="1:13">
+    <row r="754" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A754" s="5">
         <v>46036</v>
       </c>
@@ -74566,7 +74560,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="755" spans="1:13">
+    <row r="755" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A755" s="5">
         <v>46043</v>
       </c>
@@ -74607,7 +74601,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="756" spans="1:13">
+    <row r="756" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A756" s="5">
         <v>46050</v>
       </c>
@@ -74648,7 +74642,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="757" spans="1:13">
+    <row r="757" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A757" s="5">
         <v>46057</v>
       </c>
@@ -74689,7 +74683,7 @@
         <v>1598</v>
       </c>
     </row>
-    <row r="758" spans="1:13">
+    <row r="758" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A758" s="5">
         <v>46064</v>
       </c>
@@ -74730,7 +74724,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="759" spans="1:13">
+    <row r="759" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A759" s="5">
         <v>46071</v>
       </c>
@@ -74771,7 +74765,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="760" spans="1:13">
+    <row r="760" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A760" s="5">
         <v>46078</v>
       </c>
@@ -74812,7 +74806,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="761" spans="1:13">
+    <row r="761" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A761" s="5">
         <v>46085</v>
       </c>
@@ -74853,7 +74847,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="762" spans="1:13">
+    <row r="762" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A762" s="5">
         <v>46092</v>
       </c>
@@ -74894,7 +74888,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="763" spans="1:13">
+    <row r="763" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A763" s="5">
         <v>46099</v>
       </c>
@@ -74935,7 +74929,7 @@
         <v>1504</v>
       </c>
     </row>
-    <row r="764" spans="1:13">
+    <row r="764" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A764" s="5">
         <v>46106</v>
       </c>
@@ -74976,7 +74970,7 @@
         <v>1542</v>
       </c>
     </row>
-    <row r="765" spans="1:13">
+    <row r="765" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A765" s="5">
         <v>46113</v>
       </c>
@@ -75017,7 +75011,7 @@
         <v>1579</v>
       </c>
     </row>
-    <row r="766" spans="1:13">
+    <row r="766" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A766" s="5">
         <v>46120</v>
       </c>
@@ -75058,7 +75052,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="767" spans="1:13">
+    <row r="767" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A767" s="5">
         <v>46127</v>
       </c>
@@ -75099,7 +75093,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="768" spans="1:13">
+    <row r="768" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A768" s="5">
         <v>46134</v>
       </c>
@@ -75140,7 +75134,7 @@
         <v>2326</v>
       </c>
     </row>
-    <row r="769" spans="1:13">
+    <row r="769" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A769" s="5">
         <v>46141</v>
       </c>
@@ -75181,7 +75175,7 @@
         <v>2327</v>
       </c>
     </row>
-    <row r="770" spans="1:13">
+    <row r="770" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A770" s="5">
         <v>46148</v>
       </c>
@@ -75222,7 +75216,7 @@
         <v>2314</v>
       </c>
     </row>
-    <row r="771" spans="1:13">
+    <row r="771" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A771" s="5">
         <v>46155</v>
       </c>
@@ -75263,7 +75257,7 @@
         <v>2388</v>
       </c>
     </row>
-    <row r="772" spans="1:13">
+    <row r="772" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A772" s="5">
         <v>46162</v>
       </c>
@@ -75304,7 +75298,7 @@
         <v>2453</v>
       </c>
     </row>
-    <row r="773" spans="1:13">
+    <row r="773" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A773" s="5">
         <v>46169</v>
       </c>
@@ -75345,7 +75339,7 @@
         <v>2435</v>
       </c>
     </row>
-    <row r="774" spans="1:13">
+    <row r="774" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A774" s="5">
         <v>46176</v>
       </c>
@@ -75386,7 +75380,7 @@
         <v>2560</v>
       </c>
     </row>
-    <row r="775" spans="1:13">
+    <row r="775" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A775" s="5">
         <v>46183</v>
       </c>
@@ -75427,7 +75421,7 @@
         <v>2508</v>
       </c>
     </row>
-    <row r="776" spans="1:13">
+    <row r="776" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A776" s="5">
         <v>46190</v>
       </c>
@@ -75478,7 +75472,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86BC2DE8-BCE4-43AE-95F3-3DF06CDF8905}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -75489,12 +75483,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C789BCF2-DC16-4FFC-AF71-3351D156D960}">
   <dimension ref="B2:N3"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B2" s="9" t="s">
         <v>9</v>
       </c>
@@ -75513,7 +75507,7 @@
       <c r="M2" s="11"/>
       <c r="N2" s="11"/>
     </row>
-    <row r="3" spans="2:14">
+    <row r="3" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B3" s="9" t="s">
         <v>10</v>
       </c>

--- a/data/freight/world container index.xlsx
+++ b/data/freight/world container index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data/freight/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB082035-55E6-DD49-AE07-0D08ED6A2E59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{564CE1BC-85A0-42EC-8BA2-36559258C54F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22160" yWindow="600" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WCI" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="19">
   <si>
     <t>WCI Composite</t>
   </si>
@@ -112,7 +112,7 @@
     <numFmt numFmtId="165" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -208,9 +208,9 @@
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표 [0]" xfId="2" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -228,7 +228,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2602,6 +2602,9 @@
                 <c:pt idx="774">
                   <c:v>46191</c:v>
                 </c:pt>
+                <c:pt idx="775">
+                  <c:v>46198</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4934,7 +4937,10 @@
                   <c:v>3549.26</c:v>
                 </c:pt>
                 <c:pt idx="774">
-                  <c:v>3969</c:v>
+                  <c:v>3968.87</c:v>
+                </c:pt>
+                <c:pt idx="775">
+                  <c:v>4166</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7304,6 +7310,9 @@
                 <c:pt idx="774">
                   <c:v>46191</c:v>
                 </c:pt>
+                <c:pt idx="775">
+                  <c:v>46198</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9637,6 +9646,9 @@
                 </c:pt>
                 <c:pt idx="774">
                   <c:v>4342</c:v>
+                </c:pt>
+                <c:pt idx="775">
+                  <c:v>4392</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12006,6 +12018,9 @@
                 <c:pt idx="774">
                   <c:v>46191</c:v>
                 </c:pt>
+                <c:pt idx="775">
+                  <c:v>46198</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -14339,6 +14354,9 @@
                 </c:pt>
                 <c:pt idx="774">
                   <c:v>5756</c:v>
+                </c:pt>
+                <c:pt idx="775">
+                  <c:v>5759</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16708,6 +16726,9 @@
                 <c:pt idx="774">
                   <c:v>46191</c:v>
                 </c:pt>
+                <c:pt idx="775">
+                  <c:v>46198</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -19041,6 +19062,9 @@
                 </c:pt>
                 <c:pt idx="774">
                   <c:v>5142</c:v>
+                </c:pt>
+                <c:pt idx="775">
+                  <c:v>5750</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -21410,6 +21434,9 @@
                 <c:pt idx="774">
                   <c:v>46191</c:v>
                 </c:pt>
+                <c:pt idx="775">
+                  <c:v>46198</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -23743,6 +23770,9 @@
                 </c:pt>
                 <c:pt idx="774">
                   <c:v>6769</c:v>
+                </c:pt>
+                <c:pt idx="775">
+                  <c:v>7149</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -26112,6 +26142,9 @@
                 <c:pt idx="774">
                   <c:v>46191</c:v>
                 </c:pt>
+                <c:pt idx="775">
+                  <c:v>46198</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -28445,6 +28478,9 @@
                 </c:pt>
                 <c:pt idx="774">
                   <c:v>643</c:v>
+                </c:pt>
+                <c:pt idx="775">
+                  <c:v>648</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -30816,6 +30852,9 @@
                 <c:pt idx="774">
                   <c:v>46191</c:v>
                 </c:pt>
+                <c:pt idx="775">
+                  <c:v>46198</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -33149,6 +33188,9 @@
                 </c:pt>
                 <c:pt idx="774">
                   <c:v>822</c:v>
+                </c:pt>
+                <c:pt idx="775">
+                  <c:v>828</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -35520,6 +35562,9 @@
                 <c:pt idx="774">
                   <c:v>46191</c:v>
                 </c:pt>
+                <c:pt idx="775">
+                  <c:v>46198</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -37853,6 +37898,9 @@
                 </c:pt>
                 <c:pt idx="774">
                   <c:v>957</c:v>
+                </c:pt>
+                <c:pt idx="775">
+                  <c:v>1011</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -40224,6 +40272,9 @@
                 <c:pt idx="774">
                   <c:v>46191</c:v>
                 </c:pt>
+                <c:pt idx="775">
+                  <c:v>46198</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -42557,6 +42608,9 @@
                 </c:pt>
                 <c:pt idx="774">
                   <c:v>2507</c:v>
+                </c:pt>
+                <c:pt idx="775">
+                  <c:v>2584</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -43634,19 +43688,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M776"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="7.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:M777"/>
+  <sheetFormatPr defaultColWidth="7.44140625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.77734375" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.83203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="13" width="10.5" style="8" customWidth="1"/>
-    <col min="14" max="16384" width="7.5" style="8"/>
+    <col min="5" max="5" width="15.77734375" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="13" width="10.44140625" style="8" customWidth="1"/>
+    <col min="14" max="16384" width="7.44140625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" s="4" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
@@ -43687,7 +43741,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13">
       <c r="A2" s="5">
         <v>40716</v>
       </c>
@@ -43728,7 +43782,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13">
       <c r="A3" s="5">
         <v>40723</v>
       </c>
@@ -43769,7 +43823,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13">
       <c r="A4" s="5">
         <v>40730</v>
       </c>
@@ -43810,7 +43864,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13">
       <c r="A5" s="5">
         <v>40737</v>
       </c>
@@ -43851,7 +43905,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13">
       <c r="A6" s="5">
         <v>40744</v>
       </c>
@@ -43892,7 +43946,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13">
       <c r="A7" s="5">
         <v>40751</v>
       </c>
@@ -43933,7 +43987,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13">
       <c r="A8" s="5">
         <v>40758</v>
       </c>
@@ -43974,7 +44028,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13">
       <c r="A9" s="5">
         <v>40765</v>
       </c>
@@ -44015,7 +44069,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13">
       <c r="A10" s="5">
         <v>40772</v>
       </c>
@@ -44056,7 +44110,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13">
       <c r="A11" s="5">
         <v>40779</v>
       </c>
@@ -44097,7 +44151,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13">
       <c r="A12" s="5">
         <v>40786</v>
       </c>
@@ -44138,7 +44192,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13">
       <c r="A13" s="5">
         <v>40793</v>
       </c>
@@ -44179,7 +44233,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13">
       <c r="A14" s="5">
         <v>40800</v>
       </c>
@@ -44220,7 +44274,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13">
       <c r="A15" s="5">
         <v>40807</v>
       </c>
@@ -44261,7 +44315,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13">
       <c r="A16" s="5">
         <v>40814</v>
       </c>
@@ -44302,7 +44356,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:13">
       <c r="A17" s="5">
         <v>40821</v>
       </c>
@@ -44343,7 +44397,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:13">
       <c r="A18" s="5">
         <v>40828</v>
       </c>
@@ -44384,7 +44438,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:13">
       <c r="A19" s="5">
         <v>40835</v>
       </c>
@@ -44425,7 +44479,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:13">
       <c r="A20" s="5">
         <v>40842</v>
       </c>
@@ -44466,7 +44520,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:13">
       <c r="A21" s="5">
         <v>40849</v>
       </c>
@@ -44507,7 +44561,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:13">
       <c r="A22" s="5">
         <v>40856</v>
       </c>
@@ -44548,7 +44602,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:13">
       <c r="A23" s="5">
         <v>40863</v>
       </c>
@@ -44589,7 +44643,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:13">
       <c r="A24" s="5">
         <v>40870</v>
       </c>
@@ -44630,7 +44684,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:13">
       <c r="A25" s="5">
         <v>40877</v>
       </c>
@@ -44671,7 +44725,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:13">
       <c r="A26" s="5">
         <v>40884</v>
       </c>
@@ -44712,7 +44766,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:13">
       <c r="A27" s="5">
         <v>40891</v>
       </c>
@@ -44753,7 +44807,7 @@
         <v>2183</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:13">
       <c r="A28" s="5">
         <v>40898</v>
       </c>
@@ -44794,7 +44848,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:13">
       <c r="A29" s="5">
         <v>40905</v>
       </c>
@@ -44835,7 +44889,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:13">
       <c r="A30" s="5">
         <v>40912</v>
       </c>
@@ -44876,7 +44930,7 @@
         <v>2208</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:13">
       <c r="A31" s="5">
         <v>40919</v>
       </c>
@@ -44917,7 +44971,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:13">
       <c r="A32" s="5">
         <v>40926</v>
       </c>
@@ -44958,7 +45012,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:13">
       <c r="A33" s="5">
         <v>40933</v>
       </c>
@@ -44999,7 +45053,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:13">
       <c r="A34" s="5">
         <v>40940</v>
       </c>
@@ -45040,7 +45094,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:13">
       <c r="A35" s="5">
         <v>40947</v>
       </c>
@@ -45081,7 +45135,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:13">
       <c r="A36" s="5">
         <v>40954</v>
       </c>
@@ -45122,7 +45176,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:13">
       <c r="A37" s="5">
         <v>40961</v>
       </c>
@@ -45163,7 +45217,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:13">
       <c r="A38" s="5">
         <v>40968</v>
       </c>
@@ -45204,7 +45258,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:13">
       <c r="A39" s="5">
         <v>40975</v>
       </c>
@@ -45245,7 +45299,7 @@
         <v>2220</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:13">
       <c r="A40" s="5">
         <v>40982</v>
       </c>
@@ -45286,7 +45340,7 @@
         <v>2420</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:13">
       <c r="A41" s="5">
         <v>40989</v>
       </c>
@@ -45327,7 +45381,7 @@
         <v>2419</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:13">
       <c r="A42" s="5">
         <v>40996</v>
       </c>
@@ -45368,7 +45422,7 @@
         <v>2454</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:13">
       <c r="A43" s="5">
         <v>41003</v>
       </c>
@@ -45409,7 +45463,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:13">
       <c r="A44" s="5">
         <v>41010</v>
       </c>
@@ -45450,7 +45504,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:13">
       <c r="A45" s="5">
         <v>41017</v>
       </c>
@@ -45491,7 +45545,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:13">
       <c r="A46" s="5">
         <v>41024</v>
       </c>
@@ -45532,7 +45586,7 @@
         <v>2529</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:13">
       <c r="A47" s="5">
         <v>41031</v>
       </c>
@@ -45573,7 +45627,7 @@
         <v>2534</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:13">
       <c r="A48" s="5">
         <v>41038</v>
       </c>
@@ -45614,7 +45668,7 @@
         <v>2516</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:13">
       <c r="A49" s="5">
         <v>41045</v>
       </c>
@@ -45655,7 +45709,7 @@
         <v>2668</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:13">
       <c r="A50" s="5">
         <v>41052</v>
       </c>
@@ -45696,7 +45750,7 @@
         <v>2676</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:13">
       <c r="A51" s="5">
         <v>41059</v>
       </c>
@@ -45737,7 +45791,7 @@
         <v>2605</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:13">
       <c r="A52" s="5">
         <v>41066</v>
       </c>
@@ -45778,7 +45832,7 @@
         <v>2674</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:13">
       <c r="A53" s="5">
         <v>41073</v>
       </c>
@@ -45819,7 +45873,7 @@
         <v>2696</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:13">
       <c r="A54" s="5">
         <v>41080</v>
       </c>
@@ -45860,7 +45914,7 @@
         <v>2696</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:13">
       <c r="A55" s="5">
         <v>41087</v>
       </c>
@@ -45901,7 +45955,7 @@
         <v>2696</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:13">
       <c r="A56" s="5">
         <v>41094</v>
       </c>
@@ -45942,7 +45996,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:13">
       <c r="A57" s="5">
         <v>41101</v>
       </c>
@@ -45983,7 +46037,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:13">
       <c r="A58" s="5">
         <v>41108</v>
       </c>
@@ -46024,7 +46078,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:13">
       <c r="A59" s="5">
         <v>41115</v>
       </c>
@@ -46065,7 +46119,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:13">
       <c r="A60" s="5">
         <v>41122</v>
       </c>
@@ -46106,7 +46160,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:13">
       <c r="A61" s="5">
         <v>41129</v>
       </c>
@@ -46147,7 +46201,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:13">
       <c r="A62" s="5">
         <v>41136</v>
       </c>
@@ -46188,7 +46242,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:13">
       <c r="A63" s="5">
         <v>41143</v>
       </c>
@@ -46229,7 +46283,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:13">
       <c r="A64" s="5">
         <v>41150</v>
       </c>
@@ -46270,7 +46324,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:13">
       <c r="A65" s="5">
         <v>41157</v>
       </c>
@@ -46311,7 +46365,7 @@
         <v>2660</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:13">
       <c r="A66" s="5">
         <v>41164</v>
       </c>
@@ -46352,7 +46406,7 @@
         <v>2659</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:13">
       <c r="A67" s="5">
         <v>41171</v>
       </c>
@@ -46393,7 +46447,7 @@
         <v>2659</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:13">
       <c r="A68" s="5">
         <v>41178</v>
       </c>
@@ -46434,7 +46488,7 @@
         <v>2527</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:13">
       <c r="A69" s="5">
         <v>41185</v>
       </c>
@@ -46475,7 +46529,7 @@
         <v>2428</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:13">
       <c r="A70" s="5">
         <v>41192</v>
       </c>
@@ -46516,7 +46570,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:13">
       <c r="A71" s="5">
         <v>41199</v>
       </c>
@@ -46557,7 +46611,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:13">
       <c r="A72" s="5">
         <v>41206</v>
       </c>
@@ -46598,7 +46652,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:13">
       <c r="A73" s="5">
         <v>41213</v>
       </c>
@@ -46639,7 +46693,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:13">
       <c r="A74" s="5">
         <v>41220</v>
       </c>
@@ -46680,7 +46734,7 @@
         <v>2624</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:13">
       <c r="A75" s="5">
         <v>41227</v>
       </c>
@@ -46721,7 +46775,7 @@
         <v>2624</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:13">
       <c r="A76" s="5">
         <v>41234</v>
       </c>
@@ -46762,7 +46816,7 @@
         <v>2418</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:13">
       <c r="A77" s="5">
         <v>41241</v>
       </c>
@@ -46803,7 +46857,7 @@
         <v>2418</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:13">
       <c r="A78" s="5">
         <v>41248</v>
       </c>
@@ -46844,7 +46898,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:13">
       <c r="A79" s="5">
         <v>41255</v>
       </c>
@@ -46885,7 +46939,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:13">
       <c r="A80" s="5">
         <v>41262</v>
       </c>
@@ -46926,7 +46980,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:13">
       <c r="A81" s="5">
         <v>41269</v>
       </c>
@@ -46967,7 +47021,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:13">
       <c r="A82" s="5">
         <v>41276</v>
       </c>
@@ -47008,7 +47062,7 @@
         <v>2443</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:13">
       <c r="A83" s="5">
         <v>41283</v>
       </c>
@@ -47049,7 +47103,7 @@
         <v>2443</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:13">
       <c r="A84" s="5">
         <v>41290</v>
       </c>
@@ -47090,7 +47144,7 @@
         <v>2430</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:13">
       <c r="A85" s="5">
         <v>41297</v>
       </c>
@@ -47131,7 +47185,7 @@
         <v>2430</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:13">
       <c r="A86" s="5">
         <v>41304</v>
       </c>
@@ -47172,7 +47226,7 @@
         <v>2496</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:13">
       <c r="A87" s="5">
         <v>41311</v>
       </c>
@@ -47213,7 +47267,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:13">
       <c r="A88" s="5">
         <v>41318</v>
       </c>
@@ -47254,7 +47308,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:13">
       <c r="A89" s="5">
         <v>41325</v>
       </c>
@@ -47295,7 +47349,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:13">
       <c r="A90" s="5">
         <v>41332</v>
       </c>
@@ -47336,7 +47390,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:13">
       <c r="A91" s="5">
         <v>41339</v>
       </c>
@@ -47377,7 +47431,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:13">
       <c r="A92" s="5">
         <v>41346</v>
       </c>
@@ -47418,7 +47472,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:13">
       <c r="A93" s="5">
         <v>41353</v>
       </c>
@@ -47459,7 +47513,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:13">
       <c r="A94" s="5">
         <v>41360</v>
       </c>
@@ -47500,7 +47554,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:13">
       <c r="A95" s="5">
         <v>41367</v>
       </c>
@@ -47541,7 +47595,7 @@
         <v>2411</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:13">
       <c r="A96" s="5">
         <v>41374</v>
       </c>
@@ -47582,7 +47636,7 @@
         <v>2411</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:13">
       <c r="A97" s="5">
         <v>41381</v>
       </c>
@@ -47623,7 +47677,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:13">
       <c r="A98" s="5">
         <v>41388</v>
       </c>
@@ -47664,7 +47718,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:13">
       <c r="A99" s="5">
         <v>41395</v>
       </c>
@@ -47705,7 +47759,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:13">
       <c r="A100" s="5">
         <v>41402</v>
       </c>
@@ -47746,7 +47800,7 @@
         <v>2091</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:13">
       <c r="A101" s="5">
         <v>41409</v>
       </c>
@@ -47787,7 +47841,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:13">
       <c r="A102" s="5">
         <v>41416</v>
       </c>
@@ -47828,7 +47882,7 @@
         <v>2034</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:13">
       <c r="A103" s="5">
         <v>41423</v>
       </c>
@@ -47869,7 +47923,7 @@
         <v>2082</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:13">
       <c r="A104" s="5">
         <v>41430</v>
       </c>
@@ -47910,7 +47964,7 @@
         <v>2053</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:13">
       <c r="A105" s="5">
         <v>41437</v>
       </c>
@@ -47951,7 +48005,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:13">
       <c r="A106" s="5">
         <v>41444</v>
       </c>
@@ -47992,7 +48046,7 @@
         <v>2047</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:13">
       <c r="A107" s="5">
         <v>41451</v>
       </c>
@@ -48033,7 +48087,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:13">
       <c r="A108" s="5">
         <v>41458</v>
       </c>
@@ -48074,7 +48128,7 @@
         <v>1965</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:13">
       <c r="A109" s="5">
         <v>41465</v>
       </c>
@@ -48115,7 +48169,7 @@
         <v>1967</v>
       </c>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:13">
       <c r="A110" s="5">
         <v>41472</v>
       </c>
@@ -48156,7 +48210,7 @@
         <v>1970</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:13">
       <c r="A111" s="5">
         <v>41479</v>
       </c>
@@ -48197,7 +48251,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:13">
       <c r="A112" s="5">
         <v>41486</v>
       </c>
@@ -48238,7 +48292,7 @@
         <v>1928</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:13">
       <c r="A113" s="5">
         <v>41493</v>
       </c>
@@ -48279,7 +48333,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:13">
       <c r="A114" s="5">
         <v>41500</v>
       </c>
@@ -48320,7 +48374,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:13">
       <c r="A115" s="5">
         <v>41507</v>
       </c>
@@ -48361,7 +48415,7 @@
         <v>1897</v>
       </c>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:13">
       <c r="A116" s="5">
         <v>41514</v>
       </c>
@@ -48402,7 +48456,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:13">
       <c r="A117" s="5">
         <v>41521</v>
       </c>
@@ -48443,7 +48497,7 @@
         <v>1909</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:13">
       <c r="A118" s="5">
         <v>41528</v>
       </c>
@@ -48484,7 +48538,7 @@
         <v>1963</v>
       </c>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:13">
       <c r="A119" s="5">
         <v>41535</v>
       </c>
@@ -48525,7 +48579,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:13">
       <c r="A120" s="5">
         <v>41542</v>
       </c>
@@ -48566,7 +48620,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:13">
       <c r="A121" s="5">
         <v>41549</v>
       </c>
@@ -48607,7 +48661,7 @@
         <v>2047</v>
       </c>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:13">
       <c r="A122" s="5">
         <v>41556</v>
       </c>
@@ -48648,7 +48702,7 @@
         <v>1966</v>
       </c>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:13">
       <c r="A123" s="5">
         <v>41563</v>
       </c>
@@ -48689,7 +48743,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:13">
       <c r="A124" s="5">
         <v>41570</v>
       </c>
@@ -48730,7 +48784,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:13">
       <c r="A125" s="5">
         <v>41577</v>
       </c>
@@ -48771,7 +48825,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:13">
       <c r="A126" s="5">
         <v>41584</v>
       </c>
@@ -48812,7 +48866,7 @@
         <v>1946</v>
       </c>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:13">
       <c r="A127" s="5">
         <v>41591</v>
       </c>
@@ -48853,7 +48907,7 @@
         <v>1948</v>
       </c>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:13">
       <c r="A128" s="5">
         <v>41598</v>
       </c>
@@ -48894,7 +48948,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:13">
       <c r="A129" s="5">
         <v>41605</v>
       </c>
@@ -48935,7 +48989,7 @@
         <v>1994</v>
       </c>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:13">
       <c r="A130" s="5">
         <v>41612</v>
       </c>
@@ -48976,7 +49030,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:13">
       <c r="A131" s="5">
         <v>41619</v>
       </c>
@@ -49017,7 +49071,7 @@
         <v>1971</v>
       </c>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:13">
       <c r="A132" s="5">
         <v>41626</v>
       </c>
@@ -49058,7 +49112,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:13">
       <c r="A133" s="5">
         <v>41640</v>
       </c>
@@ -49099,7 +49153,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:13">
       <c r="A134" s="5">
         <v>41647</v>
       </c>
@@ -49140,7 +49194,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:13">
       <c r="A135" s="5">
         <v>41654</v>
       </c>
@@ -49181,7 +49235,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:13">
       <c r="A136" s="5">
         <v>41661</v>
       </c>
@@ -49222,7 +49276,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:13">
       <c r="A137" s="5">
         <v>41668</v>
       </c>
@@ -49263,7 +49317,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:13">
       <c r="A138" s="5">
         <v>41675</v>
       </c>
@@ -49304,7 +49358,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:13">
       <c r="A139" s="5">
         <v>41682</v>
       </c>
@@ -49345,7 +49399,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:13">
       <c r="A140" s="5">
         <v>41689</v>
       </c>
@@ -49386,7 +49440,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:13">
       <c r="A141" s="5">
         <v>41696</v>
       </c>
@@ -49427,7 +49481,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:13">
       <c r="A142" s="5">
         <v>41703</v>
       </c>
@@ -49468,7 +49522,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:13">
       <c r="A143" s="5">
         <v>41710</v>
       </c>
@@ -49509,7 +49563,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:13">
       <c r="A144" s="5">
         <v>41717</v>
       </c>
@@ -49550,7 +49604,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:13">
       <c r="A145" s="5">
         <v>41724</v>
       </c>
@@ -49591,7 +49645,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:13">
       <c r="A146" s="5">
         <v>41731</v>
       </c>
@@ -49632,7 +49686,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:13">
       <c r="A147" s="5">
         <v>41738</v>
       </c>
@@ -49673,7 +49727,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:13">
       <c r="A148" s="5">
         <v>41745</v>
       </c>
@@ -49714,7 +49768,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:13">
       <c r="A149" s="5">
         <v>41752</v>
       </c>
@@ -49755,7 +49809,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:13">
       <c r="A150" s="5">
         <v>41759</v>
       </c>
@@ -49796,7 +49850,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:13">
       <c r="A151" s="5">
         <v>41766</v>
       </c>
@@ -49837,7 +49891,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:13">
       <c r="A152" s="5">
         <v>41773</v>
       </c>
@@ -49878,7 +49932,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:13">
       <c r="A153" s="5">
         <v>41780</v>
       </c>
@@ -49919,7 +49973,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:13">
       <c r="A154" s="5">
         <v>41787</v>
       </c>
@@ -49960,7 +50014,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:13">
       <c r="A155" s="5">
         <v>41794</v>
       </c>
@@ -50001,7 +50055,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:13">
       <c r="A156" s="5">
         <v>41801</v>
       </c>
@@ -50042,7 +50096,7 @@
         <v>2142</v>
       </c>
     </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:13">
       <c r="A157" s="5">
         <v>41808</v>
       </c>
@@ -50083,7 +50137,7 @@
         <v>2142</v>
       </c>
     </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:13">
       <c r="A158" s="5">
         <v>41815</v>
       </c>
@@ -50124,7 +50178,7 @@
         <v>2138</v>
       </c>
     </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:13">
       <c r="A159" s="5">
         <v>41822</v>
       </c>
@@ -50165,7 +50219,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:13">
       <c r="A160" s="5">
         <v>41829</v>
       </c>
@@ -50206,7 +50260,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:13">
       <c r="A161" s="5">
         <v>41836</v>
       </c>
@@ -50247,7 +50301,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:13">
       <c r="A162" s="5">
         <v>41843</v>
       </c>
@@ -50288,7 +50342,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:13">
       <c r="A163" s="5">
         <v>41850</v>
       </c>
@@ -50329,7 +50383,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:13">
       <c r="A164" s="5">
         <v>41857</v>
       </c>
@@ -50370,7 +50424,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:13">
       <c r="A165" s="5">
         <v>41864</v>
       </c>
@@ -50411,7 +50465,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="166" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:13">
       <c r="A166" s="5">
         <v>41871</v>
       </c>
@@ -50452,7 +50506,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="167" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:13">
       <c r="A167" s="5">
         <v>41878</v>
       </c>
@@ -50493,7 +50547,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="168" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:13">
       <c r="A168" s="5">
         <v>41885</v>
       </c>
@@ -50534,7 +50588,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="169" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:13">
       <c r="A169" s="5">
         <v>41892</v>
       </c>
@@ -50575,7 +50629,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:13">
       <c r="A170" s="5">
         <v>41899</v>
       </c>
@@ -50616,7 +50670,7 @@
         <v>2203</v>
       </c>
     </row>
-    <row r="171" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:13">
       <c r="A171" s="5">
         <v>41906</v>
       </c>
@@ -50657,7 +50711,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="172" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:13">
       <c r="A172" s="5">
         <v>41913</v>
       </c>
@@ -50698,7 +50752,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="173" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:13">
       <c r="A173" s="5">
         <v>41920</v>
       </c>
@@ -50739,7 +50793,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:13">
       <c r="A174" s="5">
         <v>41927</v>
       </c>
@@ -50780,7 +50834,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:13">
       <c r="A175" s="5">
         <v>41934</v>
       </c>
@@ -50821,7 +50875,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:13">
       <c r="A176" s="5">
         <v>41941</v>
       </c>
@@ -50862,7 +50916,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:13">
       <c r="A177" s="5">
         <v>41948</v>
       </c>
@@ -50903,7 +50957,7 @@
         <v>2232</v>
       </c>
     </row>
-    <row r="178" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:13">
       <c r="A178" s="5">
         <v>41955</v>
       </c>
@@ -50944,7 +50998,7 @@
         <v>2232</v>
       </c>
     </row>
-    <row r="179" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:13">
       <c r="A179" s="5">
         <v>41962</v>
       </c>
@@ -50985,7 +51039,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:13">
       <c r="A180" s="5">
         <v>41969</v>
       </c>
@@ -51026,7 +51080,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="181" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:13">
       <c r="A181" s="5">
         <v>41976</v>
       </c>
@@ -51067,7 +51121,7 @@
         <v>2229</v>
       </c>
     </row>
-    <row r="182" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:13">
       <c r="A182" s="5">
         <v>41983</v>
       </c>
@@ -51108,7 +51162,7 @@
         <v>2219</v>
       </c>
     </row>
-    <row r="183" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:13">
       <c r="A183" s="5">
         <v>41990</v>
       </c>
@@ -51149,7 +51203,7 @@
         <v>2219</v>
       </c>
     </row>
-    <row r="184" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:13">
       <c r="A184" s="5">
         <v>42011</v>
       </c>
@@ -51190,7 +51244,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="185" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:13">
       <c r="A185" s="5">
         <v>42018</v>
       </c>
@@ -51231,7 +51285,7 @@
         <v>2274</v>
       </c>
     </row>
-    <row r="186" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:13">
       <c r="A186" s="5">
         <v>42025</v>
       </c>
@@ -51272,7 +51326,7 @@
         <v>2268</v>
       </c>
     </row>
-    <row r="187" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:13">
       <c r="A187" s="5">
         <v>42032</v>
       </c>
@@ -51313,7 +51367,7 @@
         <v>2260</v>
       </c>
     </row>
-    <row r="188" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:13">
       <c r="A188" s="5">
         <v>42039</v>
       </c>
@@ -51354,7 +51408,7 @@
         <v>2276</v>
       </c>
     </row>
-    <row r="189" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:13">
       <c r="A189" s="5">
         <v>42046</v>
       </c>
@@ -51395,7 +51449,7 @@
         <v>2333</v>
       </c>
     </row>
-    <row r="190" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:13">
       <c r="A190" s="5">
         <v>42053</v>
       </c>
@@ -51436,7 +51490,7 @@
         <v>2287</v>
       </c>
     </row>
-    <row r="191" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:13">
       <c r="A191" s="5">
         <v>42060</v>
       </c>
@@ -51477,7 +51531,7 @@
         <v>2287</v>
       </c>
     </row>
-    <row r="192" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:13">
       <c r="A192" s="5">
         <v>42067</v>
       </c>
@@ -51518,7 +51572,7 @@
         <v>2309</v>
       </c>
     </row>
-    <row r="193" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:13">
       <c r="A193" s="5">
         <v>42074</v>
       </c>
@@ -51559,7 +51613,7 @@
         <v>2277</v>
       </c>
     </row>
-    <row r="194" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:13">
       <c r="A194" s="5">
         <v>42081</v>
       </c>
@@ -51600,7 +51654,7 @@
         <v>2277</v>
       </c>
     </row>
-    <row r="195" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:13">
       <c r="A195" s="5">
         <v>42088</v>
       </c>
@@ -51641,7 +51695,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="196" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:13">
       <c r="A196" s="5">
         <v>42095</v>
       </c>
@@ -51682,7 +51736,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="197" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:13">
       <c r="A197" s="5">
         <v>42102</v>
       </c>
@@ -51723,7 +51777,7 @@
         <v>2290</v>
       </c>
     </row>
-    <row r="198" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:13">
       <c r="A198" s="5">
         <v>42109</v>
       </c>
@@ -51764,7 +51818,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="199" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:13">
       <c r="A199" s="5">
         <v>42116</v>
       </c>
@@ -51805,7 +51859,7 @@
         <v>2237</v>
       </c>
     </row>
-    <row r="200" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:13">
       <c r="A200" s="5">
         <v>42123</v>
       </c>
@@ -51846,7 +51900,7 @@
         <v>2253</v>
       </c>
     </row>
-    <row r="201" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:13">
       <c r="A201" s="5">
         <v>42130</v>
       </c>
@@ -51887,7 +51941,7 @@
         <v>2263</v>
       </c>
     </row>
-    <row r="202" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:13">
       <c r="A202" s="5">
         <v>42137</v>
       </c>
@@ -51928,7 +51982,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="203" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:13">
       <c r="A203" s="5">
         <v>42144</v>
       </c>
@@ -51969,7 +52023,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="204" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:13">
       <c r="A204" s="5">
         <v>42151</v>
       </c>
@@ -52010,7 +52064,7 @@
         <v>2154</v>
       </c>
     </row>
-    <row r="205" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:13">
       <c r="A205" s="5">
         <v>42158</v>
       </c>
@@ -52051,7 +52105,7 @@
         <v>2199</v>
       </c>
     </row>
-    <row r="206" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:13">
       <c r="A206" s="5">
         <v>42165</v>
       </c>
@@ -52092,7 +52146,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="207" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:13">
       <c r="A207" s="5">
         <v>42172</v>
       </c>
@@ -52133,7 +52187,7 @@
         <v>2207</v>
       </c>
     </row>
-    <row r="208" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:13">
       <c r="A208" s="5">
         <v>42179</v>
       </c>
@@ -52174,7 +52228,7 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:13">
       <c r="A209" s="5">
         <v>42186</v>
       </c>
@@ -52215,7 +52269,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="210" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:13">
       <c r="A210" s="5">
         <v>42193</v>
       </c>
@@ -52256,7 +52310,7 @@
         <v>2210</v>
       </c>
     </row>
-    <row r="211" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:13">
       <c r="A211" s="5">
         <v>42200</v>
       </c>
@@ -52297,7 +52351,7 @@
         <v>2195</v>
       </c>
     </row>
-    <row r="212" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:13">
       <c r="A212" s="5">
         <v>42207</v>
       </c>
@@ -52338,7 +52392,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="213" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:13">
       <c r="A213" s="5">
         <v>42214</v>
       </c>
@@ -52379,7 +52433,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="214" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:13">
       <c r="A214" s="5">
         <v>42221</v>
       </c>
@@ -52420,7 +52474,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="215" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:13">
       <c r="A215" s="5">
         <v>42228</v>
       </c>
@@ -52461,7 +52515,7 @@
         <v>2184</v>
       </c>
     </row>
-    <row r="216" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:13">
       <c r="A216" s="5">
         <v>42235</v>
       </c>
@@ -52502,7 +52556,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="217" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:13">
       <c r="A217" s="5">
         <v>42242</v>
       </c>
@@ -52543,7 +52597,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="218" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:13">
       <c r="A218" s="5">
         <v>42249</v>
       </c>
@@ -52584,7 +52638,7 @@
         <v>2147</v>
       </c>
     </row>
-    <row r="219" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:13">
       <c r="A219" s="5">
         <v>42256</v>
       </c>
@@ -52625,7 +52679,7 @@
         <v>2138</v>
       </c>
     </row>
-    <row r="220" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:13">
       <c r="A220" s="5">
         <v>42263</v>
       </c>
@@ -52666,7 +52720,7 @@
         <v>2139</v>
       </c>
     </row>
-    <row r="221" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:13">
       <c r="A221" s="5">
         <v>42270</v>
       </c>
@@ -52707,7 +52761,7 @@
         <v>2090</v>
       </c>
     </row>
-    <row r="222" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:13">
       <c r="A222" s="5">
         <v>42277</v>
       </c>
@@ -52748,7 +52802,7 @@
         <v>2074</v>
       </c>
     </row>
-    <row r="223" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:13">
       <c r="A223" s="5">
         <v>42284</v>
       </c>
@@ -52789,7 +52843,7 @@
         <v>2095</v>
       </c>
     </row>
-    <row r="224" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:13">
       <c r="A224" s="5">
         <v>42291</v>
       </c>
@@ -52830,7 +52884,7 @@
         <v>2079</v>
       </c>
     </row>
-    <row r="225" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:13">
       <c r="A225" s="5">
         <v>42298</v>
       </c>
@@ -52871,7 +52925,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="226" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:13">
       <c r="A226" s="5">
         <v>42305</v>
       </c>
@@ -52912,7 +52966,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="227" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:13">
       <c r="A227" s="5">
         <v>42312</v>
       </c>
@@ -52953,7 +53007,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="228" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:13">
       <c r="A228" s="5">
         <v>42319</v>
       </c>
@@ -52994,7 +53048,7 @@
         <v>2066</v>
       </c>
     </row>
-    <row r="229" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:13">
       <c r="A229" s="5">
         <v>42326</v>
       </c>
@@ -53035,7 +53089,7 @@
         <v>2066</v>
       </c>
     </row>
-    <row r="230" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:13">
       <c r="A230" s="5">
         <v>42333</v>
       </c>
@@ -53076,7 +53130,7 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="231" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:13">
       <c r="A231" s="5">
         <v>42340</v>
       </c>
@@ -53117,7 +53171,7 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="232" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:13">
       <c r="A232" s="5">
         <v>42347</v>
       </c>
@@ -53158,7 +53212,7 @@
         <v>2079</v>
       </c>
     </row>
-    <row r="233" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:13">
       <c r="A233" s="5">
         <v>42354</v>
       </c>
@@ -53199,7 +53253,7 @@
         <v>2074</v>
       </c>
     </row>
-    <row r="234" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:13">
       <c r="A234" s="5">
         <v>42361</v>
       </c>
@@ -53240,7 +53294,7 @@
         <v>2077</v>
       </c>
     </row>
-    <row r="235" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:13">
       <c r="A235" s="5">
         <v>42368</v>
       </c>
@@ -53281,7 +53335,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="236" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:13">
       <c r="A236" s="5">
         <v>42375</v>
       </c>
@@ -53322,7 +53376,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="237" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:13">
       <c r="A237" s="5">
         <v>42382</v>
       </c>
@@ -53363,7 +53417,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="238" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:13">
       <c r="A238" s="5">
         <v>42389</v>
       </c>
@@ -53404,7 +53458,7 @@
         <v>2042</v>
       </c>
     </row>
-    <row r="239" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:13">
       <c r="A239" s="5">
         <v>42396</v>
       </c>
@@ -53445,7 +53499,7 @@
         <v>2042</v>
       </c>
     </row>
-    <row r="240" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:13">
       <c r="A240" s="5">
         <v>42403</v>
       </c>
@@ -53486,7 +53540,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="241" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:13">
       <c r="A241" s="5">
         <v>42410</v>
       </c>
@@ -53527,7 +53581,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="242" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:13">
       <c r="A242" s="5">
         <v>42417</v>
       </c>
@@ -53568,7 +53622,7 @@
         <v>2048</v>
       </c>
     </row>
-    <row r="243" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:13">
       <c r="A243" s="5">
         <v>42424</v>
       </c>
@@ -53609,7 +53663,7 @@
         <v>1880</v>
       </c>
     </row>
-    <row r="244" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:13">
       <c r="A244" s="5">
         <v>42431</v>
       </c>
@@ -53650,7 +53704,7 @@
         <v>1856</v>
       </c>
     </row>
-    <row r="245" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:13">
       <c r="A245" s="5">
         <v>42438</v>
       </c>
@@ -53691,7 +53745,7 @@
         <v>1857</v>
       </c>
     </row>
-    <row r="246" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:13">
       <c r="A246" s="5">
         <v>42445</v>
       </c>
@@ -53732,7 +53786,7 @@
         <v>1846</v>
       </c>
     </row>
-    <row r="247" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:13">
       <c r="A247" s="5">
         <v>42452</v>
       </c>
@@ -53773,7 +53827,7 @@
         <v>1835</v>
       </c>
     </row>
-    <row r="248" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:13">
       <c r="A248" s="5">
         <v>42459</v>
       </c>
@@ -53814,7 +53868,7 @@
         <v>1828</v>
       </c>
     </row>
-    <row r="249" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:13">
       <c r="A249" s="5">
         <v>42466</v>
       </c>
@@ -53855,7 +53909,7 @@
         <v>1872</v>
       </c>
     </row>
-    <row r="250" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:13">
       <c r="A250" s="5">
         <v>42473</v>
       </c>
@@ -53896,7 +53950,7 @@
         <v>1847</v>
       </c>
     </row>
-    <row r="251" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:13">
       <c r="A251" s="5">
         <v>42480</v>
       </c>
@@ -53937,7 +53991,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="252" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:13">
       <c r="A252" s="5">
         <v>42487</v>
       </c>
@@ -53978,7 +54032,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="253" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:13">
       <c r="A253" s="5">
         <v>42494</v>
       </c>
@@ -54019,7 +54073,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="254" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:13">
       <c r="A254" s="5">
         <v>42501</v>
       </c>
@@ -54060,7 +54114,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="255" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:13">
       <c r="A255" s="5">
         <v>42508</v>
       </c>
@@ -54101,7 +54155,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="256" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:13">
       <c r="A256" s="5">
         <v>42515</v>
       </c>
@@ -54142,7 +54196,7 @@
         <v>1843</v>
       </c>
     </row>
-    <row r="257" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:13">
       <c r="A257" s="5">
         <v>42522</v>
       </c>
@@ -54183,7 +54237,7 @@
         <v>1844</v>
       </c>
     </row>
-    <row r="258" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:13">
       <c r="A258" s="5">
         <v>42529</v>
       </c>
@@ -54224,7 +54278,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="259" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:13">
       <c r="A259" s="5">
         <v>42536</v>
       </c>
@@ -54265,7 +54319,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="260" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:13">
       <c r="A260" s="5">
         <v>42543</v>
       </c>
@@ -54306,7 +54360,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="261" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:13">
       <c r="A261" s="5">
         <v>42550</v>
       </c>
@@ -54347,7 +54401,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="262" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:13">
       <c r="A262" s="5">
         <v>42557</v>
       </c>
@@ -54388,7 +54442,7 @@
         <v>1848</v>
       </c>
     </row>
-    <row r="263" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:13">
       <c r="A263" s="5">
         <v>42564</v>
       </c>
@@ -54429,7 +54483,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="264" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:13">
       <c r="A264" s="5">
         <v>42571</v>
       </c>
@@ -54470,7 +54524,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="265" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:13">
       <c r="A265" s="5">
         <v>42578</v>
       </c>
@@ -54511,7 +54565,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="266" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:13">
       <c r="A266" s="5">
         <v>42585</v>
       </c>
@@ -54552,7 +54606,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="267" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:13">
       <c r="A267" s="5">
         <v>42592</v>
       </c>
@@ -54593,7 +54647,7 @@
         <v>1816</v>
       </c>
     </row>
-    <row r="268" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:13">
       <c r="A268" s="5">
         <v>42599</v>
       </c>
@@ -54634,7 +54688,7 @@
         <v>1814</v>
       </c>
     </row>
-    <row r="269" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:13">
       <c r="A269" s="5">
         <v>42606</v>
       </c>
@@ -54675,7 +54729,7 @@
         <v>1814</v>
       </c>
     </row>
-    <row r="270" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:13">
       <c r="A270" s="5">
         <v>42613</v>
       </c>
@@ -54716,7 +54770,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="271" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:13">
       <c r="A271" s="5">
         <v>42620</v>
       </c>
@@ -54757,7 +54811,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="272" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:13">
       <c r="A272" s="5">
         <v>42627</v>
       </c>
@@ -54798,7 +54852,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="273" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:13">
       <c r="A273" s="5">
         <v>42634</v>
       </c>
@@ -54839,7 +54893,7 @@
         <v>1766</v>
       </c>
     </row>
-    <row r="274" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:13">
       <c r="A274" s="5">
         <v>42641</v>
       </c>
@@ -54880,7 +54934,7 @@
         <v>1766</v>
       </c>
     </row>
-    <row r="275" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:13">
       <c r="A275" s="5">
         <v>42648</v>
       </c>
@@ -54921,7 +54975,7 @@
         <v>1743</v>
       </c>
     </row>
-    <row r="276" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:13">
       <c r="A276" s="5">
         <v>42655</v>
       </c>
@@ -54962,7 +55016,7 @@
         <v>1770</v>
       </c>
     </row>
-    <row r="277" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:13">
       <c r="A277" s="5">
         <v>42662</v>
       </c>
@@ -55003,7 +55057,7 @@
         <v>1770</v>
       </c>
     </row>
-    <row r="278" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:13">
       <c r="A278" s="5">
         <v>42669</v>
       </c>
@@ -55044,7 +55098,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="279" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:13">
       <c r="A279" s="5">
         <v>42676</v>
       </c>
@@ -55085,7 +55139,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="280" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:13">
       <c r="A280" s="5">
         <v>42683</v>
       </c>
@@ -55126,7 +55180,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="281" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:13">
       <c r="A281" s="5">
         <v>42690</v>
       </c>
@@ -55167,7 +55221,7 @@
         <v>1740</v>
       </c>
     </row>
-    <row r="282" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:13">
       <c r="A282" s="5">
         <v>42697</v>
       </c>
@@ -55208,7 +55262,7 @@
         <v>1745</v>
       </c>
     </row>
-    <row r="283" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:13">
       <c r="A283" s="5">
         <v>42704</v>
       </c>
@@ -55249,7 +55303,7 @@
         <v>1735</v>
       </c>
     </row>
-    <row r="284" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:13">
       <c r="A284" s="5">
         <v>42711</v>
       </c>
@@ -55290,7 +55344,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="285" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:13">
       <c r="A285" s="5">
         <v>42718</v>
       </c>
@@ -55331,7 +55385,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="286" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:13">
       <c r="A286" s="5">
         <v>42725</v>
       </c>
@@ -55372,7 +55426,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="287" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:13">
       <c r="A287" s="5">
         <v>42732</v>
       </c>
@@ -55413,7 +55467,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="288" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:13">
       <c r="A288" s="5">
         <v>42739</v>
       </c>
@@ -55454,7 +55508,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="289" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:13">
       <c r="A289" s="5">
         <v>42746</v>
       </c>
@@ -55495,7 +55549,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="290" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:13">
       <c r="A290" s="5">
         <v>42753</v>
       </c>
@@ -55536,7 +55590,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="291" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:13">
       <c r="A291" s="5">
         <v>42760</v>
       </c>
@@ -55577,7 +55631,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="292" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:13">
       <c r="A292" s="5">
         <v>42767</v>
       </c>
@@ -55618,7 +55672,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="293" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:13">
       <c r="A293" s="5">
         <v>42774</v>
       </c>
@@ -55659,7 +55713,7 @@
         <v>1778</v>
       </c>
     </row>
-    <row r="294" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:13">
       <c r="A294" s="5">
         <v>42781</v>
       </c>
@@ -55700,7 +55754,7 @@
         <v>1728</v>
       </c>
     </row>
-    <row r="295" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:13">
       <c r="A295" s="5">
         <v>42788</v>
       </c>
@@ -55741,7 +55795,7 @@
         <v>1728</v>
       </c>
     </row>
-    <row r="296" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:13">
       <c r="A296" s="5">
         <v>42795</v>
       </c>
@@ -55782,7 +55836,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="297" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:13">
       <c r="A297" s="5">
         <v>42802</v>
       </c>
@@ -55823,7 +55877,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="298" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:13">
       <c r="A298" s="5">
         <v>42809</v>
       </c>
@@ -55864,7 +55918,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="299" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:13">
       <c r="A299" s="5">
         <v>42816</v>
       </c>
@@ -55905,7 +55959,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="300" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:13">
       <c r="A300" s="5">
         <v>42823</v>
       </c>
@@ -55946,7 +56000,7 @@
         <v>1777</v>
       </c>
     </row>
-    <row r="301" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:13">
       <c r="A301" s="5">
         <v>42830</v>
       </c>
@@ -55987,7 +56041,7 @@
         <v>1810</v>
       </c>
     </row>
-    <row r="302" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:13">
       <c r="A302" s="5">
         <v>42837</v>
       </c>
@@ -56028,7 +56082,7 @@
         <v>1810</v>
       </c>
     </row>
-    <row r="303" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:13">
       <c r="A303" s="5">
         <v>42844</v>
       </c>
@@ -56069,7 +56123,7 @@
         <v>1775</v>
       </c>
     </row>
-    <row r="304" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:13">
       <c r="A304" s="5">
         <v>42851</v>
       </c>
@@ -56110,7 +56164,7 @@
         <v>1802</v>
       </c>
     </row>
-    <row r="305" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:13">
       <c r="A305" s="5">
         <v>42858</v>
       </c>
@@ -56151,7 +56205,7 @@
         <v>1778</v>
       </c>
     </row>
-    <row r="306" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:13">
       <c r="A306" s="5">
         <v>42865</v>
       </c>
@@ -56192,7 +56246,7 @@
         <v>1749</v>
       </c>
     </row>
-    <row r="307" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:13">
       <c r="A307" s="5">
         <v>42872</v>
       </c>
@@ -56233,7 +56287,7 @@
         <v>1755</v>
       </c>
     </row>
-    <row r="308" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:13">
       <c r="A308" s="5">
         <v>42879</v>
       </c>
@@ -56274,7 +56328,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="309" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:13">
       <c r="A309" s="5">
         <v>42886</v>
       </c>
@@ -56315,7 +56369,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="310" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:13">
       <c r="A310" s="5">
         <v>42893</v>
       </c>
@@ -56356,7 +56410,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="311" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:13">
       <c r="A311" s="5">
         <v>42900</v>
       </c>
@@ -56397,7 +56451,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="312" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:13">
       <c r="A312" s="5">
         <v>42907</v>
       </c>
@@ -56438,7 +56492,7 @@
         <v>1734</v>
       </c>
     </row>
-    <row r="313" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:13">
       <c r="A313" s="5">
         <v>42914</v>
       </c>
@@ -56479,7 +56533,7 @@
         <v>1734</v>
       </c>
     </row>
-    <row r="314" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:13">
       <c r="A314" s="5">
         <v>42921</v>
       </c>
@@ -56520,7 +56574,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="315" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:13">
       <c r="A315" s="5">
         <v>42928</v>
       </c>
@@ -56561,7 +56615,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="316" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:13">
       <c r="A316" s="5">
         <v>42935</v>
       </c>
@@ -56602,7 +56656,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="317" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:13">
       <c r="A317" s="5">
         <v>42942</v>
       </c>
@@ -56643,7 +56697,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="318" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:13">
       <c r="A318" s="5">
         <v>42949</v>
       </c>
@@ -56684,7 +56738,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="319" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:13">
       <c r="A319" s="5">
         <v>42956</v>
       </c>
@@ -56725,7 +56779,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="320" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:13">
       <c r="A320" s="5">
         <v>42963</v>
       </c>
@@ -56766,7 +56820,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="321" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:13">
       <c r="A321" s="5">
         <v>42970</v>
       </c>
@@ -56807,7 +56861,7 @@
         <v>1730</v>
       </c>
     </row>
-    <row r="322" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:13">
       <c r="A322" s="5">
         <v>42977</v>
       </c>
@@ -56848,7 +56902,7 @@
         <v>1730</v>
       </c>
     </row>
-    <row r="323" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:13">
       <c r="A323" s="5">
         <v>42984</v>
       </c>
@@ -56889,7 +56943,7 @@
         <v>1742</v>
       </c>
     </row>
-    <row r="324" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:13">
       <c r="A324" s="5">
         <v>42991</v>
       </c>
@@ -56930,7 +56984,7 @@
         <v>1742</v>
       </c>
     </row>
-    <row r="325" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:13">
       <c r="A325" s="5">
         <v>42998</v>
       </c>
@@ -56971,7 +57025,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="326" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:13">
       <c r="A326" s="5">
         <v>43005</v>
       </c>
@@ -57012,7 +57066,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="327" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:13">
       <c r="A327" s="5">
         <v>43012</v>
       </c>
@@ -57053,7 +57107,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="328" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:13">
       <c r="A328" s="5">
         <v>43019</v>
       </c>
@@ -57094,7 +57148,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="329" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:13">
       <c r="A329" s="5">
         <v>43026</v>
       </c>
@@ -57135,7 +57189,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="330" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:13">
       <c r="A330" s="5">
         <v>43033</v>
       </c>
@@ -57176,7 +57230,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="331" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:13">
       <c r="A331" s="5">
         <v>43040</v>
       </c>
@@ -57217,7 +57271,7 @@
         <v>1691</v>
       </c>
     </row>
-    <row r="332" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:13">
       <c r="A332" s="5">
         <v>43047</v>
       </c>
@@ -57258,7 +57312,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="333" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:13">
       <c r="A333" s="5">
         <v>43054</v>
       </c>
@@ -57299,7 +57353,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="334" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:13">
       <c r="A334" s="5">
         <v>43061</v>
       </c>
@@ -57340,7 +57394,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="335" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:13">
       <c r="A335" s="5">
         <v>43068</v>
       </c>
@@ -57381,7 +57435,7 @@
         <v>1853</v>
       </c>
     </row>
-    <row r="336" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:13">
       <c r="A336" s="5">
         <v>43075</v>
       </c>
@@ -57422,7 +57476,7 @@
         <v>2063</v>
       </c>
     </row>
-    <row r="337" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:13">
       <c r="A337" s="5">
         <v>43082</v>
       </c>
@@ -57463,7 +57517,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="338" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:13">
       <c r="A338" s="5">
         <v>43089</v>
       </c>
@@ -57504,7 +57558,7 @@
         <v>1748</v>
       </c>
     </row>
-    <row r="339" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:13">
       <c r="A339" s="5">
         <v>43096</v>
       </c>
@@ -57545,7 +57599,7 @@
         <v>1824</v>
       </c>
     </row>
-    <row r="340" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:13">
       <c r="A340" s="5">
         <v>43103</v>
       </c>
@@ -57586,7 +57640,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="341" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:13">
       <c r="A341" s="5">
         <v>43110</v>
       </c>
@@ -57627,7 +57681,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="342" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:13">
       <c r="A342" s="5">
         <v>43117</v>
       </c>
@@ -57668,7 +57722,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="343" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:13">
       <c r="A343" s="5">
         <v>43124</v>
       </c>
@@ -57709,7 +57763,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="344" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:13">
       <c r="A344" s="5">
         <v>43131</v>
       </c>
@@ -57750,7 +57804,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="345" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:13">
       <c r="A345" s="5">
         <v>43138</v>
       </c>
@@ -57791,7 +57845,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="346" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:13">
       <c r="A346" s="5">
         <v>43145</v>
       </c>
@@ -57832,7 +57886,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="347" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:13">
       <c r="A347" s="5">
         <v>43152</v>
       </c>
@@ -57873,7 +57927,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="348" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:13">
       <c r="A348" s="5">
         <v>43159</v>
       </c>
@@ -57914,7 +57968,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="349" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:13">
       <c r="A349" s="5">
         <v>43166</v>
       </c>
@@ -57955,7 +58009,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="350" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:13">
       <c r="A350" s="5">
         <v>43173</v>
       </c>
@@ -57996,7 +58050,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="351" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:13">
       <c r="A351" s="5">
         <v>43180</v>
       </c>
@@ -58037,7 +58091,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="352" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:13">
       <c r="A352" s="5">
         <v>43187</v>
       </c>
@@ -58078,7 +58132,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="353" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:13">
       <c r="A353" s="5">
         <v>43194</v>
       </c>
@@ -58119,7 +58173,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="354" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:13">
       <c r="A354" s="5">
         <v>43201</v>
       </c>
@@ -58160,7 +58214,7 @@
         <v>1864</v>
       </c>
     </row>
-    <row r="355" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:13">
       <c r="A355" s="5">
         <v>43208</v>
       </c>
@@ -58201,7 +58255,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="356" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:13">
       <c r="A356" s="5">
         <v>43215</v>
       </c>
@@ -58242,7 +58296,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="357" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:13">
       <c r="A357" s="5">
         <v>43222</v>
       </c>
@@ -58283,7 +58337,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="358" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:13">
       <c r="A358" s="5">
         <v>43229</v>
       </c>
@@ -58324,7 +58378,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="359" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:13">
       <c r="A359" s="5">
         <v>43236</v>
       </c>
@@ -58365,7 +58419,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="360" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:13">
       <c r="A360" s="5">
         <v>43243</v>
       </c>
@@ -58406,7 +58460,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="361" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:13">
       <c r="A361" s="5">
         <v>43250</v>
       </c>
@@ -58447,7 +58501,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="362" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:13">
       <c r="A362" s="5">
         <v>43257</v>
       </c>
@@ -58488,7 +58542,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="363" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:13">
       <c r="A363" s="5">
         <v>43264</v>
       </c>
@@ -58529,7 +58583,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="364" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:13">
       <c r="A364" s="5">
         <v>43271</v>
       </c>
@@ -58570,7 +58624,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="365" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:13">
       <c r="A365" s="5">
         <v>43278</v>
       </c>
@@ -58611,7 +58665,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="366" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:13">
       <c r="A366" s="5">
         <v>43285</v>
       </c>
@@ -58652,7 +58706,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="367" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:13">
       <c r="A367" s="5">
         <v>43292</v>
       </c>
@@ -58693,7 +58747,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="368" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:13">
       <c r="A368" s="5">
         <v>43299</v>
       </c>
@@ -58734,7 +58788,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="369" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:13">
       <c r="A369" s="5">
         <v>43306</v>
       </c>
@@ -58775,7 +58829,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="370" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:13">
       <c r="A370" s="5">
         <v>43313</v>
       </c>
@@ -58816,7 +58870,7 @@
         <v>1965</v>
       </c>
     </row>
-    <row r="371" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:13">
       <c r="A371" s="5">
         <v>43320</v>
       </c>
@@ -58857,7 +58911,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="372" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:13">
       <c r="A372" s="5">
         <v>43327</v>
       </c>
@@ -58898,7 +58952,7 @@
         <v>1962</v>
       </c>
     </row>
-    <row r="373" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:13">
       <c r="A373" s="5">
         <v>43334</v>
       </c>
@@ -58939,7 +58993,7 @@
         <v>1962</v>
       </c>
     </row>
-    <row r="374" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:13">
       <c r="A374" s="5">
         <v>43341</v>
       </c>
@@ -58980,7 +59034,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="375" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:13">
       <c r="A375" s="5">
         <v>43348</v>
       </c>
@@ -59021,7 +59075,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="376" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:13">
       <c r="A376" s="5">
         <v>43355</v>
       </c>
@@ -59062,7 +59116,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="377" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:13">
       <c r="A377" s="5">
         <v>43362</v>
       </c>
@@ -59103,7 +59157,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="378" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:13">
       <c r="A378" s="5">
         <v>43369</v>
       </c>
@@ -59144,7 +59198,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="379" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:13">
       <c r="A379" s="5">
         <v>43376</v>
       </c>
@@ -59185,7 +59239,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="380" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:13">
       <c r="A380" s="5">
         <v>43383</v>
       </c>
@@ -59226,7 +59280,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="381" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:13">
       <c r="A381" s="5">
         <v>43390</v>
       </c>
@@ -59267,7 +59321,7 @@
         <v>1970</v>
       </c>
     </row>
-    <row r="382" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:13">
       <c r="A382" s="5">
         <v>43397</v>
       </c>
@@ -59308,7 +59362,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="383" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:13">
       <c r="A383" s="5">
         <v>43404</v>
       </c>
@@ -59349,7 +59403,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="384" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:13">
       <c r="A384" s="5">
         <v>43411</v>
       </c>
@@ -59390,7 +59444,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="385" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:13">
       <c r="A385" s="5">
         <v>43418</v>
       </c>
@@ -59431,7 +59485,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="386" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:13">
       <c r="A386" s="5">
         <v>43425</v>
       </c>
@@ -59472,7 +59526,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="387" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:13">
       <c r="A387" s="5">
         <v>43432</v>
       </c>
@@ -59513,7 +59567,7 @@
         <v>2045</v>
       </c>
     </row>
-    <row r="388" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:13">
       <c r="A388" s="5">
         <v>43439</v>
       </c>
@@ -59554,7 +59608,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="389" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:13">
       <c r="A389" s="5">
         <v>43446</v>
       </c>
@@ -59595,7 +59649,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="390" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:13">
       <c r="A390" s="5">
         <v>43453</v>
       </c>
@@ -59636,7 +59690,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="391" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:13">
       <c r="A391" s="5">
         <v>43460</v>
       </c>
@@ -59677,7 +59731,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="392" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:13">
       <c r="A392" s="5">
         <v>43467</v>
       </c>
@@ -59718,7 +59772,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="393" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:13">
       <c r="A393" s="5">
         <v>43474</v>
       </c>
@@ -59759,7 +59813,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="394" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:13">
       <c r="A394" s="5">
         <v>43481</v>
       </c>
@@ -59800,7 +59854,7 @@
         <v>2049</v>
       </c>
     </row>
-    <row r="395" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:13">
       <c r="A395" s="5">
         <v>43488</v>
       </c>
@@ -59841,7 +59895,7 @@
         <v>2049</v>
       </c>
     </row>
-    <row r="396" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:13">
       <c r="A396" s="5">
         <v>43495</v>
       </c>
@@ -59882,7 +59936,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="397" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:13">
       <c r="A397" s="5">
         <v>43502</v>
       </c>
@@ -59923,7 +59977,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="398" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:13">
       <c r="A398" s="5">
         <v>43509</v>
       </c>
@@ -59964,7 +60018,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="399" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:13">
       <c r="A399" s="5">
         <v>43516</v>
       </c>
@@ -60005,7 +60059,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="400" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:13">
       <c r="A400" s="5">
         <v>43523</v>
       </c>
@@ -60046,7 +60100,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="401" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:13">
       <c r="A401" s="5">
         <v>43530</v>
       </c>
@@ -60087,7 +60141,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="402" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:13">
       <c r="A402" s="5">
         <v>43537</v>
       </c>
@@ -60128,7 +60182,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="403" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:13">
       <c r="A403" s="5">
         <v>43544</v>
       </c>
@@ -60169,7 +60223,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="404" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:13">
       <c r="A404" s="5">
         <v>43551</v>
       </c>
@@ -60210,7 +60264,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="405" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:13">
       <c r="A405" s="5">
         <v>43558</v>
       </c>
@@ -60251,7 +60305,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="406" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:13">
       <c r="A406" s="5">
         <v>43565</v>
       </c>
@@ -60292,7 +60346,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="407" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:13">
       <c r="A407" s="5">
         <v>43572</v>
       </c>
@@ -60333,7 +60387,7 @@
         <v>2302</v>
       </c>
     </row>
-    <row r="408" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:13">
       <c r="A408" s="5">
         <v>43579</v>
       </c>
@@ -60374,7 +60428,7 @@
         <v>2302</v>
       </c>
     </row>
-    <row r="409" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:13">
       <c r="A409" s="5">
         <v>43586</v>
       </c>
@@ -60415,7 +60469,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="410" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:13">
       <c r="A410" s="5">
         <v>43593</v>
       </c>
@@ -60456,7 +60510,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="411" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:13">
       <c r="A411" s="5">
         <v>43600</v>
       </c>
@@ -60497,7 +60551,7 @@
         <v>2343</v>
       </c>
     </row>
-    <row r="412" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:13">
       <c r="A412" s="5">
         <v>43607</v>
       </c>
@@ -60538,7 +60592,7 @@
         <v>2343</v>
       </c>
     </row>
-    <row r="413" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:13">
       <c r="A413" s="5">
         <v>43614</v>
       </c>
@@ -60579,7 +60633,7 @@
         <v>2272</v>
       </c>
     </row>
-    <row r="414" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:13">
       <c r="A414" s="5">
         <v>43621</v>
       </c>
@@ -60620,7 +60674,7 @@
         <v>2344</v>
       </c>
     </row>
-    <row r="415" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:13">
       <c r="A415" s="5">
         <v>43628</v>
       </c>
@@ -60661,7 +60715,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="416" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:13">
       <c r="A416" s="5">
         <v>43635</v>
       </c>
@@ -60702,7 +60756,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="417" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:13">
       <c r="A417" s="5">
         <v>43642</v>
       </c>
@@ -60743,7 +60797,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="418" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:13">
       <c r="A418" s="5">
         <v>43649</v>
       </c>
@@ -60784,7 +60838,7 @@
         <v>2378</v>
       </c>
     </row>
-    <row r="419" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:13">
       <c r="A419" s="5">
         <v>43656</v>
       </c>
@@ -60825,7 +60879,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="420" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:13">
       <c r="A420" s="5">
         <v>43663</v>
       </c>
@@ -60866,7 +60920,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="421" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:13">
       <c r="A421" s="5">
         <v>43670</v>
       </c>
@@ -60907,7 +60961,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="422" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:13">
       <c r="A422" s="5">
         <v>43677</v>
       </c>
@@ -60948,7 +61002,7 @@
         <v>2369</v>
       </c>
     </row>
-    <row r="423" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:13">
       <c r="A423" s="5">
         <v>43684</v>
       </c>
@@ -60989,7 +61043,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="424" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:13">
       <c r="A424" s="5">
         <v>43691</v>
       </c>
@@ -61030,7 +61084,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="425" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:13">
       <c r="A425" s="5">
         <v>43698</v>
       </c>
@@ -61071,7 +61125,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="426" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:13">
       <c r="A426" s="5">
         <v>43705</v>
       </c>
@@ -61112,7 +61166,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="427" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:13">
       <c r="A427" s="5">
         <v>43712</v>
       </c>
@@ -61153,7 +61207,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="428" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:13">
       <c r="A428" s="5">
         <v>43719</v>
       </c>
@@ -61194,7 +61248,7 @@
         <v>2346</v>
       </c>
     </row>
-    <row r="429" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:13">
       <c r="A429" s="5">
         <v>43726</v>
       </c>
@@ -61235,7 +61289,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="430" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:13">
       <c r="A430" s="5">
         <v>43733</v>
       </c>
@@ -61276,7 +61330,7 @@
         <v>2346</v>
       </c>
     </row>
-    <row r="431" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:13">
       <c r="A431" s="5">
         <v>43740</v>
       </c>
@@ -61317,7 +61371,7 @@
         <v>2349</v>
       </c>
     </row>
-    <row r="432" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:13">
       <c r="A432" s="5">
         <v>43747</v>
       </c>
@@ -61358,7 +61412,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="433" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:13">
       <c r="A433" s="5">
         <v>43754</v>
       </c>
@@ -61399,7 +61453,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="434" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:13">
       <c r="A434" s="5">
         <v>43761</v>
       </c>
@@ -61440,7 +61494,7 @@
         <v>2350</v>
       </c>
     </row>
-    <row r="435" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:13">
       <c r="A435" s="5">
         <v>43768</v>
       </c>
@@ -61481,7 +61535,7 @@
         <v>2356</v>
       </c>
     </row>
-    <row r="436" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:13">
       <c r="A436" s="5">
         <v>43775</v>
       </c>
@@ -61522,7 +61576,7 @@
         <v>2363</v>
       </c>
     </row>
-    <row r="437" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:13">
       <c r="A437" s="5">
         <v>43782</v>
       </c>
@@ -61563,7 +61617,7 @@
         <v>2338</v>
       </c>
     </row>
-    <row r="438" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:13">
       <c r="A438" s="5">
         <v>43789</v>
       </c>
@@ -61604,7 +61658,7 @@
         <v>2391</v>
       </c>
     </row>
-    <row r="439" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:13">
       <c r="A439" s="5">
         <v>43796</v>
       </c>
@@ -61645,7 +61699,7 @@
         <v>2397</v>
       </c>
     </row>
-    <row r="440" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:13">
       <c r="A440" s="5">
         <v>43803</v>
       </c>
@@ -61686,7 +61740,7 @@
         <v>2388</v>
       </c>
     </row>
-    <row r="441" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:13">
       <c r="A441" s="5">
         <v>43810</v>
       </c>
@@ -61727,7 +61781,7 @@
         <v>2363</v>
       </c>
     </row>
-    <row r="442" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:13">
       <c r="A442" s="5">
         <v>43817</v>
       </c>
@@ -61768,7 +61822,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="443" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:13">
       <c r="A443" s="5">
         <v>43831</v>
       </c>
@@ -61809,7 +61863,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="444" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:13">
       <c r="A444" s="5">
         <v>43838</v>
       </c>
@@ -61850,7 +61904,7 @@
         <v>2415</v>
       </c>
     </row>
-    <row r="445" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:13">
       <c r="A445" s="5">
         <v>43845</v>
       </c>
@@ -61891,7 +61945,7 @@
         <v>2415</v>
       </c>
     </row>
-    <row r="446" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:13">
       <c r="A446" s="5">
         <v>43852</v>
       </c>
@@ -61932,7 +61986,7 @@
         <v>2410</v>
       </c>
     </row>
-    <row r="447" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:13">
       <c r="A447" s="5">
         <v>43859</v>
       </c>
@@ -61973,7 +62027,7 @@
         <v>2344</v>
       </c>
     </row>
-    <row r="448" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:13">
       <c r="A448" s="5">
         <v>43866</v>
       </c>
@@ -62014,7 +62068,7 @@
         <v>2188</v>
       </c>
     </row>
-    <row r="449" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:13">
       <c r="A449" s="5">
         <v>43873</v>
       </c>
@@ -62055,7 +62109,7 @@
         <v>2214</v>
       </c>
     </row>
-    <row r="450" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:13">
       <c r="A450" s="5">
         <v>43880</v>
       </c>
@@ -62096,7 +62150,7 @@
         <v>2214</v>
       </c>
     </row>
-    <row r="451" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:13">
       <c r="A451" s="5">
         <v>43887</v>
       </c>
@@ -62137,7 +62191,7 @@
         <v>2206</v>
       </c>
     </row>
-    <row r="452" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:13">
       <c r="A452" s="5">
         <v>43894</v>
       </c>
@@ -62178,7 +62232,7 @@
         <v>2217</v>
       </c>
     </row>
-    <row r="453" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:13">
       <c r="A453" s="5">
         <v>43901</v>
       </c>
@@ -62219,7 +62273,7 @@
         <v>2234</v>
       </c>
     </row>
-    <row r="454" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:13">
       <c r="A454" s="5">
         <v>43908</v>
       </c>
@@ -62260,7 +62314,7 @@
         <v>2513</v>
       </c>
     </row>
-    <row r="455" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:13">
       <c r="A455" s="5">
         <v>43915</v>
       </c>
@@ -62301,7 +62355,7 @@
         <v>2322</v>
       </c>
     </row>
-    <row r="456" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:13">
       <c r="A456" s="5">
         <v>43922</v>
       </c>
@@ -62342,7 +62396,7 @@
         <v>2322</v>
       </c>
     </row>
-    <row r="457" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:13">
       <c r="A457" s="5">
         <v>43929</v>
       </c>
@@ -62383,7 +62437,7 @@
         <v>2548</v>
       </c>
     </row>
-    <row r="458" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:13">
       <c r="A458" s="5">
         <v>43936</v>
       </c>
@@ -62424,7 +62478,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="459" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:13">
       <c r="A459" s="5">
         <v>43943</v>
       </c>
@@ -62465,7 +62519,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="460" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:13">
       <c r="A460" s="5">
         <v>43950</v>
       </c>
@@ -62506,7 +62560,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="461" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:13">
       <c r="A461" s="5">
         <v>43957</v>
       </c>
@@ -62547,7 +62601,7 @@
         <v>2592</v>
       </c>
     </row>
-    <row r="462" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:13">
       <c r="A462" s="5">
         <v>43964</v>
       </c>
@@ -62588,7 +62642,7 @@
         <v>2592</v>
       </c>
     </row>
-    <row r="463" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:13">
       <c r="A463" s="5">
         <v>43971</v>
       </c>
@@ -62629,7 +62683,7 @@
         <v>2516</v>
       </c>
     </row>
-    <row r="464" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:13">
       <c r="A464" s="5">
         <v>43978</v>
       </c>
@@ -62670,7 +62724,7 @@
         <v>2516</v>
       </c>
     </row>
-    <row r="465" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:13">
       <c r="A465" s="5">
         <v>43985</v>
       </c>
@@ -62711,7 +62765,7 @@
         <v>2398</v>
       </c>
     </row>
-    <row r="466" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:13">
       <c r="A466" s="5">
         <v>43992</v>
       </c>
@@ -62752,7 +62806,7 @@
         <v>2398</v>
       </c>
     </row>
-    <row r="467" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:13">
       <c r="A467" s="5">
         <v>43999</v>
       </c>
@@ -62793,7 +62847,7 @@
         <v>2577</v>
       </c>
     </row>
-    <row r="468" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:13">
       <c r="A468" s="5">
         <v>44006</v>
       </c>
@@ -62834,7 +62888,7 @@
         <v>2443</v>
       </c>
     </row>
-    <row r="469" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:13">
       <c r="A469" s="5">
         <v>44013</v>
       </c>
@@ -62875,7 +62929,7 @@
         <v>2369</v>
       </c>
     </row>
-    <row r="470" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:13">
       <c r="A470" s="5">
         <v>44020</v>
       </c>
@@ -62916,7 +62970,7 @@
         <v>2326</v>
       </c>
     </row>
-    <row r="471" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:13">
       <c r="A471" s="5">
         <v>44027</v>
       </c>
@@ -62957,7 +63011,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="472" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:13">
       <c r="A472" s="5">
         <v>44034</v>
       </c>
@@ -62998,7 +63052,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="473" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:13">
       <c r="A473" s="5">
         <v>44041</v>
       </c>
@@ -63039,7 +63093,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="474" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:13">
       <c r="A474" s="5">
         <v>44048</v>
       </c>
@@ -63080,7 +63134,7 @@
         <v>2264</v>
       </c>
     </row>
-    <row r="475" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:13">
       <c r="A475" s="5">
         <v>44055</v>
       </c>
@@ -63121,7 +63175,7 @@
         <v>2202</v>
       </c>
     </row>
-    <row r="476" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:13">
       <c r="A476" s="5">
         <v>44062</v>
       </c>
@@ -63162,7 +63216,7 @@
         <v>2449</v>
       </c>
     </row>
-    <row r="477" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:13">
       <c r="A477" s="5">
         <v>44069</v>
       </c>
@@ -63203,7 +63257,7 @@
         <v>2449</v>
       </c>
     </row>
-    <row r="478" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:13">
       <c r="A478" s="5">
         <v>44076</v>
       </c>
@@ -63244,7 +63298,7 @@
         <v>2449</v>
       </c>
     </row>
-    <row r="479" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:13">
       <c r="A479" s="5">
         <v>44083</v>
       </c>
@@ -63285,7 +63339,7 @@
         <v>2421</v>
       </c>
     </row>
-    <row r="480" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:13">
       <c r="A480" s="5">
         <v>44090</v>
       </c>
@@ -63326,7 +63380,7 @@
         <v>2437</v>
       </c>
     </row>
-    <row r="481" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:13">
       <c r="A481" s="5">
         <v>44097</v>
       </c>
@@ -63367,7 +63421,7 @@
         <v>2437</v>
       </c>
     </row>
-    <row r="482" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:13">
       <c r="A482" s="5">
         <v>44104</v>
       </c>
@@ -63408,7 +63462,7 @@
         <v>2222</v>
       </c>
     </row>
-    <row r="483" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:13">
       <c r="A483" s="5">
         <v>44111</v>
       </c>
@@ -63449,7 +63503,7 @@
         <v>2134</v>
       </c>
     </row>
-    <row r="484" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:13">
       <c r="A484" s="5">
         <v>44118</v>
       </c>
@@ -63490,7 +63544,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="485" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:13">
       <c r="A485" s="5">
         <v>44125</v>
       </c>
@@ -63531,7 +63585,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="486" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:13">
       <c r="A486" s="5">
         <v>44132</v>
       </c>
@@ -63572,7 +63626,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="487" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:13">
       <c r="A487" s="5">
         <v>44139</v>
       </c>
@@ -63613,7 +63667,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="488" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:13">
       <c r="A488" s="5">
         <v>44146</v>
       </c>
@@ -63654,7 +63708,7 @@
         <v>2034</v>
       </c>
     </row>
-    <row r="489" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:13">
       <c r="A489" s="5">
         <v>44153</v>
       </c>
@@ -63695,7 +63749,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="490" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:13">
       <c r="A490" s="5">
         <v>44160</v>
       </c>
@@ -63736,7 +63790,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="491" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:13">
       <c r="A491" s="5">
         <v>44167</v>
       </c>
@@ -63777,7 +63831,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="492" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:13">
       <c r="A492" s="5">
         <v>44174</v>
       </c>
@@ -63818,7 +63872,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="493" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:13">
       <c r="A493" s="5">
         <v>44181</v>
       </c>
@@ -63859,7 +63913,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="494" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:13">
       <c r="A494" s="5">
         <v>44188</v>
       </c>
@@ -63900,7 +63954,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="495" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:13">
       <c r="A495" s="5">
         <v>44195</v>
       </c>
@@ -63941,7 +63995,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="496" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:13">
       <c r="A496" s="5">
         <v>44202</v>
       </c>
@@ -63982,7 +64036,7 @@
         <v>2185</v>
       </c>
     </row>
-    <row r="497" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:13">
       <c r="A497" s="5">
         <v>44209</v>
       </c>
@@ -64023,7 +64077,7 @@
         <v>2116</v>
       </c>
     </row>
-    <row r="498" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:13">
       <c r="A498" s="5">
         <v>44216</v>
       </c>
@@ -64064,7 +64118,7 @@
         <v>2283</v>
       </c>
     </row>
-    <row r="499" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:13">
       <c r="A499" s="5">
         <v>44223</v>
       </c>
@@ -64105,7 +64159,7 @@
         <v>2283</v>
       </c>
     </row>
-    <row r="500" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:13">
       <c r="A500" s="5">
         <v>44230</v>
       </c>
@@ -64146,7 +64200,7 @@
         <v>2254</v>
       </c>
     </row>
-    <row r="501" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:13">
       <c r="A501" s="5">
         <v>44237</v>
       </c>
@@ -64187,7 +64241,7 @@
         <v>2299</v>
       </c>
     </row>
-    <row r="502" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:13">
       <c r="A502" s="5">
         <v>44244</v>
       </c>
@@ -64228,7 +64282,7 @@
         <v>2299</v>
       </c>
     </row>
-    <row r="503" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:13">
       <c r="A503" s="5">
         <v>44251</v>
       </c>
@@ -64269,7 +64323,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="504" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:13">
       <c r="A504" s="5">
         <v>44258</v>
       </c>
@@ -64310,7 +64364,7 @@
         <v>2342</v>
       </c>
     </row>
-    <row r="505" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:13">
       <c r="A505" s="5">
         <v>44265</v>
       </c>
@@ -64351,7 +64405,7 @@
         <v>2359</v>
       </c>
     </row>
-    <row r="506" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:13">
       <c r="A506" s="5">
         <v>44272</v>
       </c>
@@ -64392,7 +64446,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="507" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:13">
       <c r="A507" s="5">
         <v>44279</v>
       </c>
@@ -64433,7 +64487,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="508" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:13">
       <c r="A508" s="5">
         <v>44286</v>
       </c>
@@ -64474,7 +64528,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="509" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:13">
       <c r="A509" s="5">
         <v>44293</v>
       </c>
@@ -64515,7 +64569,7 @@
         <v>2621</v>
       </c>
     </row>
-    <row r="510" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:13">
       <c r="A510" s="5">
         <v>44300</v>
       </c>
@@ -64556,7 +64610,7 @@
         <v>2623</v>
       </c>
     </row>
-    <row r="511" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:13">
       <c r="A511" s="5">
         <v>44307</v>
       </c>
@@ -64597,7 +64651,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="512" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:13">
       <c r="A512" s="5">
         <v>44314</v>
       </c>
@@ -64638,7 +64692,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="513" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:13">
       <c r="A513" s="5">
         <v>44321</v>
       </c>
@@ -64679,7 +64733,7 @@
         <v>3505</v>
       </c>
     </row>
-    <row r="514" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:13">
       <c r="A514" s="5">
         <v>44328</v>
       </c>
@@ -64720,7 +64774,7 @@
         <v>3550</v>
       </c>
     </row>
-    <row r="515" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:13">
       <c r="A515" s="5">
         <v>44335</v>
       </c>
@@ -64761,7 +64815,7 @@
         <v>3553</v>
       </c>
     </row>
-    <row r="516" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:13">
       <c r="A516" s="5">
         <v>44342</v>
       </c>
@@ -64802,7 +64856,7 @@
         <v>3670</v>
       </c>
     </row>
-    <row r="517" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:13">
       <c r="A517" s="5">
         <v>44349</v>
       </c>
@@ -64843,7 +64897,7 @@
         <v>3720</v>
       </c>
     </row>
-    <row r="518" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:13">
       <c r="A518" s="5">
         <v>44356</v>
       </c>
@@ -64884,7 +64938,7 @@
         <v>3988</v>
       </c>
     </row>
-    <row r="519" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:13">
       <c r="A519" s="5">
         <v>44363</v>
       </c>
@@ -64925,7 +64979,7 @@
         <v>4607</v>
       </c>
     </row>
-    <row r="520" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:13">
       <c r="A520" s="5">
         <v>44370</v>
       </c>
@@ -64966,7 +65020,7 @@
         <v>4744</v>
       </c>
     </row>
-    <row r="521" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:13">
       <c r="A521" s="5">
         <v>44377</v>
       </c>
@@ -65007,7 +65061,7 @@
         <v>5008</v>
       </c>
     </row>
-    <row r="522" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:13">
       <c r="A522" s="5">
         <v>44384</v>
       </c>
@@ -65048,7 +65102,7 @@
         <v>5336</v>
       </c>
     </row>
-    <row r="523" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:13">
       <c r="A523" s="5">
         <v>44391</v>
       </c>
@@ -65089,7 +65143,7 @@
         <v>5362</v>
       </c>
     </row>
-    <row r="524" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:13">
       <c r="A524" s="5">
         <v>44398</v>
       </c>
@@ -65130,7 +65184,7 @@
         <v>5364</v>
       </c>
     </row>
-    <row r="525" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:13">
       <c r="A525" s="5">
         <v>44405</v>
       </c>
@@ -65171,7 +65225,7 @@
         <v>5624</v>
       </c>
     </row>
-    <row r="526" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:13">
       <c r="A526" s="5">
         <v>44412</v>
       </c>
@@ -65212,7 +65266,7 @@
         <v>6417</v>
       </c>
     </row>
-    <row r="527" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:13">
       <c r="A527" s="5">
         <v>44419</v>
       </c>
@@ -65253,7 +65307,7 @@
         <v>6390</v>
       </c>
     </row>
-    <row r="528" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:13">
       <c r="A528" s="5">
         <v>44426</v>
       </c>
@@ -65294,7 +65348,7 @@
         <v>6435</v>
       </c>
     </row>
-    <row r="529" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:13">
       <c r="A529" s="5">
         <v>44433</v>
       </c>
@@ -65335,7 +65389,7 @@
         <v>6461</v>
       </c>
     </row>
-    <row r="530" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:13">
       <c r="A530" s="5">
         <v>44440</v>
       </c>
@@ -65376,7 +65430,7 @@
         <v>5776</v>
       </c>
     </row>
-    <row r="531" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:13">
       <c r="A531" s="5">
         <v>44447</v>
       </c>
@@ -65417,7 +65471,7 @@
         <v>6160</v>
       </c>
     </row>
-    <row r="532" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:13">
       <c r="A532" s="5">
         <v>44454</v>
       </c>
@@ -65458,7 +65512,7 @@
         <v>6162</v>
       </c>
     </row>
-    <row r="533" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:13">
       <c r="A533" s="5">
         <v>44461</v>
       </c>
@@ -65499,7 +65553,7 @@
         <v>6179</v>
       </c>
     </row>
-    <row r="534" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:13">
       <c r="A534" s="5">
         <v>44468</v>
       </c>
@@ -65540,7 +65594,7 @@
         <v>6192</v>
       </c>
     </row>
-    <row r="535" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:13">
       <c r="A535" s="5">
         <v>44475</v>
       </c>
@@ -65581,7 +65635,7 @@
         <v>6209</v>
       </c>
     </row>
-    <row r="536" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:13">
       <c r="A536" s="5">
         <v>44482</v>
       </c>
@@ -65622,7 +65676,7 @@
         <v>6200</v>
       </c>
     </row>
-    <row r="537" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:13">
       <c r="A537" s="5">
         <v>44489</v>
       </c>
@@ -65663,7 +65717,7 @@
         <v>6157</v>
       </c>
     </row>
-    <row r="538" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:13">
       <c r="A538" s="5">
         <v>44496</v>
       </c>
@@ -65704,7 +65758,7 @@
         <v>6161</v>
       </c>
     </row>
-    <row r="539" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:13">
       <c r="A539" s="5">
         <v>44503</v>
       </c>
@@ -65745,7 +65799,7 @@
         <v>6123</v>
       </c>
     </row>
-    <row r="540" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:13">
       <c r="A540" s="5">
         <v>44510</v>
       </c>
@@ -65786,7 +65840,7 @@
         <v>6255</v>
       </c>
     </row>
-    <row r="541" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:13">
       <c r="A541" s="5">
         <v>44517</v>
       </c>
@@ -65827,7 +65881,7 @@
         <v>6272</v>
       </c>
     </row>
-    <row r="542" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:13">
       <c r="A542" s="5">
         <v>44524</v>
       </c>
@@ -65868,7 +65922,7 @@
         <v>6232</v>
       </c>
     </row>
-    <row r="543" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:13">
       <c r="A543" s="5">
         <v>44531</v>
       </c>
@@ -65909,7 +65963,7 @@
         <v>6214</v>
       </c>
     </row>
-    <row r="544" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:13">
       <c r="A544" s="5">
         <v>44538</v>
       </c>
@@ -65950,7 +66004,7 @@
         <v>6283</v>
       </c>
     </row>
-    <row r="545" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:13">
       <c r="A545" s="5">
         <v>44545</v>
       </c>
@@ -65991,7 +66045,7 @@
         <v>6272</v>
       </c>
     </row>
-    <row r="546" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:13">
       <c r="A546" s="5">
         <v>44552</v>
       </c>
@@ -66032,7 +66086,7 @@
         <v>6290</v>
       </c>
     </row>
-    <row r="547" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:13">
       <c r="A547" s="5">
         <v>44566</v>
       </c>
@@ -66073,7 +66127,7 @@
         <v>6280</v>
       </c>
     </row>
-    <row r="548" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:13">
       <c r="A548" s="5">
         <v>44573</v>
       </c>
@@ -66114,7 +66168,7 @@
         <v>6233</v>
       </c>
     </row>
-    <row r="549" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:13">
       <c r="A549" s="5">
         <v>44580</v>
       </c>
@@ -66155,7 +66209,7 @@
         <v>6292</v>
       </c>
     </row>
-    <row r="550" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:13">
       <c r="A550" s="5">
         <v>44587</v>
       </c>
@@ -66196,7 +66250,7 @@
         <v>6315</v>
       </c>
     </row>
-    <row r="551" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:13">
       <c r="A551" s="5">
         <v>44594</v>
       </c>
@@ -66237,7 +66291,7 @@
         <v>6455</v>
       </c>
     </row>
-    <row r="552" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:13">
       <c r="A552" s="5">
         <v>44601</v>
       </c>
@@ -66278,7 +66332,7 @@
         <v>6453</v>
       </c>
     </row>
-    <row r="553" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:13">
       <c r="A553" s="5">
         <v>44608</v>
       </c>
@@ -66319,7 +66373,7 @@
         <v>6514</v>
       </c>
     </row>
-    <row r="554" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:13">
       <c r="A554" s="5">
         <v>44615</v>
       </c>
@@ -66360,7 +66414,7 @@
         <v>6518</v>
       </c>
     </row>
-    <row r="555" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:13">
       <c r="A555" s="5">
         <v>44622</v>
       </c>
@@ -66401,7 +66455,7 @@
         <v>6476</v>
       </c>
     </row>
-    <row r="556" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:13">
       <c r="A556" s="5">
         <v>44629</v>
       </c>
@@ -66442,7 +66496,7 @@
         <v>6494</v>
       </c>
     </row>
-    <row r="557" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:13">
       <c r="A557" s="5">
         <v>44636</v>
       </c>
@@ -66483,7 +66537,7 @@
         <v>6491</v>
       </c>
     </row>
-    <row r="558" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:13">
       <c r="A558" s="5">
         <v>44643</v>
       </c>
@@ -66524,7 +66578,7 @@
         <v>6793</v>
       </c>
     </row>
-    <row r="559" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:13">
       <c r="A559" s="5">
         <v>44650</v>
       </c>
@@ -66565,7 +66619,7 @@
         <v>6680</v>
       </c>
     </row>
-    <row r="560" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:13">
       <c r="A560" s="5">
         <v>44657</v>
       </c>
@@ -66606,7 +66660,7 @@
         <v>6903</v>
       </c>
     </row>
-    <row r="561" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:13">
       <c r="A561" s="5">
         <v>44664</v>
       </c>
@@ -66647,7 +66701,7 @@
         <v>6929</v>
       </c>
     </row>
-    <row r="562" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:13">
       <c r="A562" s="5">
         <v>44671</v>
       </c>
@@ -66688,7 +66742,7 @@
         <v>6934</v>
       </c>
     </row>
-    <row r="563" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:13">
       <c r="A563" s="5">
         <v>44678</v>
       </c>
@@ -66729,7 +66783,7 @@
         <v>6940</v>
       </c>
     </row>
-    <row r="564" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:13">
       <c r="A564" s="5">
         <v>44685</v>
       </c>
@@ -66770,7 +66824,7 @@
         <v>7212</v>
       </c>
     </row>
-    <row r="565" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:13">
       <c r="A565" s="5">
         <v>44692</v>
       </c>
@@ -66811,7 +66865,7 @@
         <v>7201</v>
       </c>
     </row>
-    <row r="566" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:13">
       <c r="A566" s="5">
         <v>44699</v>
       </c>
@@ -66852,7 +66906,7 @@
         <v>7189</v>
       </c>
     </row>
-    <row r="567" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:13">
       <c r="A567" s="5">
         <v>44706</v>
       </c>
@@ -66893,7 +66947,7 @@
         <v>7186</v>
       </c>
     </row>
-    <row r="568" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:13">
       <c r="A568" s="5">
         <v>44713</v>
       </c>
@@ -66934,7 +66988,7 @@
         <v>7186</v>
       </c>
     </row>
-    <row r="569" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:13">
       <c r="A569" s="5">
         <v>44720</v>
       </c>
@@ -66975,7 +67029,7 @@
         <v>7100</v>
       </c>
     </row>
-    <row r="570" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:13">
       <c r="A570" s="5">
         <v>44727</v>
       </c>
@@ -67016,7 +67070,7 @@
         <v>6938</v>
       </c>
     </row>
-    <row r="571" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:13">
       <c r="A571" s="5">
         <v>44734</v>
       </c>
@@ -67057,7 +67111,7 @@
         <v>6849</v>
       </c>
     </row>
-    <row r="572" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:13">
       <c r="A572" s="5">
         <v>44741</v>
       </c>
@@ -67098,7 +67152,7 @@
         <v>6783</v>
       </c>
     </row>
-    <row r="573" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:13">
       <c r="A573" s="5">
         <v>44748</v>
       </c>
@@ -67139,7 +67193,7 @@
         <v>6801</v>
       </c>
     </row>
-    <row r="574" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:13">
       <c r="A574" s="5">
         <v>44755</v>
       </c>
@@ -67180,7 +67234,7 @@
         <v>6929</v>
       </c>
     </row>
-    <row r="575" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:13">
       <c r="A575" s="5">
         <v>44762</v>
       </c>
@@ -67221,7 +67275,7 @@
         <v>6926</v>
       </c>
     </row>
-    <row r="576" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:13">
       <c r="A576" s="5">
         <v>44769</v>
       </c>
@@ -67262,7 +67316,7 @@
         <v>6921</v>
       </c>
     </row>
-    <row r="577" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:13">
       <c r="A577" s="5">
         <v>44776</v>
       </c>
@@ -67303,7 +67357,7 @@
         <v>6939</v>
       </c>
     </row>
-    <row r="578" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:13">
       <c r="A578" s="5">
         <v>44783</v>
       </c>
@@ -67344,7 +67398,7 @@
         <v>6945</v>
       </c>
     </row>
-    <row r="579" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:13">
       <c r="A579" s="5">
         <v>44790</v>
       </c>
@@ -67385,7 +67439,7 @@
         <v>6936</v>
       </c>
     </row>
-    <row r="580" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:13">
       <c r="A580" s="5">
         <v>44797</v>
       </c>
@@ -67426,7 +67480,7 @@
         <v>6922</v>
       </c>
     </row>
-    <row r="581" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:13">
       <c r="A581" s="5">
         <v>44804</v>
       </c>
@@ -67467,7 +67521,7 @@
         <v>6839</v>
       </c>
     </row>
-    <row r="582" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:13">
       <c r="A582" s="5">
         <v>44811</v>
       </c>
@@ -67508,7 +67562,7 @@
         <v>6688</v>
       </c>
     </row>
-    <row r="583" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:13">
       <c r="A583" s="5">
         <v>44818</v>
       </c>
@@ -67549,7 +67603,7 @@
         <v>6607</v>
       </c>
     </row>
-    <row r="584" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:13">
       <c r="A584" s="5">
         <v>44825</v>
       </c>
@@ -67590,7 +67644,7 @@
         <v>6737</v>
       </c>
     </row>
-    <row r="585" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:13">
       <c r="A585" s="5">
         <v>44832</v>
       </c>
@@ -67631,7 +67685,7 @@
         <v>7038</v>
       </c>
     </row>
-    <row r="586" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:13">
       <c r="A586" s="5">
         <v>44839</v>
       </c>
@@ -67672,7 +67726,7 @@
         <v>7252</v>
       </c>
     </row>
-    <row r="587" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:13">
       <c r="A587" s="5">
         <v>44846</v>
       </c>
@@ -67713,7 +67767,7 @@
         <v>7295</v>
       </c>
     </row>
-    <row r="588" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:13">
       <c r="A588" s="5">
         <v>44853</v>
       </c>
@@ -67754,7 +67808,7 @@
         <v>7264</v>
       </c>
     </row>
-    <row r="589" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:13">
       <c r="A589" s="5">
         <v>44860</v>
       </c>
@@ -67795,7 +67849,7 @@
         <v>7284</v>
       </c>
     </row>
-    <row r="590" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:13">
       <c r="A590" s="5">
         <v>44867</v>
       </c>
@@ -67836,7 +67890,7 @@
         <v>7426</v>
       </c>
     </row>
-    <row r="591" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:13">
       <c r="A591" s="5">
         <v>44874</v>
       </c>
@@ -67877,7 +67931,7 @@
         <v>7336</v>
       </c>
     </row>
-    <row r="592" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:13">
       <c r="A592" s="5">
         <v>44881</v>
       </c>
@@ -67918,7 +67972,7 @@
         <v>7363</v>
       </c>
     </row>
-    <row r="593" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:13">
       <c r="A593" s="5">
         <v>44888</v>
       </c>
@@ -67959,7 +68013,7 @@
         <v>7224</v>
       </c>
     </row>
-    <row r="594" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:13">
       <c r="A594" s="5">
         <v>44895</v>
       </c>
@@ -68000,7 +68054,7 @@
         <v>7240</v>
       </c>
     </row>
-    <row r="595" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:13">
       <c r="A595" s="5">
         <v>44902</v>
       </c>
@@ -68041,7 +68095,7 @@
         <v>7151</v>
       </c>
     </row>
-    <row r="596" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:13">
       <c r="A596" s="5">
         <v>44909</v>
       </c>
@@ -68082,7 +68136,7 @@
         <v>7050</v>
       </c>
     </row>
-    <row r="597" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:13">
       <c r="A597" s="5">
         <v>44916</v>
       </c>
@@ -68123,7 +68177,7 @@
         <v>6989</v>
       </c>
     </row>
-    <row r="598" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:13">
       <c r="A598" s="5">
         <v>44930</v>
       </c>
@@ -68164,7 +68218,7 @@
         <v>6589</v>
       </c>
     </row>
-    <row r="599" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:13">
       <c r="A599" s="5">
         <v>44937</v>
       </c>
@@ -68205,7 +68259,7 @@
         <v>6363</v>
       </c>
     </row>
-    <row r="600" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:13">
       <c r="A600" s="5">
         <v>44944</v>
       </c>
@@ -68246,7 +68300,7 @@
         <v>6296</v>
       </c>
     </row>
-    <row r="601" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:13">
       <c r="A601" s="5">
         <v>44951</v>
       </c>
@@ -68287,7 +68341,7 @@
         <v>6322</v>
       </c>
     </row>
-    <row r="602" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:13">
       <c r="A602" s="5">
         <v>44958</v>
       </c>
@@ -68328,7 +68382,7 @@
         <v>6262</v>
       </c>
     </row>
-    <row r="603" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:13">
       <c r="A603" s="5">
         <v>44965</v>
       </c>
@@ -68369,7 +68423,7 @@
         <v>6010</v>
       </c>
     </row>
-    <row r="604" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:13">
       <c r="A604" s="5">
         <v>44972</v>
       </c>
@@ -68410,7 +68464,7 @@
         <v>5675</v>
       </c>
     </row>
-    <row r="605" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:13">
       <c r="A605" s="5">
         <v>44979</v>
       </c>
@@ -68451,7 +68505,7 @@
         <v>5640</v>
       </c>
     </row>
-    <row r="606" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:13">
       <c r="A606" s="5">
         <v>44986</v>
       </c>
@@ -68492,7 +68546,7 @@
         <v>5573</v>
       </c>
     </row>
-    <row r="607" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:13">
       <c r="A607" s="5">
         <v>44993</v>
       </c>
@@ -68533,7 +68587,7 @@
         <v>5377</v>
       </c>
     </row>
-    <row r="608" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:13">
       <c r="A608" s="5">
         <v>45000</v>
       </c>
@@ -68574,7 +68628,7 @@
         <v>5326</v>
       </c>
     </row>
-    <row r="609" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:13">
       <c r="A609" s="5">
         <v>45007</v>
       </c>
@@ -68615,7 +68669,7 @@
         <v>5061</v>
       </c>
     </row>
-    <row r="610" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:13">
       <c r="A610" s="5">
         <v>45014</v>
       </c>
@@ -68656,7 +68710,7 @@
         <v>4978</v>
       </c>
     </row>
-    <row r="611" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:13">
       <c r="A611" s="5">
         <v>45021</v>
       </c>
@@ -68697,7 +68751,7 @@
         <v>4936</v>
       </c>
     </row>
-    <row r="612" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:13">
       <c r="A612" s="5">
         <v>45028</v>
       </c>
@@ -68738,7 +68792,7 @@
         <v>4919</v>
       </c>
     </row>
-    <row r="613" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:13">
       <c r="A613" s="5">
         <v>45035</v>
       </c>
@@ -68779,7 +68833,7 @@
         <v>4881</v>
       </c>
     </row>
-    <row r="614" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:13">
       <c r="A614" s="5">
         <v>45042</v>
       </c>
@@ -68820,7 +68874,7 @@
         <v>4806</v>
       </c>
     </row>
-    <row r="615" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:13">
       <c r="A615" s="5">
         <v>45049</v>
       </c>
@@ -68861,7 +68915,7 @@
         <v>4783</v>
       </c>
     </row>
-    <row r="616" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:13">
       <c r="A616" s="5">
         <v>45056</v>
       </c>
@@ -68902,7 +68956,7 @@
         <v>4530</v>
       </c>
     </row>
-    <row r="617" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:13">
       <c r="A617" s="5">
         <v>45063</v>
       </c>
@@ -68943,7 +68997,7 @@
         <v>4434</v>
       </c>
     </row>
-    <row r="618" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:13">
       <c r="A618" s="5">
         <v>45070</v>
       </c>
@@ -68984,7 +69038,7 @@
         <v>3969</v>
       </c>
     </row>
-    <row r="619" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:13">
       <c r="A619" s="5">
         <v>45077</v>
       </c>
@@ -69025,7 +69079,7 @@
         <v>3714</v>
       </c>
     </row>
-    <row r="620" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:13">
       <c r="A620" s="5">
         <v>45084</v>
       </c>
@@ -69066,7 +69120,7 @@
         <v>3375</v>
       </c>
     </row>
-    <row r="621" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:13">
       <c r="A621" s="5">
         <v>45091</v>
       </c>
@@ -69107,7 +69161,7 @@
         <v>3195</v>
       </c>
     </row>
-    <row r="622" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:13">
       <c r="A622" s="5">
         <v>45098</v>
       </c>
@@ -69148,7 +69202,7 @@
         <v>3226</v>
       </c>
     </row>
-    <row r="623" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:13">
       <c r="A623" s="5">
         <v>45105</v>
       </c>
@@ -69189,7 +69243,7 @@
         <v>2670</v>
       </c>
     </row>
-    <row r="624" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:13">
       <c r="A624" s="5">
         <v>45112</v>
       </c>
@@ -69230,7 +69284,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="625" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:13">
       <c r="A625" s="5">
         <v>45119</v>
       </c>
@@ -69271,7 +69325,7 @@
         <v>1769</v>
       </c>
     </row>
-    <row r="626" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:13">
       <c r="A626" s="5">
         <v>45126</v>
       </c>
@@ -69312,7 +69366,7 @@
         <v>1640</v>
       </c>
     </row>
-    <row r="627" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:13">
       <c r="A627" s="5">
         <v>45133</v>
       </c>
@@ -69353,7 +69407,7 @@
         <v>1590</v>
       </c>
     </row>
-    <row r="628" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:13">
       <c r="A628" s="5">
         <v>45140</v>
       </c>
@@ -69394,7 +69448,7 @@
         <v>1587</v>
       </c>
     </row>
-    <row r="629" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:13">
       <c r="A629" s="5">
         <v>45147</v>
       </c>
@@ -69435,7 +69489,7 @@
         <v>1593</v>
       </c>
     </row>
-    <row r="630" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:13">
       <c r="A630" s="5">
         <v>45154</v>
       </c>
@@ -69476,7 +69530,7 @@
         <v>1577</v>
       </c>
     </row>
-    <row r="631" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:13">
       <c r="A631" s="5">
         <v>45161</v>
       </c>
@@ -69517,7 +69571,7 @@
         <v>1585</v>
       </c>
     </row>
-    <row r="632" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:13">
       <c r="A632" s="5">
         <v>45168</v>
       </c>
@@ -69558,7 +69612,7 @@
         <v>1562</v>
       </c>
     </row>
-    <row r="633" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:13">
       <c r="A633" s="5">
         <v>45175</v>
       </c>
@@ -69599,7 +69653,7 @@
         <v>1561</v>
       </c>
     </row>
-    <row r="634" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:13">
       <c r="A634" s="5">
         <v>45182</v>
       </c>
@@ -69640,7 +69694,7 @@
         <v>1565</v>
       </c>
     </row>
-    <row r="635" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:13">
       <c r="A635" s="5">
         <v>45189</v>
       </c>
@@ -69681,7 +69735,7 @@
         <v>1534</v>
       </c>
     </row>
-    <row r="636" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:13">
       <c r="A636" s="5">
         <v>45196</v>
       </c>
@@ -69722,7 +69776,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="637" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:13">
       <c r="A637" s="5">
         <v>45203</v>
       </c>
@@ -69763,7 +69817,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="638" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:13">
       <c r="A638" s="5">
         <v>45210</v>
       </c>
@@ -69804,7 +69858,7 @@
         <v>1535</v>
       </c>
     </row>
-    <row r="639" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:13">
       <c r="A639" s="5">
         <v>45217</v>
       </c>
@@ -69845,7 +69899,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="640" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:13">
       <c r="A640" s="5">
         <v>45224</v>
       </c>
@@ -69886,7 +69940,7 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="641" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:13">
       <c r="A641" s="5">
         <v>45231</v>
       </c>
@@ -69927,7 +69981,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="642" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:13">
       <c r="A642" s="5">
         <v>45238</v>
       </c>
@@ -69968,7 +70022,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="643" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:13">
       <c r="A643" s="5">
         <v>45245</v>
       </c>
@@ -70009,7 +70063,7 @@
         <v>1510</v>
       </c>
     </row>
-    <row r="644" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:13">
       <c r="A644" s="5">
         <v>45252</v>
       </c>
@@ -70050,7 +70104,7 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="645" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:13">
       <c r="A645" s="5">
         <v>45259</v>
       </c>
@@ -70091,7 +70145,7 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="646" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:13">
       <c r="A646" s="5">
         <v>45266</v>
       </c>
@@ -70132,7 +70186,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="647" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:13">
       <c r="A647" s="5">
         <v>45273</v>
       </c>
@@ -70173,7 +70227,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="648" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:13">
       <c r="A648" s="5">
         <v>45280</v>
       </c>
@@ -70214,7 +70268,7 @@
         <v>1480</v>
       </c>
     </row>
-    <row r="649" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:13">
       <c r="A649" s="5">
         <v>45294</v>
       </c>
@@ -70255,7 +70309,7 @@
         <v>1503</v>
       </c>
     </row>
-    <row r="650" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:13">
       <c r="A650" s="5">
         <v>45301</v>
       </c>
@@ -70296,7 +70350,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="651" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:13">
       <c r="A651" s="5">
         <v>45308</v>
       </c>
@@ -70337,7 +70391,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="652" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:13">
       <c r="A652" s="5">
         <v>45315</v>
       </c>
@@ -70378,7 +70432,7 @@
         <v>1576</v>
       </c>
     </row>
-    <row r="653" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:13">
       <c r="A653" s="5">
         <v>45322</v>
       </c>
@@ -70419,7 +70473,7 @@
         <v>1589</v>
       </c>
     </row>
-    <row r="654" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:13">
       <c r="A654" s="5">
         <v>45329</v>
       </c>
@@ -70460,7 +70514,7 @@
         <v>1978</v>
       </c>
     </row>
-    <row r="655" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:13">
       <c r="A655" s="5">
         <v>45336</v>
       </c>
@@ -70501,7 +70555,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="656" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:13">
       <c r="A656" s="5">
         <v>45343</v>
       </c>
@@ -70542,7 +70596,7 @@
         <v>2204</v>
       </c>
     </row>
-    <row r="657" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:13">
       <c r="A657" s="5">
         <v>45350</v>
       </c>
@@ -70583,7 +70637,7 @@
         <v>2220</v>
       </c>
     </row>
-    <row r="658" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:13">
       <c r="A658" s="5">
         <v>45357</v>
       </c>
@@ -70624,7 +70678,7 @@
         <v>2192</v>
       </c>
     </row>
-    <row r="659" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:13">
       <c r="A659" s="5">
         <v>45364</v>
       </c>
@@ -70665,7 +70719,7 @@
         <v>2242</v>
       </c>
     </row>
-    <row r="660" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:13">
       <c r="A660" s="5">
         <v>45371</v>
       </c>
@@ -70706,7 +70760,7 @@
         <v>2281</v>
       </c>
     </row>
-    <row r="661" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:13">
       <c r="A661" s="5">
         <v>45378</v>
       </c>
@@ -70747,7 +70801,7 @@
         <v>2261</v>
       </c>
     </row>
-    <row r="662" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:13">
       <c r="A662" s="5">
         <v>45385</v>
       </c>
@@ -70788,7 +70842,7 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="663" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:13">
       <c r="A663" s="5">
         <v>45392</v>
       </c>
@@ -70829,7 +70883,7 @@
         <v>2224</v>
       </c>
     </row>
-    <row r="664" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:13">
       <c r="A664" s="5">
         <v>45399</v>
       </c>
@@ -70870,7 +70924,7 @@
         <v>2291</v>
       </c>
     </row>
-    <row r="665" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:13">
       <c r="A665" s="5">
         <v>45406</v>
       </c>
@@ -70911,7 +70965,7 @@
         <v>2214</v>
       </c>
     </row>
-    <row r="666" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:13">
       <c r="A666" s="5">
         <v>45413</v>
       </c>
@@ -70952,7 +71006,7 @@
         <v>2210</v>
       </c>
     </row>
-    <row r="667" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:13">
       <c r="A667" s="5">
         <v>45420</v>
       </c>
@@ -70993,7 +71047,7 @@
         <v>2160</v>
       </c>
     </row>
-    <row r="668" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:13">
       <c r="A668" s="5">
         <v>45427</v>
       </c>
@@ -71034,7 +71088,7 @@
         <v>2209</v>
       </c>
     </row>
-    <row r="669" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:13">
       <c r="A669" s="5">
         <v>45434</v>
       </c>
@@ -71075,7 +71129,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="670" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:13">
       <c r="A670" s="5">
         <v>45441</v>
       </c>
@@ -71116,7 +71170,7 @@
         <v>2222</v>
       </c>
     </row>
-    <row r="671" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:13">
       <c r="A671" s="5">
         <v>45448</v>
       </c>
@@ -71157,7 +71211,7 @@
         <v>2136</v>
       </c>
     </row>
-    <row r="672" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:13">
       <c r="A672" s="5">
         <v>45455</v>
       </c>
@@ -71198,7 +71252,7 @@
         <v>2118</v>
       </c>
     </row>
-    <row r="673" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:13">
       <c r="A673" s="5">
         <v>45462</v>
       </c>
@@ -71239,7 +71293,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="674" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:13">
       <c r="A674" s="5">
         <v>45469</v>
       </c>
@@ -71280,7 +71334,7 @@
         <v>2044</v>
       </c>
     </row>
-    <row r="675" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:13">
       <c r="A675" s="5">
         <v>45476</v>
       </c>
@@ -71321,7 +71375,7 @@
         <v>1977</v>
       </c>
     </row>
-    <row r="676" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:13">
       <c r="A676" s="5">
         <v>45483</v>
       </c>
@@ -71362,7 +71416,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="677" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:13">
       <c r="A677" s="5">
         <v>45490</v>
       </c>
@@ -71403,7 +71457,7 @@
         <v>1943</v>
       </c>
     </row>
-    <row r="678" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:13">
       <c r="A678" s="5">
         <v>45497</v>
       </c>
@@ -71444,7 +71498,7 @@
         <v>1954</v>
       </c>
     </row>
-    <row r="679" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:13">
       <c r="A679" s="5">
         <v>45504</v>
       </c>
@@ -71485,7 +71539,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="680" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:13">
       <c r="A680" s="5">
         <v>45511</v>
       </c>
@@ -71526,7 +71580,7 @@
         <v>1967</v>
       </c>
     </row>
-    <row r="681" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:13">
       <c r="A681" s="5">
         <v>45518</v>
       </c>
@@ -71567,7 +71621,7 @@
         <v>1961</v>
       </c>
     </row>
-    <row r="682" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:13">
       <c r="A682" s="5">
         <v>45525</v>
       </c>
@@ -71608,7 +71662,7 @@
         <v>1934</v>
       </c>
     </row>
-    <row r="683" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:13">
       <c r="A683" s="5">
         <v>45532</v>
       </c>
@@ -71649,7 +71703,7 @@
         <v>1908</v>
       </c>
     </row>
-    <row r="684" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:13">
       <c r="A684" s="5">
         <v>45539</v>
       </c>
@@ -71690,7 +71744,7 @@
         <v>2212</v>
       </c>
     </row>
-    <row r="685" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:13">
       <c r="A685" s="5">
         <v>45546</v>
       </c>
@@ -71731,7 +71785,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="686" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:13">
       <c r="A686" s="5">
         <v>45553</v>
       </c>
@@ -71772,7 +71826,7 @@
         <v>2056</v>
       </c>
     </row>
-    <row r="687" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:13">
       <c r="A687" s="5">
         <v>45560</v>
       </c>
@@ -71813,7 +71867,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="688" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:13">
       <c r="A688" s="5">
         <v>45567</v>
       </c>
@@ -71854,7 +71908,7 @@
         <v>2061</v>
       </c>
     </row>
-    <row r="689" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:13">
       <c r="A689" s="5">
         <v>45574</v>
       </c>
@@ -71895,7 +71949,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="690" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:13">
       <c r="A690" s="5">
         <v>45581</v>
       </c>
@@ -71936,7 +71990,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="691" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:13">
       <c r="A691" s="5">
         <v>45588</v>
       </c>
@@ -71977,7 +72031,7 @@
         <v>2663</v>
       </c>
     </row>
-    <row r="692" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:13">
       <c r="A692" s="5">
         <v>45595</v>
       </c>
@@ -72018,7 +72072,7 @@
         <v>2664</v>
       </c>
     </row>
-    <row r="693" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:13">
       <c r="A693" s="5">
         <v>45602</v>
       </c>
@@ -72059,7 +72113,7 @@
         <v>2624</v>
       </c>
     </row>
-    <row r="694" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:13">
       <c r="A694" s="5">
         <v>45609</v>
       </c>
@@ -72100,7 +72154,7 @@
         <v>2658</v>
       </c>
     </row>
-    <row r="695" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:13">
       <c r="A695" s="5">
         <v>45616</v>
       </c>
@@ -72141,7 +72195,7 @@
         <v>2672</v>
       </c>
     </row>
-    <row r="696" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:13">
       <c r="A696" s="5">
         <v>45623</v>
       </c>
@@ -72182,7 +72236,7 @@
         <v>2665</v>
       </c>
     </row>
-    <row r="697" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:13">
       <c r="A697" s="5">
         <v>45630</v>
       </c>
@@ -72223,7 +72277,7 @@
         <v>2649</v>
       </c>
     </row>
-    <row r="698" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:13">
       <c r="A698" s="5">
         <v>45637</v>
       </c>
@@ -72264,7 +72318,7 @@
         <v>2622</v>
       </c>
     </row>
-    <row r="699" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:13">
       <c r="A699" s="5">
         <v>45644</v>
       </c>
@@ -72305,7 +72359,7 @@
         <v>2713</v>
       </c>
     </row>
-    <row r="700" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:13">
       <c r="A700" s="5">
         <v>45658</v>
       </c>
@@ -72346,7 +72400,7 @@
         <v>2720</v>
       </c>
     </row>
-    <row r="701" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:13">
       <c r="A701" s="5">
         <v>45665</v>
       </c>
@@ -72387,7 +72441,7 @@
         <v>2698</v>
       </c>
     </row>
-    <row r="702" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:13">
       <c r="A702" s="5">
         <v>45672</v>
       </c>
@@ -72428,7 +72482,7 @@
         <v>2798</v>
       </c>
     </row>
-    <row r="703" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:13">
       <c r="A703" s="5">
         <v>45679</v>
       </c>
@@ -72469,7 +72523,7 @@
         <v>2778</v>
       </c>
     </row>
-    <row r="704" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:13">
       <c r="A704" s="5">
         <v>45686</v>
       </c>
@@ -72510,7 +72564,7 @@
         <v>2732</v>
       </c>
     </row>
-    <row r="705" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:13">
       <c r="A705" s="5">
         <v>45693</v>
       </c>
@@ -72551,7 +72605,7 @@
         <v>2469</v>
       </c>
     </row>
-    <row r="706" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:13">
       <c r="A706" s="5">
         <v>45700</v>
       </c>
@@ -72592,7 +72646,7 @@
         <v>2463</v>
       </c>
     </row>
-    <row r="707" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:13">
       <c r="A707" s="5">
         <v>45707</v>
       </c>
@@ -72633,7 +72687,7 @@
         <v>2394</v>
       </c>
     </row>
-    <row r="708" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:13">
       <c r="A708" s="5">
         <v>45714</v>
       </c>
@@ -72674,7 +72728,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="709" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:13">
       <c r="A709" s="5">
         <v>45721</v>
       </c>
@@ -72715,7 +72769,7 @@
         <v>2359</v>
       </c>
     </row>
-    <row r="710" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:13">
       <c r="A710" s="5">
         <v>45728</v>
       </c>
@@ -72756,7 +72810,7 @@
         <v>2373</v>
       </c>
     </row>
-    <row r="711" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:13">
       <c r="A711" s="5">
         <v>45735</v>
       </c>
@@ -72797,7 +72851,7 @@
         <v>2316</v>
       </c>
     </row>
-    <row r="712" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:13">
       <c r="A712" s="5">
         <v>45742</v>
       </c>
@@ -72838,7 +72892,7 @@
         <v>2162</v>
       </c>
     </row>
-    <row r="713" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:13">
       <c r="A713" s="5">
         <v>45749</v>
       </c>
@@ -72879,7 +72933,7 @@
         <v>2124</v>
       </c>
     </row>
-    <row r="714" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:13">
       <c r="A714" s="5">
         <v>45756</v>
       </c>
@@ -72920,7 +72974,7 @@
         <v>2153</v>
       </c>
     </row>
-    <row r="715" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:13">
       <c r="A715" s="5">
         <v>45763</v>
       </c>
@@ -72961,7 +73015,7 @@
         <v>2129</v>
       </c>
     </row>
-    <row r="716" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:13">
       <c r="A716" s="5">
         <v>45770</v>
       </c>
@@ -73002,7 +73056,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="717" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:13">
       <c r="A717" s="5">
         <v>45777</v>
       </c>
@@ -73043,7 +73097,7 @@
         <v>2041</v>
       </c>
     </row>
-    <row r="718" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:13">
       <c r="A718" s="5">
         <v>45784</v>
       </c>
@@ -73084,7 +73138,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="719" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:13">
       <c r="A719" s="5">
         <v>45791</v>
       </c>
@@ -73125,7 +73179,7 @@
         <v>1961</v>
       </c>
     </row>
-    <row r="720" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:13">
       <c r="A720" s="5">
         <v>45798</v>
       </c>
@@ -73166,7 +73220,7 @@
         <v>1952</v>
       </c>
     </row>
-    <row r="721" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:13">
       <c r="A721" s="5">
         <v>45805</v>
       </c>
@@ -73207,7 +73261,7 @@
         <v>1939</v>
       </c>
     </row>
-    <row r="722" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:13">
       <c r="A722" s="5">
         <v>45812</v>
       </c>
@@ -73248,7 +73302,7 @@
         <v>1977</v>
       </c>
     </row>
-    <row r="723" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="723" spans="1:13">
       <c r="A723" s="5">
         <v>45819</v>
       </c>
@@ -73289,7 +73343,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="724" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="724" spans="1:13">
       <c r="A724" s="5">
         <v>45826</v>
       </c>
@@ -73330,7 +73384,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="725" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="725" spans="1:13">
       <c r="A725" s="5">
         <v>45833</v>
       </c>
@@ -73371,7 +73425,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="726" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="726" spans="1:13">
       <c r="A726" s="5">
         <v>45840</v>
       </c>
@@ -73412,7 +73466,7 @@
         <v>2119</v>
       </c>
     </row>
-    <row r="727" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="727" spans="1:13">
       <c r="A727" s="5">
         <v>45847</v>
       </c>
@@ -73453,7 +73507,7 @@
         <v>1990</v>
       </c>
     </row>
-    <row r="728" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="728" spans="1:13">
       <c r="A728" s="5">
         <v>45854</v>
       </c>
@@ -73494,7 +73548,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="729" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="729" spans="1:13">
       <c r="A729" s="5">
         <v>45861</v>
       </c>
@@ -73535,7 +73589,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="730" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="730" spans="1:13">
       <c r="A730" s="5">
         <v>45868</v>
       </c>
@@ -73576,7 +73630,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="731" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="731" spans="1:13">
       <c r="A731" s="5">
         <v>45875</v>
       </c>
@@ -73617,7 +73671,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="732" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="732" spans="1:13">
       <c r="A732" s="5">
         <v>45882</v>
       </c>
@@ -73658,7 +73712,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="733" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="733" spans="1:13">
       <c r="A733" s="5">
         <v>45889</v>
       </c>
@@ -73699,7 +73753,7 @@
         <v>1951</v>
       </c>
     </row>
-    <row r="734" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="734" spans="1:13">
       <c r="A734" s="5">
         <v>45896</v>
       </c>
@@ -73740,7 +73794,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="735" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="735" spans="1:13">
       <c r="A735" s="5">
         <v>45903</v>
       </c>
@@ -73781,7 +73835,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="736" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="736" spans="1:13">
       <c r="A736" s="5">
         <v>45910</v>
       </c>
@@ -73822,7 +73876,7 @@
         <v>1938</v>
       </c>
     </row>
-    <row r="737" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="737" spans="1:13">
       <c r="A737" s="5">
         <v>45917</v>
       </c>
@@ -73863,7 +73917,7 @@
         <v>1926</v>
       </c>
     </row>
-    <row r="738" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="738" spans="1:13">
       <c r="A738" s="5">
         <v>45924</v>
       </c>
@@ -73904,7 +73958,7 @@
         <v>1819</v>
       </c>
     </row>
-    <row r="739" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="739" spans="1:13">
       <c r="A739" s="5">
         <v>45931</v>
       </c>
@@ -73945,7 +73999,7 @@
         <v>1796</v>
       </c>
     </row>
-    <row r="740" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="740" spans="1:13">
       <c r="A740" s="5">
         <v>45938</v>
       </c>
@@ -73986,7 +74040,7 @@
         <v>1759</v>
       </c>
     </row>
-    <row r="741" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="741" spans="1:13">
       <c r="A741" s="5">
         <v>45945</v>
       </c>
@@ -74027,7 +74081,7 @@
         <v>1797</v>
       </c>
     </row>
-    <row r="742" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="742" spans="1:13">
       <c r="A742" s="5">
         <v>45952</v>
       </c>
@@ -74068,7 +74122,7 @@
         <v>1720</v>
       </c>
     </row>
-    <row r="743" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="743" spans="1:13">
       <c r="A743" s="5">
         <v>45959</v>
       </c>
@@ -74109,7 +74163,7 @@
         <v>1678</v>
       </c>
     </row>
-    <row r="744" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="744" spans="1:13">
       <c r="A744" s="5">
         <v>45966</v>
       </c>
@@ -74150,7 +74204,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="745" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="745" spans="1:13">
       <c r="A745" s="5">
         <v>45973</v>
       </c>
@@ -74191,7 +74245,7 @@
         <v>1633</v>
       </c>
     </row>
-    <row r="746" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="746" spans="1:13">
       <c r="A746" s="5">
         <v>45980</v>
       </c>
@@ -74232,7 +74286,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="747" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="747" spans="1:13">
       <c r="A747" s="5">
         <v>45987</v>
       </c>
@@ -74273,7 +74327,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="748" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="748" spans="1:13">
       <c r="A748" s="5">
         <v>45994</v>
       </c>
@@ -74314,7 +74368,7 @@
         <v>1632</v>
       </c>
     </row>
-    <row r="749" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="749" spans="1:13">
       <c r="A749" s="5">
         <v>46001</v>
       </c>
@@ -74355,7 +74409,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="750" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="750" spans="1:13">
       <c r="A750" s="5">
         <v>46008</v>
       </c>
@@ -74396,7 +74450,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="751" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="751" spans="1:13">
       <c r="A751" s="5">
         <v>46015</v>
       </c>
@@ -74437,7 +74491,7 @@
         <v>1652</v>
       </c>
     </row>
-    <row r="752" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="752" spans="1:13">
       <c r="A752" s="5">
         <v>46022</v>
       </c>
@@ -74478,7 +74532,7 @@
         <v>1652</v>
       </c>
     </row>
-    <row r="753" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="753" spans="1:13">
       <c r="A753" s="5">
         <v>46029</v>
       </c>
@@ -74519,7 +74573,7 @@
         <v>1685</v>
       </c>
     </row>
-    <row r="754" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="754" spans="1:13">
       <c r="A754" s="5">
         <v>46036</v>
       </c>
@@ -74560,7 +74614,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="755" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="755" spans="1:13">
       <c r="A755" s="5">
         <v>46043</v>
       </c>
@@ -74601,7 +74655,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="756" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="756" spans="1:13">
       <c r="A756" s="5">
         <v>46050</v>
       </c>
@@ -74642,7 +74696,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="757" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="757" spans="1:13">
       <c r="A757" s="5">
         <v>46057</v>
       </c>
@@ -74683,7 +74737,7 @@
         <v>1598</v>
       </c>
     </row>
-    <row r="758" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="758" spans="1:13">
       <c r="A758" s="5">
         <v>46064</v>
       </c>
@@ -74724,7 +74778,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="759" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="759" spans="1:13">
       <c r="A759" s="5">
         <v>46071</v>
       </c>
@@ -74765,7 +74819,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="760" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="760" spans="1:13">
       <c r="A760" s="5">
         <v>46078</v>
       </c>
@@ -74806,7 +74860,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="761" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="761" spans="1:13">
       <c r="A761" s="5">
         <v>46085</v>
       </c>
@@ -74847,7 +74901,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="762" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="762" spans="1:13">
       <c r="A762" s="5">
         <v>46092</v>
       </c>
@@ -74888,7 +74942,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="763" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="763" spans="1:13">
       <c r="A763" s="5">
         <v>46099</v>
       </c>
@@ -74929,7 +74983,7 @@
         <v>1504</v>
       </c>
     </row>
-    <row r="764" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="764" spans="1:13">
       <c r="A764" s="5">
         <v>46106</v>
       </c>
@@ -74970,7 +75024,7 @@
         <v>1542</v>
       </c>
     </row>
-    <row r="765" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="765" spans="1:13">
       <c r="A765" s="5">
         <v>46113</v>
       </c>
@@ -75011,7 +75065,7 @@
         <v>1579</v>
       </c>
     </row>
-    <row r="766" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="766" spans="1:13">
       <c r="A766" s="5">
         <v>46120</v>
       </c>
@@ -75052,7 +75106,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="767" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="767" spans="1:13">
       <c r="A767" s="5">
         <v>46127</v>
       </c>
@@ -75093,7 +75147,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="768" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="768" spans="1:13">
       <c r="A768" s="5">
         <v>46134</v>
       </c>
@@ -75134,7 +75188,7 @@
         <v>2326</v>
       </c>
     </row>
-    <row r="769" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="769" spans="1:13">
       <c r="A769" s="5">
         <v>46141</v>
       </c>
@@ -75175,7 +75229,7 @@
         <v>2327</v>
       </c>
     </row>
-    <row r="770" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="770" spans="1:13">
       <c r="A770" s="5">
         <v>46148</v>
       </c>
@@ -75216,7 +75270,7 @@
         <v>2314</v>
       </c>
     </row>
-    <row r="771" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="771" spans="1:13">
       <c r="A771" s="5">
         <v>46155</v>
       </c>
@@ -75257,7 +75311,7 @@
         <v>2388</v>
       </c>
     </row>
-    <row r="772" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="772" spans="1:13">
       <c r="A772" s="5">
         <v>46162</v>
       </c>
@@ -75298,7 +75352,7 @@
         <v>2453</v>
       </c>
     </row>
-    <row r="773" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="773" spans="1:13">
       <c r="A773" s="5">
         <v>46169</v>
       </c>
@@ -75339,7 +75393,7 @@
         <v>2435</v>
       </c>
     </row>
-    <row r="774" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="774" spans="1:13">
       <c r="A774" s="5">
         <v>46176</v>
       </c>
@@ -75380,7 +75434,7 @@
         <v>2560</v>
       </c>
     </row>
-    <row r="775" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="775" spans="1:13">
       <c r="A775" s="5">
         <v>46183</v>
       </c>
@@ -75421,7 +75475,7 @@
         <v>2508</v>
       </c>
     </row>
-    <row r="776" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="776" spans="1:13">
       <c r="A776" s="5">
         <v>46190</v>
       </c>
@@ -75435,7 +75489,7 @@
         <v>15</v>
       </c>
       <c r="E776" s="7">
-        <v>3969</v>
+        <v>3968.87</v>
       </c>
       <c r="F776" s="8">
         <v>4342</v>
@@ -75460,6 +75514,47 @@
       </c>
       <c r="M776" s="8">
         <v>2507</v>
+      </c>
+    </row>
+    <row r="777" spans="1:13">
+      <c r="A777" s="5">
+        <v>46197</v>
+      </c>
+      <c r="B777" s="5">
+        <v>46198</v>
+      </c>
+      <c r="C777" s="6">
+        <v>0.58333333333542503</v>
+      </c>
+      <c r="D777" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E777" s="7">
+        <v>4166</v>
+      </c>
+      <c r="F777" s="8">
+        <v>4392</v>
+      </c>
+      <c r="G777" s="8">
+        <v>5759</v>
+      </c>
+      <c r="H777" s="8">
+        <v>5750</v>
+      </c>
+      <c r="I777" s="8">
+        <v>7149</v>
+      </c>
+      <c r="J777" s="8">
+        <v>648</v>
+      </c>
+      <c r="K777" s="8">
+        <v>828</v>
+      </c>
+      <c r="L777" s="8">
+        <v>1011</v>
+      </c>
+      <c r="M777" s="8">
+        <v>2584</v>
       </c>
     </row>
   </sheetData>
@@ -75472,7 +75567,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86BC2DE8-BCE4-43AE-95F3-3DF06CDF8905}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -75483,12 +75578,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C789BCF2-DC16-4FFC-AF71-3351D156D960}">
   <dimension ref="B2:N3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:14">
       <c r="B2" s="9" t="s">
         <v>9</v>
       </c>
@@ -75507,7 +75602,7 @@
       <c r="M2" s="11"/>
       <c r="N2" s="11"/>
     </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:14">
       <c r="B3" s="9" t="s">
         <v>10</v>
       </c>

--- a/data/freight/world container index.xlsx
+++ b/data/freight/world container index.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{564CE1BC-85A0-42EC-8BA2-36559258C54F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{180CE3CC-B40A-48FC-BCC9-5CBED237410D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11430" yWindow="0" windowWidth="11700" windowHeight="14730" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WCI" sheetId="1" r:id="rId1"/>
@@ -208,9 +208,9 @@
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="쉼표 [0]" xfId="2" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
+    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -228,7 +228,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -43689,15 +43689,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M777"/>
-  <sheetFormatPr defaultColWidth="7.44140625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="7.453125" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="10.77734375" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.81640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.08984375" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6328125" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.77734375" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="13" width="10.44140625" style="8" customWidth="1"/>
-    <col min="14" max="16384" width="7.44140625" style="8"/>
+    <col min="5" max="5" width="15.81640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="13" width="10.453125" style="8" customWidth="1"/>
+    <col min="14" max="16384" width="7.453125" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="4" customFormat="1">
@@ -75567,7 +75567,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86BC2DE8-BCE4-43AE-95F3-3DF06CDF8905}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -75578,9 +75578,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C789BCF2-DC16-4FFC-AF71-3351D156D960}">
   <dimension ref="B2:N3"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:14">
